--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1487,22 +1487,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>37.38</v>
+        <v>40.1</v>
       </c>
       <c r="F10" t="n">
-        <v>52.6</v>
+        <v>57.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.82</v>
+        <v>7.97</v>
       </c>
       <c r="H10" t="n">
-        <v>0.71</v>
+        <v>1.16</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="J10" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1511,14 +1511,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.67</v>
+        <v>33.71</v>
       </c>
       <c r="N10" t="n">
-        <v>31.45</v>
+        <v>31.49</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1549,37 +1549,41 @@
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、+1σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>38.93</v>
+        <v>37.38</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.55</v>
+        <v>2.72</v>
       </c>
       <c r="Y10" t="n">
-        <v>-3.98</v>
+        <v>7.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6076</v>
+        <v>-6073</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.39</v>
+        <v>-99.34</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,26 +581,26 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3265</v>
+        <v>3325</v>
       </c>
       <c r="F2" t="n">
-        <v>46.1</v>
+        <v>46.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.34</v>
+        <v>-2.73</v>
       </c>
       <c r="H2" t="n">
-        <v>1.07</v>
+        <v>0.95</v>
       </c>
       <c r="I2" t="n">
-        <v>47.79</v>
+        <v>36.78</v>
       </c>
       <c r="J2" t="n">
-        <v>96.16</v>
+        <v>84.28</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>2978.95</v>
+        <v>2993.61</v>
       </c>
       <c r="N2" t="n">
-        <v>2711.77</v>
+        <v>2714.49</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,249 +621,23 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟠 利益確定検討</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>3355</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-90</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-2.68</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>13060</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>10800</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2260</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>20.93</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>9432.T</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NTT</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>100</v>
-      </c>
-      <c r="D3" t="n">
-        <v>158</v>
-      </c>
-      <c r="E3" t="n">
-        <v>175.7</v>
-      </c>
-      <c r="F3" t="n">
-        <v>68</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>155.05</v>
-      </c>
-      <c r="N3" t="n">
-        <v>153.66</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>85</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>175.2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>17570</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>15800</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1770</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>11.2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>420</v>
-      </c>
-      <c r="E4" t="n">
-        <v>458</v>
-      </c>
-      <c r="F4" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="J4" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>432.38</v>
-      </c>
-      <c r="N4" t="n">
-        <v>410.81</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>65</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -874,32 +648,257 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>押し目、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>3265</v>
+      </c>
+      <c r="X2" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>13300</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>10800</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>23.15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E3" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>155.4</v>
+      </c>
+      <c r="N3" t="n">
+        <v>153.79</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>85</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>RSIやや過熱、25日線上、+1σ、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>175.7</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>17650</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>15800</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1850</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11.71</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E4" t="n">
+        <v>466</v>
+      </c>
+      <c r="F4" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>432.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>411.43</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>95</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="X4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.15</v>
+        <v>1.75</v>
       </c>
       <c r="Z4" t="n">
-        <v>45800</v>
+        <v>46600</v>
       </c>
       <c r="AA4" t="n">
         <v>42000</v>
       </c>
       <c r="AB4" t="n">
-        <v>3800</v>
+        <v>4600</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.050000000000001</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="5">
@@ -920,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3031</v>
+        <v>3021</v>
       </c>
       <c r="F5" t="n">
-        <v>42.1</v>
+        <v>44.6</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.82</v>
+        <v>-1.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.19</v>
+        <v>0.48</v>
       </c>
       <c r="I5" t="n">
-        <v>7.7</v>
+        <v>4.77</v>
       </c>
       <c r="J5" t="n">
-        <v>27.13</v>
+        <v>22.66</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -948,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2933.2</v>
+        <v>2933.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.54</v>
+        <v>3164.72</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -993,25 +992,25 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>2994</v>
+        <v>3031</v>
       </c>
       <c r="X5" t="n">
-        <v>37</v>
+        <v>-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.24</v>
+        <v>-0.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>39403</v>
+        <v>39273</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2304</v>
+        <v>2174</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.21</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="6">
@@ -1032,22 +1031,22 @@
         <v>4795</v>
       </c>
       <c r="E6" t="n">
-        <v>5005</v>
+        <v>5058</v>
       </c>
       <c r="F6" t="n">
-        <v>59.7</v>
+        <v>63.1</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3</v>
+        <v>4.23</v>
       </c>
       <c r="H6" t="n">
-        <v>1.23</v>
+        <v>0.4</v>
       </c>
       <c r="I6" t="n">
-        <v>70.62</v>
+        <v>75.48</v>
       </c>
       <c r="J6" t="n">
-        <v>55.7</v>
+        <v>59.65</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1060,10 +1059,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4719.41</v>
+        <v>4719.68</v>
       </c>
       <c r="N6" t="n">
-        <v>4649.56</v>
+        <v>4657.04</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1093,7 +1092,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・RSIは良好な水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -1106,25 +1104,25 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>4987</v>
+        <v>5005</v>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.36</v>
+        <v>1.06</v>
       </c>
       <c r="Z6" t="n">
-        <v>25025</v>
+        <v>25290</v>
       </c>
       <c r="AA6" t="n">
         <v>23975</v>
       </c>
       <c r="AB6" t="n">
-        <v>1050</v>
+        <v>1315</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.38</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="7">
@@ -1145,22 +1143,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>8093</v>
+        <v>8224</v>
       </c>
       <c r="F7" t="n">
-        <v>31.9</v>
+        <v>33.9</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.51</v>
+        <v>-5.08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>0.65</v>
       </c>
       <c r="I7" t="n">
-        <v>83.61</v>
+        <v>52.57</v>
       </c>
       <c r="J7" t="n">
-        <v>230.46</v>
+        <v>194.88</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1173,10 +1171,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7698.67</v>
+        <v>7715.36</v>
       </c>
       <c r="N7" t="n">
-        <v>8794.690000000001</v>
+        <v>8771.08</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1218,25 +1216,25 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>7989</v>
+        <v>8093</v>
       </c>
       <c r="X7" t="n">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="Z7" t="n">
-        <v>8093</v>
+        <v>8224</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>100</v>
+        <v>231</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.25</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="8">
@@ -1257,22 +1255,22 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>54030</v>
+        <v>50510</v>
       </c>
       <c r="F8" t="n">
-        <v>55.5</v>
+        <v>48.8</v>
       </c>
       <c r="G8" t="n">
-        <v>2.01</v>
+        <v>-4.84</v>
       </c>
       <c r="H8" t="n">
-        <v>0.91</v>
+        <v>0.64</v>
       </c>
       <c r="I8" t="n">
-        <v>16.63</v>
+        <v>-316.42</v>
       </c>
       <c r="J8" t="n">
-        <v>-981.77</v>
+        <v>-848.7</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1285,10 +1283,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>66501.47</v>
+        <v>66357.87</v>
       </c>
       <c r="N8" t="n">
-        <v>39192.11</v>
+        <v>39393.36</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1297,20 +1295,20 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1331,29 +1329,29 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、反発局面</t>
+          <t>押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>58090</v>
+        <v>54030</v>
       </c>
       <c r="X8" t="n">
-        <v>-4060</v>
+        <v>-3520</v>
       </c>
       <c r="Y8" t="n">
-        <v>-6.99</v>
+        <v>-6.51</v>
       </c>
       <c r="Z8" t="n">
-        <v>54030</v>
+        <v>50510</v>
       </c>
       <c r="AA8" t="n">
         <v>55510</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1480</v>
+        <v>-5000</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.67</v>
+        <v>-9.01</v>
       </c>
     </row>
     <row r="9">
@@ -1374,22 +1372,22 @@
         <v>10000</v>
       </c>
       <c r="E9" t="n">
-        <v>9209</v>
+        <v>8708</v>
       </c>
       <c r="F9" t="n">
-        <v>50.8</v>
+        <v>43.4</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.69</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1.06</v>
+        <v>0.58</v>
       </c>
       <c r="I9" t="n">
-        <v>-502.34</v>
+        <v>-511.56</v>
       </c>
       <c r="J9" t="n">
-        <v>-647.09</v>
+        <v>-619.99</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1398,14 +1396,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>13275.32</v>
+        <v>13217.96</v>
       </c>
       <c r="N9" t="n">
-        <v>7835.8</v>
+        <v>7863.87</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1414,20 +1412,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1435,38 +1433,41 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD買い、反発局面</t>
+          <t>押し目、-1σ、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>9403</v>
+        <v>9209</v>
       </c>
       <c r="X9" t="n">
-        <v>-194</v>
+        <v>-501</v>
       </c>
       <c r="Y9" t="n">
-        <v>-2.06</v>
+        <v>-5.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>9209</v>
+        <v>8708</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-791</v>
+        <v>-1292</v>
       </c>
       <c r="AC9" t="n">
-        <v>-7.91</v>
+        <v>-12.92</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3325</v>
+        <v>3345</v>
       </c>
       <c r="F2" t="n">
-        <v>46.3</v>
+        <v>47.2</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.73</v>
+        <v>-2.16</v>
       </c>
       <c r="H2" t="n">
-        <v>0.95</v>
+        <v>1.68</v>
       </c>
       <c r="I2" t="n">
-        <v>36.78</v>
+        <v>38.37</v>
       </c>
       <c r="J2" t="n">
-        <v>84.28</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>2993.61</v>
+        <v>2993.88</v>
       </c>
       <c r="N2" t="n">
-        <v>2714.49</v>
+        <v>2714.59</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -638,6 +638,120 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・出来高が増加しています。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>押し目、出来高微増、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>3265</v>
+      </c>
+      <c r="X2" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>13380</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>10800</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2580</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>23.89</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>420</v>
+      </c>
+      <c r="E3" t="n">
+        <v>475</v>
+      </c>
+      <c r="F3" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>432.62</v>
+      </c>
+      <c r="N3" t="n">
+        <v>411.47</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>95</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -648,257 +762,144 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>3265</v>
-      </c>
-      <c r="X2" t="n">
-        <v>60</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>13300</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>10800</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>23.15</v>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>458</v>
+      </c>
+      <c r="X3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>47500</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5500</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13.1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>9432.T</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>NTT</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C4" t="n">
         <v>100</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>158</v>
       </c>
-      <c r="E3" t="n">
-        <v>176.5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="E4" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>+1S</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>155.4</v>
-      </c>
-      <c r="N3" t="n">
-        <v>153.79</v>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="M4" t="n">
+        <v>155.43</v>
+      </c>
+      <c r="N4" t="n">
+        <v>153.8</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>85</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>100</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは売りシグナルです。
+・MACDは買いシグナルです。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>175.7</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>17650</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>15800</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1850</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>11.71</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>420</v>
-      </c>
-      <c r="E4" t="n">
-        <v>466</v>
-      </c>
-      <c r="F4" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>432.5</v>
-      </c>
-      <c r="N4" t="n">
-        <v>411.43</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>🟢 強い買い</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>95</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>RSIやや過熱、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>458</v>
+        <v>175.7</v>
       </c>
       <c r="X4" t="n">
-        <v>8</v>
+        <v>2.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="Z4" t="n">
-        <v>46600</v>
+        <v>17830</v>
       </c>
       <c r="AA4" t="n">
-        <v>42000</v>
+        <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>4600</v>
+        <v>2030</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.95</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +920,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3021</v>
+        <v>3025</v>
       </c>
       <c r="F5" t="n">
-        <v>44.6</v>
+        <v>44.9</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2</v>
+        <v>-1.07</v>
       </c>
       <c r="H5" t="n">
-        <v>0.48</v>
+        <v>0.92</v>
       </c>
       <c r="I5" t="n">
-        <v>4.77</v>
+        <v>5.09</v>
       </c>
       <c r="J5" t="n">
-        <v>22.66</v>
+        <v>22.72</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,10 +948,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2933.08</v>
+        <v>2933.13</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.72</v>
+        <v>3164.74</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -995,22 +996,22 @@
         <v>3031</v>
       </c>
       <c r="X5" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.33</v>
+        <v>-0.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>39273</v>
+        <v>39325</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2174</v>
+        <v>2226</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.86</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -1031,22 +1032,22 @@
         <v>4795</v>
       </c>
       <c r="E6" t="n">
-        <v>5058</v>
+        <v>4991</v>
       </c>
       <c r="F6" t="n">
-        <v>63.1</v>
+        <v>60.4</v>
       </c>
       <c r="G6" t="n">
-        <v>4.23</v>
+        <v>2.91</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4</v>
+        <v>0.84</v>
       </c>
       <c r="I6" t="n">
-        <v>75.48</v>
+        <v>70.14</v>
       </c>
       <c r="J6" t="n">
-        <v>59.65</v>
+        <v>58.58</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1059,10 +1060,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4719.68</v>
+        <v>4718.79</v>
       </c>
       <c r="N6" t="n">
-        <v>4657.04</v>
+        <v>4656.71</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1107,22 +1108,22 @@
         <v>5005</v>
       </c>
       <c r="X6" t="n">
-        <v>53</v>
+        <v>-14</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.06</v>
+        <v>-0.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>25290</v>
+        <v>24955</v>
       </c>
       <c r="AA6" t="n">
         <v>23975</v>
       </c>
       <c r="AB6" t="n">
-        <v>1315</v>
+        <v>980</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.48</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="7">
@@ -1143,22 +1144,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>8224</v>
+        <v>8268</v>
       </c>
       <c r="F7" t="n">
-        <v>33.9</v>
+        <v>35.4</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.08</v>
+        <v>-4.59</v>
       </c>
       <c r="H7" t="n">
-        <v>0.65</v>
+        <v>0.93</v>
       </c>
       <c r="I7" t="n">
-        <v>52.57</v>
+        <v>56.08</v>
       </c>
       <c r="J7" t="n">
-        <v>194.88</v>
+        <v>195.58</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1171,10 +1172,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7715.36</v>
+        <v>7715.95</v>
       </c>
       <c r="N7" t="n">
-        <v>8771.08</v>
+        <v>8771.299999999999</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1219,22 +1220,22 @@
         <v>8093</v>
       </c>
       <c r="X7" t="n">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.62</v>
+        <v>2.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>8224</v>
+        <v>8268</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.89</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="8">
@@ -1255,22 +1256,22 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>50510</v>
+        <v>50590</v>
       </c>
       <c r="F8" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.84</v>
+        <v>-4.69</v>
       </c>
       <c r="H8" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="I8" t="n">
-        <v>-316.42</v>
+        <v>-310.04</v>
       </c>
       <c r="J8" t="n">
-        <v>-848.7</v>
+        <v>-847.4299999999999</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1283,10 +1284,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>66357.87</v>
+        <v>66358.92999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>39393.36</v>
+        <v>39393.76</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1336,22 +1337,22 @@
         <v>54030</v>
       </c>
       <c r="X8" t="n">
-        <v>-3520</v>
+        <v>-3440</v>
       </c>
       <c r="Y8" t="n">
-        <v>-6.51</v>
+        <v>-6.37</v>
       </c>
       <c r="Z8" t="n">
-        <v>50510</v>
+        <v>50590</v>
       </c>
       <c r="AA8" t="n">
         <v>55510</v>
       </c>
       <c r="AB8" t="n">
-        <v>-5000</v>
+        <v>-4920</v>
       </c>
       <c r="AC8" t="n">
-        <v>-9.01</v>
+        <v>-8.859999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1372,22 +1373,22 @@
         <v>10000</v>
       </c>
       <c r="E9" t="n">
-        <v>8708</v>
+        <v>8714</v>
       </c>
       <c r="F9" t="n">
         <v>43.4</v>
       </c>
       <c r="G9" t="n">
-        <v>-8.550000000000001</v>
+        <v>-8.49</v>
       </c>
       <c r="H9" t="n">
-        <v>0.58</v>
+        <v>0.87</v>
       </c>
       <c r="I9" t="n">
-        <v>-511.56</v>
+        <v>-511.08</v>
       </c>
       <c r="J9" t="n">
-        <v>-619.99</v>
+        <v>-619.89</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1400,10 +1401,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>13217.96</v>
+        <v>13218.04</v>
       </c>
       <c r="N9" t="n">
-        <v>7863.87</v>
+        <v>7863.9</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1452,22 +1453,22 @@
         <v>9209</v>
       </c>
       <c r="X9" t="n">
-        <v>-501</v>
+        <v>-495</v>
       </c>
       <c r="Y9" t="n">
-        <v>-5.44</v>
+        <v>-5.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>8708</v>
+        <v>8714</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1292</v>
+        <v>-1286</v>
       </c>
       <c r="AC9" t="n">
-        <v>-12.92</v>
+        <v>-12.86</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1489,22 +1489,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>40.1</v>
+        <v>36.74</v>
       </c>
       <c r="F10" t="n">
-        <v>57.6</v>
+        <v>53.9</v>
       </c>
       <c r="G10" t="n">
-        <v>7.97</v>
+        <v>-1.67</v>
       </c>
       <c r="H10" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="I10" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="J10" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1513,14 +1513,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.71</v>
+        <v>33.69</v>
       </c>
       <c r="N10" t="n">
-        <v>31.49</v>
+        <v>31.51</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1529,20 +1529,20 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1551,41 +1551,41 @@
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>🚀 急騰</t>
+          <t>⚠️ 急落</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+1σ、MACD売り、長期上昇</t>
+          <t>RSI適正、押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>37.38</v>
+        <v>40.1</v>
       </c>
       <c r="X10" t="n">
-        <v>2.72</v>
+        <v>-3.36</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.28</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6073</v>
+        <v>-6076</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.34</v>
+        <v>-99.40000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3345</v>
+        <v>3375</v>
       </c>
       <c r="F2" t="n">
-        <v>47.2</v>
+        <v>47.8</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.16</v>
+        <v>-1.41</v>
       </c>
       <c r="H2" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>38.37</v>
+        <v>32.95</v>
       </c>
       <c r="J2" t="n">
-        <v>84.59999999999999</v>
+        <v>74.27</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>2993.88</v>
+        <v>3007.96</v>
       </c>
       <c r="N2" t="n">
-        <v>2714.59</v>
+        <v>2718.03</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・出来高が増加しています。
+・出来高が急増しています。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -652,29 +652,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>押し目、出来高微増、MACD売り、長期上昇</t>
+          <t>押し目、出来高増加、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3265</v>
+        <v>3345</v>
       </c>
       <c r="X2" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.45</v>
+        <v>0.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>13380</v>
+        <v>13500</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2580</v>
+        <v>2700</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.89</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -695,22 +695,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F3" t="n">
-        <v>53.9</v>
+        <v>54.4</v>
       </c>
       <c r="G3" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="H3" t="n">
-        <v>0.64</v>
+        <v>0.97</v>
       </c>
       <c r="I3" t="n">
-        <v>4.01</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>6.65</v>
+        <v>6.28</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>432.62</v>
+        <v>432.79</v>
       </c>
       <c r="N3" t="n">
-        <v>411.47</v>
+        <v>412.09</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -769,25 +769,25 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="X3" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.71</v>
+        <v>0.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>47500</v>
+        <v>47700</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5500</v>
+        <v>5700</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.1</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="4">
@@ -808,22 +808,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>178.3</v>
+        <v>177.1</v>
       </c>
       <c r="F4" t="n">
-        <v>67.8</v>
+        <v>64.3</v>
       </c>
       <c r="G4" t="n">
-        <v>6.04</v>
+        <v>4.89</v>
       </c>
       <c r="H4" t="n">
-        <v>0.97</v>
+        <v>0.41</v>
       </c>
       <c r="I4" t="n">
         <v>4.63</v>
       </c>
       <c r="J4" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>155.43</v>
+        <v>155.79</v>
       </c>
       <c r="N4" t="n">
-        <v>153.8</v>
+        <v>153.93</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -877,29 +877,29 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>175.7</v>
+        <v>178.3</v>
       </c>
       <c r="X4" t="n">
-        <v>2.6</v>
+        <v>-1.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.48</v>
+        <v>-0.67</v>
       </c>
       <c r="Z4" t="n">
-        <v>17830</v>
+        <v>17710</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>2030</v>
+        <v>1910</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.85</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="5">
@@ -920,22 +920,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3025</v>
+        <v>3016</v>
       </c>
       <c r="F5" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.07</v>
+        <v>-1.41</v>
       </c>
       <c r="H5" t="n">
-        <v>0.92</v>
+        <v>0.42</v>
       </c>
       <c r="I5" t="n">
-        <v>5.09</v>
+        <v>2.27</v>
       </c>
       <c r="J5" t="n">
-        <v>22.72</v>
+        <v>18.63</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2933.13</v>
+        <v>2932.79</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.74</v>
+        <v>3164.86</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -981,6 +981,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -993,25 +994,25 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>3031</v>
+        <v>3025</v>
       </c>
       <c r="X5" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>39325</v>
+        <v>39208</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2226</v>
+        <v>2109</v>
       </c>
       <c r="AC5" t="n">
-        <v>6</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="6">
@@ -1032,22 +1033,22 @@
         <v>4795</v>
       </c>
       <c r="E6" t="n">
-        <v>4991</v>
+        <v>4928</v>
       </c>
       <c r="F6" t="n">
-        <v>60.4</v>
+        <v>59.6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.91</v>
+        <v>1.54</v>
       </c>
       <c r="H6" t="n">
-        <v>0.84</v>
+        <v>0.42</v>
       </c>
       <c r="I6" t="n">
-        <v>70.14</v>
+        <v>63.93</v>
       </c>
       <c r="J6" t="n">
-        <v>58.58</v>
+        <v>59.65</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1056,14 +1057,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4718.79</v>
+        <v>4716.96</v>
       </c>
       <c r="N6" t="n">
-        <v>4656.71</v>
+        <v>4663.56</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1093,7 +1094,8 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1101,29 +1103,29 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>5005</v>
+        <v>4991</v>
       </c>
       <c r="X6" t="n">
-        <v>-14</v>
+        <v>-63</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.28</v>
+        <v>-1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>24955</v>
+        <v>24640</v>
       </c>
       <c r="AA6" t="n">
         <v>23975</v>
       </c>
       <c r="AB6" t="n">
-        <v>980</v>
+        <v>665</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.09</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="7">
@@ -1144,22 +1146,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>8268</v>
+        <v>8173</v>
       </c>
       <c r="F7" t="n">
-        <v>35.4</v>
+        <v>32.8</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.59</v>
+        <v>-5.65</v>
       </c>
       <c r="H7" t="n">
-        <v>0.93</v>
+        <v>0.42</v>
       </c>
       <c r="I7" t="n">
-        <v>56.08</v>
+        <v>26.29</v>
       </c>
       <c r="J7" t="n">
-        <v>195.58</v>
+        <v>161.72</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1172,10 +1174,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7715.95</v>
+        <v>7729.61</v>
       </c>
       <c r="N7" t="n">
-        <v>8771.299999999999</v>
+        <v>8748.26</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1217,25 +1219,25 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>8093</v>
+        <v>8268</v>
       </c>
       <c r="X7" t="n">
-        <v>175</v>
+        <v>-95</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.16</v>
+        <v>-1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>8268</v>
+        <v>8173</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>275</v>
+        <v>180</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.44</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="8">
@@ -1256,22 +1258,22 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>50590</v>
+        <v>51970</v>
       </c>
       <c r="F8" t="n">
-        <v>48.9</v>
+        <v>53.2</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.69</v>
+        <v>-2.38</v>
       </c>
       <c r="H8" t="n">
-        <v>0.95</v>
+        <v>0.61</v>
       </c>
       <c r="I8" t="n">
-        <v>-310.04</v>
+        <v>-452.35</v>
       </c>
       <c r="J8" t="n">
-        <v>-847.4299999999999</v>
+        <v>-768.41</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1284,10 +1286,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>66358.92999999999</v>
+        <v>66173.87</v>
       </c>
       <c r="N8" t="n">
-        <v>39393.76</v>
+        <v>39599.44</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1296,20 +1298,20 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1323,36 +1325,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、MACD買い、反発局面</t>
+          <t>RSI適正、押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>54030</v>
+        <v>50590</v>
       </c>
       <c r="X8" t="n">
-        <v>-3440</v>
+        <v>1380</v>
       </c>
       <c r="Y8" t="n">
-        <v>-6.37</v>
+        <v>2.73</v>
       </c>
       <c r="Z8" t="n">
-        <v>50590</v>
+        <v>51970</v>
       </c>
       <c r="AA8" t="n">
         <v>55510</v>
       </c>
       <c r="AB8" t="n">
-        <v>-4920</v>
+        <v>-3540</v>
       </c>
       <c r="AC8" t="n">
-        <v>-8.859999999999999</v>
+        <v>-6.38</v>
       </c>
     </row>
     <row r="9">
@@ -1373,22 +1371,22 @@
         <v>10000</v>
       </c>
       <c r="E9" t="n">
-        <v>8714</v>
+        <v>9294</v>
       </c>
       <c r="F9" t="n">
-        <v>43.4</v>
+        <v>52.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-8.49</v>
+        <v>-2.29</v>
       </c>
       <c r="H9" t="n">
-        <v>0.87</v>
+        <v>0.68</v>
       </c>
       <c r="I9" t="n">
-        <v>-511.08</v>
+        <v>-465.84</v>
       </c>
       <c r="J9" t="n">
-        <v>-619.89</v>
+        <v>-589.08</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1397,14 +1395,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>13218.04</v>
+        <v>13144.43</v>
       </c>
       <c r="N9" t="n">
-        <v>7863.9</v>
+        <v>7894.81</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1413,20 +1411,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1434,41 +1432,42 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>⚠️ 急落</t>
+          <t>🚀 急騰</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD買い、反発局面</t>
+          <t>RSI適正、押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>9209</v>
+        <v>8714</v>
       </c>
       <c r="X9" t="n">
-        <v>-495</v>
+        <v>580</v>
       </c>
       <c r="Y9" t="n">
-        <v>-5.38</v>
+        <v>6.66</v>
       </c>
       <c r="Z9" t="n">
-        <v>8714</v>
+        <v>9294</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1286</v>
+        <v>-706</v>
       </c>
       <c r="AC9" t="n">
-        <v>-12.86</v>
+        <v>-7.06</v>
       </c>
     </row>
     <row r="10">
@@ -1498,7 +1497,7 @@
         <v>-1.67</v>
       </c>
       <c r="H10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="I10" t="n">
         <v>1.42</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1489,22 +1489,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>36.74</v>
+        <v>35.64</v>
       </c>
       <c r="F10" t="n">
-        <v>53.9</v>
+        <v>42.1</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.67</v>
+        <v>-5.04</v>
       </c>
       <c r="H10" t="n">
-        <v>1.07</v>
+        <v>0.78</v>
       </c>
       <c r="I10" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="J10" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1513,14 +1513,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.69</v>
+        <v>33.62</v>
       </c>
       <c r="N10" t="n">
-        <v>31.51</v>
+        <v>31.52</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1529,20 +1529,20 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1550,42 +1550,37 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、長期上昇</t>
+          <t>押し目、-1σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>40.1</v>
+        <v>36.74</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.36</v>
+        <v>-1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>-8.380000000000001</v>
+        <v>-2.99</v>
       </c>
       <c r="Z10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6076</v>
+        <v>-6077</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.40000000000001</v>
+        <v>-99.42</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3340</v>
+        <v>3285</v>
       </c>
       <c r="F2" t="n">
-        <v>46.4</v>
+        <v>39.5</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.39</v>
+        <v>-4</v>
       </c>
       <c r="H2" t="n">
-        <v>2.53</v>
+        <v>0.58</v>
       </c>
       <c r="I2" t="n">
-        <v>30.16</v>
+        <v>18.99</v>
       </c>
       <c r="J2" t="n">
-        <v>73.70999999999999</v>
+        <v>62.77</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3007.49</v>
+        <v>3018.6</v>
       </c>
       <c r="N2" t="n">
-        <v>2717.85</v>
+        <v>2720.5</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -642,8 +642,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・出来高が急増しています。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -652,29 +650,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>押し目、出来高増加、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3345</v>
+        <v>3340</v>
       </c>
       <c r="X2" t="n">
-        <v>-5</v>
+        <v>-55</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.15</v>
+        <v>-1.65</v>
       </c>
       <c r="Z2" t="n">
-        <v>13360</v>
+        <v>13140</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2560</v>
+        <v>2340</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.7</v>
+        <v>21.67</v>
       </c>
     </row>
     <row r="3">
@@ -695,26 +693,26 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="F3" t="n">
-        <v>53.9</v>
+        <v>49.4</v>
       </c>
       <c r="G3" t="n">
-        <v>2.75</v>
+        <v>3.21</v>
       </c>
       <c r="H3" t="n">
-        <v>1.71</v>
+        <v>0.22</v>
       </c>
       <c r="I3" t="n">
-        <v>4.64</v>
+        <v>5.31</v>
       </c>
       <c r="J3" t="n">
-        <v>6.25</v>
+        <v>6.06</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -723,10 +721,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>432.76</v>
+        <v>433.13</v>
       </c>
       <c r="N3" t="n">
-        <v>412.08</v>
+        <v>412.71</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -739,7 +737,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -756,8 +754,8 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
-・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -766,29 +764,29 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、出来高微増、MACD売り、長期上昇</t>
+          <t>25日線上、ゴールデンクロス、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>475</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="Z3" t="n">
-        <v>47500</v>
+        <v>47800</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5500</v>
+        <v>5800</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.1</v>
+        <v>13.81</v>
       </c>
     </row>
     <row r="4">
@@ -809,22 +807,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>178.1</v>
+        <v>176.8</v>
       </c>
       <c r="F4" t="n">
-        <v>66.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>5.46</v>
+        <v>4.24</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="I4" t="n">
-        <v>4.71</v>
+        <v>4.61</v>
       </c>
       <c r="J4" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -837,10 +835,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>155.81</v>
+        <v>156.19</v>
       </c>
       <c r="N4" t="n">
-        <v>153.94</v>
+        <v>154.07</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -882,25 +880,25 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>178.3</v>
+        <v>178.1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2</v>
+        <v>-1.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.11</v>
+        <v>-0.73</v>
       </c>
       <c r="Z4" t="n">
-        <v>17810</v>
+        <v>17680</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>2010</v>
+        <v>1880</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.72</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="5">
@@ -921,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3021</v>
+        <v>3041</v>
       </c>
       <c r="F5" t="n">
-        <v>45.5</v>
+        <v>46.8</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.26</v>
+        <v>-0.66</v>
       </c>
       <c r="H5" t="n">
-        <v>0.88</v>
+        <v>0.4</v>
       </c>
       <c r="I5" t="n">
-        <v>2.67</v>
+        <v>2.34</v>
       </c>
       <c r="J5" t="n">
-        <v>18.71</v>
+        <v>15.44</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -949,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2932.85</v>
+        <v>2934.66</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.88</v>
+        <v>3165.09</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -995,25 +993,25 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>3025</v>
+        <v>3021</v>
       </c>
       <c r="X5" t="n">
-        <v>-4</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.13</v>
+        <v>0.66</v>
       </c>
       <c r="Z5" t="n">
-        <v>39273</v>
+        <v>39533</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2174</v>
+        <v>2434</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.86</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="6">
@@ -1034,22 +1032,22 @@
         <v>4795</v>
       </c>
       <c r="E6" t="n">
-        <v>4910</v>
+        <v>4968</v>
       </c>
       <c r="F6" t="n">
-        <v>58.6</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>1.19</v>
+        <v>2.29</v>
       </c>
       <c r="H6" t="n">
-        <v>0.86</v>
+        <v>0.51</v>
       </c>
       <c r="I6" t="n">
-        <v>62.5</v>
+        <v>60.42</v>
       </c>
       <c r="J6" t="n">
-        <v>59.37</v>
+        <v>59.58</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1062,10 +1060,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4716.72</v>
+        <v>4717.35</v>
       </c>
       <c r="N6" t="n">
-        <v>4663.47</v>
+        <v>4670.4</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1108,25 +1106,25 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>4991</v>
+        <v>4910</v>
       </c>
       <c r="X6" t="n">
-        <v>-81</v>
+        <v>58</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.62</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>24550</v>
+        <v>24840</v>
       </c>
       <c r="AA6" t="n">
         <v>23975</v>
       </c>
       <c r="AB6" t="n">
-        <v>575</v>
+        <v>865</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.4</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="7">
@@ -1147,22 +1145,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>8118</v>
+        <v>8131</v>
       </c>
       <c r="F7" t="n">
-        <v>31.9</v>
+        <v>35.1</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.26</v>
+        <v>-5.95</v>
       </c>
       <c r="H7" t="n">
-        <v>0.74</v>
+        <v>0.29</v>
       </c>
       <c r="I7" t="n">
-        <v>21.9</v>
+        <v>-4.08</v>
       </c>
       <c r="J7" t="n">
-        <v>160.85</v>
+        <v>127.86</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1175,10 +1173,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7728.88</v>
+        <v>7741.79</v>
       </c>
       <c r="N7" t="n">
-        <v>8747.99</v>
+        <v>8723.540000000001</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1220,61 +1218,61 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>8268</v>
+        <v>8118</v>
       </c>
       <c r="X7" t="n">
-        <v>-150</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.81</v>
+        <v>0.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>8118</v>
+        <v>8131</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>285A.T</t>
+          <t>6976.T</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>キオクシアホールディングス</t>
+          <t>太陽誘電</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>55510</v>
+        <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>51750</v>
+        <v>9157</v>
       </c>
       <c r="F8" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.78</v>
+        <v>-3.24</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="I8" t="n">
-        <v>-469.9</v>
+        <v>-441.99</v>
       </c>
       <c r="J8" t="n">
-        <v>-771.92</v>
+        <v>-560.9</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1287,10 +1285,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>66170.92999999999</v>
+        <v>13051.09</v>
       </c>
       <c r="N8" t="n">
-        <v>39598.34</v>
+        <v>7923.97</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1333,77 +1331,77 @@
         </is>
       </c>
       <c r="W8" t="n">
-        <v>50590</v>
+        <v>9197</v>
       </c>
       <c r="X8" t="n">
-        <v>1160</v>
+        <v>-40</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.29</v>
+        <v>-0.43</v>
       </c>
       <c r="Z8" t="n">
-        <v>51750</v>
+        <v>9157</v>
       </c>
       <c r="AA8" t="n">
-        <v>55510</v>
+        <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-3760</v>
+        <v>-843</v>
       </c>
       <c r="AC8" t="n">
-        <v>-6.77</v>
+        <v>-8.43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6976.T</t>
+          <t>285A.T</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>太陽誘電</t>
+          <t>キオクシアホールディングス</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>10000</v>
+        <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>9197</v>
+        <v>49690</v>
       </c>
       <c r="F9" t="n">
-        <v>51.5</v>
+        <v>45.4</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.27</v>
+        <v>-6.64</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1</v>
+        <v>0.59</v>
       </c>
       <c r="I9" t="n">
-        <v>-473.58</v>
+        <v>-754.13</v>
       </c>
       <c r="J9" t="n">
-        <v>-590.63</v>
+        <v>-768.36</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>13143.13</v>
+        <v>65866.8</v>
       </c>
       <c r="N9" t="n">
-        <v>7894.33</v>
+        <v>39790.11</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1412,20 +1410,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1433,42 +1431,39 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD買い、反発局面</t>
+          <t>押し目、デッドクロス、-1σ、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>8714</v>
+        <v>51750</v>
       </c>
       <c r="X9" t="n">
-        <v>483</v>
+        <v>-2060</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.54</v>
+        <v>-3.98</v>
       </c>
       <c r="Z9" t="n">
-        <v>9197</v>
+        <v>49690</v>
       </c>
       <c r="AA9" t="n">
-        <v>10000</v>
+        <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-803</v>
+        <v>-5820</v>
       </c>
       <c r="AC9" t="n">
-        <v>-8.029999999999999</v>
+        <v>-10.48</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3285</v>
+        <v>3310</v>
       </c>
       <c r="F2" t="n">
-        <v>39.5</v>
+        <v>40.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-4</v>
+        <v>-3.3</v>
       </c>
       <c r="H2" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="I2" t="n">
-        <v>18.99</v>
+        <v>20.98</v>
       </c>
       <c r="J2" t="n">
-        <v>62.77</v>
+        <v>63.17</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3018.6</v>
+        <v>3018.93</v>
       </c>
       <c r="N2" t="n">
-        <v>2720.5</v>
+        <v>2720.63</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -657,22 +657,22 @@
         <v>3340</v>
       </c>
       <c r="X2" t="n">
-        <v>-55</v>
+        <v>-30</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.65</v>
+        <v>-0.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>13140</v>
+        <v>13240</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2340</v>
+        <v>2440</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.67</v>
+        <v>22.59</v>
       </c>
     </row>
     <row r="3">
@@ -693,22 +693,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F3" t="n">
-        <v>49.4</v>
+        <v>48.8</v>
       </c>
       <c r="G3" t="n">
-        <v>3.21</v>
+        <v>2.8</v>
       </c>
       <c r="H3" t="n">
-        <v>0.22</v>
+        <v>0.6</v>
       </c>
       <c r="I3" t="n">
-        <v>5.31</v>
+        <v>5.15</v>
       </c>
       <c r="J3" t="n">
-        <v>6.06</v>
+        <v>6.03</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>433.13</v>
+        <v>433.1</v>
       </c>
       <c r="N3" t="n">
-        <v>412.71</v>
+        <v>412.7</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -771,22 +771,22 @@
         <v>475</v>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.63</v>
+        <v>0.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>47800</v>
+        <v>47600</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5800</v>
+        <v>5600</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.81</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="4">
@@ -807,19 +807,19 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>176.8</v>
+        <v>177.1</v>
       </c>
       <c r="F4" t="n">
-        <v>67.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>4.24</v>
+        <v>4.41</v>
       </c>
       <c r="H4" t="n">
-        <v>0.43</v>
+        <v>0.82</v>
       </c>
       <c r="I4" t="n">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="J4" t="n">
         <v>4.58</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>156.19</v>
+        <v>156.2</v>
       </c>
       <c r="N4" t="n">
         <v>154.07</v>
@@ -883,22 +883,22 @@
         <v>178.1</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.73</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>17680</v>
+        <v>17710</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1880</v>
+        <v>1910</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.9</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3041</v>
+        <v>3016</v>
       </c>
       <c r="F5" t="n">
-        <v>46.8</v>
+        <v>44.4</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.66</v>
+        <v>-1.44</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4</v>
+        <v>0.82</v>
       </c>
       <c r="I5" t="n">
-        <v>2.34</v>
+        <v>0.34</v>
       </c>
       <c r="J5" t="n">
-        <v>15.44</v>
+        <v>15.04</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2934.66</v>
+        <v>2934.33</v>
       </c>
       <c r="N5" t="n">
-        <v>3165.09</v>
+        <v>3164.96</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -980,7 +980,6 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -996,22 +995,22 @@
         <v>3021</v>
       </c>
       <c r="X5" t="n">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.66</v>
+        <v>-0.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>39533</v>
+        <v>39208</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2434</v>
+        <v>2109</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.56</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="6">
@@ -1032,22 +1031,22 @@
         <v>4795</v>
       </c>
       <c r="E6" t="n">
-        <v>4968</v>
+        <v>4944</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>59.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.29</v>
+        <v>1.81</v>
       </c>
       <c r="H6" t="n">
-        <v>0.51</v>
+        <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>60.42</v>
+        <v>58.51</v>
       </c>
       <c r="J6" t="n">
-        <v>59.58</v>
+        <v>59.2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1060,10 +1059,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4717.35</v>
+        <v>4717.03</v>
       </c>
       <c r="N6" t="n">
-        <v>4670.4</v>
+        <v>4670.28</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1076,7 +1075,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1092,7 +1091,7 @@
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは買いシグナルです。
+・MACDは売りシグナルです。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
@@ -1102,29 +1101,29 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>4910</v>
       </c>
       <c r="X6" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z6" t="n">
-        <v>24840</v>
+        <v>24720</v>
       </c>
       <c r="AA6" t="n">
         <v>23975</v>
       </c>
       <c r="AB6" t="n">
-        <v>865</v>
+        <v>745</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.61</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="7">
@@ -1145,22 +1144,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>8131</v>
+        <v>8126</v>
       </c>
       <c r="F7" t="n">
-        <v>35.1</v>
+        <v>34.9</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.95</v>
+        <v>-6.01</v>
       </c>
       <c r="H7" t="n">
-        <v>0.29</v>
+        <v>0.49</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.08</v>
+        <v>-4.48</v>
       </c>
       <c r="J7" t="n">
-        <v>127.86</v>
+        <v>127.78</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1173,10 +1172,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7741.79</v>
+        <v>7741.72</v>
       </c>
       <c r="N7" t="n">
-        <v>8723.540000000001</v>
+        <v>8723.52</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1221,22 +1220,22 @@
         <v>8118</v>
       </c>
       <c r="X7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>8131</v>
+        <v>8126</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="8">
@@ -1257,22 +1256,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>9157</v>
+        <v>9364</v>
       </c>
       <c r="F8" t="n">
-        <v>52.9</v>
+        <v>55.1</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.24</v>
+        <v>-1.14</v>
       </c>
       <c r="H8" t="n">
-        <v>0.54</v>
+        <v>0.93</v>
       </c>
       <c r="I8" t="n">
-        <v>-441.99</v>
+        <v>-425.48</v>
       </c>
       <c r="J8" t="n">
-        <v>-560.9</v>
+        <v>-557.6</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1285,10 +1284,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>13051.09</v>
+        <v>13053.85</v>
       </c>
       <c r="N8" t="n">
-        <v>7923.97</v>
+        <v>7925</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1334,22 +1333,22 @@
         <v>9197</v>
       </c>
       <c r="X8" t="n">
-        <v>-40</v>
+        <v>167</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.43</v>
+        <v>1.82</v>
       </c>
       <c r="Z8" t="n">
-        <v>9157</v>
+        <v>9364</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-843</v>
+        <v>-636</v>
       </c>
       <c r="AC8" t="n">
-        <v>-8.43</v>
+        <v>-6.36</v>
       </c>
     </row>
     <row r="9">
@@ -1370,22 +1369,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>49690</v>
+        <v>50780</v>
       </c>
       <c r="F9" t="n">
-        <v>45.4</v>
+        <v>47.1</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.64</v>
+        <v>-4.67</v>
       </c>
       <c r="H9" t="n">
-        <v>0.59</v>
+        <v>0.96</v>
       </c>
       <c r="I9" t="n">
-        <v>-754.13</v>
+        <v>-667.1799999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-768.36</v>
+        <v>-750.97</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1394,14 +1393,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>65866.8</v>
+        <v>65881.33</v>
       </c>
       <c r="N9" t="n">
-        <v>39790.11</v>
+        <v>39795.57</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1410,11 +1409,11 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟠 利益確定検討</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1433,7 +1432,7 @@
 ・MACDは買いシグナルです。
 ・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・RSIは良好な水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -1441,29 +1440,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>押し目、デッドクロス、-1σ、MACD買い、反発局面</t>
+          <t>押し目、デッドクロス、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>51750</v>
       </c>
       <c r="X9" t="n">
-        <v>-2060</v>
+        <v>-970</v>
       </c>
       <c r="Y9" t="n">
-        <v>-3.98</v>
+        <v>-1.87</v>
       </c>
       <c r="Z9" t="n">
-        <v>49690</v>
+        <v>50780</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-5820</v>
+        <v>-4730</v>
       </c>
       <c r="AC9" t="n">
-        <v>-10.48</v>
+        <v>-8.52</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1483,38 +1483,38 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>35.64</v>
+        <v>36.85</v>
       </c>
       <c r="F10" t="n">
-        <v>42.1</v>
+        <v>48.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.04</v>
+        <v>-2.36</v>
       </c>
       <c r="H10" t="n">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="I10" t="n">
-        <v>1.13</v>
+        <v>0.98</v>
       </c>
       <c r="J10" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.62</v>
+        <v>33.49</v>
       </c>
       <c r="N10" t="n">
-        <v>31.52</v>
+        <v>31.54</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1523,20 +1523,20 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟠 利益確定検討</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1544,7 +1544,9 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1552,29 +1554,29 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、長期上昇</t>
+          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>36.74</v>
+        <v>35.64</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Y10" t="n">
-        <v>-2.99</v>
+        <v>3.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6077</v>
+        <v>-6076</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.42</v>
+        <v>-99.40000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3310</v>
+        <v>3455</v>
       </c>
       <c r="F2" t="n">
-        <v>40.3</v>
+        <v>37.4</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.3</v>
+        <v>0.66</v>
       </c>
       <c r="H2" t="n">
-        <v>0.92</v>
+        <v>0.35</v>
       </c>
       <c r="I2" t="n">
-        <v>20.98</v>
+        <v>25.12</v>
       </c>
       <c r="J2" t="n">
-        <v>63.17</v>
+        <v>55.56</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3018.93</v>
+        <v>3031.87</v>
       </c>
       <c r="N2" t="n">
-        <v>2720.63</v>
+        <v>2723.95</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -650,29 +650,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3340</v>
+        <v>3310</v>
       </c>
       <c r="X2" t="n">
-        <v>-30</v>
+        <v>145</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.9</v>
+        <v>4.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>13240</v>
+        <v>13820</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2440</v>
+        <v>3020</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.59</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="3">
@@ -693,38 +693,38 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="F3" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8</v>
+        <v>5.19</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6</v>
+        <v>0.36</v>
       </c>
       <c r="I3" t="n">
-        <v>5.15</v>
+        <v>6.61</v>
       </c>
       <c r="J3" t="n">
-        <v>6.03</v>
+        <v>6.15</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>433.1</v>
+        <v>433.58</v>
       </c>
       <c r="N3" t="n">
-        <v>412.7</v>
+        <v>413.29</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -753,10 +753,9 @@
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは売りシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -764,29 +763,29 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25日線上、ゴールデンクロス、MACD売り、長期上昇</t>
+          <t>25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.21</v>
+        <v>2.94</v>
       </c>
       <c r="Z3" t="n">
-        <v>47600</v>
+        <v>49000</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5600</v>
+        <v>7000</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.33</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="4">
@@ -807,22 +806,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>177.1</v>
+        <v>179.2</v>
       </c>
       <c r="F4" t="n">
-        <v>67.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>4.41</v>
+        <v>5.18</v>
       </c>
       <c r="H4" t="n">
-        <v>0.82</v>
+        <v>0.48</v>
       </c>
       <c r="I4" t="n">
-        <v>4.63</v>
+        <v>4.69</v>
       </c>
       <c r="J4" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -835,10 +834,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>156.2</v>
+        <v>156.61</v>
       </c>
       <c r="N4" t="n">
-        <v>154.07</v>
+        <v>154.21</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -880,25 +879,25 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>178.1</v>
+        <v>177.1</v>
       </c>
       <c r="X4" t="n">
-        <v>-1</v>
+        <v>2.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.5600000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>17710</v>
+        <v>17920</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1910</v>
+        <v>2120</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.09</v>
+        <v>13.42</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +918,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3016</v>
+        <v>3035</v>
       </c>
       <c r="F5" t="n">
-        <v>44.4</v>
+        <v>42.3</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.44</v>
+        <v>-0.88</v>
       </c>
       <c r="H5" t="n">
-        <v>0.82</v>
+        <v>0.51</v>
       </c>
       <c r="I5" t="n">
-        <v>0.34</v>
+        <v>0.03</v>
       </c>
       <c r="J5" t="n">
-        <v>15.04</v>
+        <v>12.04</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,10 +946,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2934.33</v>
+        <v>2936.87</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.96</v>
+        <v>3164.88</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -992,102 +991,214 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>3021</v>
+        <v>3016</v>
       </c>
       <c r="X5" t="n">
-        <v>-5</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.17</v>
+        <v>0.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>39208</v>
+        <v>39455</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2109</v>
+        <v>2356</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.68</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8455</v>
+      </c>
+      <c r="F6" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J6" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>7755.44</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8700.57</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>55</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>押し目、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>8126</v>
+      </c>
+      <c r="X6" t="n">
+        <v>329</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8455</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>462</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.78</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>8058.T</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>三菱商事</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>4795</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>4944</v>
       </c>
-      <c r="F6" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I6" t="n">
-        <v>58.51</v>
-      </c>
-      <c r="J6" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="F7" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I7" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="J7" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>4717.03</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4670.28</v>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="M7" t="n">
+        <v>4717.29</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4676.88</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>🟢 強い買い</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q7" t="n">
         <v>95</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>★★★★★</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -1098,221 +1209,222 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>4910</v>
-      </c>
-      <c r="X6" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>24720</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>23975</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>745</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8126</v>
-      </c>
-      <c r="F7" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-6.01</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-4.48</v>
-      </c>
-      <c r="J7" t="n">
-        <v>127.78</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>7741.72</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8723.52</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>60</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>8118</v>
+        <v>4944</v>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8126</v>
+        <v>24720</v>
       </c>
       <c r="AA7" t="n">
-        <v>7993</v>
+        <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>133</v>
+        <v>745</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.66</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6976.T</t>
+          <t>285A.T</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>太陽誘電</t>
+          <t>キオクシアホールディングス</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
+        <v>55510</v>
+      </c>
+      <c r="E8" t="n">
+        <v>49760</v>
+      </c>
+      <c r="F8" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-6.44</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-895.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-779.88</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>65510.93</v>
+      </c>
+      <c r="N8" t="n">
+        <v>39994.21</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>65</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>RSI適正、押し目、MACD売り、反発局面</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>50780</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-1020</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>49760</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>55510</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-5750</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-10.36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
         <v>10000</v>
       </c>
-      <c r="E8" t="n">
-        <v>9364</v>
-      </c>
-      <c r="F8" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-425.48</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-557.6</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="E9" t="n">
+        <v>8962</v>
+      </c>
+      <c r="F9" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-4.59</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-415.02</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-529.08</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>13053.85</v>
-      </c>
-      <c r="N8" t="n">
-        <v>7925</v>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="M9" t="n">
+        <v>12957.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7954.19</v>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>85</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>65</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -1323,146 +1435,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>RSI適正、押し目、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>9197</v>
-      </c>
-      <c r="X8" t="n">
-        <v>167</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9364</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-636</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-6.36</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>55510</v>
-      </c>
-      <c r="E9" t="n">
-        <v>50780</v>
-      </c>
-      <c r="F9" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-4.67</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-667.1799999999999</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-750.97</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>65881.33</v>
-      </c>
-      <c r="N9" t="n">
-        <v>39795.57</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>🟠 利益確定検討</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>50</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>押し目、デッドクロス、MACD買い、反発局面</t>
+          <t>押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>51750</v>
+        <v>9364</v>
       </c>
       <c r="X9" t="n">
-        <v>-970</v>
+        <v>-402</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.87</v>
+        <v>-4.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>50780</v>
+        <v>8962</v>
       </c>
       <c r="AA9" t="n">
-        <v>55510</v>
+        <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-4730</v>
+        <v>-1038</v>
       </c>
       <c r="AC9" t="n">
-        <v>-8.52</v>
+        <v>-10.38</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3455</v>
+        <v>3445</v>
       </c>
       <c r="F2" t="n">
-        <v>37.4</v>
+        <v>36.8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.66</v>
+        <v>0.38</v>
       </c>
       <c r="H2" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="I2" t="n">
-        <v>25.12</v>
+        <v>24.32</v>
       </c>
       <c r="J2" t="n">
-        <v>55.56</v>
+        <v>55.4</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3031.87</v>
+        <v>3031.73</v>
       </c>
       <c r="N2" t="n">
-        <v>2723.95</v>
+        <v>2723.9</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -657,22 +657,22 @@
         <v>3310</v>
       </c>
       <c r="X2" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.38</v>
+        <v>4.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>13820</v>
+        <v>13780</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>3020</v>
+        <v>2980</v>
       </c>
       <c r="AC2" t="n">
-        <v>27.96</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="3">
@@ -693,22 +693,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F3" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="G3" t="n">
-        <v>5.19</v>
+        <v>4.98</v>
       </c>
       <c r="H3" t="n">
-        <v>0.36</v>
+        <v>0.72</v>
       </c>
       <c r="I3" t="n">
-        <v>6.61</v>
+        <v>6.53</v>
       </c>
       <c r="J3" t="n">
-        <v>6.15</v>
+        <v>6.13</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>433.58</v>
+        <v>433.56</v>
       </c>
       <c r="N3" t="n">
         <v>413.29</v>
@@ -770,22 +770,22 @@
         <v>476</v>
       </c>
       <c r="X3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="Z3" t="n">
-        <v>49000</v>
+        <v>48900</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7000</v>
+        <v>6900</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.67</v>
+        <v>16.43</v>
       </c>
     </row>
     <row r="4">
@@ -806,22 +806,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>179.2</v>
+        <v>180</v>
       </c>
       <c r="F4" t="n">
-        <v>69.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="G4" t="n">
-        <v>5.18</v>
+        <v>5.63</v>
       </c>
       <c r="H4" t="n">
-        <v>0.48</v>
+        <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>4.69</v>
+        <v>4.76</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>156.61</v>
+        <v>156.62</v>
       </c>
       <c r="N4" t="n">
         <v>154.21</v>
@@ -867,6 +867,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
+・買われ過ぎ水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -882,22 +883,22 @@
         <v>177.1</v>
       </c>
       <c r="X4" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
       <c r="Z4" t="n">
-        <v>17920</v>
+        <v>18000</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>2120</v>
+        <v>2200</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.42</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="5">
@@ -918,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="F5" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.88</v>
+        <v>-0.92</v>
       </c>
       <c r="H5" t="n">
-        <v>0.51</v>
+        <v>0.96</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="J5" t="n">
-        <v>12.04</v>
+        <v>12.02</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -946,7 +947,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2936.87</v>
+        <v>2936.86</v>
       </c>
       <c r="N5" t="n">
         <v>3164.88</v>
@@ -994,22 +995,22 @@
         <v>3016</v>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>39455</v>
+        <v>39442</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2356</v>
+        <v>2343</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.35</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="6">
@@ -1030,22 +1031,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8455</v>
+        <v>8475</v>
       </c>
       <c r="F6" t="n">
-        <v>36.9</v>
+        <v>37.5</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.26</v>
+        <v>-2.04</v>
       </c>
       <c r="H6" t="n">
-        <v>0.59</v>
+        <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>1.14</v>
+        <v>2.74</v>
       </c>
       <c r="J6" t="n">
-        <v>102.45</v>
+        <v>102.77</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1058,10 +1059,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7755.44</v>
+        <v>7755.71</v>
       </c>
       <c r="N6" t="n">
-        <v>8700.57</v>
+        <v>8700.67</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1106,22 +1107,22 @@
         <v>8126</v>
       </c>
       <c r="X6" t="n">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.05</v>
+        <v>4.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>8455</v>
+        <v>8475</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.78</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="7">
@@ -1142,22 +1143,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4944</v>
+        <v>4979</v>
       </c>
       <c r="F7" t="n">
-        <v>57.3</v>
+        <v>58.6</v>
       </c>
       <c r="G7" t="n">
-        <v>1.72</v>
+        <v>2.41</v>
       </c>
       <c r="H7" t="n">
-        <v>0.44</v>
+        <v>0.86</v>
       </c>
       <c r="I7" t="n">
-        <v>54.72</v>
+        <v>57.51</v>
       </c>
       <c r="J7" t="n">
-        <v>58.3</v>
+        <v>58.86</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1170,10 +1171,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4717.29</v>
+        <v>4717.76</v>
       </c>
       <c r="N7" t="n">
-        <v>4676.88</v>
+        <v>4677.05</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1219,58 +1220,58 @@
         <v>4944</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="Z7" t="n">
-        <v>24720</v>
+        <v>24895</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>745</v>
+        <v>920</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.11</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>285A.T</t>
+          <t>6976.T</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>キオクシアホールディングス</t>
+          <t>太陽誘電</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>55510</v>
+        <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>49760</v>
+        <v>9000</v>
       </c>
       <c r="F8" t="n">
-        <v>53.6</v>
+        <v>47.3</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.44</v>
+        <v>-4.2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.54</v>
+        <v>0.89</v>
       </c>
       <c r="I8" t="n">
-        <v>-895.5</v>
+        <v>-411.98</v>
       </c>
       <c r="J8" t="n">
-        <v>-779.88</v>
+        <v>-528.48</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1283,10 +1284,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>65510.93</v>
+        <v>12957.52</v>
       </c>
       <c r="N8" t="n">
-        <v>39994.21</v>
+        <v>7954.38</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1312,6 +1313,119 @@
         </is>
       </c>
       <c r="T8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>押し目、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>9364</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-364</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-3.89</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>55510</v>
+      </c>
+      <c r="E9" t="n">
+        <v>49880</v>
+      </c>
+      <c r="F9" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-6.22</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-885.9299999999999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-777.96</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>65512.53</v>
+      </c>
+      <c r="N9" t="n">
+        <v>39994.82</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>65</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -1322,145 +1436,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>RSI適正、押し目、MACD売り、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>50780</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-1020</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>49760</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>55510</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-5750</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-10.36</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E9" t="n">
-        <v>8962</v>
-      </c>
-      <c r="F9" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-4.59</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-415.02</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-529.08</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>12957.01</v>
-      </c>
-      <c r="N9" t="n">
-        <v>7954.19</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>65</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>押し目、MACD買い、反発局面</t>
+          <t>RSI適正、押し目、MACD売り、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>9364</v>
+        <v>50780</v>
       </c>
       <c r="X9" t="n">
-        <v>-402</v>
+        <v>-900</v>
       </c>
       <c r="Y9" t="n">
-        <v>-4.29</v>
+        <v>-1.77</v>
       </c>
       <c r="Z9" t="n">
-        <v>8962</v>
+        <v>49880</v>
       </c>
       <c r="AA9" t="n">
-        <v>10000</v>
+        <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1038</v>
+        <v>-5630</v>
       </c>
       <c r="AC9" t="n">
-        <v>-10.38</v>
+        <v>-10.14</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1482,38 +1482,38 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>36.85</v>
+        <v>40.35</v>
       </c>
       <c r="F10" t="n">
-        <v>48.5</v>
+        <v>54.6</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.36</v>
+        <v>6.6</v>
       </c>
       <c r="H10" t="n">
-        <v>0.91</v>
+        <v>1.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.98</v>
+        <v>1.14</v>
       </c>
       <c r="J10" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.49</v>
+        <v>33.41</v>
       </c>
       <c r="N10" t="n">
-        <v>31.54</v>
+        <v>31.58</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1522,20 +1522,20 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>🟠 利益確定検討</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1543,39 +1543,44 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・出来高が増加しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、出来高微増、ゴールデンクロス、+1σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>35.64</v>
+        <v>36.85</v>
       </c>
       <c r="X10" t="n">
-        <v>1.21</v>
+        <v>3.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.4</v>
+        <v>9.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6076</v>
+        <v>-6073</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.40000000000001</v>
+        <v>-99.34</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3445</v>
+        <v>3395</v>
       </c>
       <c r="F2" t="n">
-        <v>36.8</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>0.38</v>
+        <v>-1.03</v>
       </c>
       <c r="H2" t="n">
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
       <c r="I2" t="n">
-        <v>24.32</v>
+        <v>22.68</v>
       </c>
       <c r="J2" t="n">
-        <v>55.4</v>
+        <v>48.85</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3031.73</v>
+        <v>3044.6</v>
       </c>
       <c r="N2" t="n">
-        <v>2723.9</v>
+        <v>2726.83</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -650,29 +650,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>25日線上、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3310</v>
+        <v>3445</v>
       </c>
       <c r="X2" t="n">
-        <v>135</v>
+        <v>-50</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.08</v>
+        <v>-1.45</v>
       </c>
       <c r="Z2" t="n">
-        <v>13780</v>
+        <v>13580</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2980</v>
+        <v>2780</v>
       </c>
       <c r="AC2" t="n">
-        <v>27.59</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="3">
@@ -693,22 +693,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="F3" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.98</v>
+        <v>6.1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.72</v>
+        <v>0.23</v>
       </c>
       <c r="I3" t="n">
-        <v>6.53</v>
+        <v>8.18</v>
       </c>
       <c r="J3" t="n">
-        <v>6.13</v>
+        <v>6.54</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>433.56</v>
+        <v>434.33</v>
       </c>
       <c r="N3" t="n">
-        <v>413.29</v>
+        <v>414</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -767,25 +767,25 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="X3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.73</v>
+        <v>1.64</v>
       </c>
       <c r="Z3" t="n">
-        <v>48900</v>
+        <v>49700</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6900</v>
+        <v>7700</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.43</v>
+        <v>18.33</v>
       </c>
     </row>
     <row r="4">
@@ -806,22 +806,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>180</v>
+        <v>177.3</v>
       </c>
       <c r="F4" t="n">
-        <v>70.8</v>
+        <v>59.2</v>
       </c>
       <c r="G4" t="n">
-        <v>5.63</v>
+        <v>3.69</v>
       </c>
       <c r="H4" t="n">
-        <v>0.96</v>
+        <v>0.52</v>
       </c>
       <c r="I4" t="n">
-        <v>4.76</v>
+        <v>4.58</v>
       </c>
       <c r="J4" t="n">
-        <v>4.62</v>
+        <v>4.61</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>156.62</v>
+        <v>157.02</v>
       </c>
       <c r="N4" t="n">
-        <v>154.21</v>
+        <v>154.35</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -866,8 +866,8 @@
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは買いシグナルです。
-・買われ過ぎ水準です。
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -876,29 +876,29 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、+1σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>177.1</v>
+        <v>180</v>
       </c>
       <c r="X4" t="n">
-        <v>2.9</v>
+        <v>-2.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.64</v>
+        <v>-1.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>18000</v>
+        <v>17730</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>2200</v>
+        <v>1930</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.92</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3034</v>
+        <v>3003</v>
       </c>
       <c r="F5" t="n">
-        <v>42.2</v>
+        <v>35.2</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.92</v>
+        <v>-1.91</v>
       </c>
       <c r="H5" t="n">
-        <v>0.96</v>
+        <v>0.59</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05</v>
+        <v>-2.83</v>
       </c>
       <c r="J5" t="n">
-        <v>12.02</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2936.86</v>
+        <v>2938.49</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.88</v>
+        <v>3164.73</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -992,25 +992,25 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>3016</v>
+        <v>3034</v>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>-31</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6</v>
+        <v>-1.02</v>
       </c>
       <c r="Z5" t="n">
-        <v>39442</v>
+        <v>39039</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2343</v>
+        <v>1940</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.32</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="6">
@@ -1031,22 +1031,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8475</v>
+        <v>8307</v>
       </c>
       <c r="F6" t="n">
-        <v>37.5</v>
+        <v>33.2</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.04</v>
+        <v>-3.72</v>
       </c>
       <c r="H6" t="n">
-        <v>0.97</v>
+        <v>0.39</v>
       </c>
       <c r="I6" t="n">
-        <v>2.74</v>
+        <v>-5.04</v>
       </c>
       <c r="J6" t="n">
-        <v>102.77</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1055,14 +1055,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7755.71</v>
+        <v>7767.04</v>
       </c>
       <c r="N6" t="n">
-        <v>8700.67</v>
+        <v>8677.870000000001</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -1100,29 +1100,29 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、上昇トレンド</t>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>8126</v>
+        <v>8475</v>
       </c>
       <c r="X6" t="n">
-        <v>349</v>
+        <v>-168</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.29</v>
+        <v>-1.98</v>
       </c>
       <c r="Z6" t="n">
-        <v>8475</v>
+        <v>8307</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>482</v>
+        <v>314</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.03</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="7">
@@ -1143,22 +1143,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4979</v>
+        <v>4944</v>
       </c>
       <c r="F7" t="n">
-        <v>58.6</v>
+        <v>56.2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.41</v>
+        <v>1.54</v>
       </c>
       <c r="H7" t="n">
-        <v>0.86</v>
+        <v>0.38</v>
       </c>
       <c r="I7" t="n">
-        <v>57.51</v>
+        <v>53.28</v>
       </c>
       <c r="J7" t="n">
-        <v>58.86</v>
+        <v>57.74</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4717.76</v>
+        <v>4717.29</v>
       </c>
       <c r="N7" t="n">
-        <v>4677.05</v>
+        <v>4683.76</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1217,61 +1217,61 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4944</v>
+        <v>4979</v>
       </c>
       <c r="X7" t="n">
-        <v>35</v>
+        <v>-35</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.71</v>
+        <v>-0.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>24895</v>
+        <v>24720</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>920</v>
+        <v>745</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.84</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6976.T</t>
+          <t>285A.T</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>太陽誘電</t>
+          <t>キオクシアホールディングス</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>10000</v>
+        <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>9000</v>
+        <v>51960</v>
       </c>
       <c r="F8" t="n">
-        <v>47.3</v>
+        <v>53.8</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.2</v>
+        <v>-2.18</v>
       </c>
       <c r="H8" t="n">
-        <v>0.89</v>
+        <v>0.59</v>
       </c>
       <c r="I8" t="n">
-        <v>-411.98</v>
+        <v>-881.3</v>
       </c>
       <c r="J8" t="n">
-        <v>-528.48</v>
+        <v>-798.63</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>12957.52</v>
+        <v>65164.27</v>
       </c>
       <c r="N8" t="n">
-        <v>7954.38</v>
+        <v>40205.35</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1313,6 +1313,119 @@
         </is>
       </c>
       <c r="T8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>RSI適正、押し目、MACD売り、反発局面</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>49880</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2080</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>51960</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>55510</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-3550</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-6.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9157</v>
+      </c>
+      <c r="F9" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-384.19</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-499.62</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>12856.28</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7984.31</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>65</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -1323,145 +1436,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>押し目、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>9364</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-364</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-3.89</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>55510</v>
-      </c>
-      <c r="E9" t="n">
-        <v>49880</v>
-      </c>
-      <c r="F9" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-6.22</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-885.9299999999999</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-777.96</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>65512.53</v>
-      </c>
-      <c r="N9" t="n">
-        <v>39994.82</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>65</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、反発局面</t>
+          <t>押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>50780</v>
+        <v>9000</v>
       </c>
       <c r="X9" t="n">
-        <v>-900</v>
+        <v>157</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.77</v>
+        <v>1.74</v>
       </c>
       <c r="Z9" t="n">
-        <v>49880</v>
+        <v>9157</v>
       </c>
       <c r="AA9" t="n">
-        <v>55510</v>
+        <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-5630</v>
+        <v>-843</v>
       </c>
       <c r="AC9" t="n">
-        <v>-10.14</v>
+        <v>-8.43</v>
       </c>
     </row>
     <row r="10">
@@ -1491,7 +1491,7 @@
         <v>6.6</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I10" t="n">
         <v>1.14</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3395</v>
+        <v>3340</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>29.5</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.03</v>
+        <v>-2.57</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31</v>
+        <v>0.58</v>
       </c>
       <c r="I2" t="n">
-        <v>22.68</v>
+        <v>18.29</v>
       </c>
       <c r="J2" t="n">
-        <v>48.85</v>
+        <v>47.98</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3044.6</v>
+        <v>3043.87</v>
       </c>
       <c r="N2" t="n">
-        <v>2726.83</v>
+        <v>2726.56</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,20 +621,20 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -642,6 +642,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・売られ過ぎ水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -650,29 +651,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>RSI売られすぎ、押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>3445</v>
       </c>
       <c r="X2" t="n">
-        <v>-50</v>
+        <v>-105</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.45</v>
+        <v>-3.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>13580</v>
+        <v>13360</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2780</v>
+        <v>2560</v>
       </c>
       <c r="AC2" t="n">
-        <v>25.74</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="3">
@@ -693,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="F3" t="n">
-        <v>49.1</v>
+        <v>47.1</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1</v>
+        <v>4.87</v>
       </c>
       <c r="H3" t="n">
-        <v>0.23</v>
+        <v>0.65</v>
       </c>
       <c r="I3" t="n">
-        <v>8.18</v>
+        <v>7.7</v>
       </c>
       <c r="J3" t="n">
-        <v>6.54</v>
+        <v>6.45</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -721,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>434.33</v>
+        <v>434.25</v>
       </c>
       <c r="N3" t="n">
-        <v>414</v>
+        <v>413.97</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -770,22 +771,22 @@
         <v>489</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.64</v>
+        <v>0.41</v>
       </c>
       <c r="Z3" t="n">
-        <v>49700</v>
+        <v>49100</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7700</v>
+        <v>7100</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.33</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="4">
@@ -815,7 +816,7 @@
         <v>3.69</v>
       </c>
       <c r="H4" t="n">
-        <v>0.52</v>
+        <v>1.35</v>
       </c>
       <c r="I4" t="n">
         <v>4.58</v>
@@ -919,22 +920,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3003</v>
+        <v>3025</v>
       </c>
       <c r="F5" t="n">
-        <v>35.2</v>
+        <v>36.8</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.91</v>
+        <v>-1.22</v>
       </c>
       <c r="H5" t="n">
-        <v>0.59</v>
+        <v>1.82</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.83</v>
+        <v>-1.07</v>
       </c>
       <c r="J5" t="n">
-        <v>9.050000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,10 +948,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2938.49</v>
+        <v>2938.78</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.73</v>
+        <v>3164.84</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -963,19 +964,132 @@
         </is>
       </c>
       <c r="Q5" t="n">
+        <v>60</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・出来高が増加しています。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>押し目、出来高微増、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>3034</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-9</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>39325</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>37099</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2226</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8339</v>
+      </c>
+      <c r="F6" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-3.36</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="J6" t="n">
+        <v>81.72</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>7767.47</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8678.030000000001</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
         <v>55</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -985,144 +1099,32 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>3034</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-31</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>39039</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1940</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.23</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E6" t="n">
-        <v>8307</v>
-      </c>
-      <c r="F6" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-3.72</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-5.04</v>
-      </c>
-      <c r="J6" t="n">
-        <v>81.20999999999999</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>7767.04</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8677.870000000001</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>60</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+          <t>押し目、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>8475</v>
       </c>
       <c r="X6" t="n">
-        <v>-168</v>
+        <v>-136</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.98</v>
+        <v>-1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>8307</v>
+        <v>8339</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>314</v>
+        <v>346</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="7">
@@ -1143,22 +1145,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4944</v>
+        <v>4947</v>
       </c>
       <c r="F7" t="n">
-        <v>56.2</v>
+        <v>56.3</v>
       </c>
       <c r="G7" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="H7" t="n">
-        <v>0.38</v>
+        <v>1.39</v>
       </c>
       <c r="I7" t="n">
-        <v>53.28</v>
+        <v>53.52</v>
       </c>
       <c r="J7" t="n">
-        <v>57.74</v>
+        <v>57.79</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1171,10 +1173,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4717.29</v>
+        <v>4717.33</v>
       </c>
       <c r="N7" t="n">
-        <v>4683.76</v>
+        <v>4683.77</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1220,22 +1222,22 @@
         <v>4979</v>
       </c>
       <c r="X7" t="n">
-        <v>-35</v>
+        <v>-32</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.7</v>
+        <v>-0.64</v>
       </c>
       <c r="Z7" t="n">
-        <v>24720</v>
+        <v>24735</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.11</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="8">
@@ -1256,22 +1258,22 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>51960</v>
+        <v>54570</v>
       </c>
       <c r="F8" t="n">
-        <v>53.8</v>
+        <v>58.1</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.18</v>
+        <v>2.53</v>
       </c>
       <c r="H8" t="n">
-        <v>0.59</v>
+        <v>1.19</v>
       </c>
       <c r="I8" t="n">
-        <v>-881.3</v>
+        <v>-673.09</v>
       </c>
       <c r="J8" t="n">
-        <v>-798.63</v>
+        <v>-756.99</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1284,10 +1286,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>65164.27</v>
+        <v>65199.07</v>
       </c>
       <c r="N8" t="n">
-        <v>40205.35</v>
+        <v>40218.4</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1296,136 +1298,23 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>RSI適正、押し目、MACD売り、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>49880</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2080</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>51960</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>55510</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-3550</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-6.4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9157</v>
-      </c>
-      <c r="F9" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-384.19</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-499.62</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>12856.28</v>
-      </c>
-      <c r="N9" t="n">
-        <v>7984.31</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>65</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -1436,32 +1325,149 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>49880</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4690</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>54570</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>55510</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-940</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9375</v>
+      </c>
+      <c r="F9" t="n">
+        <v>52</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-366.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-496.14</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>12859.19</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7985.4</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>95</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>押し目、MACD買い、反発局面</t>
+          <t>RSI適正、25日線上、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>9000</v>
       </c>
       <c r="X9" t="n">
-        <v>157</v>
+        <v>375</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.74</v>
+        <v>4.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>9157</v>
+        <v>9375</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-843</v>
+        <v>-625</v>
       </c>
       <c r="AC9" t="n">
-        <v>-8.43</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1488,38 +1488,38 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>40.35</v>
+        <v>39.09</v>
       </c>
       <c r="F10" t="n">
-        <v>54.6</v>
+        <v>54.9</v>
       </c>
       <c r="G10" t="n">
-        <v>6.6</v>
+        <v>3.28</v>
       </c>
       <c r="H10" t="n">
-        <v>1.51</v>
+        <v>1.15</v>
       </c>
       <c r="I10" t="n">
         <v>1.14</v>
       </c>
       <c r="J10" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.41</v>
+        <v>33.26</v>
       </c>
       <c r="N10" t="n">
-        <v>31.58</v>
+        <v>31.6</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1528,20 +1528,20 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1549,44 +1549,39 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・RSIは良好な水準です。
-・出来高が増加しています。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、出来高微増、ゴールデンクロス、+1σ、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、デッドクロス、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>36.85</v>
+        <v>40.35</v>
       </c>
       <c r="X10" t="n">
-        <v>3.5</v>
+        <v>-1.26</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.5</v>
+        <v>-3.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6073</v>
+        <v>-6074</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.34</v>
+        <v>-99.36</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1488,38 +1488,38 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>39.09</v>
+        <v>41.2</v>
       </c>
       <c r="F10" t="n">
-        <v>54.9</v>
+        <v>58.8</v>
       </c>
       <c r="G10" t="n">
-        <v>3.28</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="I10" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="J10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+2S</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.26</v>
+        <v>33.18</v>
       </c>
       <c r="N10" t="n">
-        <v>31.6</v>
+        <v>31.64</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1528,20 +1528,20 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1549,39 +1549,43 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、デッドクロス、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、ゴールデンクロス、+2σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>40.35</v>
+        <v>39.09</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.26</v>
+        <v>2.11</v>
       </c>
       <c r="Y10" t="n">
-        <v>-3.12</v>
+        <v>5.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6074</v>
+        <v>-6072</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.36</v>
+        <v>-99.33</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1497,7 +1497,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I10" t="n">
         <v>1.31</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1488,26 +1488,26 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>41.2</v>
+        <v>41.54</v>
       </c>
       <c r="F10" t="n">
-        <v>58.8</v>
+        <v>61</v>
       </c>
       <c r="G10" t="n">
-        <v>8.699999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>1.11</v>
+        <v>0.68</v>
       </c>
       <c r="I10" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="J10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.18</v>
+        <v>33.1</v>
       </c>
       <c r="N10" t="n">
-        <v>31.64</v>
+        <v>31.68</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1548,44 +1548,38 @@
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは売りシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・RSIは良好な水準です。
+・MACDは買いシグナルです。
 ・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、ゴールデンクロス、+2σ、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、+2σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>39.09</v>
+        <v>41.2</v>
       </c>
       <c r="X10" t="n">
-        <v>2.11</v>
+        <v>0.34</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.4</v>
+        <v>0.83</v>
       </c>
       <c r="Z10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6072</v>
+        <v>-6071</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.33</v>
+        <v>-99.31999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1488,22 +1488,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>41.54</v>
+        <v>41.44</v>
       </c>
       <c r="F10" t="n">
-        <v>61</v>
+        <v>60.2</v>
       </c>
       <c r="G10" t="n">
-        <v>9.220000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.68</v>
+        <v>0.89</v>
       </c>
       <c r="I10" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="J10" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1512,14 +1512,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+2S</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>33.1</v>
       </c>
       <c r="N10" t="n">
-        <v>31.68</v>
+        <v>31.72</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1557,26 +1557,26 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+2σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>41.2</v>
+        <v>41.54</v>
       </c>
       <c r="X10" t="n">
-        <v>0.34</v>
+        <v>-0.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.83</v>
+        <v>-0.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6071</v>
+        <v>-6072</v>
       </c>
       <c r="AC10" t="n">
         <v>-99.31999999999999</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3340</v>
+        <v>3375</v>
       </c>
       <c r="F2" t="n">
-        <v>29.5</v>
+        <v>36.8</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.57</v>
+        <v>-1.57</v>
       </c>
       <c r="H2" t="n">
-        <v>0.58</v>
+        <v>0.18</v>
       </c>
       <c r="I2" t="n">
-        <v>18.29</v>
+        <v>16.14</v>
       </c>
       <c r="J2" t="n">
-        <v>47.98</v>
+        <v>41.61</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3043.87</v>
+        <v>3056.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2726.56</v>
+        <v>2729.36</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,20 +621,20 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -642,7 +642,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・売られ過ぎ水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -651,29 +650,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>RSI売られすぎ、押し目、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3445</v>
+        <v>3340</v>
       </c>
       <c r="X2" t="n">
-        <v>-105</v>
+        <v>35</v>
       </c>
       <c r="Y2" t="n">
-        <v>-3.05</v>
+        <v>1.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>13360</v>
+        <v>13500</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2560</v>
+        <v>2700</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -697,19 +696,19 @@
         <v>491</v>
       </c>
       <c r="F3" t="n">
-        <v>47.1</v>
+        <v>54.1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.87</v>
+        <v>4.38</v>
       </c>
       <c r="H3" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="I3" t="n">
-        <v>7.7</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>6.45</v>
+        <v>6.86</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -722,10 +721,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>434.25</v>
+        <v>435.12</v>
       </c>
       <c r="N3" t="n">
-        <v>413.97</v>
+        <v>414.62</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -738,7 +737,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -764,17 +763,17 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
         <v>49100</v>
@@ -807,22 +806,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>177.3</v>
+        <v>175.3</v>
       </c>
       <c r="F4" t="n">
-        <v>59.2</v>
+        <v>49.4</v>
       </c>
       <c r="G4" t="n">
-        <v>3.69</v>
+        <v>2.19</v>
       </c>
       <c r="H4" t="n">
-        <v>1.35</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>4.58</v>
+        <v>4.23</v>
       </c>
       <c r="J4" t="n">
-        <v>4.61</v>
+        <v>4.53</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -831,14 +830,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>157.02</v>
+        <v>157.4</v>
       </c>
       <c r="N4" t="n">
-        <v>154.35</v>
+        <v>154.46</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -847,361 +846,23 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、+1σ、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>180</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>17730</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>15800</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1930</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>12.22</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>トヨタ自動車</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>13</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2853.77</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3025</v>
-      </c>
-      <c r="F5" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="J5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>2938.78</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3164.84</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>60</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・出来高が増加しています。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>押し目、出来高微増、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>3034</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-9</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>39325</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2226</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E6" t="n">
-        <v>8339</v>
-      </c>
-      <c r="F6" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-3.36</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="J6" t="n">
-        <v>81.72</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>7767.47</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8678.030000000001</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>55</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>8475</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-136</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>8339</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>7993</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>346</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>8058.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>三菱商事</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4795</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4947</v>
-      </c>
-      <c r="F7" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="I7" t="n">
-        <v>53.52</v>
-      </c>
-      <c r="J7" t="n">
-        <v>57.79</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>4717.33</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4683.77</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>🟢 強い買い</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>95</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -1212,32 +873,370 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>25日線上、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>177.3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>17530</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>15800</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1730</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>10.95</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>トヨタ自動車</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2853.77</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2971.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-6.13</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>2940.55</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3164.23</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>75</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>RSI売られすぎ、押し目、-1σ、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>3025</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-53.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>38630</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>37099</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1530</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8235</v>
+      </c>
+      <c r="F6" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-14.85</v>
+      </c>
+      <c r="J6" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>7780.31</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8654.299999999999</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>60</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>8339</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-104</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8235</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>242</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>三菱商事</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4795</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4863</v>
+      </c>
+      <c r="F7" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="I7" t="n">
+        <v>43.09</v>
+      </c>
+      <c r="J7" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>4716.89</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4689.84</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>65</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4979</v>
+        <v>4947</v>
       </c>
       <c r="X7" t="n">
-        <v>-32</v>
+        <v>-84</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.64</v>
+        <v>-1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>24735</v>
+        <v>24315</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>760</v>
+        <v>340</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.17</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="8">
@@ -1258,22 +1257,22 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>54570</v>
+        <v>54980</v>
       </c>
       <c r="F8" t="n">
-        <v>58.1</v>
+        <v>57.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.53</v>
+        <v>3.84</v>
       </c>
       <c r="H8" t="n">
-        <v>1.19</v>
+        <v>0.65</v>
       </c>
       <c r="I8" t="n">
-        <v>-673.09</v>
+        <v>-465.96</v>
       </c>
       <c r="J8" t="n">
-        <v>-756.99</v>
+        <v>-698.78</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1286,10 +1285,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>65199.07</v>
+        <v>64906.53</v>
       </c>
       <c r="N8" t="n">
-        <v>40218.4</v>
+        <v>40451.37</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1325,36 +1324,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>RSI適正、25日線上、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>49880</v>
+        <v>54570</v>
       </c>
       <c r="X8" t="n">
-        <v>4690</v>
+        <v>410</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.4</v>
+        <v>0.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>54570</v>
+        <v>54980</v>
       </c>
       <c r="AA8" t="n">
         <v>55510</v>
       </c>
       <c r="AB8" t="n">
-        <v>-940</v>
+        <v>-530</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.69</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="9">
@@ -1375,22 +1370,22 @@
         <v>10000</v>
       </c>
       <c r="E9" t="n">
-        <v>9375</v>
+        <v>9268</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>49.8</v>
       </c>
       <c r="G9" t="n">
-        <v>0.49</v>
+        <v>0.21</v>
       </c>
       <c r="H9" t="n">
-        <v>0.92</v>
+        <v>0.58</v>
       </c>
       <c r="I9" t="n">
-        <v>-366.8</v>
+        <v>-335.75</v>
       </c>
       <c r="J9" t="n">
-        <v>-496.14</v>
+        <v>-464.06</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1403,10 +1398,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>12859.19</v>
+        <v>12768.16</v>
       </c>
       <c r="N9" t="n">
-        <v>7985.4</v>
+        <v>8015.78</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1415,20 +1410,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1445,29 +1440,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、反発局面</t>
+          <t>25日線上、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>9000</v>
+        <v>9375</v>
       </c>
       <c r="X9" t="n">
-        <v>375</v>
+        <v>-107</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.17</v>
+        <v>-1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>9375</v>
+        <v>9268</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-625</v>
+        <v>-732</v>
       </c>
       <c r="AC9" t="n">
-        <v>-6.25</v>
+        <v>-7.32</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3375</v>
+        <v>3330</v>
       </c>
       <c r="F2" t="n">
-        <v>36.8</v>
+        <v>34.2</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.57</v>
+        <v>-2.84</v>
       </c>
       <c r="H2" t="n">
-        <v>0.18</v>
+        <v>0.34</v>
       </c>
       <c r="I2" t="n">
-        <v>16.14</v>
+        <v>12.56</v>
       </c>
       <c r="J2" t="n">
-        <v>41.61</v>
+        <v>40.89</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3056.11</v>
+        <v>3055.51</v>
       </c>
       <c r="N2" t="n">
-        <v>2729.36</v>
+        <v>2729.13</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -657,22 +657,22 @@
         <v>3340</v>
       </c>
       <c r="X2" t="n">
-        <v>35</v>
+        <v>-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.05</v>
+        <v>-0.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>13500</v>
+        <v>13320</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2700</v>
+        <v>2520</v>
       </c>
       <c r="AC2" t="n">
-        <v>25</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="3">
@@ -693,22 +693,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F3" t="n">
-        <v>54.1</v>
+        <v>52.9</v>
       </c>
       <c r="G3" t="n">
-        <v>4.38</v>
+        <v>3.77</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4</v>
+        <v>0.98</v>
       </c>
       <c r="I3" t="n">
-        <v>8.529999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>6.86</v>
+        <v>6.81</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>435.12</v>
+        <v>435.08</v>
       </c>
       <c r="N3" t="n">
-        <v>414.62</v>
+        <v>414.6</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -770,22 +770,22 @@
         <v>491</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="Z3" t="n">
-        <v>49100</v>
+        <v>48800</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7100</v>
+        <v>6800</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.9</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="4">
@@ -806,19 +806,19 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>175.3</v>
+        <v>174.9</v>
       </c>
       <c r="F4" t="n">
-        <v>49.4</v>
+        <v>48.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.19</v>
+        <v>1.97</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="I4" t="n">
-        <v>4.23</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
         <v>4.53</v>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>157.4</v>
+        <v>157.39</v>
       </c>
       <c r="N4" t="n">
         <v>154.46</v>
@@ -883,22 +883,22 @@
         <v>177.3</v>
       </c>
       <c r="X4" t="n">
-        <v>-2</v>
+        <v>-2.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.13</v>
+        <v>-1.35</v>
       </c>
       <c r="Z4" t="n">
-        <v>17530</v>
+        <v>17490</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1730</v>
+        <v>1690</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.95</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2971.5</v>
+        <v>2969</v>
       </c>
       <c r="F5" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.91</v>
+        <v>-2.99</v>
       </c>
       <c r="H5" t="n">
-        <v>0.73</v>
+        <v>1.22</v>
       </c>
       <c r="I5" t="n">
-        <v>-6.13</v>
+        <v>-6.33</v>
       </c>
       <c r="J5" t="n">
-        <v>6.3</v>
+        <v>6.26</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2940.55</v>
+        <v>2940.52</v>
       </c>
       <c r="N5" t="n">
-        <v>3164.23</v>
+        <v>3164.21</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -996,22 +996,22 @@
         <v>3025</v>
       </c>
       <c r="X5" t="n">
-        <v>-53.5</v>
+        <v>-56</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.77</v>
+        <v>-1.85</v>
       </c>
       <c r="Z5" t="n">
-        <v>38630</v>
+        <v>38597</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>1530</v>
+        <v>1498</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.13</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="6">
@@ -1032,22 +1032,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8235</v>
+        <v>8196</v>
       </c>
       <c r="F6" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.33</v>
+        <v>-4.77</v>
       </c>
       <c r="H6" t="n">
-        <v>0.62</v>
+        <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>-14.85</v>
+        <v>-17.96</v>
       </c>
       <c r="J6" t="n">
-        <v>62.4</v>
+        <v>61.78</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7780.31</v>
+        <v>7779.79</v>
       </c>
       <c r="N6" t="n">
-        <v>8654.299999999999</v>
+        <v>8654.1</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1072,20 +1072,20 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1093,6 +1093,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは売りシグナルです。
+・売られ過ぎ水準です。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -1101,29 +1102,29 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+          <t>RSI売られすぎ、押し目、-1σ、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>8339</v>
       </c>
       <c r="X6" t="n">
-        <v>-104</v>
+        <v>-143</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.25</v>
+        <v>-1.71</v>
       </c>
       <c r="Z6" t="n">
-        <v>8235</v>
+        <v>8196</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>242</v>
+        <v>203</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.03</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="7">
@@ -1144,22 +1145,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4863</v>
+        <v>4811</v>
       </c>
       <c r="F7" t="n">
-        <v>45.6</v>
+        <v>43.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.25</v>
+        <v>-1.27</v>
       </c>
       <c r="H7" t="n">
-        <v>0.66</v>
+        <v>1.32</v>
       </c>
       <c r="I7" t="n">
-        <v>43.09</v>
+        <v>38.94</v>
       </c>
       <c r="J7" t="n">
-        <v>54.85</v>
+        <v>54.02</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1172,10 +1173,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4716.89</v>
+        <v>4716.2</v>
       </c>
       <c r="N7" t="n">
-        <v>4689.84</v>
+        <v>4689.58</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1205,7 +1206,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -1221,22 +1221,22 @@
         <v>4947</v>
       </c>
       <c r="X7" t="n">
-        <v>-84</v>
+        <v>-136</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.7</v>
+        <v>-2.75</v>
       </c>
       <c r="Z7" t="n">
-        <v>24315</v>
+        <v>24055</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>340</v>
+        <v>80</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.42</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="8">
@@ -1257,22 +1257,22 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>54980</v>
+        <v>54580</v>
       </c>
       <c r="F8" t="n">
-        <v>57.2</v>
+        <v>56.5</v>
       </c>
       <c r="G8" t="n">
-        <v>3.84</v>
+        <v>3.11</v>
       </c>
       <c r="H8" t="n">
-        <v>0.65</v>
+        <v>0.97</v>
       </c>
       <c r="I8" t="n">
-        <v>-465.96</v>
+        <v>-497.87</v>
       </c>
       <c r="J8" t="n">
-        <v>-698.78</v>
+        <v>-705.17</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>64906.53</v>
+        <v>64901.2</v>
       </c>
       <c r="N8" t="n">
-        <v>40451.37</v>
+        <v>40449.37</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1334,22 +1334,22 @@
         <v>54570</v>
       </c>
       <c r="X8" t="n">
-        <v>410</v>
+        <v>10</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.75</v>
+        <v>0.02</v>
       </c>
       <c r="Z8" t="n">
-        <v>54980</v>
+        <v>54580</v>
       </c>
       <c r="AA8" t="n">
         <v>55510</v>
       </c>
       <c r="AB8" t="n">
-        <v>-530</v>
+        <v>-930</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.95</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="9">
@@ -1370,22 +1370,22 @@
         <v>10000</v>
       </c>
       <c r="E9" t="n">
-        <v>9268</v>
+        <v>8935</v>
       </c>
       <c r="F9" t="n">
-        <v>49.8</v>
+        <v>46.6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.21</v>
+        <v>-3.25</v>
       </c>
       <c r="H9" t="n">
-        <v>0.58</v>
+        <v>0.96</v>
       </c>
       <c r="I9" t="n">
-        <v>-335.75</v>
+        <v>-362.32</v>
       </c>
       <c r="J9" t="n">
-        <v>-464.06</v>
+        <v>-469.38</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>12768.16</v>
+        <v>12763.72</v>
       </c>
       <c r="N9" t="n">
-        <v>8015.78</v>
+        <v>8014.11</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1410,11 +1410,11 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1440,29 +1440,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25日線上、MACD買い、反発局面</t>
+          <t>押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>9375</v>
       </c>
       <c r="X9" t="n">
-        <v>-107</v>
+        <v>-440</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.14</v>
+        <v>-4.69</v>
       </c>
       <c r="Z9" t="n">
-        <v>9268</v>
+        <v>8935</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-732</v>
+        <v>-1065</v>
       </c>
       <c r="AC9" t="n">
-        <v>-7.32</v>
+        <v>-10.65</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1483,22 +1483,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>41.44</v>
+        <v>41.51</v>
       </c>
       <c r="F10" t="n">
-        <v>60.2</v>
+        <v>58.7</v>
       </c>
       <c r="G10" t="n">
-        <v>8.5</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="I10" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="J10" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.1</v>
+        <v>33.07</v>
       </c>
       <c r="N10" t="n">
-        <v>31.72</v>
+        <v>31.75</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1544,6 +1544,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -1556,22 +1557,22 @@
         </is>
       </c>
       <c r="W10" t="n">
-        <v>41.54</v>
+        <v>41.44</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.24</v>
+        <v>0.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6072</v>
+        <v>-6071</v>
       </c>
       <c r="AC10" t="n">
         <v>-99.31999999999999</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1492,7 +1492,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="I10" t="n">
         <v>1.58</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3355</v>
+        <v>3330</v>
       </c>
       <c r="F2" t="n">
-        <v>41.6</v>
+        <v>39.9</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.2</v>
+        <v>-2.9</v>
       </c>
       <c r="H2" t="n">
-        <v>0.71</v>
+        <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>9.91</v>
+        <v>7.92</v>
       </c>
       <c r="J2" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3067.01</v>
+        <v>3066.68</v>
       </c>
       <c r="N2" t="n">
-        <v>2731.7</v>
+        <v>2731.58</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -657,22 +657,22 @@
         <v>3330</v>
       </c>
       <c r="X2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>13420</v>
+        <v>13320</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2620</v>
+        <v>2520</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.26</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="3">
@@ -693,22 +693,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="F3" t="n">
-        <v>53.7</v>
+        <v>52.1</v>
       </c>
       <c r="G3" t="n">
-        <v>1.88</v>
+        <v>1.07</v>
       </c>
       <c r="H3" t="n">
-        <v>0.35</v>
+        <v>0.72</v>
       </c>
       <c r="I3" t="n">
-        <v>8.1</v>
+        <v>7.78</v>
       </c>
       <c r="J3" t="n">
-        <v>7.07</v>
+        <v>7.01</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>435.93</v>
+        <v>435.88</v>
       </c>
       <c r="N3" t="n">
-        <v>415.2</v>
+        <v>415.18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -770,22 +770,22 @@
         <v>488</v>
       </c>
       <c r="X3" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.43</v>
+        <v>-2.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>48100</v>
+        <v>47700</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6100</v>
+        <v>5700</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.52</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="4">
@@ -806,19 +806,19 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>175.7</v>
+        <v>176.1</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>51.7</v>
       </c>
       <c r="G4" t="n">
-        <v>2.07</v>
+        <v>2.29</v>
       </c>
       <c r="H4" t="n">
-        <v>0.36</v>
+        <v>0.93</v>
       </c>
       <c r="I4" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="J4" t="n">
         <v>4.41</v>
@@ -883,22 +883,22 @@
         <v>174.9</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.46</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>17570</v>
+        <v>17610</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1770</v>
+        <v>1810</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.2</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2988</v>
+        <v>2989.5</v>
       </c>
       <c r="F5" t="n">
-        <v>30.6</v>
+        <v>30.9</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.32</v>
+        <v>-2.28</v>
       </c>
       <c r="H5" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="I5" t="n">
-        <v>-8.859999999999999</v>
+        <v>-8.74</v>
       </c>
       <c r="J5" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2942.36</v>
+        <v>2942.38</v>
       </c>
       <c r="N5" t="n">
-        <v>3163.69</v>
+        <v>3163.7</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -995,22 +995,22 @@
         <v>2969</v>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>20.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>38844</v>
+        <v>38864</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>1745</v>
+        <v>1764</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.7</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="6">
@@ -1031,22 +1031,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8181</v>
+        <v>8100</v>
       </c>
       <c r="F6" t="n">
-        <v>33.8</v>
+        <v>32.5</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.69</v>
+        <v>-5.59</v>
       </c>
       <c r="H6" t="n">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>-31.08</v>
+        <v>-37.54</v>
       </c>
       <c r="J6" t="n">
-        <v>43.21</v>
+        <v>41.92</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7788.55</v>
+        <v>7787.47</v>
       </c>
       <c r="N6" t="n">
-        <v>8630.42</v>
+        <v>8630.02</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1107,22 +1107,22 @@
         <v>8196</v>
       </c>
       <c r="X6" t="n">
-        <v>-15</v>
+        <v>-96</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.18</v>
+        <v>-1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>8181</v>
+        <v>8100</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.35</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="7">
@@ -1143,22 +1143,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4857</v>
+        <v>4859</v>
       </c>
       <c r="F7" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.39</v>
+        <v>-0.35</v>
       </c>
       <c r="H7" t="n">
-        <v>0.37</v>
+        <v>0.91</v>
       </c>
       <c r="I7" t="n">
-        <v>30.74</v>
+        <v>30.9</v>
       </c>
       <c r="J7" t="n">
-        <v>49.36</v>
+        <v>49.4</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4716.17</v>
+        <v>4716.2</v>
       </c>
       <c r="N7" t="n">
-        <v>4695.67</v>
+        <v>4695.68</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1183,20 +1183,20 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1213,29 +1213,29 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>RSI適正、押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>4811</v>
       </c>
       <c r="X7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>24285</v>
+        <v>24295</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="8">
@@ -1256,22 +1256,22 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>55880</v>
+        <v>55780</v>
       </c>
       <c r="F8" t="n">
-        <v>58.5</v>
+        <v>58.4</v>
       </c>
       <c r="G8" t="n">
-        <v>5.67</v>
+        <v>5.49</v>
       </c>
       <c r="H8" t="n">
-        <v>0.51</v>
+        <v>0.8</v>
       </c>
       <c r="I8" t="n">
-        <v>-251.21</v>
+        <v>-259.18</v>
       </c>
       <c r="J8" t="n">
-        <v>-614.37</v>
+        <v>-615.97</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1280,14 +1280,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>64604.4</v>
+        <v>64603.07</v>
       </c>
       <c r="N8" t="n">
-        <v>40683.53</v>
+        <v>40683.03</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
 ・MACDは買いシグナルです。
 ・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -1327,29 +1327,29 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、ゴールデンクロス、+1σ、MACD買い、反発局面</t>
+          <t>RSI適正、25日線上、ゴールデンクロス、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>54580</v>
       </c>
       <c r="X8" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>55880</v>
+        <v>55780</v>
       </c>
       <c r="AA8" t="n">
         <v>55510</v>
       </c>
       <c r="AB8" t="n">
-        <v>370</v>
+        <v>270</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.67</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="9">
@@ -1370,22 +1370,22 @@
         <v>10000</v>
       </c>
       <c r="E9" t="n">
-        <v>9301</v>
+        <v>9160</v>
       </c>
       <c r="F9" t="n">
-        <v>54.3</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>1.02</v>
+        <v>-0.45</v>
       </c>
       <c r="H9" t="n">
-        <v>0.63</v>
+        <v>1.01</v>
       </c>
       <c r="I9" t="n">
-        <v>-325.48</v>
+        <v>-336.73</v>
       </c>
       <c r="J9" t="n">
-        <v>-440.6</v>
+        <v>-442.85</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>12676.4</v>
+        <v>12674.52</v>
       </c>
       <c r="N9" t="n">
-        <v>8044.56</v>
+        <v>8043.86</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1410,20 +1410,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1440,29 +1440,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、反発局面</t>
+          <t>RSI適正、押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>8935</v>
       </c>
       <c r="X9" t="n">
-        <v>366</v>
+        <v>225</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.1</v>
+        <v>2.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>9301</v>
+        <v>9160</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-699</v>
+        <v>-840</v>
       </c>
       <c r="AC9" t="n">
-        <v>-6.99</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1483,22 +1483,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>41.51</v>
+        <v>43.26</v>
       </c>
       <c r="F10" t="n">
         <v>58.7</v>
       </c>
       <c r="G10" t="n">
-        <v>8.119999999999999</v>
+        <v>11.89</v>
       </c>
       <c r="H10" t="n">
-        <v>0.86</v>
+        <v>1.21</v>
       </c>
       <c r="I10" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="J10" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1507,14 +1507,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>+2S</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.07</v>
+        <v>33.1</v>
       </c>
       <c r="N10" t="n">
-        <v>31.75</v>
+        <v>31.79</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1545,7 +1545,8 @@
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・25日線から大きく上に乖離しています。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1553,29 +1554,29 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSI適正、上昇加速、+2σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>41.44</v>
+        <v>41.51</v>
       </c>
       <c r="X10" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.75</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.17</v>
+        <v>4.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6071</v>
+        <v>-6070</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.31999999999999</v>
+        <v>-99.29000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3330</v>
+        <v>3360</v>
       </c>
       <c r="F2" t="n">
-        <v>39.9</v>
+        <v>44.5</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.9</v>
+        <v>-2.18</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1</v>
+        <v>0.61</v>
       </c>
       <c r="I2" t="n">
-        <v>7.92</v>
+        <v>6.59</v>
       </c>
       <c r="J2" t="n">
-        <v>34.3</v>
+        <v>28.76</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3066.68</v>
+        <v>3079.65</v>
       </c>
       <c r="N2" t="n">
-        <v>2731.58</v>
+        <v>2734.2</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -657,22 +657,22 @@
         <v>3330</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>13320</v>
+        <v>13440</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2520</v>
+        <v>2640</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.33</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="3">
@@ -693,22 +693,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F3" t="n">
-        <v>52.1</v>
+        <v>57.7</v>
       </c>
       <c r="G3" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="H3" t="n">
-        <v>0.72</v>
+        <v>0.28</v>
       </c>
       <c r="I3" t="n">
-        <v>7.78</v>
+        <v>7.45</v>
       </c>
       <c r="J3" t="n">
-        <v>7.01</v>
+        <v>7.1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>435.88</v>
+        <v>436.81</v>
       </c>
       <c r="N3" t="n">
-        <v>415.18</v>
+        <v>415.73</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -767,25 +767,25 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="X3" t="n">
-        <v>-11</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2.25</v>
+        <v>0.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>47700</v>
+        <v>47900</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5700</v>
+        <v>5900</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.57</v>
+        <v>14.05</v>
       </c>
     </row>
     <row r="4">
@@ -806,22 +806,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>176.1</v>
+        <v>175.5</v>
       </c>
       <c r="F4" t="n">
-        <v>51.7</v>
+        <v>54.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.29</v>
+        <v>1.56</v>
       </c>
       <c r="H4" t="n">
-        <v>0.93</v>
+        <v>0.52</v>
       </c>
       <c r="I4" t="n">
-        <v>3.95</v>
+        <v>3.66</v>
       </c>
       <c r="J4" t="n">
-        <v>4.41</v>
+        <v>4.26</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>157.79</v>
+        <v>158.17</v>
       </c>
       <c r="N4" t="n">
-        <v>154.58</v>
+        <v>154.69</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -880,25 +880,25 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>174.9</v>
+        <v>176.1</v>
       </c>
       <c r="X4" t="n">
-        <v>1.2</v>
+        <v>-0.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>17610</v>
+        <v>17550</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1810</v>
+        <v>1750</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.46</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2989.5</v>
+        <v>3016</v>
       </c>
       <c r="F5" t="n">
-        <v>30.9</v>
+        <v>36.9</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.28</v>
+        <v>-1.51</v>
       </c>
       <c r="H5" t="n">
-        <v>0.75</v>
+        <v>0.34</v>
       </c>
       <c r="I5" t="n">
-        <v>-8.74</v>
+        <v>-8.41</v>
       </c>
       <c r="J5" t="n">
-        <v>3.26</v>
+        <v>0.92</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2942.38</v>
+        <v>2944.96</v>
       </c>
       <c r="N5" t="n">
-        <v>3163.7</v>
+        <v>3163.35</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -992,102 +992,214 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>2969</v>
+        <v>2989.5</v>
       </c>
       <c r="X5" t="n">
-        <v>20.5</v>
+        <v>26.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="Z5" t="n">
-        <v>38864</v>
+        <v>39208</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>1764</v>
+        <v>2109</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.76</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>三菱商事</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4795</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4845</v>
+      </c>
+      <c r="F6" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I6" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="J6" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>4716.36</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4701.58</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>押し目、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>4859</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-14</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>24225</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>23975</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>250</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>7974.T</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>任天堂</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>7993</v>
       </c>
-      <c r="E6" t="n">
-        <v>8100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-5.59</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-37.54</v>
-      </c>
-      <c r="J6" t="n">
-        <v>41.92</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="E7" t="n">
+        <v>8065</v>
+      </c>
+      <c r="F7" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-5.78</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-55.24</v>
+      </c>
+      <c r="J7" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>-1S</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>7787.47</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8630.02</v>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="M7" t="n">
+        <v>7793.13</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8605.219999999999</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>🟢 上昇</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>⚪ 様子見</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q7" t="n">
         <v>60</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -1097,145 +1209,32 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>8196</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-96</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-1.17</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>8100</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>7993</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>107</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>8058.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>三菱商事</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4795</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4859</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="I7" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>4716.2</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4695.68</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>85</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、長期上昇</t>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4811</v>
+        <v>8100</v>
       </c>
       <c r="X7" t="n">
-        <v>48</v>
+        <v>-35</v>
       </c>
       <c r="Y7" t="n">
-        <v>1</v>
+        <v>-0.43</v>
       </c>
       <c r="Z7" t="n">
-        <v>24295</v>
+        <v>8065</v>
       </c>
       <c r="AA7" t="n">
-        <v>23975</v>
+        <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>320</v>
+        <v>72</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.33</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
@@ -1256,26 +1255,26 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>55780</v>
+        <v>54480</v>
       </c>
       <c r="F8" t="n">
-        <v>58.4</v>
+        <v>54.8</v>
       </c>
       <c r="G8" t="n">
-        <v>5.49</v>
+        <v>2.68</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8</v>
+        <v>0.46</v>
       </c>
       <c r="I8" t="n">
-        <v>-259.18</v>
+        <v>-172.93</v>
       </c>
       <c r="J8" t="n">
-        <v>-615.97</v>
+        <v>-527.36</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1284,10 +1283,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>64603.07</v>
+        <v>64371.07</v>
       </c>
       <c r="N8" t="n">
-        <v>40683.03</v>
+        <v>40908.39</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1300,7 +1299,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1313,120 +1312,6 @@
         </is>
       </c>
       <c r="T8" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、ゴールデンクロス、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>54580</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>55780</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>55510</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>270</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9160</v>
-      </c>
-      <c r="F9" t="n">
-        <v>53</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-336.73</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-442.85</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>12674.52</v>
-      </c>
-      <c r="N9" t="n">
-        <v>8043.86</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>85</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -1437,6 +1322,119 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>55780</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-1300</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>54480</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>55510</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-1030</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9153</v>
+      </c>
+      <c r="F9" t="n">
+        <v>53</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-313.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-416.96</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>12596.89</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8073.51</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>85</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
@@ -1444,25 +1442,25 @@
         </is>
       </c>
       <c r="W9" t="n">
-        <v>8935</v>
+        <v>9160</v>
       </c>
       <c r="X9" t="n">
-        <v>225</v>
+        <v>-7</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.52</v>
+        <v>-0.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>9160</v>
+        <v>9153</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-840</v>
+        <v>-847</v>
       </c>
       <c r="AC9" t="n">
-        <v>-8.4</v>
+        <v>-8.470000000000001</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3360</v>
+        <v>3340</v>
       </c>
       <c r="F2" t="n">
-        <v>44.5</v>
+        <v>43.1</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.18</v>
+        <v>-2.74</v>
       </c>
       <c r="H2" t="n">
-        <v>0.61</v>
+        <v>0.9</v>
       </c>
       <c r="I2" t="n">
-        <v>6.59</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>28.76</v>
+        <v>28.44</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3079.65</v>
+        <v>3079.39</v>
       </c>
       <c r="N2" t="n">
-        <v>2734.2</v>
+        <v>2734.1</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -657,22 +657,22 @@
         <v>3330</v>
       </c>
       <c r="X2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>13440</v>
+        <v>13360</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2640</v>
+        <v>2560</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.44</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="3">
@@ -702,7 +702,7 @@
         <v>1.19</v>
       </c>
       <c r="H3" t="n">
-        <v>0.28</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>7.45</v>
@@ -806,22 +806,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>175.5</v>
+        <v>174.7</v>
       </c>
       <c r="F4" t="n">
-        <v>54.6</v>
+        <v>52.9</v>
       </c>
       <c r="G4" t="n">
-        <v>1.56</v>
+        <v>1.12</v>
       </c>
       <c r="H4" t="n">
-        <v>0.52</v>
+        <v>1.08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>158.17</v>
+        <v>158.16</v>
       </c>
       <c r="N4" t="n">
         <v>154.69</v>
@@ -883,22 +883,22 @@
         <v>176.1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6</v>
+        <v>-1.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.34</v>
+        <v>-0.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>17550</v>
+        <v>17470</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1750</v>
+        <v>1670</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.08</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3016</v>
+        <v>2986.5</v>
       </c>
       <c r="F5" t="n">
-        <v>36.9</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.51</v>
+        <v>-2.43</v>
       </c>
       <c r="H5" t="n">
-        <v>0.34</v>
+        <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>-8.41</v>
+        <v>-10.77</v>
       </c>
       <c r="J5" t="n">
-        <v>0.92</v>
+        <v>0.45</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -943,14 +943,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2944.96</v>
+        <v>2944.57</v>
       </c>
       <c r="N5" t="n">
-        <v>3163.35</v>
+        <v>3163.2</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -976,230 +976,6 @@
         </is>
       </c>
       <c r="T5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>2989.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>39208</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2109</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.68</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>8058.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>三菱商事</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4795</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4845</v>
-      </c>
-      <c r="F6" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="I6" t="n">
-        <v>23.13</v>
-      </c>
-      <c r="J6" t="n">
-        <v>44.14</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>4716.36</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4701.58</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>65</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>4859</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-14</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>24225</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>23975</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>250</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8065</v>
-      </c>
-      <c r="F7" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-5.78</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-55.24</v>
-      </c>
-      <c r="J7" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>7793.13</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8605.219999999999</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>60</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -1209,32 +985,258 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>2989.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>38824</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>37099</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1726</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.65</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>三菱商事</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4795</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4818</v>
+      </c>
+      <c r="F6" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I6" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="J6" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>4716</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4701.44</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>🟠 利益確定検討</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>50</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>4859</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-41</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>24090</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>23975</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>115</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-6.52</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>7792.25</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8604.889999999999</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+          <t>RSI売られすぎ、押し目、-1σ、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>8100</v>
       </c>
       <c r="X7" t="n">
-        <v>-35</v>
+        <v>-101</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.43</v>
+        <v>-1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>8065</v>
+        <v>7999</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.9</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="8">
@@ -1255,22 +1257,22 @@
         <v>55510</v>
       </c>
       <c r="E8" t="n">
-        <v>54480</v>
+        <v>53340</v>
       </c>
       <c r="F8" t="n">
-        <v>54.8</v>
+        <v>52.8</v>
       </c>
       <c r="G8" t="n">
-        <v>2.68</v>
+        <v>0.62</v>
       </c>
       <c r="H8" t="n">
-        <v>0.46</v>
+        <v>0.72</v>
       </c>
       <c r="I8" t="n">
-        <v>-172.93</v>
+        <v>-263.87</v>
       </c>
       <c r="J8" t="n">
-        <v>-527.36</v>
+        <v>-545.55</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1283,10 +1285,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>64371.07</v>
+        <v>64355.87</v>
       </c>
       <c r="N8" t="n">
-        <v>40908.39</v>
+        <v>40902.69</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1332,22 +1334,22 @@
         <v>55780</v>
       </c>
       <c r="X8" t="n">
-        <v>-1300</v>
+        <v>-2440</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.33</v>
+        <v>-4.37</v>
       </c>
       <c r="Z8" t="n">
-        <v>54480</v>
+        <v>53340</v>
       </c>
       <c r="AA8" t="n">
         <v>55510</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1030</v>
+        <v>-2170</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.86</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="9">
@@ -1368,22 +1370,22 @@
         <v>10000</v>
       </c>
       <c r="E9" t="n">
-        <v>9153</v>
+        <v>9093</v>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>52.3</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3</v>
+        <v>-0.92</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I9" t="n">
-        <v>-313.4</v>
+        <v>-318.19</v>
       </c>
       <c r="J9" t="n">
-        <v>-416.96</v>
+        <v>-417.92</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1396,10 +1398,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>12596.89</v>
+        <v>12596.09</v>
       </c>
       <c r="N9" t="n">
-        <v>8073.51</v>
+        <v>8073.21</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1445,22 +1447,22 @@
         <v>9160</v>
       </c>
       <c r="X9" t="n">
-        <v>-7</v>
+        <v>-67</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.08</v>
+        <v>-0.73</v>
       </c>
       <c r="Z9" t="n">
-        <v>9153</v>
+        <v>9093</v>
       </c>
       <c r="AA9" t="n">
         <v>10000</v>
       </c>
       <c r="AB9" t="n">
-        <v>-847</v>
+        <v>-907</v>
       </c>
       <c r="AC9" t="n">
-        <v>-8.470000000000001</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -806,7 +806,7 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>174.7</v>
+        <v>172</v>
       </c>
       <c r="F4" t="n">
         <v>52.9</v>
@@ -818,10 +818,10 @@
         <v>1.08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="J4" t="n">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>158.16</v>
+        <v>155.71</v>
       </c>
       <c r="N4" t="n">
-        <v>154.69</v>
+        <v>152.3</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -880,25 +880,25 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>176.1</v>
+        <v>173.38</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4</v>
+        <v>-1.38</v>
       </c>
       <c r="Y4" t="n">
         <v>-0.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>17470</v>
+        <v>17200</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1670</v>
+        <v>1400</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.57</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -919,7 +919,7 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2986.5</v>
+        <v>2936.5</v>
       </c>
       <c r="F5" t="n">
         <v>32</v>
@@ -931,7 +931,7 @@
         <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>-10.77</v>
+        <v>-10.59</v>
       </c>
       <c r="J5" t="n">
         <v>0.45</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2944.57</v>
+        <v>2895.27</v>
       </c>
       <c r="N5" t="n">
-        <v>3163.2</v>
+        <v>3110.24</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -992,102 +992,215 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>2989.5</v>
+        <v>2939.45</v>
       </c>
       <c r="X5" t="n">
-        <v>-3</v>
+        <v>-2.95</v>
       </c>
       <c r="Y5" t="n">
         <v>-0.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>38824</v>
+        <v>38174</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>1726</v>
+        <v>1076</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.65</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-6.52</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>7792.25</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8604.889999999999</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>75</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>RSI売られすぎ、押し目、-1σ、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>8100</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-101</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>8058.T</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>三菱商事</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>4795</v>
       </c>
-      <c r="E6" t="n">
-        <v>4818</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="E7" t="n">
+        <v>4756</v>
+      </c>
+      <c r="F7" t="n">
         <v>36.7</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G7" t="n">
         <v>-1.33</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H7" t="n">
         <v>1.03</v>
       </c>
-      <c r="I6" t="n">
-        <v>20.97</v>
-      </c>
-      <c r="J6" t="n">
-        <v>43.71</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="I7" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>DC</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>4716</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4701.44</v>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="M7" t="n">
+        <v>4655.31</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4640.94</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>🟠 利益確定検討</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q7" t="n">
         <v>50</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -1098,181 +1211,68 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>4859</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-41</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>24090</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>23975</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>115</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E7" t="n">
-        <v>7999</v>
-      </c>
-      <c r="F7" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-6.52</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-60.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>21.43</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>7792.25</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8604.889999999999</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>75</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSI売られすぎ、押し目、-1σ、MACD売り、上昇トレンド</t>
+          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>8100</v>
+        <v>4796.47</v>
       </c>
       <c r="X7" t="n">
-        <v>-101</v>
+        <v>-40.47</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.25</v>
+        <v>-0.84</v>
       </c>
       <c r="Z7" t="n">
-        <v>7999</v>
+        <v>23780</v>
       </c>
       <c r="AA7" t="n">
-        <v>7993</v>
+        <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>6</v>
+        <v>-195</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.08</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>285A.T</t>
+          <t>6976.T</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>キオクシアホールディングス</t>
+          <t>太陽誘電</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>55510</v>
+        <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>53340</v>
+        <v>9048</v>
       </c>
       <c r="F8" t="n">
-        <v>52.8</v>
+        <v>52.3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.62</v>
+        <v>-0.92</v>
       </c>
       <c r="H8" t="n">
-        <v>0.72</v>
+        <v>0.9</v>
       </c>
       <c r="I8" t="n">
-        <v>-263.87</v>
+        <v>-316.61</v>
       </c>
       <c r="J8" t="n">
-        <v>-545.55</v>
+        <v>-415.85</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>64355.87</v>
+        <v>12533.76</v>
       </c>
       <c r="N8" t="n">
-        <v>40902.69</v>
+        <v>8033.25</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1297,20 +1297,20 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1327,142 +1327,149 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、反発局面</t>
+          <t>RSI適正、押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>55780</v>
+        <v>9114.67</v>
       </c>
       <c r="X8" t="n">
-        <v>-2440</v>
+        <v>-66.67</v>
       </c>
       <c r="Y8" t="n">
-        <v>-4.37</v>
+        <v>-0.73</v>
       </c>
       <c r="Z8" t="n">
-        <v>53340</v>
+        <v>9048</v>
       </c>
       <c r="AA8" t="n">
-        <v>55510</v>
+        <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2170</v>
+        <v>-952</v>
       </c>
       <c r="AC8" t="n">
-        <v>-3.91</v>
+        <v>-9.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6976.T</t>
+          <t>285A.T</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>太陽誘電</t>
+          <t>キオクシアホールディングス</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>10000</v>
+        <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>9093</v>
+        <v>17780</v>
       </c>
       <c r="F9" t="n">
-        <v>52.3</v>
+        <v>24.3</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.92</v>
+        <v>-65.54000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>1.68</v>
       </c>
       <c r="I9" t="n">
-        <v>-318.19</v>
+        <v>-3100.57</v>
       </c>
       <c r="J9" t="n">
-        <v>-417.92</v>
+        <v>-1112.89</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-2S</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>12596.09</v>
+        <v>63881.73</v>
       </c>
       <c r="N9" t="n">
-        <v>8073.21</v>
+        <v>40724.89</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>🟡 反発中</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🔴 売り注意</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr"/>
+・🔴 下降
+・MACDは売りシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・売られ過ぎ水準です。
+・25日線から大きく下に乖離しています。
+・出来高が増加しています。
+・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD買い、反発局面</t>
+          <t>RSI売られすぎ、25日線大幅割れ、出来高微増、デッドクロス、-2σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>9160</v>
+        <v>55780</v>
       </c>
       <c r="X9" t="n">
-        <v>-67</v>
+        <v>-38000</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.73</v>
+        <v>-68.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>9093</v>
+        <v>17780</v>
       </c>
       <c r="AA9" t="n">
-        <v>10000</v>
+        <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-907</v>
+        <v>-37730</v>
       </c>
       <c r="AC9" t="n">
-        <v>-9.07</v>
+        <v>-67.97</v>
       </c>
     </row>
     <row r="10">
@@ -1483,22 +1490,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>43.26</v>
+        <v>41.78</v>
       </c>
       <c r="F10" t="n">
-        <v>58.7</v>
+        <v>53.5</v>
       </c>
       <c r="G10" t="n">
-        <v>11.89</v>
+        <v>7.56</v>
       </c>
       <c r="H10" t="n">
-        <v>1.21</v>
+        <v>0.79</v>
       </c>
       <c r="I10" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="J10" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1507,14 +1514,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+2S</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.1</v>
+        <v>33.27</v>
       </c>
       <c r="N10" t="n">
-        <v>31.79</v>
+        <v>31.83</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1527,7 +1534,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1545,8 +1552,7 @@
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・25日線から大きく上に乖離しています。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1554,29 +1560,29 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、上昇加速、+2σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>41.51</v>
+        <v>43.26</v>
       </c>
       <c r="X10" t="n">
-        <v>1.75</v>
+        <v>-1.48</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.22</v>
+        <v>-3.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6070</v>
+        <v>-6071</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.29000000000001</v>
+        <v>-99.31999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3340</v>
+        <v>3345</v>
       </c>
       <c r="F2" t="n">
-        <v>43.1</v>
+        <v>36.4</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.74</v>
+        <v>-2.51</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9</v>
+        <v>0.23</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="J2" t="n">
-        <v>28.44</v>
+        <v>23.36</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3079.39</v>
+        <v>3092</v>
       </c>
       <c r="N2" t="n">
-        <v>2734.1</v>
+        <v>2736.82</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -654,25 +654,25 @@
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3330</v>
+        <v>3340</v>
       </c>
       <c r="X2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>13360</v>
+        <v>13380</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2560</v>
+        <v>2580</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.7</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="3">
@@ -693,22 +693,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="F3" t="n">
-        <v>57.7</v>
+        <v>45.4</v>
       </c>
       <c r="G3" t="n">
-        <v>1.19</v>
+        <v>0.45</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.19</v>
       </c>
       <c r="I3" t="n">
-        <v>7.45</v>
+        <v>6.79</v>
       </c>
       <c r="J3" t="n">
-        <v>7.1</v>
+        <v>7.03</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>436.81</v>
+        <v>437.82</v>
       </c>
       <c r="N3" t="n">
-        <v>415.73</v>
+        <v>416.31</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -733,136 +733,23 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>477</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>47900</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>42000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5900</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>14.05</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>9432.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NTT</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>158</v>
-      </c>
-      <c r="E4" t="n">
-        <v>172</v>
-      </c>
-      <c r="F4" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>155.71</v>
-      </c>
-      <c r="N4" t="n">
-        <v>152.3</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>🟢 強い買い</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>95</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -873,6 +760,119 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>25日線上、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>479</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>47500</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5500</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>171</v>
+      </c>
+      <c r="F4" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>156.07</v>
+      </c>
+      <c r="N4" t="n">
+        <v>152.4</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>95</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
@@ -880,25 +880,25 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>173.38</v>
+        <v>172</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.38</v>
+        <v>-1</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.8</v>
+        <v>-0.58</v>
       </c>
       <c r="Z4" t="n">
-        <v>17200</v>
+        <v>17100</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.859999999999999</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2936.5</v>
+        <v>2901</v>
       </c>
       <c r="F5" t="n">
         <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.43</v>
+        <v>-3.47</v>
       </c>
       <c r="H5" t="n">
-        <v>0.88</v>
+        <v>0.44</v>
       </c>
       <c r="I5" t="n">
-        <v>-10.59</v>
+        <v>-14.86</v>
       </c>
       <c r="J5" t="n">
-        <v>0.45</v>
+        <v>-2.62</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2895.27</v>
+        <v>2896.85</v>
       </c>
       <c r="N5" t="n">
-        <v>3110.24</v>
+        <v>3109.82</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -992,25 +992,25 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>2939.45</v>
+        <v>2936.5</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.95</v>
+        <v>-35.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1</v>
+        <v>-1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>38174</v>
+        <v>37713</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>1076</v>
+        <v>614</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.9</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="6">
@@ -1031,22 +1031,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>7999</v>
+        <v>7896</v>
       </c>
       <c r="F6" t="n">
-        <v>29.9</v>
+        <v>28.7</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.52</v>
+        <v>-7.34</v>
       </c>
       <c r="H6" t="n">
-        <v>1.24</v>
+        <v>0.54</v>
       </c>
       <c r="I6" t="n">
-        <v>-60.5</v>
+        <v>-86.02</v>
       </c>
       <c r="J6" t="n">
-        <v>21.43</v>
+        <v>-0.06</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7792.25</v>
+        <v>7794.36</v>
       </c>
       <c r="N6" t="n">
-        <v>8604.889999999999</v>
+        <v>8580.299999999999</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>8100</v>
+        <v>7999</v>
       </c>
       <c r="X6" t="n">
-        <v>-101</v>
+        <v>-103</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.25</v>
+        <v>-1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>7999</v>
+        <v>7896</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>6</v>
+        <v>-97</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.08</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="7">
@@ -1144,38 +1144,38 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4756</v>
+        <v>4674</v>
       </c>
       <c r="F7" t="n">
-        <v>36.7</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.33</v>
+        <v>-3.06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.03</v>
+        <v>0.38</v>
       </c>
       <c r="I7" t="n">
-        <v>20.7</v>
+        <v>6.25</v>
       </c>
       <c r="J7" t="n">
-        <v>43.15</v>
+        <v>35.77</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4655.31</v>
+        <v>4654.39</v>
       </c>
       <c r="N7" t="n">
-        <v>4640.94</v>
+        <v>4646.39</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1184,20 +1184,20 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟠 利益確定検討</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1205,8 +1205,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1214,29 +1213,29 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
+          <t>押し目、-1σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4796.47</v>
+        <v>4756</v>
       </c>
       <c r="X7" t="n">
-        <v>-40.47</v>
+        <v>-82</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.84</v>
+        <v>-1.72</v>
       </c>
       <c r="Z7" t="n">
-        <v>23780</v>
+        <v>23370</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>-195</v>
+        <v>-605</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="8">
@@ -1257,22 +1256,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>9048</v>
+        <v>8968</v>
       </c>
       <c r="F8" t="n">
-        <v>52.3</v>
+        <v>45.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.92</v>
+        <v>-1.54</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9</v>
+        <v>0.54</v>
       </c>
       <c r="I8" t="n">
-        <v>-316.61</v>
+        <v>-304.93</v>
       </c>
       <c r="J8" t="n">
-        <v>-415.85</v>
+        <v>-393.66</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1285,10 +1284,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>12533.76</v>
+        <v>12414.85</v>
       </c>
       <c r="N8" t="n">
-        <v>8033.25</v>
+        <v>8061.58</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1297,20 +1296,20 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1327,29 +1326,29 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD買い、反発局面</t>
+          <t>押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>9114.67</v>
+        <v>9048</v>
       </c>
       <c r="X8" t="n">
-        <v>-66.67</v>
+        <v>-80</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.73</v>
+        <v>-0.88</v>
       </c>
       <c r="Z8" t="n">
-        <v>9048</v>
+        <v>8968</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-952</v>
+        <v>-1032</v>
       </c>
       <c r="AC8" t="n">
-        <v>-9.52</v>
+        <v>-10.32</v>
       </c>
     </row>
     <row r="9">
@@ -1370,106 +1369,99 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
+        <v>17655</v>
+      </c>
+      <c r="F9" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-98.15000000000001</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-165.11</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>21347.58</v>
+      </c>
+      <c r="N9" t="n">
+        <v>13707.7</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>65</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>押し目、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
         <v>17780</v>
       </c>
-      <c r="F9" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-65.54000000000001</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-3100.57</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-1112.89</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-2S</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>63881.73</v>
-      </c>
-      <c r="N9" t="n">
-        <v>40724.89</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>🔴 売り注意</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>10</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・売られ過ぎ水準です。
-・25日線から大きく下に乖離しています。
-・出来高が増加しています。
-・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>RSI売られすぎ、25日線大幅割れ、出来高微増、デッドクロス、-2σ、MACD売り、下降トレンド</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>55780</v>
-      </c>
       <c r="X9" t="n">
-        <v>-38000</v>
+        <v>-125</v>
       </c>
       <c r="Y9" t="n">
-        <v>-68.12</v>
+        <v>-0.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>17780</v>
+        <v>17655</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-37730</v>
+        <v>-37855</v>
       </c>
       <c r="AC9" t="n">
-        <v>-67.97</v>
+        <v>-68.19</v>
       </c>
     </row>
     <row r="10">
@@ -1499,7 +1491,7 @@
         <v>7.56</v>
       </c>
       <c r="H10" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="n">
         <v>1.74</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3345</v>
+        <v>3375</v>
       </c>
       <c r="F2" t="n">
-        <v>36.4</v>
+        <v>38.9</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.51</v>
+        <v>-1.67</v>
       </c>
       <c r="H2" t="n">
-        <v>0.23</v>
+        <v>0.73</v>
       </c>
       <c r="I2" t="n">
-        <v>3.05</v>
+        <v>5.44</v>
       </c>
       <c r="J2" t="n">
-        <v>23.36</v>
+        <v>23.84</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3092</v>
+        <v>3092.4</v>
       </c>
       <c r="N2" t="n">
-        <v>2736.82</v>
+        <v>2736.97</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -657,22 +657,22 @@
         <v>3340</v>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.15</v>
+        <v>1.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>13380</v>
+        <v>13500</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2580</v>
+        <v>2700</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.89</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -693,22 +693,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F3" t="n">
-        <v>45.4</v>
+        <v>46.2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="H3" t="n">
-        <v>0.19</v>
+        <v>0.8</v>
       </c>
       <c r="I3" t="n">
-        <v>6.79</v>
+        <v>6.94</v>
       </c>
       <c r="J3" t="n">
-        <v>7.03</v>
+        <v>7.07</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>437.82</v>
+        <v>437.85</v>
       </c>
       <c r="N3" t="n">
-        <v>416.31</v>
+        <v>416.32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -770,22 +770,22 @@
         <v>479</v>
       </c>
       <c r="X3" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.84</v>
+        <v>-0.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>47500</v>
+        <v>47700</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5500</v>
+        <v>5700</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.1</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="4">
@@ -806,19 +806,19 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>171</v>
+        <v>171.3</v>
       </c>
       <c r="F4" t="n">
-        <v>52.1</v>
+        <v>52.7</v>
       </c>
       <c r="G4" t="n">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="H4" t="n">
-        <v>0.46</v>
+        <v>0.97</v>
       </c>
       <c r="I4" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="J4" t="n">
         <v>3.98</v>
@@ -883,22 +883,22 @@
         <v>172</v>
       </c>
       <c r="X4" t="n">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.58</v>
+        <v>-0.41</v>
       </c>
       <c r="Z4" t="n">
-        <v>17100</v>
+        <v>17130</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1300</v>
+        <v>1330</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.23</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2901</v>
+        <v>2881.5</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>30.3</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.47</v>
+        <v>-4.09</v>
       </c>
       <c r="H5" t="n">
-        <v>0.44</v>
+        <v>1.06</v>
       </c>
       <c r="I5" t="n">
-        <v>-14.86</v>
+        <v>-16.42</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.62</v>
+        <v>-2.93</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,70 +947,70 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2896.85</v>
+        <v>2896.59</v>
       </c>
       <c r="N5" t="n">
-        <v>3109.82</v>
+        <v>3109.72</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>🟢 上昇</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🔴 売り注意</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟢 上昇
+・🔴 下降
 ・MACDは売りシグナルです。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+          <t>押し目、-1σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>2936.5</v>
       </c>
       <c r="X5" t="n">
-        <v>-35.5</v>
+        <v>-55</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.21</v>
+        <v>-1.87</v>
       </c>
       <c r="Z5" t="n">
-        <v>37713</v>
+        <v>37460</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>614</v>
+        <v>360</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.66</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="6">
@@ -1040,7 +1040,7 @@
         <v>-7.34</v>
       </c>
       <c r="H6" t="n">
-        <v>0.54</v>
+        <v>0.98</v>
       </c>
       <c r="I6" t="n">
         <v>-86.02</v>
@@ -1144,22 +1144,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4674</v>
+        <v>4637</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>38.3</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.06</v>
+        <v>-3.8</v>
       </c>
       <c r="H7" t="n">
-        <v>0.38</v>
+        <v>1.06</v>
       </c>
       <c r="I7" t="n">
-        <v>6.25</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>35.77</v>
+        <v>35.18</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1172,70 +1172,70 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4654.39</v>
+        <v>4653.9</v>
       </c>
       <c r="N7" t="n">
-        <v>4646.39</v>
+        <v>4646.2</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>🟢 強い上昇</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🔴 売り注意</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟢 強い上昇
+・🔴 下降
 ・MACDは売りシグナルです。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、長期上昇</t>
+          <t>押し目、-1σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>4756</v>
       </c>
       <c r="X7" t="n">
-        <v>-82</v>
+        <v>-119</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.72</v>
+        <v>-2.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>23370</v>
+        <v>23185</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>-605</v>
+        <v>-790</v>
       </c>
       <c r="AC7" t="n">
-        <v>-2.52</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="8">
@@ -1256,22 +1256,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>8968</v>
+        <v>9117</v>
       </c>
       <c r="F8" t="n">
-        <v>45.5</v>
+        <v>47.1</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.54</v>
+        <v>0.03</v>
       </c>
       <c r="H8" t="n">
-        <v>0.54</v>
+        <v>0.87</v>
       </c>
       <c r="I8" t="n">
-        <v>-304.93</v>
+        <v>-293.05</v>
       </c>
       <c r="J8" t="n">
-        <v>-393.66</v>
+        <v>-391.29</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>12414.85</v>
+        <v>12416.84</v>
       </c>
       <c r="N8" t="n">
-        <v>8061.58</v>
+        <v>8062.32</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1296,11 +1296,11 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1326,29 +1326,29 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、MACD買い、反発局面</t>
+          <t>25日線上、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>9048</v>
       </c>
       <c r="X8" t="n">
-        <v>-80</v>
+        <v>69</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.88</v>
+        <v>0.76</v>
       </c>
       <c r="Z8" t="n">
-        <v>8968</v>
+        <v>9117</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1032</v>
+        <v>-883</v>
       </c>
       <c r="AC8" t="n">
-        <v>-10.32</v>
+        <v>-8.83</v>
       </c>
     </row>
     <row r="9">
@@ -1369,22 +1369,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>17655</v>
+        <v>17880</v>
       </c>
       <c r="F9" t="n">
-        <v>47.3</v>
+        <v>48.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.09</v>
+        <v>1.13</v>
       </c>
       <c r="H9" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="I9" t="n">
-        <v>-98.15000000000001</v>
+        <v>-80.2</v>
       </c>
       <c r="J9" t="n">
-        <v>-165.11</v>
+        <v>-161.52</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>21347.58</v>
+        <v>21350.58</v>
       </c>
       <c r="N9" t="n">
-        <v>13707.7</v>
+        <v>13708.83</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1409,11 +1409,11 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1439,29 +1439,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>押し目、MACD買い、反発局面</t>
+          <t>25日線上、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>17780</v>
       </c>
       <c r="X9" t="n">
-        <v>-125</v>
+        <v>100</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>17655</v>
+        <v>17880</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-37855</v>
+        <v>-37630</v>
       </c>
       <c r="AC9" t="n">
-        <v>-68.19</v>
+        <v>-67.79000000000001</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1482,22 +1482,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>41.78</v>
+        <v>41.02</v>
       </c>
       <c r="F10" t="n">
-        <v>53.5</v>
+        <v>54.9</v>
       </c>
       <c r="G10" t="n">
-        <v>7.56</v>
+        <v>4.97</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="J10" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1506,14 +1506,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.27</v>
+        <v>33.39</v>
       </c>
       <c r="N10" t="n">
-        <v>31.83</v>
+        <v>31.86</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1552,29 +1552,29 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>43.26</v>
+        <v>41.78</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.48</v>
+        <v>-0.76</v>
       </c>
       <c r="Y10" t="n">
-        <v>-3.42</v>
+        <v>-1.82</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6071</v>
+        <v>-6072</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.31999999999999</v>
+        <v>-99.33</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3375</v>
+        <v>3350</v>
       </c>
       <c r="F2" t="n">
-        <v>38.9</v>
+        <v>40.6</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.67</v>
+        <v>-2.35</v>
       </c>
       <c r="H2" t="n">
-        <v>0.73</v>
+        <v>1.06</v>
       </c>
       <c r="I2" t="n">
-        <v>5.44</v>
+        <v>3.73</v>
       </c>
       <c r="J2" t="n">
-        <v>23.84</v>
+        <v>19.82</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3092.4</v>
+        <v>3105.71</v>
       </c>
       <c r="N2" t="n">
-        <v>2736.97</v>
+        <v>2739.78</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -654,25 +654,25 @@
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3340</v>
+        <v>3375</v>
       </c>
       <c r="X2" t="n">
-        <v>35</v>
+        <v>-25</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.05</v>
+        <v>-0.74</v>
       </c>
       <c r="Z2" t="n">
-        <v>13500</v>
+        <v>13400</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="AC2" t="n">
-        <v>25</v>
+        <v>24.07</v>
       </c>
     </row>
     <row r="3">
@@ -693,22 +693,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="F3" t="n">
-        <v>46.2</v>
+        <v>48.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.85</v>
+        <v>-2.83</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8</v>
+        <v>0.43</v>
       </c>
       <c r="I3" t="n">
-        <v>6.94</v>
+        <v>5.04</v>
       </c>
       <c r="J3" t="n">
-        <v>7.07</v>
+        <v>6.66</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>437.85</v>
+        <v>438.57</v>
       </c>
       <c r="N3" t="n">
-        <v>416.32</v>
+        <v>416.83</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -733,11 +733,11 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -763,29 +763,29 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25日線上、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="X3" t="n">
-        <v>-2</v>
+        <v>-18</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.42</v>
+        <v>-3.77</v>
       </c>
       <c r="Z3" t="n">
-        <v>47700</v>
+        <v>45900</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5700</v>
+        <v>3900</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.57</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -806,22 +806,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>171.3</v>
+        <v>170.6</v>
       </c>
       <c r="F4" t="n">
-        <v>52.7</v>
+        <v>59.9</v>
       </c>
       <c r="G4" t="n">
-        <v>0.42</v>
+        <v>-0.16</v>
       </c>
       <c r="H4" t="n">
-        <v>0.97</v>
+        <v>0.41</v>
       </c>
       <c r="I4" t="n">
-        <v>3.18</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.98</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>156.07</v>
+        <v>156.39</v>
       </c>
       <c r="N4" t="n">
-        <v>152.4</v>
+        <v>152.5</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -876,11 +876,11 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>RSI適正、押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>172</v>
+        <v>171.3</v>
       </c>
       <c r="X4" t="n">
         <v>-0.7</v>
@@ -889,16 +889,16 @@
         <v>-0.41</v>
       </c>
       <c r="Z4" t="n">
-        <v>17130</v>
+        <v>17060</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1330</v>
+        <v>1260</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.42</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2881.5</v>
+        <v>2898</v>
       </c>
       <c r="F5" t="n">
-        <v>30.3</v>
+        <v>30.7</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.09</v>
+        <v>-3.31</v>
       </c>
       <c r="H5" t="n">
-        <v>1.06</v>
+        <v>0.37</v>
       </c>
       <c r="I5" t="n">
-        <v>-16.42</v>
+        <v>-19.48</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.93</v>
+        <v>-6.24</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2896.59</v>
+        <v>2898.34</v>
       </c>
       <c r="N5" t="n">
-        <v>3109.72</v>
+        <v>3109.46</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -992,25 +992,25 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>2936.5</v>
+        <v>2881.5</v>
       </c>
       <c r="X5" t="n">
-        <v>-55</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.87</v>
+        <v>0.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>37460</v>
+        <v>37674</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>360</v>
+        <v>575</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.97</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="6">
@@ -1031,22 +1031,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>7896</v>
+        <v>7882</v>
       </c>
       <c r="F6" t="n">
-        <v>28.7</v>
+        <v>29.7</v>
       </c>
       <c r="G6" t="n">
-        <v>-7.34</v>
+        <v>-7.19</v>
       </c>
       <c r="H6" t="n">
-        <v>0.98</v>
+        <v>0.42</v>
       </c>
       <c r="I6" t="n">
-        <v>-86.02</v>
+        <v>-106.16</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.06</v>
+        <v>-21.28</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7794.36</v>
+        <v>7803.25</v>
       </c>
       <c r="N6" t="n">
-        <v>8580.299999999999</v>
+        <v>8556.620000000001</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>7999</v>
+        <v>7896</v>
       </c>
       <c r="X6" t="n">
-        <v>-103</v>
+        <v>-14</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.29</v>
+        <v>-0.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>7896</v>
+        <v>7882</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>-97</v>
+        <v>-111</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.21</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="7">
@@ -1144,22 +1144,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4637</v>
+        <v>4726</v>
       </c>
       <c r="F7" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.8</v>
+        <v>-1.95</v>
       </c>
       <c r="H7" t="n">
-        <v>1.06</v>
+        <v>0.33</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>-3.27</v>
       </c>
       <c r="J7" t="n">
-        <v>35.18</v>
+        <v>27.49</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1168,74 +1168,74 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4653.9</v>
+        <v>4656.17</v>
       </c>
       <c r="N7" t="n">
-        <v>4646.2</v>
+        <v>4651.85</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>🔴 下降</t>
+          <t>🟢 強い上昇</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 売り注意</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🔴 下降
+・🟢 強い上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、下降トレンド</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4756</v>
+        <v>4637</v>
       </c>
       <c r="X7" t="n">
-        <v>-119</v>
+        <v>89</v>
       </c>
       <c r="Y7" t="n">
-        <v>-2.5</v>
+        <v>1.92</v>
       </c>
       <c r="Z7" t="n">
-        <v>23185</v>
+        <v>23630</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>-790</v>
+        <v>-345</v>
       </c>
       <c r="AC7" t="n">
-        <v>-3.3</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="8">
@@ -1256,38 +1256,38 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>9117</v>
+        <v>9450</v>
       </c>
       <c r="F8" t="n">
-        <v>47.1</v>
+        <v>46.4</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03</v>
+        <v>3.6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="I8" t="n">
-        <v>-293.05</v>
+        <v>-244.68</v>
       </c>
       <c r="J8" t="n">
-        <v>-391.29</v>
+        <v>-361.97</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>12416.84</v>
+        <v>12335.14</v>
       </c>
       <c r="N8" t="n">
-        <v>8062.32</v>
+        <v>8092.48</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1296,20 +1296,20 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1317,125 +1317,125 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>25日線上、ゴールデンクロス、+1σ、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>9117</v>
+      </c>
+      <c r="X8" t="n">
+        <v>333</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9450</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-550</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-5.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>55510</v>
+      </c>
+      <c r="E9" t="n">
+        <v>18265</v>
+      </c>
+      <c r="F9" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-42.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-137.72</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>21280.78</v>
+      </c>
+      <c r="N9" t="n">
+        <v>13784.79</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>75</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>25日線上、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>9048</v>
-      </c>
-      <c r="X8" t="n">
-        <v>69</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9117</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-883</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-8.83</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>55510</v>
-      </c>
-      <c r="E9" t="n">
-        <v>17880</v>
-      </c>
-      <c r="F9" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-80.2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-161.52</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>21350.58</v>
-      </c>
-      <c r="N9" t="n">
-        <v>13708.83</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>75</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
@@ -1443,25 +1443,25 @@
         </is>
       </c>
       <c r="W9" t="n">
-        <v>17780</v>
+        <v>17880</v>
       </c>
       <c r="X9" t="n">
-        <v>100</v>
+        <v>385</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>17880</v>
+        <v>18265</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-37630</v>
+        <v>-37245</v>
       </c>
       <c r="AC9" t="n">
-        <v>-67.79000000000001</v>
+        <v>-67.09999999999999</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3350</v>
+        <v>3375</v>
       </c>
       <c r="F2" t="n">
-        <v>40.6</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.35</v>
+        <v>-1.65</v>
       </c>
       <c r="H2" t="n">
-        <v>1.06</v>
+        <v>1.66</v>
       </c>
       <c r="I2" t="n">
-        <v>3.73</v>
+        <v>5.72</v>
       </c>
       <c r="J2" t="n">
-        <v>19.82</v>
+        <v>20.22</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3105.71</v>
+        <v>3106.04</v>
       </c>
       <c r="N2" t="n">
-        <v>2739.78</v>
+        <v>2739.91</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -642,6 +642,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -650,29 +651,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>押し目、出来高微増、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>3375</v>
       </c>
       <c r="X2" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.74</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>13400</v>
+        <v>13500</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.07</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -693,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="F3" t="n">
-        <v>48.5</v>
+        <v>54.4</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.83</v>
+        <v>-0.59</v>
       </c>
       <c r="H3" t="n">
-        <v>0.43</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="n">
-        <v>5.04</v>
+        <v>5.91</v>
       </c>
       <c r="J3" t="n">
-        <v>6.66</v>
+        <v>6.83</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -721,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>438.57</v>
+        <v>438.71</v>
       </c>
       <c r="N3" t="n">
-        <v>416.83</v>
+        <v>416.88</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -733,20 +734,20 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -763,29 +764,29 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>RSI適正、押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>477</v>
       </c>
       <c r="X3" t="n">
-        <v>-18</v>
+        <v>-7</v>
       </c>
       <c r="Y3" t="n">
-        <v>-3.77</v>
+        <v>-1.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>45900</v>
+        <v>47000</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>3900</v>
+        <v>5000</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.289999999999999</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="4">
@@ -806,22 +807,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>170.6</v>
+        <v>171.6</v>
       </c>
       <c r="F4" t="n">
-        <v>59.9</v>
+        <v>62.3</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.16</v>
+        <v>0.4</v>
       </c>
       <c r="H4" t="n">
-        <v>0.41</v>
+        <v>0.93</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -834,10 +835,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>156.39</v>
+        <v>156.4</v>
       </c>
       <c r="N4" t="n">
-        <v>152.5</v>
+        <v>152.51</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -846,361 +847,23 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>RSI適正、押し目、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>171.3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>17060</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>15800</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1260</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.97</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>トヨタ自動車</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>13</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2853.77</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2898</v>
-      </c>
-      <c r="F5" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-3.31</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-19.48</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-6.24</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>2898.34</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3109.46</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>🔴 売り注意</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>15</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>押し目、-1σ、MACD売り、下降トレンド</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>2881.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>37674</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>575</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7882</v>
-      </c>
-      <c r="F6" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-7.19</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-106.16</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-21.28</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>7803.25</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8556.620000000001</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>75</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>RSI売られすぎ、押し目、-1σ、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>7896</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-14</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>7882</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>7993</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-111</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>8058.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>三菱商事</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4795</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4726</v>
-      </c>
-      <c r="F7" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-1.95</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-3.27</v>
-      </c>
-      <c r="J7" t="n">
-        <v>27.49</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>4656.17</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4651.85</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>65</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -1210,32 +873,368 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>171.3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>17160</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>15800</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1360</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.609999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>トヨタ自動車</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2853.77</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2920</v>
+      </c>
+      <c r="F5" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-17.73</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-5.89</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>2898.63</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3109.57</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>60</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>2881.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>37960</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>37099</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>861</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>三菱商事</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4795</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F6" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28.17</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>4656.74</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4652.07</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>押し目、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>4637</v>
+      </c>
+      <c r="X6" t="n">
+        <v>132</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>23845</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>23975</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-130</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7944</v>
+      </c>
+      <c r="F7" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-6.49</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-101.21</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-20.29</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>7804.08</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8556.93</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>60</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4637</v>
+        <v>7896</v>
       </c>
       <c r="X7" t="n">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.92</v>
+        <v>0.61</v>
       </c>
       <c r="Z7" t="n">
-        <v>23630</v>
+        <v>7944</v>
       </c>
       <c r="AA7" t="n">
-        <v>23975</v>
+        <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>-345</v>
+        <v>-49</v>
       </c>
       <c r="AC7" t="n">
-        <v>-1.44</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="8">
@@ -1256,38 +1255,38 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>9450</v>
+        <v>9324</v>
       </c>
       <c r="F8" t="n">
-        <v>46.4</v>
+        <v>44.8</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6</v>
+        <v>2.27</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9</v>
+        <v>1.32</v>
       </c>
       <c r="I8" t="n">
-        <v>-244.68</v>
+        <v>-254.73</v>
       </c>
       <c r="J8" t="n">
-        <v>-361.97</v>
+        <v>-363.98</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>12335.14</v>
+        <v>12333.46</v>
       </c>
       <c r="N8" t="n">
-        <v>8092.48</v>
+        <v>8091.85</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1296,137 +1295,23 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>25日線上、ゴールデンクロス、+1σ、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>9117</v>
-      </c>
-      <c r="X8" t="n">
-        <v>333</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9450</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-550</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>55510</v>
-      </c>
-      <c r="E9" t="n">
-        <v>18265</v>
-      </c>
-      <c r="F9" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-42.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-137.72</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>21280.78</v>
-      </c>
-      <c r="N9" t="n">
-        <v>13784.79</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>75</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -1436,6 +1321,118 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>25日線上、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>9117</v>
+      </c>
+      <c r="X8" t="n">
+        <v>207</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9324</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-676</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-6.76</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>55510</v>
+      </c>
+      <c r="E9" t="n">
+        <v>18095</v>
+      </c>
+      <c r="F9" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-56.06</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-140.43</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>21278.51</v>
+      </c>
+      <c r="N9" t="n">
+        <v>13783.94</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>75</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
@@ -1446,22 +1443,22 @@
         <v>17880</v>
       </c>
       <c r="X9" t="n">
-        <v>385</v>
+        <v>215</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>18265</v>
+        <v>18095</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-37245</v>
+        <v>-37415</v>
       </c>
       <c r="AC9" t="n">
-        <v>-67.09999999999999</v>
+        <v>-67.40000000000001</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1479,19 +1479,19 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>41.02</v>
+        <v>41.07</v>
       </c>
       <c r="F10" t="n">
-        <v>54.9</v>
+        <v>59.3</v>
       </c>
       <c r="G10" t="n">
-        <v>4.97</v>
+        <v>4.82</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="I10" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="J10" t="n">
         <v>1.56</v>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.39</v>
+        <v>33.53</v>
       </c>
       <c r="N10" t="n">
-        <v>31.86</v>
+        <v>31.89</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは買いシグナルです。
+・MACDは売りシグナルです。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
@@ -1549,17 +1549,17 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>41.78</v>
+        <v>41.02</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.76</v>
+        <v>0.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.82</v>
+        <v>0.12</v>
       </c>
       <c r="Z10" t="n">
         <v>41</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3360</v>
+        <v>3435</v>
       </c>
       <c r="F2" t="n">
-        <v>45.3</v>
+        <v>51.1</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.09</v>
+        <v>0.01</v>
       </c>
       <c r="H2" t="n">
-        <v>0.22</v>
+        <v>0.52</v>
       </c>
       <c r="I2" t="n">
-        <v>4.69</v>
+        <v>10.67</v>
       </c>
       <c r="J2" t="n">
-        <v>17.11</v>
+        <v>18.31</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3120.6</v>
+        <v>3121.6</v>
       </c>
       <c r="N2" t="n">
-        <v>2742.75</v>
+        <v>2743.12</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,20 +621,20 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -651,29 +651,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>3375</v>
       </c>
       <c r="X2" t="n">
-        <v>-15</v>
+        <v>60</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.44</v>
+        <v>1.78</v>
       </c>
       <c r="Z2" t="n">
-        <v>13440</v>
+        <v>13740</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2640</v>
+        <v>2940</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.44</v>
+        <v>27.22</v>
       </c>
     </row>
     <row r="3">
@@ -694,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F3" t="n">
-        <v>53.3</v>
+        <v>54.9</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.07</v>
+        <v>-0.46</v>
       </c>
       <c r="H3" t="n">
-        <v>0.26</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>4.88</v>
+        <v>5.12</v>
       </c>
       <c r="J3" t="n">
-        <v>6.44</v>
+        <v>6.49</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>439.66</v>
+        <v>439.7</v>
       </c>
       <c r="N3" t="n">
-        <v>417.46</v>
+        <v>417.47</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -771,22 +771,22 @@
         <v>470</v>
       </c>
       <c r="X3" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.43</v>
+        <v>0.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>46800</v>
+        <v>47100</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.43</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="4">
@@ -807,22 +807,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>170.7</v>
+        <v>170.3</v>
       </c>
       <c r="F4" t="n">
-        <v>53.4</v>
+        <v>52.4</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.28</v>
+        <v>-0.51</v>
       </c>
       <c r="H4" t="n">
-        <v>0.51</v>
+        <v>1.15</v>
       </c>
       <c r="I4" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -884,22 +884,22 @@
         <v>171.6</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.9</v>
+        <v>-1.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.52</v>
+        <v>-0.76</v>
       </c>
       <c r="Z4" t="n">
-        <v>17070</v>
+        <v>17030</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1270</v>
+        <v>1230</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.039999999999999</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="5">
@@ -920,22 +920,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2910.5</v>
+        <v>2925</v>
       </c>
       <c r="F5" t="n">
-        <v>48.5</v>
+        <v>51.1</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.71</v>
+        <v>-2.24</v>
       </c>
       <c r="H5" t="n">
-        <v>0.39</v>
+        <v>0.98</v>
       </c>
       <c r="I5" t="n">
-        <v>-19.31</v>
+        <v>-18.15</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.57</v>
+        <v>-8.34</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -944,14 +944,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2901.42</v>
+        <v>2901.61</v>
       </c>
       <c r="N5" t="n">
-        <v>3109.56</v>
+        <v>3109.64</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -960,20 +960,20 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -982,7 +982,7 @@
 ・🟢 上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -990,29 +990,29 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+          <t>RSI適正、押し目、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>2920</v>
       </c>
       <c r="X5" t="n">
-        <v>-9.5</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.33</v>
+        <v>0.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>37836</v>
+        <v>38025</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>738</v>
+        <v>926</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6">
@@ -1033,22 +1033,22 @@
         <v>10000</v>
       </c>
       <c r="E6" t="n">
-        <v>10185</v>
+        <v>10100</v>
       </c>
       <c r="F6" t="n">
-        <v>63.3</v>
+        <v>62.6</v>
       </c>
       <c r="G6" t="n">
-        <v>11.19</v>
+        <v>10.3</v>
       </c>
       <c r="H6" t="n">
-        <v>0.87</v>
+        <v>1.14</v>
       </c>
       <c r="I6" t="n">
-        <v>-153.12</v>
+        <v>-159.9</v>
       </c>
       <c r="J6" t="n">
-        <v>-321.81</v>
+        <v>-323.16</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>12248.62</v>
+        <v>12247.49</v>
       </c>
       <c r="N6" t="n">
-        <v>8124.57</v>
+        <v>8124.15</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1115,22 +1115,22 @@
         <v>9324</v>
       </c>
       <c r="X6" t="n">
-        <v>861</v>
+        <v>776</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.23</v>
+        <v>8.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>10185</v>
+        <v>10100</v>
       </c>
       <c r="AA6" t="n">
         <v>10000</v>
       </c>
       <c r="AB6" t="n">
-        <v>185</v>
+        <v>100</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1151,22 +1151,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>7920</v>
+        <v>7940</v>
       </c>
       <c r="F7" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.39</v>
+        <v>-6.16</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="I7" t="n">
-        <v>-113.87</v>
+        <v>-112.27</v>
       </c>
       <c r="J7" t="n">
-        <v>-39</v>
+        <v>-38.68</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7814.43</v>
+        <v>7814.69</v>
       </c>
       <c r="N7" t="n">
-        <v>8534.469999999999</v>
+        <v>8534.57</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1227,22 +1227,22 @@
         <v>7944</v>
       </c>
       <c r="X7" t="n">
-        <v>-24</v>
+        <v>-4</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.3</v>
+        <v>-0.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>7920</v>
+        <v>7940</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>-73</v>
+        <v>-53</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.91</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="8">
@@ -1263,22 +1263,22 @@
         <v>4795</v>
       </c>
       <c r="E8" t="n">
-        <v>4701</v>
+        <v>4722</v>
       </c>
       <c r="F8" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.48</v>
+        <v>-2.06</v>
       </c>
       <c r="H8" t="n">
-        <v>0.36</v>
+        <v>0.91</v>
       </c>
       <c r="I8" t="n">
-        <v>-7.73</v>
+        <v>-6.06</v>
       </c>
       <c r="J8" t="n">
-        <v>20.99</v>
+        <v>21.33</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1287,14 +1287,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4658.81</v>
+        <v>4659.09</v>
       </c>
       <c r="N8" t="n">
-        <v>4657.63</v>
+        <v>4657.74</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1332,29 +1332,29 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>4769</v>
       </c>
       <c r="X8" t="n">
-        <v>-68</v>
+        <v>-47</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.43</v>
+        <v>-0.99</v>
       </c>
       <c r="Z8" t="n">
-        <v>23505</v>
+        <v>23610</v>
       </c>
       <c r="AA8" t="n">
         <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-470</v>
+        <v>-365</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.96</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="9">
@@ -1375,22 +1375,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>18855</v>
+        <v>19100</v>
       </c>
       <c r="F9" t="n">
-        <v>48.2</v>
+        <v>49.8</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2</v>
+        <v>7.52</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6</v>
+        <v>1.03</v>
       </c>
       <c r="I9" t="n">
-        <v>24.12</v>
+        <v>43.66</v>
       </c>
       <c r="J9" t="n">
-        <v>-107.52</v>
+        <v>-103.61</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>21194.62</v>
+        <v>21197.89</v>
       </c>
       <c r="N9" t="n">
-        <v>13863.2</v>
+        <v>13864.42</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1442,7 +1442,11 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>25日線上、+1σ、MACD買い、反発局面</t>
@@ -1452,22 +1456,22 @@
         <v>18095</v>
       </c>
       <c r="X9" t="n">
-        <v>760</v>
+        <v>1005</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.2</v>
+        <v>5.55</v>
       </c>
       <c r="Z9" t="n">
-        <v>18855</v>
+        <v>19100</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-36655</v>
+        <v>-36410</v>
       </c>
       <c r="AC9" t="n">
-        <v>-66.03</v>
+        <v>-65.59</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1492,19 +1492,19 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>41.07</v>
+        <v>41.92</v>
       </c>
       <c r="F10" t="n">
-        <v>59.3</v>
+        <v>55.1</v>
       </c>
       <c r="G10" t="n">
-        <v>4.82</v>
+        <v>6.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="J10" t="n">
         <v>1.56</v>
@@ -1516,14 +1516,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.53</v>
+        <v>33.68</v>
       </c>
       <c r="N10" t="n">
-        <v>31.89</v>
+        <v>31.94</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1562,29 +1562,29 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、長期上昇</t>
+          <t>RSI適正、25日線上、+1σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>41.02</v>
+        <v>41.07</v>
       </c>
       <c r="X10" t="n">
-        <v>0.05</v>
+        <v>0.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.12</v>
+        <v>2.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6072</v>
+        <v>-6071</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.33</v>
+        <v>-99.31</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3435</v>
+        <v>3360</v>
       </c>
       <c r="F2" t="n">
-        <v>51.1</v>
+        <v>52.6</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01</v>
+        <v>-2.11</v>
       </c>
       <c r="H2" t="n">
-        <v>0.52</v>
+        <v>0.36</v>
       </c>
       <c r="I2" t="n">
-        <v>10.67</v>
+        <v>8.44</v>
       </c>
       <c r="J2" t="n">
-        <v>18.31</v>
+        <v>16.33</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3121.6</v>
+        <v>3134.41</v>
       </c>
       <c r="N2" t="n">
-        <v>2743.12</v>
+        <v>2745.87</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,20 +621,20 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -651,29 +651,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>RSI適正、押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3375</v>
+        <v>3435</v>
       </c>
       <c r="X2" t="n">
-        <v>60</v>
+        <v>-75</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.78</v>
+        <v>-2.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>13740</v>
+        <v>13440</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2940</v>
+        <v>2640</v>
       </c>
       <c r="AC2" t="n">
-        <v>27.22</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="3">
@@ -694,26 +694,26 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="F3" t="n">
-        <v>54.9</v>
+        <v>63.3</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.46</v>
+        <v>-1.55</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="I3" t="n">
-        <v>5.12</v>
+        <v>4.04</v>
       </c>
       <c r="J3" t="n">
-        <v>6.49</v>
+        <v>6</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>439.7</v>
+        <v>440.69</v>
       </c>
       <c r="N3" t="n">
-        <v>417.47</v>
+        <v>418.01</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -734,20 +734,20 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -755,151 +755,152 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>RSI適正、押し目、デッドクロス、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>471</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>46600</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>4600</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10.95</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>169.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>157.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>152.7</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟠 利益確定検討</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>50</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>RSI適正、押し目、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>470</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>47100</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>42000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5100</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>12.14</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>9432.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NTT</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>158</v>
-      </c>
-      <c r="E4" t="n">
-        <v>170.3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>156.7</v>
-      </c>
-      <c r="N4" t="n">
-        <v>152.61</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>85</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、長期上昇</t>
+          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>171.6</v>
+        <v>170.3</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.76</v>
+        <v>-0.59</v>
       </c>
       <c r="Z4" t="n">
-        <v>17030</v>
+        <v>16930</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1230</v>
+        <v>1130</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.78</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="5">
@@ -920,22 +921,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>2925</v>
+        <v>2855</v>
       </c>
       <c r="F5" t="n">
-        <v>51.1</v>
+        <v>40.5</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.24</v>
+        <v>-4.36</v>
       </c>
       <c r="H5" t="n">
-        <v>0.98</v>
+        <v>0.54</v>
       </c>
       <c r="I5" t="n">
-        <v>-18.15</v>
+        <v>-23.86</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.34</v>
+        <v>-11.44</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -944,75 +945,74 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2901.61</v>
+        <v>2903.29</v>
       </c>
       <c r="N5" t="n">
-        <v>3109.64</v>
+        <v>3108.88</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>🟢 上昇</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🔴 売り注意</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟢 上昇
+・🔴 下降
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、上昇トレンド</t>
+          <t>押し目、-1σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>2920</v>
+        <v>2925</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>-70</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.17</v>
+        <v>-2.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>38025</v>
+        <v>37115</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>926</v>
+        <v>16</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.5</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="6">
@@ -1033,26 +1033,26 @@
         <v>10000</v>
       </c>
       <c r="E6" t="n">
-        <v>10100</v>
+        <v>9871</v>
       </c>
       <c r="F6" t="n">
-        <v>62.6</v>
+        <v>60.5</v>
       </c>
       <c r="G6" t="n">
-        <v>10.3</v>
+        <v>7.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.14</v>
+        <v>0.73</v>
       </c>
       <c r="I6" t="n">
-        <v>-159.9</v>
+        <v>-102.06</v>
       </c>
       <c r="J6" t="n">
-        <v>-323.16</v>
+        <v>-278.94</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>12247.49</v>
+        <v>12170.47</v>
       </c>
       <c r="N6" t="n">
-        <v>8124.15</v>
+        <v>8154.44</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1073,20 +1073,20 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1094,43 +1094,37 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・25日線から大きく上に乖離しています。
 ・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSI適正、上昇加速、ゴールデンクロス、+2σ、MACD買い、反発局面</t>
+          <t>RSI適正、25日線上、+2σ、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>9324</v>
+        <v>10100</v>
       </c>
       <c r="X6" t="n">
-        <v>776</v>
+        <v>-229</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.32</v>
+        <v>-2.27</v>
       </c>
       <c r="Z6" t="n">
-        <v>10100</v>
+        <v>9871</v>
       </c>
       <c r="AA6" t="n">
         <v>10000</v>
       </c>
       <c r="AB6" t="n">
-        <v>100</v>
+        <v>-129</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="7">
@@ -1151,22 +1145,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>7940</v>
+        <v>7832</v>
       </c>
       <c r="F7" t="n">
-        <v>31.4</v>
+        <v>35.3</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.16</v>
+        <v>-6.98</v>
       </c>
       <c r="H7" t="n">
-        <v>0.92</v>
+        <v>0.45</v>
       </c>
       <c r="I7" t="n">
-        <v>-112.27</v>
+        <v>-128.28</v>
       </c>
       <c r="J7" t="n">
-        <v>-38.68</v>
+        <v>-56.6</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1179,10 +1173,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7814.69</v>
+        <v>7823.47</v>
       </c>
       <c r="N7" t="n">
-        <v>8534.57</v>
+        <v>8510.59</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1224,25 +1218,25 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>7944</v>
+        <v>7940</v>
       </c>
       <c r="X7" t="n">
-        <v>-4</v>
+        <v>-108</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.05</v>
+        <v>-1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>7940</v>
+        <v>7832</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>-53</v>
+        <v>-161</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.66</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="8">
@@ -1263,22 +1257,22 @@
         <v>4795</v>
       </c>
       <c r="E8" t="n">
-        <v>4722</v>
+        <v>4683</v>
       </c>
       <c r="F8" t="n">
-        <v>42.1</v>
+        <v>32.3</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.06</v>
+        <v>-2.85</v>
       </c>
       <c r="H8" t="n">
-        <v>0.91</v>
+        <v>0.37</v>
       </c>
       <c r="I8" t="n">
-        <v>-6.06</v>
+        <v>-13.97</v>
       </c>
       <c r="J8" t="n">
-        <v>21.33</v>
+        <v>14.27</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1287,18 +1281,18 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4659.09</v>
+        <v>4659.9</v>
       </c>
       <c r="N8" t="n">
-        <v>4657.74</v>
+        <v>4662.39</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>🟢 強い上昇</t>
+          <t>🟢 上昇</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1307,54 +1301,54 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟢 強い上昇
+・🟢 上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>4769</v>
+        <v>4722</v>
       </c>
       <c r="X8" t="n">
-        <v>-47</v>
+        <v>-39</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.99</v>
+        <v>-0.83</v>
       </c>
       <c r="Z8" t="n">
-        <v>23610</v>
+        <v>23415</v>
       </c>
       <c r="AA8" t="n">
         <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-365</v>
+        <v>-560</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.52</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="9">
@@ -1375,22 +1369,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>19100</v>
+        <v>19170</v>
       </c>
       <c r="F9" t="n">
-        <v>49.8</v>
+        <v>51.1</v>
       </c>
       <c r="G9" t="n">
-        <v>7.52</v>
+        <v>7.41</v>
       </c>
       <c r="H9" t="n">
-        <v>1.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>43.66</v>
+        <v>126.88</v>
       </c>
       <c r="J9" t="n">
-        <v>-103.61</v>
+        <v>-57.51</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1403,10 +1397,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>21197.89</v>
+        <v>21092.6</v>
       </c>
       <c r="N9" t="n">
-        <v>13864.42</v>
+        <v>13945.16</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1415,20 +1409,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1442,36 +1436,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25日線上、+1σ、MACD買い、反発局面</t>
+          <t>RSI適正、25日線上、+1σ、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>18095</v>
+        <v>19100</v>
       </c>
       <c r="X9" t="n">
-        <v>1005</v>
+        <v>70</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.55</v>
+        <v>0.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>19100</v>
+        <v>19170</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-36410</v>
+        <v>-36340</v>
       </c>
       <c r="AC9" t="n">
-        <v>-65.59</v>
+        <v>-65.47</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3360</v>
+        <v>3370</v>
       </c>
       <c r="F2" t="n">
-        <v>52.6</v>
+        <v>53.4</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.11</v>
+        <v>-1.83</v>
       </c>
       <c r="H2" t="n">
-        <v>0.36</v>
+        <v>0.64</v>
       </c>
       <c r="I2" t="n">
-        <v>8.44</v>
+        <v>9.24</v>
       </c>
       <c r="J2" t="n">
-        <v>16.33</v>
+        <v>16.49</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3134.41</v>
+        <v>3134.55</v>
       </c>
       <c r="N2" t="n">
-        <v>2745.87</v>
+        <v>2745.92</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -658,22 +658,22 @@
         <v>3435</v>
       </c>
       <c r="X2" t="n">
-        <v>-75</v>
+        <v>-65</v>
       </c>
       <c r="Y2" t="n">
-        <v>-2.18</v>
+        <v>-1.89</v>
       </c>
       <c r="Z2" t="n">
-        <v>13440</v>
+        <v>13480</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2640</v>
+        <v>2680</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.44</v>
+        <v>24.81</v>
       </c>
     </row>
     <row r="3">
@@ -694,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F3" t="n">
-        <v>63.3</v>
+        <v>61.7</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.55</v>
+        <v>-1.96</v>
       </c>
       <c r="H3" t="n">
-        <v>0.45</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.04</v>
+        <v>3.88</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>5.97</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>440.69</v>
+        <v>440.67</v>
       </c>
       <c r="N3" t="n">
-        <v>418.01</v>
+        <v>418</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -771,22 +771,22 @@
         <v>471</v>
       </c>
       <c r="X3" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.06</v>
+        <v>-1.49</v>
       </c>
       <c r="Z3" t="n">
-        <v>46600</v>
+        <v>46400</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>4600</v>
+        <v>4400</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.95</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="4">
@@ -807,22 +807,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>169.3</v>
+        <v>169.9</v>
       </c>
       <c r="F4" t="n">
-        <v>49.4</v>
+        <v>50.9</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.15</v>
+        <v>-0.82</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="J4" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>157.01</v>
+        <v>157.02</v>
       </c>
       <c r="N4" t="n">
         <v>152.7</v>
@@ -847,20 +847,20 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 利益確定検討</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -878,106 +878,218 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
+          <t>RSI適正、押し目、デッドクロス、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>170.3</v>
       </c>
       <c r="X4" t="n">
-        <v>-1</v>
+        <v>-0.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.59</v>
+        <v>-0.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>16930</v>
+        <v>16990</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1130</v>
+        <v>1190</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.15</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10095</v>
+      </c>
+      <c r="F5" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-84.19</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-275.37</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>+2S</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>12173.46</v>
+      </c>
+      <c r="N5" t="n">
+        <v>8155.56</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>85</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、+2σ、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>10100</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>10095</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>7203.T</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>トヨタ自動車</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C6" t="n">
         <v>13</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>2853.77</v>
       </c>
-      <c r="E5" t="n">
-        <v>2855</v>
-      </c>
-      <c r="F5" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-4.36</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-23.86</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-11.44</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="E6" t="n">
+        <v>2856.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-4.31</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-23.74</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-11.42</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>-1S</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>2903.29</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3108.88</v>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="M6" t="n">
+        <v>2903.31</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3108.89</v>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>🔴 下降</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>🔴 売り注意</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q6" t="n">
         <v>15</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🔴 下降
@@ -987,144 +1099,32 @@
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>押し目、-1σ、MACD売り、下降トレンド</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>2925</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-70</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-2.39</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>37115</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E6" t="n">
-        <v>9871</v>
-      </c>
-      <c r="F6" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-102.06</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-278.94</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>+2S</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>12170.47</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8154.44</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>85</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+2σ、MACD買い、反発局面</t>
+          <t>押し目、-1σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>10100</v>
+        <v>2925</v>
       </c>
       <c r="X6" t="n">
-        <v>-229</v>
+        <v>-68.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>-2.27</v>
+        <v>-2.34</v>
       </c>
       <c r="Z6" t="n">
-        <v>9871</v>
+        <v>37134</v>
       </c>
       <c r="AA6" t="n">
-        <v>10000</v>
+        <v>37099</v>
       </c>
       <c r="AB6" t="n">
-        <v>-129</v>
+        <v>36</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.29</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -1145,22 +1145,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>7832</v>
+        <v>7849</v>
       </c>
       <c r="F7" t="n">
-        <v>35.3</v>
+        <v>35.6</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.98</v>
+        <v>-6.79</v>
       </c>
       <c r="H7" t="n">
-        <v>0.45</v>
+        <v>0.86</v>
       </c>
       <c r="I7" t="n">
-        <v>-128.28</v>
+        <v>-126.92</v>
       </c>
       <c r="J7" t="n">
-        <v>-56.6</v>
+        <v>-56.33</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7823.47</v>
+        <v>7823.69</v>
       </c>
       <c r="N7" t="n">
-        <v>8510.59</v>
+        <v>8510.67</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1221,22 +1221,22 @@
         <v>7940</v>
       </c>
       <c r="X7" t="n">
-        <v>-108</v>
+        <v>-91</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.36</v>
+        <v>-1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>7832</v>
+        <v>7849</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>-161</v>
+        <v>-144</v>
       </c>
       <c r="AC7" t="n">
-        <v>-2.01</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="8">
@@ -1257,22 +1257,22 @@
         <v>4795</v>
       </c>
       <c r="E8" t="n">
-        <v>4683</v>
+        <v>4694</v>
       </c>
       <c r="F8" t="n">
-        <v>32.3</v>
+        <v>32.8</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.85</v>
+        <v>-2.63</v>
       </c>
       <c r="H8" t="n">
-        <v>0.37</v>
+        <v>0.82</v>
       </c>
       <c r="I8" t="n">
-        <v>-13.97</v>
+        <v>-13.09</v>
       </c>
       <c r="J8" t="n">
-        <v>14.27</v>
+        <v>14.44</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4659.9</v>
+        <v>4660.04</v>
       </c>
       <c r="N8" t="n">
-        <v>4662.39</v>
+        <v>4662.45</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1333,22 +1333,22 @@
         <v>4722</v>
       </c>
       <c r="X8" t="n">
-        <v>-39</v>
+        <v>-28</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.83</v>
+        <v>-0.59</v>
       </c>
       <c r="Z8" t="n">
-        <v>23415</v>
+        <v>23470</v>
       </c>
       <c r="AA8" t="n">
         <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-560</v>
+        <v>-505</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.34</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="9">
@@ -1369,22 +1369,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>19170</v>
+        <v>19300</v>
       </c>
       <c r="F9" t="n">
-        <v>51.1</v>
+        <v>51.8</v>
       </c>
       <c r="G9" t="n">
-        <v>7.41</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="I9" t="n">
-        <v>126.88</v>
+        <v>137.25</v>
       </c>
       <c r="J9" t="n">
-        <v>-57.51</v>
+        <v>-55.44</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>21092.6</v>
+        <v>21094.33</v>
       </c>
       <c r="N9" t="n">
-        <v>13945.16</v>
+        <v>13945.81</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1446,22 +1446,22 @@
         <v>19100</v>
       </c>
       <c r="X9" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.37</v>
+        <v>1.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>19170</v>
+        <v>19300</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-36340</v>
+        <v>-36210</v>
       </c>
       <c r="AC9" t="n">
-        <v>-65.47</v>
+        <v>-65.23</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1482,22 +1482,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>41.92</v>
+        <v>43.69</v>
       </c>
       <c r="F10" t="n">
-        <v>55.1</v>
+        <v>71.3</v>
       </c>
       <c r="G10" t="n">
-        <v>6.5</v>
+        <v>10.41</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.41</v>
       </c>
       <c r="I10" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="J10" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.68</v>
+        <v>33.87</v>
       </c>
       <c r="N10" t="n">
-        <v>31.94</v>
+        <v>32</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1542,8 +1542,9 @@
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
+・MACDは買いシグナルです。
+・買われ過ぎ水準です。
+・25日線から大きく上に乖離しています。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -1552,29 +1553,29 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+1σ、MACD売り、長期上昇</t>
+          <t>RSIやや過熱、上昇加速、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>41.07</v>
+        <v>41.92</v>
       </c>
       <c r="X10" t="n">
-        <v>0.85</v>
+        <v>1.77</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.07</v>
+        <v>4.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6071</v>
+        <v>-6069</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.31</v>
+        <v>-99.29000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3370</v>
+        <v>3495</v>
       </c>
       <c r="F2" t="n">
-        <v>53.4</v>
+        <v>59.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.83</v>
+        <v>1.73</v>
       </c>
       <c r="H2" t="n">
-        <v>0.64</v>
+        <v>0.52</v>
       </c>
       <c r="I2" t="n">
-        <v>9.24</v>
+        <v>17.98</v>
       </c>
       <c r="J2" t="n">
-        <v>16.49</v>
+        <v>16.79</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3134.55</v>
+        <v>3147.03</v>
       </c>
       <c r="N2" t="n">
-        <v>2745.92</v>
+        <v>2749.1</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,27 +621,27 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは売りシグナルです。
+・MACDは買いシグナルです。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
@@ -651,29 +651,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3435</v>
+        <v>3370</v>
       </c>
       <c r="X2" t="n">
-        <v>-65</v>
+        <v>125</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.89</v>
+        <v>3.71</v>
       </c>
       <c r="Z2" t="n">
-        <v>13480</v>
+        <v>13980</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>2680</v>
+        <v>3180</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.81</v>
+        <v>29.44</v>
       </c>
     </row>
     <row r="3">
@@ -697,23 +697,23 @@
         <v>464</v>
       </c>
       <c r="F3" t="n">
-        <v>61.7</v>
+        <v>62.5</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.96</v>
+        <v>-1.99</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>0.3</v>
       </c>
       <c r="I3" t="n">
-        <v>3.88</v>
+        <v>2.86</v>
       </c>
       <c r="J3" t="n">
-        <v>5.97</v>
+        <v>5.35</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>440.67</v>
+        <v>441.59</v>
       </c>
       <c r="N3" t="n">
-        <v>418</v>
+        <v>418.55</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -734,20 +734,20 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -755,7 +755,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -764,17 +763,17 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、デッドクロス、MACD売り、長期上昇</t>
+          <t>RSI適正、押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="X3" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.49</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
         <v>46400</v>
@@ -792,227 +791,230 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10685</v>
+      </c>
+      <c r="F4" t="n">
+        <v>65</v>
+      </c>
+      <c r="G4" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I4" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-215.66</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>+2S</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>12060.06</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8189.98</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>75</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・25日線から大きく上に乖離しています。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>RSI適正、上昇加速、+2σ、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>10095</v>
+      </c>
+      <c r="X4" t="n">
+        <v>590</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>10685</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>685</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>9432.T</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>NTT</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C5" t="n">
         <v>100</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>158</v>
       </c>
-      <c r="E4" t="n">
-        <v>169.9</v>
-      </c>
-      <c r="F4" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>DC</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>157.02</v>
-      </c>
-      <c r="N4" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="E5" t="n">
+        <v>167.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>37</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>157.32</v>
+      </c>
+      <c r="N5" t="n">
+        <v>152.8</v>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>⚪ 様子見</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q5" t="n">
         <v>70</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>RSI適正、押し目、デッドクロス、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>170.3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>16990</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>15800</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1190</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.53</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>10095</v>
-      </c>
-      <c r="F5" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-84.19</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-275.37</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>+2S</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>12173.46</v>
-      </c>
-      <c r="N5" t="n">
-        <v>8155.56</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>85</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+2σ、MACD買い、反発局面</t>
+          <t>押し目、-1σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>10100</v>
+        <v>169.9</v>
       </c>
       <c r="X5" t="n">
-        <v>-5</v>
+        <v>-2.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.05</v>
+        <v>-1.53</v>
       </c>
       <c r="Z5" t="n">
-        <v>10095</v>
+        <v>16730</v>
       </c>
       <c r="AA5" t="n">
-        <v>10000</v>
+        <v>15800</v>
       </c>
       <c r="AB5" t="n">
-        <v>95</v>
+        <v>930</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.95</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="6">
@@ -1033,22 +1035,22 @@
         <v>2853.77</v>
       </c>
       <c r="E6" t="n">
-        <v>2856.5</v>
+        <v>2889.5</v>
       </c>
       <c r="F6" t="n">
-        <v>40.6</v>
+        <v>42.4</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.31</v>
+        <v>-3.04</v>
       </c>
       <c r="H6" t="n">
-        <v>1.05</v>
+        <v>0.37</v>
       </c>
       <c r="I6" t="n">
-        <v>-23.74</v>
+        <v>-25.22</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.42</v>
+        <v>-14.18</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1061,10 +1063,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2903.31</v>
+        <v>2903.78</v>
       </c>
       <c r="N6" t="n">
-        <v>3108.89</v>
+        <v>3108.65</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1106,25 +1108,25 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>2925</v>
+        <v>2856.5</v>
       </c>
       <c r="X6" t="n">
-        <v>-68.5</v>
+        <v>33</v>
       </c>
       <c r="Y6" t="n">
-        <v>-2.34</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>37134</v>
+        <v>37564</v>
       </c>
       <c r="AA6" t="n">
         <v>37099</v>
       </c>
       <c r="AB6" t="n">
-        <v>36</v>
+        <v>464</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="7">
@@ -1145,22 +1147,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>7849</v>
+        <v>7853</v>
       </c>
       <c r="F7" t="n">
-        <v>35.6</v>
+        <v>45.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.79</v>
+        <v>-6.27</v>
       </c>
       <c r="H7" t="n">
-        <v>0.86</v>
+        <v>0.58</v>
       </c>
       <c r="I7" t="n">
-        <v>-126.92</v>
+        <v>-136.63</v>
       </c>
       <c r="J7" t="n">
-        <v>-56.33</v>
+        <v>-72.39</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1173,10 +1175,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7823.69</v>
+        <v>7833.6</v>
       </c>
       <c r="N7" t="n">
-        <v>8510.67</v>
+        <v>8488.639999999999</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1202,6 +1204,119 @@
         </is>
       </c>
       <c r="T7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>7849</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>7853</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7993</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-140</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>三菱商事</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4795</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4691</v>
+      </c>
+      <c r="F8" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-18.69</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>4660.36</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4667.6</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>60</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -1211,118 +1326,6 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
-        <v>7940</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-91</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-1.15</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>7849</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>7993</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-144</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>8058.T</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>三菱商事</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4795</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4694</v>
-      </c>
-      <c r="F8" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-2.63</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-13.09</v>
-      </c>
-      <c r="J8" t="n">
-        <v>14.44</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>4660.04</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4662.45</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>60</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
@@ -1330,25 +1333,25 @@
         </is>
       </c>
       <c r="W8" t="n">
-        <v>4722</v>
+        <v>4694</v>
       </c>
       <c r="X8" t="n">
-        <v>-28</v>
+        <v>-3</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.59</v>
+        <v>-0.06</v>
       </c>
       <c r="Z8" t="n">
-        <v>23470</v>
+        <v>23455</v>
       </c>
       <c r="AA8" t="n">
         <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-505</v>
+        <v>-520</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.11</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="9">
@@ -1369,22 +1372,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>19300</v>
+        <v>19395</v>
       </c>
       <c r="F9" t="n">
-        <v>51.8</v>
+        <v>50.2</v>
       </c>
       <c r="G9" t="n">
-        <v>8.109999999999999</v>
+        <v>7.98</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>0.59</v>
       </c>
       <c r="I9" t="n">
-        <v>137.25</v>
+        <v>216.59</v>
       </c>
       <c r="J9" t="n">
-        <v>-55.44</v>
+        <v>-1.03</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1397,10 +1400,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>21094.33</v>
+        <v>20948.89</v>
       </c>
       <c r="N9" t="n">
-        <v>13945.81</v>
+        <v>14027.07</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1443,25 +1446,25 @@
         </is>
       </c>
       <c r="W9" t="n">
-        <v>19100</v>
+        <v>19300</v>
       </c>
       <c r="X9" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.05</v>
+        <v>0.49</v>
       </c>
       <c r="Z9" t="n">
-        <v>19300</v>
+        <v>19395</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-36210</v>
+        <v>-36115</v>
       </c>
       <c r="AC9" t="n">
-        <v>-65.23</v>
+        <v>-65.06</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3495</v>
+        <v>3560</v>
       </c>
       <c r="F2" t="n">
-        <v>59.3</v>
+        <v>62.6</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73</v>
+        <v>3.55</v>
       </c>
       <c r="H2" t="n">
-        <v>0.52</v>
+        <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>17.98</v>
+        <v>23.17</v>
       </c>
       <c r="J2" t="n">
-        <v>16.79</v>
+        <v>17.83</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3147.03</v>
+        <v>3147.89</v>
       </c>
       <c r="N2" t="n">
-        <v>2749.1</v>
+        <v>2749.42</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -642,13 +642,16 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>RSI適正、25日線上、MACD買い、長期上昇</t>
@@ -658,22 +661,22 @@
         <v>3370</v>
       </c>
       <c r="X2" t="n">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.71</v>
+        <v>5.64</v>
       </c>
       <c r="Z2" t="n">
-        <v>13980</v>
+        <v>14240</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>3180</v>
+        <v>3440</v>
       </c>
       <c r="AC2" t="n">
-        <v>29.44</v>
+        <v>31.85</v>
       </c>
     </row>
     <row r="3">
@@ -694,22 +697,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F3" t="n">
-        <v>62.5</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.99</v>
+        <v>-1.78</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3</v>
+        <v>0.68</v>
       </c>
       <c r="I3" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="J3" t="n">
-        <v>5.35</v>
+        <v>5.36</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -722,7 +725,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>441.59</v>
+        <v>441.61</v>
       </c>
       <c r="N3" t="n">
         <v>418.55</v>
@@ -770,99 +773,211 @@
         <v>464</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>46400</v>
+        <v>46500</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.48</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>170</v>
+      </c>
+      <c r="F4" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>157.36</v>
+      </c>
+      <c r="N4" t="n">
+        <v>152.81</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>65</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>押し目、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>17000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>15800</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>6976.T</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>太陽誘電</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C5" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>10000</v>
       </c>
-      <c r="E4" t="n">
-        <v>10685</v>
-      </c>
-      <c r="F4" t="n">
-        <v>65</v>
-      </c>
-      <c r="G4" t="n">
-        <v>15.41</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="I4" t="n">
-        <v>23.16</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-215.66</v>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="E5" t="n">
+        <v>10490</v>
+      </c>
+      <c r="F5" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-218.77</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>+2S</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>12060.06</v>
-      </c>
-      <c r="N4" t="n">
-        <v>8189.98</v>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="M5" t="n">
+        <v>12057.46</v>
+      </c>
+      <c r="N5" t="n">
+        <v>8189.01</v>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>🟡 買い</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q5" t="n">
         <v>75</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -873,148 +988,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>RSI適正、上昇加速、+2σ、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>10095</v>
-      </c>
-      <c r="X4" t="n">
-        <v>590</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>10685</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>685</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>6.85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>9432.T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NTT</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>100</v>
-      </c>
-      <c r="D5" t="n">
-        <v>158</v>
-      </c>
-      <c r="E5" t="n">
-        <v>167.3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>37</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>157.32</v>
-      </c>
-      <c r="N5" t="n">
-        <v>152.8</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>70</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、長期上昇</t>
+          <t>RSI適正、上昇加速、+2σ、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>169.9</v>
+        <v>10095</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.6</v>
+        <v>395</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.53</v>
+        <v>3.91</v>
       </c>
       <c r="Z5" t="n">
-        <v>16730</v>
+        <v>10490</v>
       </c>
       <c r="AA5" t="n">
-        <v>15800</v>
+        <v>10000</v>
       </c>
       <c r="AB5" t="n">
-        <v>930</v>
+        <v>490</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.89</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="6">
@@ -1035,22 +1034,22 @@
         <v>2853.77</v>
       </c>
       <c r="E6" t="n">
-        <v>2889.5</v>
+        <v>2893.5</v>
       </c>
       <c r="F6" t="n">
-        <v>42.4</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.04</v>
+        <v>-2.91</v>
       </c>
       <c r="H6" t="n">
-        <v>0.37</v>
+        <v>0.82</v>
       </c>
       <c r="I6" t="n">
-        <v>-25.22</v>
+        <v>-24.9</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.18</v>
+        <v>-14.12</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1063,10 +1062,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2903.78</v>
+        <v>2903.84</v>
       </c>
       <c r="N6" t="n">
-        <v>3108.65</v>
+        <v>3108.67</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1111,58 +1110,58 @@
         <v>2856.5</v>
       </c>
       <c r="X6" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>37564</v>
+        <v>37616</v>
       </c>
       <c r="AA6" t="n">
         <v>37099</v>
       </c>
       <c r="AB6" t="n">
-        <v>464</v>
+        <v>516</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7974.T</t>
+          <t>8058.T</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>任天堂</t>
+          <t>三菱商事</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>7993</v>
+        <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>7853</v>
+        <v>4709</v>
       </c>
       <c r="F7" t="n">
-        <v>45.5</v>
+        <v>36.2</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.27</v>
+        <v>-2.36</v>
       </c>
       <c r="H7" t="n">
-        <v>0.58</v>
+        <v>0.85</v>
       </c>
       <c r="I7" t="n">
-        <v>-136.63</v>
+        <v>-17.25</v>
       </c>
       <c r="J7" t="n">
-        <v>-72.39</v>
+        <v>8.1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1175,10 +1174,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7833.6</v>
+        <v>4660.6</v>
       </c>
       <c r="N7" t="n">
-        <v>8488.639999999999</v>
+        <v>4667.69</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1204,119 +1203,6 @@
         </is>
       </c>
       <c r="T7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
-        <v>7849</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>7853</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>7993</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-140</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-1.75</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>8058.T</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>三菱商事</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4795</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4691</v>
-      </c>
-      <c r="F8" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-2.72</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-18.69</v>
-      </c>
-      <c r="J8" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>4660.36</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4667.6</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>60</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -1326,32 +1212,144 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>4694</v>
+      </c>
+      <c r="X7" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>23545</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>23975</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-430</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-1.79</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7742</v>
+      </c>
+      <c r="F8" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-7.55</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-145.49</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-74.16</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>7832.12</v>
+      </c>
+      <c r="N8" t="n">
+        <v>8488.08</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>🔴 売り注意</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>15</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+          <t>押し目、-1σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>4694</v>
+        <v>7849</v>
       </c>
       <c r="X8" t="n">
-        <v>-3</v>
+        <v>-107</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.06</v>
+        <v>-1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>23455</v>
+        <v>7742</v>
       </c>
       <c r="AA8" t="n">
-        <v>23975</v>
+        <v>7993</v>
       </c>
       <c r="AB8" t="n">
-        <v>-520</v>
+        <v>-251</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.17</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="9">
@@ -1372,22 +1370,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>19395</v>
+        <v>19120</v>
       </c>
       <c r="F9" t="n">
-        <v>50.2</v>
+        <v>48.5</v>
       </c>
       <c r="G9" t="n">
-        <v>7.98</v>
+        <v>6.51</v>
       </c>
       <c r="H9" t="n">
-        <v>0.59</v>
+        <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>216.59</v>
+        <v>194.65</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.03</v>
+        <v>-5.42</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1400,10 +1398,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>20948.89</v>
+        <v>20945.22</v>
       </c>
       <c r="N9" t="n">
-        <v>14027.07</v>
+        <v>14025.69</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1412,20 +1410,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1442,29 +1440,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+1σ、MACD買い、反発局面</t>
+          <t>25日線上、+1σ、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>19300</v>
       </c>
       <c r="X9" t="n">
-        <v>95</v>
+        <v>-180</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.49</v>
+        <v>-0.93</v>
       </c>
       <c r="Z9" t="n">
-        <v>19395</v>
+        <v>19120</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-36115</v>
+        <v>-36390</v>
       </c>
       <c r="AC9" t="n">
-        <v>-65.06</v>
+        <v>-65.56</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1483,22 +1483,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>43.69</v>
+        <v>43.19</v>
       </c>
       <c r="F10" t="n">
-        <v>71.3</v>
+        <v>74</v>
       </c>
       <c r="G10" t="n">
-        <v>10.41</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>1.41</v>
+        <v>0.73</v>
       </c>
       <c r="I10" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="J10" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33.87</v>
+        <v>34.08</v>
       </c>
       <c r="N10" t="n">
-        <v>32</v>
+        <v>32.06</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1545,7 +1545,6 @@
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
 ・買われ過ぎ水準です。
-・25日線から大きく上に乖離しています。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -1554,26 +1553,26 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSIやや過熱、上昇加速、+1σ、MACD買い、長期上昇</t>
+          <t>RSIやや過熱、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>41.92</v>
+        <v>43.69</v>
       </c>
       <c r="X10" t="n">
-        <v>1.77</v>
+        <v>-0.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.22</v>
+        <v>-1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6069</v>
+        <v>-6070</v>
       </c>
       <c r="AC10" t="n">
         <v>-99.29000000000001</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,38 +581,38 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3560</v>
+        <v>3730</v>
       </c>
       <c r="F2" t="n">
-        <v>62.6</v>
+        <v>76</v>
       </c>
       <c r="G2" t="n">
-        <v>3.55</v>
+        <v>8.25</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1</v>
+        <v>0.79</v>
       </c>
       <c r="I2" t="n">
-        <v>23.17</v>
+        <v>47.38</v>
       </c>
       <c r="J2" t="n">
-        <v>17.83</v>
+        <v>23.74</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3147.89</v>
+        <v>3164.29</v>
       </c>
       <c r="N2" t="n">
-        <v>2749.42</v>
+        <v>2753.53</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -642,118 +642,229 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・買われ過ぎ水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>RSI過熱、25日線上、ゴールデンクロス、+1σ、MACD買い、長期上昇</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>3560</v>
+      </c>
+      <c r="X2" t="n">
+        <v>170</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>14920</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>10800</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>4120</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>38.15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>420</v>
+      </c>
+      <c r="E3" t="n">
+        <v>471</v>
+      </c>
+      <c r="F3" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>442.69</v>
+      </c>
+      <c r="N3" t="n">
+        <v>419.11</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>85</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>3370</v>
-      </c>
-      <c r="X2" t="n">
-        <v>190</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>14240</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>10800</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>3440</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>31.85</v>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>RSI適正、押し目、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>465</v>
+      </c>
+      <c r="X3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>47100</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5100</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>12.14</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>100</v>
       </c>
-      <c r="D3" t="n">
-        <v>420</v>
-      </c>
-      <c r="E3" t="n">
-        <v>465</v>
-      </c>
-      <c r="F3" t="n">
-        <v>63</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-1.78</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="D4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>169.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>441.61</v>
-      </c>
-      <c r="N3" t="n">
-        <v>418.55</v>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="M4" t="n">
+        <v>157.71</v>
+      </c>
+      <c r="N4" t="n">
+        <v>152.91</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>85</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>65</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -763,118 +874,6 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>RSI適正、押し目、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>464</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>46500</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>42000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>4500</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>10.71</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>9432.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NTT</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>158</v>
-      </c>
-      <c r="E4" t="n">
-        <v>170</v>
-      </c>
-      <c r="F4" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>157.36</v>
-      </c>
-      <c r="N4" t="n">
-        <v>152.81</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>65</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
@@ -882,25 +881,25 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>169.9</v>
+        <v>170</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="Z4" t="n">
-        <v>17000</v>
+        <v>16980</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1200</v>
+        <v>1180</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.59</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="5">
@@ -921,22 +920,22 @@
         <v>10000</v>
       </c>
       <c r="E5" t="n">
-        <v>10490</v>
+        <v>10635</v>
       </c>
       <c r="F5" t="n">
-        <v>63.3</v>
+        <v>67.5</v>
       </c>
       <c r="G5" t="n">
-        <v>13.4</v>
+        <v>14.09</v>
       </c>
       <c r="H5" t="n">
-        <v>0.67</v>
+        <v>0.37</v>
       </c>
       <c r="I5" t="n">
-        <v>7.6</v>
+        <v>91</v>
       </c>
       <c r="J5" t="n">
-        <v>-218.77</v>
+        <v>-156.82</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -949,10 +948,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>12057.46</v>
+        <v>11931.4</v>
       </c>
       <c r="N5" t="n">
-        <v>8189.01</v>
+        <v>8223.190000000001</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -961,11 +960,11 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -991,29 +990,29 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>RSI適正、上昇加速、+2σ、MACD買い、反発局面</t>
+          <t>RSIやや過熱、上昇加速、+2σ、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>10095</v>
+        <v>10490</v>
       </c>
       <c r="X5" t="n">
-        <v>395</v>
+        <v>145</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.91</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>10490</v>
+        <v>10635</v>
       </c>
       <c r="AA5" t="n">
         <v>10000</v>
       </c>
       <c r="AB5" t="n">
-        <v>490</v>
+        <v>635</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.9</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="6">
@@ -1034,63 +1033,287 @@
         <v>2853.77</v>
       </c>
       <c r="E6" t="n">
+        <v>2919</v>
+      </c>
+      <c r="F6" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-23.49</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-15.99</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>2905.43</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3108.44</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>55</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>押し目、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
         <v>2893.5</v>
       </c>
-      <c r="F6" t="n">
-        <v>43</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-2.91</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-24.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-14.12</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="X6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>37947</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>37099</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>848</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>三菱商事</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4795</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4717</v>
+      </c>
+      <c r="F7" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-19.68</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>-1S</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>2903.84</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3108.67</v>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="M7" t="n">
+        <v>4663.02</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4672.6</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>60</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>4709</v>
+      </c>
+      <c r="X7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>23585</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>23975</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-390</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7805</v>
+      </c>
+      <c r="F8" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-6.39</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-153.35</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-90</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>7839.95</v>
+      </c>
+      <c r="N8" t="n">
+        <v>8466.690000000001</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>🔴 下降</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>🔴 売り注意</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q8" t="n">
         <v>15</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🔴 下降
@@ -1100,230 +1323,6 @@
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>押し目、-1σ、MACD売り、下降トレンド</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>2856.5</v>
-      </c>
-      <c r="X6" t="n">
-        <v>37</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>37616</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>516</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>8058.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>三菱商事</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4795</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4709</v>
-      </c>
-      <c r="F7" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-2.36</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-17.25</v>
-      </c>
-      <c r="J7" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>4660.6</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4667.69</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>60</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
-        <v>4694</v>
-      </c>
-      <c r="X7" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>23545</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>23975</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-430</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-1.79</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7742</v>
-      </c>
-      <c r="F8" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-7.55</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-145.49</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-74.16</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>7832.12</v>
-      </c>
-      <c r="N8" t="n">
-        <v>8488.08</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>🔴 売り注意</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>15</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
@@ -1331,25 +1330,25 @@
         </is>
       </c>
       <c r="W8" t="n">
-        <v>7849</v>
+        <v>7742</v>
       </c>
       <c r="X8" t="n">
-        <v>-107</v>
+        <v>63</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.36</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>7742</v>
+        <v>7805</v>
       </c>
       <c r="AA8" t="n">
         <v>7993</v>
       </c>
       <c r="AB8" t="n">
-        <v>-251</v>
+        <v>-188</v>
       </c>
       <c r="AC8" t="n">
-        <v>-3.14</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="9">
@@ -1370,22 +1369,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>19120</v>
+        <v>18535</v>
       </c>
       <c r="F9" t="n">
-        <v>48.5</v>
+        <v>53.6</v>
       </c>
       <c r="G9" t="n">
-        <v>6.51</v>
+        <v>3.01</v>
       </c>
       <c r="H9" t="n">
-        <v>0.88</v>
+        <v>0.55</v>
       </c>
       <c r="I9" t="n">
-        <v>194.65</v>
+        <v>190.74</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.42</v>
+        <v>33.81</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1394,14 +1393,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>20945.22</v>
+        <v>20771.38</v>
       </c>
       <c r="N9" t="n">
-        <v>14025.69</v>
+        <v>14101.45</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1410,20 +1409,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1432,7 +1431,7 @@
 ・🟡 反発中
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -1440,29 +1439,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25日線上、+1σ、MACD買い、反発局面</t>
+          <t>RSI適正、25日線上、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>19300</v>
+        <v>19120</v>
       </c>
       <c r="X9" t="n">
-        <v>-180</v>
+        <v>-585</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.93</v>
+        <v>-3.06</v>
       </c>
       <c r="Z9" t="n">
-        <v>19120</v>
+        <v>18535</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-36390</v>
+        <v>-36975</v>
       </c>
       <c r="AC9" t="n">
-        <v>-65.56</v>
+        <v>-66.61</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3730</v>
+        <v>3780</v>
       </c>
       <c r="F2" t="n">
-        <v>76</v>
+        <v>77.2</v>
       </c>
       <c r="G2" t="n">
-        <v>8.25</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.79</v>
+        <v>1.38</v>
       </c>
       <c r="I2" t="n">
-        <v>47.38</v>
+        <v>51.37</v>
       </c>
       <c r="J2" t="n">
-        <v>23.74</v>
+        <v>24.53</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -605,14 +605,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>+2S</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3164.29</v>
+        <v>3164.96</v>
       </c>
       <c r="N2" t="n">
-        <v>2753.53</v>
+        <v>2753.78</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -644,37 +644,41 @@
 ・MACDは買いシグナルです。
 ・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・買われ過ぎ水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>RSI過熱、25日線上、ゴールデンクロス、+1σ、MACD買い、長期上昇</t>
+          <t>RSI過熱、25日線上、ゴールデンクロス、+2σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>3560</v>
       </c>
       <c r="X2" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.78</v>
+        <v>6.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>14920</v>
+        <v>15120</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4120</v>
+        <v>4320</v>
       </c>
       <c r="AC2" t="n">
-        <v>38.15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -695,22 +699,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F3" t="n">
-        <v>58.9</v>
+        <v>58.3</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.44</v>
+        <v>-0.64</v>
       </c>
       <c r="H3" t="n">
-        <v>0.34</v>
+        <v>0.87</v>
       </c>
       <c r="I3" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="J3" t="n">
-        <v>4.82</v>
+        <v>4.81</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -723,7 +727,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>442.69</v>
+        <v>442.68</v>
       </c>
       <c r="N3" t="n">
         <v>419.11</v>
@@ -772,58 +776,58 @@
         <v>465</v>
       </c>
       <c r="X3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>47100</v>
+        <v>47000</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.14</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9432.T</t>
+          <t>6976.T</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NTT</t>
+          <t>太陽誘電</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>158</v>
+        <v>10000</v>
       </c>
       <c r="E4" t="n">
-        <v>169.8</v>
+        <v>11135</v>
       </c>
       <c r="F4" t="n">
-        <v>40.7</v>
+        <v>71</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.04</v>
+        <v>19.2</v>
       </c>
       <c r="H4" t="n">
-        <v>0.33</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>1.59</v>
+        <v>130.89</v>
       </c>
       <c r="J4" t="n">
-        <v>2.69</v>
+        <v>-148.84</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -832,18 +836,18 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+2S</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>157.71</v>
+        <v>11938.06</v>
       </c>
       <c r="N4" t="n">
-        <v>152.91</v>
+        <v>8225.690000000001</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>🟢 強い上昇</t>
+          <t>🟡 反発中</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -865,6 +869,124 @@
         </is>
       </c>
       <c r="T4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・買われ過ぎ水準です。
+・25日線から大きく上に乖離しています。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>RSIやや過熱、上昇加速、+2σ、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>10490</v>
+      </c>
+      <c r="X4" t="n">
+        <v>645</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>11135</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1135</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>11.35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>158</v>
+      </c>
+      <c r="E5" t="n">
+        <v>170.1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>157.71</v>
+      </c>
+      <c r="N5" t="n">
+        <v>152.91</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>65</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -874,145 +996,32 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>170</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>16980</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>15800</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1180</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.47</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>10635</v>
-      </c>
-      <c r="F5" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>14.09</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="I5" t="n">
-        <v>91</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-156.82</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>+2S</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>11931.4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>8223.190000000001</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>65</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・25日線から大きく上に乖離しています。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>RSIやや過熱、上昇加速、+2σ、MACD買い、反発局面</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>10490</v>
+        <v>170</v>
       </c>
       <c r="X5" t="n">
-        <v>145</v>
+        <v>0.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>0.06</v>
       </c>
       <c r="Z5" t="n">
-        <v>10635</v>
+        <v>17010</v>
       </c>
       <c r="AA5" t="n">
-        <v>10000</v>
+        <v>15800</v>
       </c>
       <c r="AB5" t="n">
-        <v>635</v>
+        <v>1210</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.35</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="6">
@@ -1033,22 +1042,22 @@
         <v>2853.77</v>
       </c>
       <c r="E6" t="n">
-        <v>2919</v>
+        <v>2930.5</v>
       </c>
       <c r="F6" t="n">
-        <v>41.2</v>
+        <v>43.1</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.91</v>
+        <v>-1.54</v>
       </c>
       <c r="H6" t="n">
-        <v>0.35</v>
+        <v>0.75</v>
       </c>
       <c r="I6" t="n">
-        <v>-23.49</v>
+        <v>-22.57</v>
       </c>
       <c r="J6" t="n">
-        <v>-15.99</v>
+        <v>-15.81</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1061,10 +1070,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2905.43</v>
+        <v>2905.58</v>
       </c>
       <c r="N6" t="n">
-        <v>3108.44</v>
+        <v>3108.5</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1109,22 +1118,22 @@
         <v>2893.5</v>
       </c>
       <c r="X6" t="n">
-        <v>25.5</v>
+        <v>37</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.88</v>
+        <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>37947</v>
+        <v>38096</v>
       </c>
       <c r="AA6" t="n">
         <v>37099</v>
       </c>
       <c r="AB6" t="n">
-        <v>848</v>
+        <v>998</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.29</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="7">
@@ -1145,22 +1154,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4717</v>
+        <v>4713</v>
       </c>
       <c r="F7" t="n">
-        <v>35.4</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.23</v>
+        <v>-2.31</v>
       </c>
       <c r="H7" t="n">
-        <v>0.29</v>
+        <v>0.7</v>
       </c>
       <c r="I7" t="n">
-        <v>-19.68</v>
+        <v>-20</v>
       </c>
       <c r="J7" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1173,10 +1182,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4663.02</v>
+        <v>4662.96</v>
       </c>
       <c r="N7" t="n">
-        <v>4672.6</v>
+        <v>4672.58</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1221,22 +1230,22 @@
         <v>4709</v>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>23585</v>
+        <v>23565</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>-390</v>
+        <v>-410</v>
       </c>
       <c r="AC7" t="n">
-        <v>-1.63</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="8">
@@ -1257,22 +1266,22 @@
         <v>7993</v>
       </c>
       <c r="E8" t="n">
-        <v>7805</v>
+        <v>7815</v>
       </c>
       <c r="F8" t="n">
-        <v>40.9</v>
+        <v>41.2</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.39</v>
+        <v>-6.27</v>
       </c>
       <c r="H8" t="n">
-        <v>0.51</v>
+        <v>0.88</v>
       </c>
       <c r="I8" t="n">
-        <v>-153.35</v>
+        <v>-152.55</v>
       </c>
       <c r="J8" t="n">
-        <v>-90</v>
+        <v>-89.84</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1285,10 +1294,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>7839.95</v>
+        <v>7840.08</v>
       </c>
       <c r="N8" t="n">
-        <v>8466.690000000001</v>
+        <v>8466.74</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1333,22 +1342,22 @@
         <v>7742</v>
       </c>
       <c r="X8" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>7805</v>
+        <v>7815</v>
       </c>
       <c r="AA8" t="n">
         <v>7993</v>
       </c>
       <c r="AB8" t="n">
-        <v>-188</v>
+        <v>-178</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.35</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="9">
@@ -1369,22 +1378,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>18535</v>
+        <v>18735</v>
       </c>
       <c r="F9" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
       <c r="G9" t="n">
-        <v>3.01</v>
+        <v>4.08</v>
       </c>
       <c r="H9" t="n">
-        <v>0.55</v>
+        <v>0.82</v>
       </c>
       <c r="I9" t="n">
-        <v>190.74</v>
+        <v>206.69</v>
       </c>
       <c r="J9" t="n">
-        <v>33.81</v>
+        <v>37</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1397,10 +1406,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>20771.38</v>
+        <v>20774.04</v>
       </c>
       <c r="N9" t="n">
-        <v>14101.45</v>
+        <v>14102.45</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1446,22 +1455,22 @@
         <v>19120</v>
       </c>
       <c r="X9" t="n">
-        <v>-585</v>
+        <v>-385</v>
       </c>
       <c r="Y9" t="n">
-        <v>-3.06</v>
+        <v>-2.01</v>
       </c>
       <c r="Z9" t="n">
-        <v>18535</v>
+        <v>18735</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-36975</v>
+        <v>-36775</v>
       </c>
       <c r="AC9" t="n">
-        <v>-66.61</v>
+        <v>-66.25</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1491,22 +1491,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>43.19</v>
+        <v>43.46</v>
       </c>
       <c r="F10" t="n">
-        <v>74</v>
+        <v>72.3</v>
       </c>
       <c r="G10" t="n">
-        <v>8.470000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="H10" t="n">
-        <v>0.73</v>
+        <v>0.91</v>
       </c>
       <c r="I10" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>34.08</v>
+        <v>34.25</v>
       </c>
       <c r="N10" t="n">
-        <v>32.06</v>
+        <v>32.13</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="W10" t="n">
-        <v>43.69</v>
+        <v>43.19</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5</v>
+        <v>0.27</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.14</v>
+        <v>0.63</v>
       </c>
       <c r="Z10" t="n">
         <v>43</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,26 +581,26 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3780</v>
+        <v>3850</v>
       </c>
       <c r="F2" t="n">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="G2" t="n">
-        <v>9.640000000000001</v>
+        <v>11.52</v>
       </c>
       <c r="H2" t="n">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
-        <v>51.37</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>24.53</v>
+        <v>35.32</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3164.96</v>
+        <v>3183.43</v>
       </c>
       <c r="N2" t="n">
-        <v>2753.78</v>
+        <v>2758.54</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,20 +621,20 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -642,79 +642,75 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・買われ過ぎ水準です。
+・25日線から大きく上に乖離しています。
 ・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>RSI過熱、25日線上、ゴールデンクロス、+2σ、MACD買い、長期上昇</t>
+          <t>RSI過熱、上昇加速、+2σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3560</v>
+        <v>3780</v>
       </c>
       <c r="X2" t="n">
-        <v>220</v>
+        <v>70</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.18</v>
+        <v>1.85</v>
       </c>
       <c r="Z2" t="n">
-        <v>15120</v>
+        <v>15400</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4320</v>
+        <v>4600</v>
       </c>
       <c r="AC2" t="n">
-        <v>40</v>
+        <v>42.59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3673.T</t>
+          <t>6976.T</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ブロードリーフ</t>
+          <t>太陽誘電</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>420</v>
+        <v>10000</v>
       </c>
       <c r="E3" t="n">
-        <v>470</v>
+        <v>11645</v>
       </c>
       <c r="F3" t="n">
-        <v>58.3</v>
+        <v>81.5</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.64</v>
+        <v>23.36</v>
       </c>
       <c r="H3" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="I3" t="n">
-        <v>2.57</v>
+        <v>266.67</v>
       </c>
       <c r="J3" t="n">
-        <v>4.81</v>
+        <v>-65.73999999999999</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -723,152 +719,39 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+2S</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>442.68</v>
+        <v>11816.77</v>
       </c>
       <c r="N3" t="n">
-        <v>419.11</v>
+        <v>8265.01</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>🟢 強い上昇</t>
+          <t>🟡 反発中</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟠 利益確定検討</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>RSI適正、押し目、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>465</v>
-      </c>
-      <c r="X3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>47000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>42000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>11135</v>
-      </c>
-      <c r="F4" t="n">
-        <v>71</v>
-      </c>
-      <c r="G4" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I4" t="n">
-        <v>130.89</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-148.84</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>+2S</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>11938.06</v>
-      </c>
-      <c r="N4" t="n">
-        <v>8225.690000000001</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>65</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -880,113 +763,109 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>RSIやや過熱、上昇加速、+2σ、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>10490</v>
-      </c>
-      <c r="X4" t="n">
-        <v>645</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>RSI過熱、上昇加速、+2σ、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
         <v>11135</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="X3" t="n">
+        <v>510</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>11645</v>
+      </c>
+      <c r="AA3" t="n">
         <v>10000</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1135</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>11.35</v>
+      <c r="AB3" t="n">
+        <v>1645</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>16.45</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>9432.T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NTT</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>100</v>
       </c>
-      <c r="D5" t="n">
-        <v>158</v>
-      </c>
-      <c r="E5" t="n">
-        <v>170.1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="D4" t="n">
+        <v>420</v>
+      </c>
+      <c r="E4" t="n">
+        <v>463</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>157.71</v>
-      </c>
-      <c r="N5" t="n">
-        <v>152.91</v>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="M4" t="n">
+        <v>443.75</v>
+      </c>
+      <c r="N4" t="n">
+        <v>419.63</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>⚪ 様子見</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q4" t="n">
         <v>65</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -996,6 +875,118 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>押し目、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>470</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>4300</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>158</v>
+      </c>
+      <c r="E5" t="n">
+        <v>170</v>
+      </c>
+      <c r="F5" t="n">
+        <v>31</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>158.05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>153.02</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>65</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
@@ -1003,25 +994,25 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>170</v>
+        <v>170.1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="Z5" t="n">
-        <v>17010</v>
+        <v>17000</v>
       </c>
       <c r="AA5" t="n">
         <v>15800</v>
       </c>
       <c r="AB5" t="n">
-        <v>1210</v>
+        <v>1200</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.66</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="6">
@@ -1042,22 +1033,22 @@
         <v>2853.77</v>
       </c>
       <c r="E6" t="n">
-        <v>2930.5</v>
+        <v>2915</v>
       </c>
       <c r="F6" t="n">
-        <v>43.1</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.54</v>
+        <v>-1.87</v>
       </c>
       <c r="H6" t="n">
-        <v>0.75</v>
+        <v>0.37</v>
       </c>
       <c r="I6" t="n">
-        <v>-22.57</v>
+        <v>-21.73</v>
       </c>
       <c r="J6" t="n">
-        <v>-15.81</v>
+        <v>-16.99</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1070,10 +1061,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2905.58</v>
+        <v>2907.61</v>
       </c>
       <c r="N6" t="n">
-        <v>3108.5</v>
+        <v>3108.22</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1115,25 +1106,25 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>2893.5</v>
+        <v>2930.5</v>
       </c>
       <c r="X6" t="n">
-        <v>37</v>
+        <v>-15.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.28</v>
+        <v>-0.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>38096</v>
+        <v>37895</v>
       </c>
       <c r="AA6" t="n">
         <v>37099</v>
       </c>
       <c r="AB6" t="n">
-        <v>998</v>
+        <v>796</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.69</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="7">
@@ -1154,22 +1145,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4713</v>
+        <v>4682</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>34.3</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.31</v>
+        <v>-2.92</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7</v>
+        <v>0.38</v>
       </c>
       <c r="I7" t="n">
-        <v>-20</v>
+        <v>-24.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.48</v>
+        <v>-2.89</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1182,10 +1173,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4662.96</v>
+        <v>4664.71</v>
       </c>
       <c r="N7" t="n">
-        <v>4672.58</v>
+        <v>4677.37</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1227,25 +1218,25 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4709</v>
+        <v>4713</v>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>-31</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.08</v>
+        <v>-0.66</v>
       </c>
       <c r="Z7" t="n">
-        <v>23565</v>
+        <v>23410</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>-410</v>
+        <v>-565</v>
       </c>
       <c r="AC7" t="n">
-        <v>-1.71</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="8">
@@ -1266,22 +1257,22 @@
         <v>7993</v>
       </c>
       <c r="E8" t="n">
-        <v>7815</v>
+        <v>7795</v>
       </c>
       <c r="F8" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.27</v>
+        <v>-5.97</v>
       </c>
       <c r="H8" t="n">
-        <v>0.88</v>
+        <v>0.53</v>
       </c>
       <c r="I8" t="n">
-        <v>-152.55</v>
+        <v>-157.94</v>
       </c>
       <c r="J8" t="n">
-        <v>-89.84</v>
+        <v>-103.46</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1294,10 +1285,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>7840.08</v>
+        <v>7847.01</v>
       </c>
       <c r="N8" t="n">
-        <v>8466.74</v>
+        <v>8447.360000000001</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1339,25 +1330,25 @@
         </is>
       </c>
       <c r="W8" t="n">
-        <v>7742</v>
+        <v>7815</v>
       </c>
       <c r="X8" t="n">
-        <v>73</v>
+        <v>-20</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>7815</v>
+        <v>7795</v>
       </c>
       <c r="AA8" t="n">
         <v>7993</v>
       </c>
       <c r="AB8" t="n">
-        <v>-178</v>
+        <v>-198</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.23</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="9">
@@ -1378,22 +1369,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>18735</v>
+        <v>17975</v>
       </c>
       <c r="F9" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
       <c r="G9" t="n">
-        <v>4.08</v>
+        <v>-0.59</v>
       </c>
       <c r="H9" t="n">
-        <v>0.82</v>
+        <v>0.6</v>
       </c>
       <c r="I9" t="n">
-        <v>206.69</v>
+        <v>153.15</v>
       </c>
       <c r="J9" t="n">
-        <v>37</v>
+        <v>60.23</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1406,10 +1397,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>20774.04</v>
+        <v>20587.04</v>
       </c>
       <c r="N9" t="n">
-        <v>14102.45</v>
+        <v>14175.87</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1418,20 +1409,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1448,29 +1439,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、反発局面</t>
+          <t>RSI適正、押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>19120</v>
+        <v>18735</v>
       </c>
       <c r="X9" t="n">
-        <v>-385</v>
+        <v>-760</v>
       </c>
       <c r="Y9" t="n">
-        <v>-2.01</v>
+        <v>-4.06</v>
       </c>
       <c r="Z9" t="n">
-        <v>18735</v>
+        <v>17975</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-36775</v>
+        <v>-37535</v>
       </c>
       <c r="AC9" t="n">
-        <v>-66.25</v>
+        <v>-67.62</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3850</v>
+        <v>3835</v>
       </c>
       <c r="F2" t="n">
-        <v>77</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>11.52</v>
+        <v>11.1</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>1.54</v>
       </c>
       <c r="I2" t="n">
-        <v>78.45999999999999</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>35.32</v>
+        <v>35.08</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3183.43</v>
+        <v>3183.23</v>
       </c>
       <c r="N2" t="n">
-        <v>2758.54</v>
+        <v>2758.46</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -644,6 +644,7 @@
 ・MACDは買いシグナルです。
 ・買われ過ぎ水準です。
 ・25日線から大きく上に乖離しています。
+・出来高が増加しています。
 ・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -652,29 +653,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>RSI過熱、上昇加速、+2σ、MACD買い、長期上昇</t>
+          <t>RSI過熱、上昇加速、出来高微増、+2σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>3780</v>
       </c>
       <c r="X2" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="Z2" t="n">
-        <v>15400</v>
+        <v>15340</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4600</v>
+        <v>4540</v>
       </c>
       <c r="AC2" t="n">
-        <v>42.59</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="3">
@@ -695,22 +696,22 @@
         <v>10000</v>
       </c>
       <c r="E3" t="n">
-        <v>11645</v>
+        <v>11460</v>
       </c>
       <c r="F3" t="n">
-        <v>81.5</v>
+        <v>80.8</v>
       </c>
       <c r="G3" t="n">
-        <v>23.36</v>
+        <v>21.5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.84</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="n">
-        <v>266.67</v>
+        <v>251.91</v>
       </c>
       <c r="J3" t="n">
-        <v>-65.73999999999999</v>
+        <v>-68.69</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -723,10 +724,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>11816.77</v>
+        <v>11814.3</v>
       </c>
       <c r="N3" t="n">
-        <v>8265.01</v>
+        <v>8264.08</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -773,22 +774,22 @@
         <v>11135</v>
       </c>
       <c r="X3" t="n">
-        <v>510</v>
+        <v>325</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.58</v>
+        <v>2.92</v>
       </c>
       <c r="Z3" t="n">
-        <v>11645</v>
+        <v>11460</v>
       </c>
       <c r="AA3" t="n">
         <v>10000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1645</v>
+        <v>1460</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.45</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="4">
@@ -809,22 +810,22 @@
         <v>420</v>
       </c>
       <c r="E4" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F4" t="n">
-        <v>40.3</v>
+        <v>41.7</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.87</v>
+        <v>-1.47</v>
       </c>
       <c r="H4" t="n">
-        <v>0.59</v>
+        <v>1.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="J4" t="n">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -837,10 +838,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>443.75</v>
+        <v>443.77</v>
       </c>
       <c r="N4" t="n">
-        <v>419.63</v>
+        <v>419.64</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -853,7 +854,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -866,6 +867,119 @@
         </is>
       </c>
       <c r="T4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・出来高が増加しています。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>押し目、出来高微増、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>470</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>46500</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>4500</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>10.71</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>158</v>
+      </c>
+      <c r="E5" t="n">
+        <v>172.1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>158.08</v>
+      </c>
+      <c r="N5" t="n">
+        <v>153.03</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>75</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -875,144 +989,32 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>470</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>46300</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>42000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>4300</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>10.24</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>9432.T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NTT</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>100</v>
-      </c>
-      <c r="D5" t="n">
-        <v>158</v>
-      </c>
-      <c r="E5" t="n">
-        <v>170</v>
-      </c>
-      <c r="F5" t="n">
-        <v>31</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>158.05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>153.02</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>65</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>170.1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.06</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>17000</v>
+        <v>17210</v>
       </c>
       <c r="AA5" t="n">
         <v>15800</v>
       </c>
       <c r="AB5" t="n">
-        <v>1200</v>
+        <v>1410</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.59</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="6">
@@ -1033,22 +1035,22 @@
         <v>2853.77</v>
       </c>
       <c r="E6" t="n">
-        <v>2915</v>
+        <v>2900.5</v>
       </c>
       <c r="F6" t="n">
-        <v>42</v>
+        <v>40.4</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.87</v>
+        <v>-2.33</v>
       </c>
       <c r="H6" t="n">
-        <v>0.37</v>
+        <v>0.86</v>
       </c>
       <c r="I6" t="n">
-        <v>-21.73</v>
+        <v>-22.88</v>
       </c>
       <c r="J6" t="n">
-        <v>-16.99</v>
+        <v>-17.22</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1061,70 +1063,70 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2907.61</v>
+        <v>2907.41</v>
       </c>
       <c r="N6" t="n">
-        <v>3108.22</v>
+        <v>3108.15</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>🟢 上昇</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🔴 売り注意</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟢 上昇
+・🔴 下降
 ・MACDは売りシグナルです。
 ・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、上昇トレンド</t>
+          <t>押し目、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>2930.5</v>
       </c>
       <c r="X6" t="n">
-        <v>-15.5</v>
+        <v>-30</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.53</v>
+        <v>-1.02</v>
       </c>
       <c r="Z6" t="n">
-        <v>37895</v>
+        <v>37706</v>
       </c>
       <c r="AA6" t="n">
         <v>37099</v>
       </c>
       <c r="AB6" t="n">
-        <v>796</v>
+        <v>608</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.15</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="7">
@@ -1145,22 +1147,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4682</v>
+        <v>4676</v>
       </c>
       <c r="F7" t="n">
-        <v>34.3</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.92</v>
+        <v>-3.04</v>
       </c>
       <c r="H7" t="n">
-        <v>0.38</v>
+        <v>0.84</v>
       </c>
       <c r="I7" t="n">
-        <v>-24.4</v>
+        <v>-24.88</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.89</v>
+        <v>-2.99</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1173,10 +1175,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4664.71</v>
+        <v>4664.63</v>
       </c>
       <c r="N7" t="n">
-        <v>4677.37</v>
+        <v>4677.34</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1221,22 +1223,22 @@
         <v>4713</v>
       </c>
       <c r="X7" t="n">
-        <v>-31</v>
+        <v>-37</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.66</v>
+        <v>-0.79</v>
       </c>
       <c r="Z7" t="n">
-        <v>23410</v>
+        <v>23380</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>-565</v>
+        <v>-595</v>
       </c>
       <c r="AC7" t="n">
-        <v>-2.36</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="8">
@@ -1257,22 +1259,22 @@
         <v>7993</v>
       </c>
       <c r="E8" t="n">
-        <v>7795</v>
+        <v>7775</v>
       </c>
       <c r="F8" t="n">
-        <v>33.4</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.97</v>
+        <v>-6.2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.53</v>
+        <v>0.85</v>
       </c>
       <c r="I8" t="n">
-        <v>-157.94</v>
+        <v>-159.54</v>
       </c>
       <c r="J8" t="n">
-        <v>-103.46</v>
+        <v>-103.78</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1285,10 +1287,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>7847.01</v>
+        <v>7846.75</v>
       </c>
       <c r="N8" t="n">
-        <v>8447.360000000001</v>
+        <v>8447.26</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1333,22 +1335,22 @@
         <v>7815</v>
       </c>
       <c r="X8" t="n">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.26</v>
+        <v>-0.51</v>
       </c>
       <c r="Z8" t="n">
-        <v>7795</v>
+        <v>7775</v>
       </c>
       <c r="AA8" t="n">
         <v>7993</v>
       </c>
       <c r="AB8" t="n">
-        <v>-198</v>
+        <v>-218</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.48</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="9">
@@ -1369,22 +1371,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>17975</v>
+        <v>17900</v>
       </c>
       <c r="F9" t="n">
-        <v>58.4</v>
+        <v>57.7</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.59</v>
+        <v>-0.98</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6</v>
+        <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>153.15</v>
+        <v>147.16</v>
       </c>
       <c r="J9" t="n">
-        <v>60.23</v>
+        <v>59.04</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1397,10 +1399,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>20587.04</v>
+        <v>20586.04</v>
       </c>
       <c r="N9" t="n">
-        <v>14175.87</v>
+        <v>14175.49</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1446,22 +1448,22 @@
         <v>18735</v>
       </c>
       <c r="X9" t="n">
-        <v>-760</v>
+        <v>-835</v>
       </c>
       <c r="Y9" t="n">
-        <v>-4.06</v>
+        <v>-4.46</v>
       </c>
       <c r="Z9" t="n">
-        <v>17975</v>
+        <v>17900</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-37535</v>
+        <v>-37610</v>
       </c>
       <c r="AC9" t="n">
-        <v>-67.62</v>
+        <v>-67.75</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1484,22 +1484,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>43.46</v>
+        <v>44.94</v>
       </c>
       <c r="F10" t="n">
-        <v>72.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>8.48</v>
+        <v>11.26</v>
       </c>
       <c r="H10" t="n">
-        <v>0.91</v>
+        <v>1.25</v>
       </c>
       <c r="I10" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="J10" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>34.25</v>
+        <v>34.38</v>
       </c>
       <c r="N10" t="n">
-        <v>32.13</v>
+        <v>32.21</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・買われ過ぎ水準です。
+・25日線から大きく上に乖離しています。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -1554,29 +1554,29 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSIやや過熱、上昇加速、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>43.19</v>
+        <v>43.46</v>
       </c>
       <c r="X10" t="n">
-        <v>0.27</v>
+        <v>1.48</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.63</v>
+        <v>3.41</v>
       </c>
       <c r="Z10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6070</v>
+        <v>-6068</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.29000000000001</v>
+        <v>-99.26000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3835</v>
+        <v>3920</v>
       </c>
       <c r="F2" t="n">
-        <v>76.59999999999999</v>
+        <v>79</v>
       </c>
       <c r="G2" t="n">
-        <v>11.1</v>
+        <v>13.41</v>
       </c>
       <c r="H2" t="n">
-        <v>1.54</v>
+        <v>0.96</v>
       </c>
       <c r="I2" t="n">
-        <v>77.26000000000001</v>
+        <v>103.45</v>
       </c>
       <c r="J2" t="n">
-        <v>35.08</v>
+        <v>48.75</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3183.23</v>
+        <v>3202.69</v>
       </c>
       <c r="N2" t="n">
-        <v>2758.46</v>
+        <v>2763.48</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -644,7 +644,6 @@
 ・MACDは買いシグナルです。
 ・買われ過ぎ水準です。
 ・25日線から大きく上に乖離しています。
-・出来高が増加しています。
 ・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -653,29 +652,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>RSI過熱、上昇加速、出来高微増、+2σ、MACD買い、長期上昇</t>
+          <t>RSI過熱、上昇加速、+2σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3780</v>
+        <v>3835</v>
       </c>
       <c r="X2" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.46</v>
+        <v>2.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>15340</v>
+        <v>15680</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4540</v>
+        <v>4880</v>
       </c>
       <c r="AC2" t="n">
-        <v>42.04</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="3">
@@ -696,22 +695,22 @@
         <v>10000</v>
       </c>
       <c r="E3" t="n">
-        <v>11460</v>
+        <v>11405</v>
       </c>
       <c r="F3" t="n">
-        <v>80.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>21.5</v>
+        <v>19.76</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>0.74</v>
       </c>
       <c r="I3" t="n">
-        <v>251.91</v>
+        <v>339.47</v>
       </c>
       <c r="J3" t="n">
-        <v>-68.69</v>
+        <v>12.94</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -724,10 +723,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>11814.3</v>
+        <v>11702.88</v>
       </c>
       <c r="N3" t="n">
-        <v>8264.08</v>
+        <v>8302.43</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -771,25 +770,25 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>11135</v>
+        <v>11460</v>
       </c>
       <c r="X3" t="n">
-        <v>325</v>
+        <v>-55</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.92</v>
+        <v>-0.48</v>
       </c>
       <c r="Z3" t="n">
-        <v>11460</v>
+        <v>11405</v>
       </c>
       <c r="AA3" t="n">
         <v>10000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1460</v>
+        <v>1405</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.6</v>
+        <v>14.05</v>
       </c>
     </row>
     <row r="4">
@@ -810,22 +809,22 @@
         <v>420</v>
       </c>
       <c r="E4" t="n">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="F4" t="n">
-        <v>41.7</v>
+        <v>50.7</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.47</v>
+        <v>1.07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9</v>
+        <v>0.52</v>
       </c>
       <c r="I4" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="J4" t="n">
-        <v>4.22</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -838,10 +837,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>443.77</v>
+        <v>444.98</v>
       </c>
       <c r="N4" t="n">
-        <v>419.64</v>
+        <v>420.25</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -850,20 +849,20 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -871,7 +870,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・出来高が増加しています。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -880,29 +879,29 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>押し目、出来高微増、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="X4" t="n">
-        <v>-5</v>
+        <v>11</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.06</v>
+        <v>2.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>46500</v>
+        <v>47600</v>
       </c>
       <c r="AA4" t="n">
         <v>42000</v>
       </c>
       <c r="AB4" t="n">
-        <v>4500</v>
+        <v>5600</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.71</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="5">
@@ -923,22 +922,22 @@
         <v>158</v>
       </c>
       <c r="E5" t="n">
-        <v>172.1</v>
+        <v>170.1</v>
       </c>
       <c r="F5" t="n">
-        <v>39.6</v>
+        <v>35.7</v>
       </c>
       <c r="G5" t="n">
-        <v>0.15</v>
+        <v>-1.02</v>
       </c>
       <c r="H5" t="n">
-        <v>1.06</v>
+        <v>0.47</v>
       </c>
       <c r="I5" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="J5" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -951,10 +950,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>158.08</v>
+        <v>158.41</v>
       </c>
       <c r="N5" t="n">
-        <v>153.03</v>
+        <v>153.13</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -963,11 +962,11 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -992,29 +991,29 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>25日線上、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>170.1</v>
+        <v>172.1</v>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>-1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>17210</v>
+        <v>17010</v>
       </c>
       <c r="AA5" t="n">
         <v>15800</v>
       </c>
       <c r="AB5" t="n">
-        <v>1410</v>
+        <v>1210</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.92</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="6">
@@ -1035,22 +1034,22 @@
         <v>2853.77</v>
       </c>
       <c r="E6" t="n">
-        <v>2900.5</v>
+        <v>2898.5</v>
       </c>
       <c r="F6" t="n">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.33</v>
+        <v>-2.13</v>
       </c>
       <c r="H6" t="n">
-        <v>0.86</v>
+        <v>0.39</v>
       </c>
       <c r="I6" t="n">
-        <v>-22.88</v>
+        <v>-23.03</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.22</v>
+        <v>-18.38</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1063,10 +1062,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2907.41</v>
+        <v>2909.44</v>
       </c>
       <c r="N6" t="n">
-        <v>3108.15</v>
+        <v>3107.54</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1108,61 +1107,61 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>2930.5</v>
+        <v>2900.5</v>
       </c>
       <c r="X6" t="n">
-        <v>-30</v>
+        <v>-2</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>37706</v>
+        <v>37680</v>
       </c>
       <c r="AA6" t="n">
         <v>37099</v>
       </c>
       <c r="AB6" t="n">
-        <v>608</v>
+        <v>582</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8058.T</t>
+          <t>7974.T</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>三菱商事</t>
+          <t>任天堂</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4795</v>
+        <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>4676</v>
+        <v>7789</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>37.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.04</v>
+        <v>-5.46</v>
       </c>
       <c r="H7" t="n">
-        <v>0.84</v>
+        <v>0.53</v>
       </c>
       <c r="I7" t="n">
-        <v>-24.88</v>
+        <v>-162.08</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.99</v>
+        <v>-115.44</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1175,147 +1174,35 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4664.63</v>
+        <v>7855.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4677.34</v>
+        <v>8429.42</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>🟢 上昇</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🔴 売り注意</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>押し目、-1σ、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
-        <v>4713</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-37</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-0.79</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>23380</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>23975</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-595</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-2.48</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7775</v>
-      </c>
-      <c r="F8" t="n">
-        <v>33</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-159.54</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-103.78</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>7846.75</v>
-      </c>
-      <c r="N8" t="n">
-        <v>8447.26</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>🔴 売り注意</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>15</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🔴 下降
@@ -1325,32 +1212,144 @@
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>押し目、-1σ、MACD売り、下降トレンド</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>7775</v>
+      </c>
+      <c r="X7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>7789</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7993</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-204</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-2.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>三菱商事</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4795</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4555</v>
+      </c>
+      <c r="F8" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-38.07</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-2S</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>4665.22</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4681.82</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>🔴 売り注意</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>20</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは売りシグナルです。
+・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、下降トレンド</t>
+          <t>押し目、-2σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>7815</v>
+        <v>4676</v>
       </c>
       <c r="X8" t="n">
-        <v>-40</v>
+        <v>-121</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.51</v>
+        <v>-2.59</v>
       </c>
       <c r="Z8" t="n">
-        <v>7775</v>
+        <v>22775</v>
       </c>
       <c r="AA8" t="n">
-        <v>7993</v>
+        <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-218</v>
+        <v>-1200</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.73</v>
+        <v>-5.01</v>
       </c>
     </row>
     <row r="9">
@@ -1371,22 +1370,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>17900</v>
+        <v>18450</v>
       </c>
       <c r="F9" t="n">
-        <v>57.7</v>
+        <v>58.7</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.98</v>
+        <v>1.66</v>
       </c>
       <c r="H9" t="n">
-        <v>0.88</v>
+        <v>0.64</v>
       </c>
       <c r="I9" t="n">
-        <v>147.16</v>
+        <v>142.72</v>
       </c>
       <c r="J9" t="n">
-        <v>59.04</v>
+        <v>75.77</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1399,10 +1398,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>20586.04</v>
+        <v>20401.38</v>
       </c>
       <c r="N9" t="n">
-        <v>14175.49</v>
+        <v>14251.96</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1411,20 +1410,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1441,29 +1440,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD買い、反発局面</t>
+          <t>RSI適正、25日線上、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>18735</v>
+        <v>17900</v>
       </c>
       <c r="X9" t="n">
-        <v>-835</v>
+        <v>550</v>
       </c>
       <c r="Y9" t="n">
-        <v>-4.46</v>
+        <v>3.07</v>
       </c>
       <c r="Z9" t="n">
-        <v>17900</v>
+        <v>18450</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-37610</v>
+        <v>-37060</v>
       </c>
       <c r="AC9" t="n">
-        <v>-67.75</v>
+        <v>-66.76000000000001</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3920</v>
+        <v>3890</v>
       </c>
       <c r="F2" t="n">
-        <v>79</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>13.41</v>
+        <v>12.58</v>
       </c>
       <c r="H2" t="n">
-        <v>0.96</v>
+        <v>1.3</v>
       </c>
       <c r="I2" t="n">
-        <v>103.45</v>
+        <v>101.06</v>
       </c>
       <c r="J2" t="n">
-        <v>48.75</v>
+        <v>48.28</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3202.69</v>
+        <v>3202.29</v>
       </c>
       <c r="N2" t="n">
-        <v>2763.48</v>
+        <v>2763.33</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -659,58 +659,58 @@
         <v>3835</v>
       </c>
       <c r="X2" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.22</v>
+        <v>1.43</v>
       </c>
       <c r="Z2" t="n">
-        <v>15680</v>
+        <v>15560</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4880</v>
+        <v>4760</v>
       </c>
       <c r="AC2" t="n">
-        <v>45.19</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6976.T</t>
+          <t>3673.T</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>太陽誘電</t>
+          <t>ブロードリーフ</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>10000</v>
+        <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>11405</v>
+        <v>479</v>
       </c>
       <c r="F3" t="n">
-        <v>77.40000000000001</v>
+        <v>52.7</v>
       </c>
       <c r="G3" t="n">
-        <v>19.76</v>
+        <v>1.68</v>
       </c>
       <c r="H3" t="n">
-        <v>0.74</v>
+        <v>1.24</v>
       </c>
       <c r="I3" t="n">
-        <v>339.47</v>
+        <v>2.39</v>
       </c>
       <c r="J3" t="n">
-        <v>12.94</v>
+        <v>3.85</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -719,153 +719,39 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+2S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>11702.88</v>
+        <v>445.02</v>
       </c>
       <c r="N3" t="n">
-        <v>8302.43</v>
+        <v>420.26</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>🟡 反発中</t>
+          <t>🟢 強い上昇</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟠 利益確定検討</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・買われ過ぎ水準です。
-・25日線から大きく上に乖離しています。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>RSI過熱、上昇加速、+2σ、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>11460</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-55</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>11405</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1405</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>14.05</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>420</v>
-      </c>
-      <c r="E4" t="n">
-        <v>476</v>
-      </c>
-      <c r="F4" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>444.98</v>
-      </c>
-      <c r="N4" t="n">
-        <v>420.25</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>🟢 強い買い</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>95</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -876,32 +762,145 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>465</v>
+      </c>
+      <c r="X3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>47900</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5900</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>14.05</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10955</v>
+      </c>
+      <c r="F4" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I4" t="n">
+        <v>303.58</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>11696.88</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8300.18</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>75</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・25日線から大きく上に乖離しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>RSIやや過熱、上昇加速、+1σ、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>465</v>
+        <v>11460</v>
       </c>
       <c r="X4" t="n">
-        <v>11</v>
+        <v>-505</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.37</v>
+        <v>-4.41</v>
       </c>
       <c r="Z4" t="n">
-        <v>47600</v>
+        <v>10955</v>
       </c>
       <c r="AA4" t="n">
-        <v>42000</v>
+        <v>10000</v>
       </c>
       <c r="AB4" t="n">
-        <v>5600</v>
+        <v>955</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.33</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -922,22 +921,22 @@
         <v>158</v>
       </c>
       <c r="E5" t="n">
-        <v>170.1</v>
+        <v>172.1</v>
       </c>
       <c r="F5" t="n">
-        <v>35.7</v>
+        <v>40.1</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.02</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.47</v>
+        <v>1.05</v>
       </c>
       <c r="I5" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="J5" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -950,10 +949,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>158.41</v>
+        <v>158.43</v>
       </c>
       <c r="N5" t="n">
-        <v>153.13</v>
+        <v>153.14</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -962,11 +961,11 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -991,29 +990,29 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>172.1</v>
       </c>
       <c r="X5" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.16</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>17010</v>
+        <v>17210</v>
       </c>
       <c r="AA5" t="n">
         <v>15800</v>
       </c>
       <c r="AB5" t="n">
-        <v>1210</v>
+        <v>1410</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.66</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="6">
@@ -1034,22 +1033,22 @@
         <v>2853.77</v>
       </c>
       <c r="E6" t="n">
-        <v>2898.5</v>
+        <v>2902</v>
       </c>
       <c r="F6" t="n">
-        <v>40.6</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.13</v>
+        <v>-2.02</v>
       </c>
       <c r="H6" t="n">
-        <v>0.39</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-23.03</v>
+        <v>-22.75</v>
       </c>
       <c r="J6" t="n">
-        <v>-18.38</v>
+        <v>-18.33</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1062,10 +1061,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2909.44</v>
+        <v>2909.48</v>
       </c>
       <c r="N6" t="n">
-        <v>3107.54</v>
+        <v>3107.56</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1110,22 +1109,22 @@
         <v>2900.5</v>
       </c>
       <c r="X6" t="n">
-        <v>-2</v>
+        <v>1.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>37680</v>
+        <v>37726</v>
       </c>
       <c r="AA6" t="n">
         <v>37099</v>
       </c>
       <c r="AB6" t="n">
-        <v>582</v>
+        <v>627</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="7">
@@ -1146,22 +1145,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>7789</v>
+        <v>7851</v>
       </c>
       <c r="F7" t="n">
-        <v>37.5</v>
+        <v>40.3</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.46</v>
+        <v>-4.74</v>
       </c>
       <c r="H7" t="n">
-        <v>0.53</v>
+        <v>0.95</v>
       </c>
       <c r="I7" t="n">
-        <v>-162.08</v>
+        <v>-157.13</v>
       </c>
       <c r="J7" t="n">
-        <v>-115.44</v>
+        <v>-114.45</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1170,14 +1169,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7855.05</v>
+        <v>7855.88</v>
       </c>
       <c r="N7" t="n">
-        <v>8429.42</v>
+        <v>8429.73</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1190,7 +1189,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1207,7 +1206,7 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
@@ -1215,29 +1214,29 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、下降トレンド</t>
+          <t>押し目、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>7775</v>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.18</v>
+        <v>0.98</v>
       </c>
       <c r="Z7" t="n">
-        <v>7789</v>
+        <v>7851</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>-204</v>
+        <v>-142</v>
       </c>
       <c r="AC7" t="n">
-        <v>-2.55</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="8">
@@ -1258,22 +1257,22 @@
         <v>4795</v>
       </c>
       <c r="E8" t="n">
-        <v>4555</v>
+        <v>4590</v>
       </c>
       <c r="F8" t="n">
-        <v>32.3</v>
+        <v>33.7</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.4</v>
+        <v>-4.7</v>
       </c>
       <c r="H8" t="n">
-        <v>0.71</v>
+        <v>1.32</v>
       </c>
       <c r="I8" t="n">
-        <v>-38.07</v>
+        <v>-35.27</v>
       </c>
       <c r="J8" t="n">
-        <v>-10</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1286,10 +1285,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4665.22</v>
+        <v>4665.68</v>
       </c>
       <c r="N8" t="n">
-        <v>4681.82</v>
+        <v>4682</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1334,22 +1333,22 @@
         <v>4676</v>
       </c>
       <c r="X8" t="n">
-        <v>-121</v>
+        <v>-86</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.59</v>
+        <v>-1.84</v>
       </c>
       <c r="Z8" t="n">
-        <v>22775</v>
+        <v>22950</v>
       </c>
       <c r="AA8" t="n">
         <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1200</v>
+        <v>-1025</v>
       </c>
       <c r="AC8" t="n">
-        <v>-5.01</v>
+        <v>-4.28</v>
       </c>
     </row>
     <row r="9">
@@ -1370,22 +1369,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>18450</v>
+        <v>17900</v>
       </c>
       <c r="F9" t="n">
-        <v>58.7</v>
+        <v>55.1</v>
       </c>
       <c r="G9" t="n">
-        <v>1.66</v>
+        <v>-1.25</v>
       </c>
       <c r="H9" t="n">
-        <v>0.64</v>
+        <v>1.08</v>
       </c>
       <c r="I9" t="n">
-        <v>142.72</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>75.77</v>
+        <v>67</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1398,10 +1397,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>20401.38</v>
+        <v>20394.04</v>
       </c>
       <c r="N9" t="n">
-        <v>14251.96</v>
+        <v>14249.21</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1410,20 +1409,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1440,29 +1439,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、反発局面</t>
+          <t>RSI適正、押し目、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>17900</v>
       </c>
       <c r="X9" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>18450</v>
+        <v>17900</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-37060</v>
+        <v>-37610</v>
       </c>
       <c r="AC9" t="n">
-        <v>-66.76000000000001</v>
+        <v>-67.75</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1482,22 +1482,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>44.94</v>
+        <v>42.77</v>
       </c>
       <c r="F10" t="n">
-        <v>67.90000000000001</v>
+        <v>63.4</v>
       </c>
       <c r="G10" t="n">
-        <v>11.26</v>
+        <v>5.28</v>
       </c>
       <c r="H10" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="I10" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="J10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1506,14 +1506,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>34.38</v>
+        <v>34.5</v>
       </c>
       <c r="N10" t="n">
-        <v>32.21</v>
+        <v>32.26</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1543,8 +1543,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・25日線から大きく上に乖離しています。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -1552,29 +1551,29 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSIやや過熱、上昇加速、+1σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>43.46</v>
+        <v>44.94</v>
       </c>
       <c r="X10" t="n">
-        <v>1.48</v>
+        <v>-2.17</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.41</v>
+        <v>-4.83</v>
       </c>
       <c r="Z10" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6068</v>
+        <v>-6070</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.26000000000001</v>
+        <v>-99.3</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3890</v>
+        <v>4070</v>
       </c>
       <c r="F2" t="n">
-        <v>78.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>12.58</v>
+        <v>17.21</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="I2" t="n">
-        <v>101.06</v>
+        <v>132.91</v>
       </c>
       <c r="J2" t="n">
-        <v>48.28</v>
+        <v>65.2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3202.29</v>
+        <v>3224.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2763.33</v>
+        <v>2769.45</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -656,25 +656,25 @@
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3835</v>
+        <v>3890</v>
       </c>
       <c r="X2" t="n">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.43</v>
+        <v>4.63</v>
       </c>
       <c r="Z2" t="n">
-        <v>15560</v>
+        <v>16280</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4760</v>
+        <v>5480</v>
       </c>
       <c r="AC2" t="n">
-        <v>44.07</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="3">
@@ -695,63 +695,177 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
+        <v>491</v>
+      </c>
+      <c r="F3" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>446.51</v>
+      </c>
+      <c r="N3" t="n">
+        <v>420.95</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>100</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・RSIは良好な水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、ゴールデンクロス、+1σ、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
         <v>479</v>
       </c>
-      <c r="F3" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="X3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>49100</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>7100</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>173.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>445.02</v>
-      </c>
-      <c r="N3" t="n">
-        <v>420.26</v>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="M4" t="n">
+        <v>158.85</v>
+      </c>
+      <c r="N4" t="n">
+        <v>153.25</v>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>🟢 強い買い</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>95</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>75</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -762,109 +876,109 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>465</v>
-      </c>
-      <c r="X3" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>47900</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>42000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5900</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>14.05</v>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>25日線上、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>172.1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>17330</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>15800</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1530</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9.68</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>6976.T</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>太陽誘電</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C5" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>10000</v>
       </c>
-      <c r="E4" t="n">
-        <v>10955</v>
-      </c>
-      <c r="F4" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>15.26</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="I4" t="n">
-        <v>303.58</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="E5" t="n">
+        <v>10850</v>
+      </c>
+      <c r="F5" t="n">
+        <v>67</v>
+      </c>
+      <c r="G5" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I5" t="n">
+        <v>332.22</v>
+      </c>
+      <c r="J5" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>+1S</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>11696.88</v>
-      </c>
-      <c r="N4" t="n">
-        <v>8300.18</v>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="M5" t="n">
+        <v>11585.29</v>
+      </c>
+      <c r="N5" t="n">
+        <v>8336.540000000001</v>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>🟡 買い</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q5" t="n">
         <v>75</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -875,144 +989,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>RSIやや過熱、上昇加速、+1σ、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>11460</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-505</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-4.41</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>10955</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>955</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9.550000000000001</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>9432.T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NTT</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>100</v>
-      </c>
-      <c r="D5" t="n">
-        <v>158</v>
-      </c>
-      <c r="E5" t="n">
-        <v>172.1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>158.43</v>
-      </c>
-      <c r="N5" t="n">
-        <v>153.14</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>75</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>25日線上、MACD売り、長期上昇</t>
+          <t>RSIやや過熱、上昇加速、+1σ、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>172.1</v>
+        <v>10955</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-105</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0.96</v>
       </c>
       <c r="Z5" t="n">
-        <v>17210</v>
+        <v>10850</v>
       </c>
       <c r="AA5" t="n">
-        <v>15800</v>
+        <v>10000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1410</v>
+        <v>850</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.92</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="6">
@@ -1033,322 +1035,323 @@
         <v>2853.77</v>
       </c>
       <c r="E6" t="n">
+        <v>2912</v>
+      </c>
+      <c r="F6" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-21.58</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-18.98</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>2911.91</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3107.06</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>55</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>押し目、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
         <v>2902</v>
       </c>
-      <c r="F6" t="n">
-        <v>41</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-22.75</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-18.33</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="X6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>37856</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>37099</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>757</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8113</v>
+      </c>
+      <c r="F7" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-132.55</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-118.07</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>2909.48</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3107.56</v>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="M7" t="n">
+        <v>7869.71</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8414.389999999999</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>55</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>押し目、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>7851</v>
+      </c>
+      <c r="X7" t="n">
+        <v>262</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>8113</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7993</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>三菱商事</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4795</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4582</v>
+      </c>
+      <c r="F8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-4.62</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-43.66</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-16.29</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>4667.02</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4686.72</v>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>🔴 下降</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>🔴 売り注意</t>
         </is>
       </c>
-      <c r="Q6" t="n">
-        <v>10</v>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="Q8" t="n">
+        <v>15</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、下降トレンド</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>2900.5</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>37726</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>627</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E7" t="n">
-        <v>7851</v>
-      </c>
-      <c r="F7" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-4.74</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-157.13</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-114.45</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>7855.88</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8429.73</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>🔴 売り注意</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>10</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、下降トレンド</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
-        <v>7775</v>
-      </c>
-      <c r="X7" t="n">
-        <v>76</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>7851</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>7993</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-142</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>8058.T</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>三菱商事</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4795</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4590</v>
-      </c>
-      <c r="F8" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-35.27</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-9.449999999999999</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-2S</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>4665.68</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4682</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>🔴 売り注意</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>20</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、-2σ、MACD売り、下降トレンド</t>
+          <t>押し目、-1σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>4676</v>
+        <v>4590</v>
       </c>
       <c r="X8" t="n">
-        <v>-86</v>
+        <v>-8</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.84</v>
+        <v>-0.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>22950</v>
+        <v>22910</v>
       </c>
       <c r="AA8" t="n">
         <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1025</v>
+        <v>-1065</v>
       </c>
       <c r="AC8" t="n">
-        <v>-4.28</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="9">
@@ -1369,22 +1372,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>17900</v>
+        <v>17220</v>
       </c>
       <c r="F9" t="n">
-        <v>55.1</v>
+        <v>52.2</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.25</v>
+        <v>-5.05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.08</v>
+        <v>0.57</v>
       </c>
       <c r="I9" t="n">
-        <v>98.84999999999999</v>
+        <v>5.62</v>
       </c>
       <c r="J9" t="n">
-        <v>67</v>
+        <v>54.72</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1393,14 +1396,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>20394.04</v>
+        <v>20140.98</v>
       </c>
       <c r="N9" t="n">
-        <v>14249.21</v>
+        <v>14319.29</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1409,29 +1412,29 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
-・MACDは買いシグナルです。
+・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -1439,29 +1442,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD買い、反発局面</t>
+          <t>RSI適正、押し目、-1σ、MACD売り、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>17900</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-680</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-3.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>17900</v>
+        <v>17220</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-37610</v>
+        <v>-38290</v>
       </c>
       <c r="AC9" t="n">
-        <v>-67.75</v>
+        <v>-68.98</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>4070</v>
+        <v>4125</v>
       </c>
       <c r="F2" t="n">
-        <v>83.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="G2" t="n">
-        <v>17.21</v>
+        <v>18.72</v>
       </c>
       <c r="H2" t="n">
-        <v>1.07</v>
+        <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>132.91</v>
+        <v>137.29</v>
       </c>
       <c r="J2" t="n">
-        <v>65.2</v>
+        <v>66.08</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3224.45</v>
+        <v>3225.19</v>
       </c>
       <c r="N2" t="n">
-        <v>2769.45</v>
+        <v>2769.72</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -649,7 +649,11 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>RSI過熱、上昇加速、+2σ、MACD買い、長期上昇</t>
@@ -659,22 +663,22 @@
         <v>3890</v>
       </c>
       <c r="X2" t="n">
-        <v>180</v>
+        <v>235</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.63</v>
+        <v>6.04</v>
       </c>
       <c r="Z2" t="n">
-        <v>16280</v>
+        <v>16500</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>5480</v>
+        <v>5700</v>
       </c>
       <c r="AC2" t="n">
-        <v>50.74</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="3">
@@ -695,22 +699,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F3" t="n">
-        <v>58.8</v>
+        <v>57.8</v>
       </c>
       <c r="G3" t="n">
-        <v>4.13</v>
+        <v>3.72</v>
       </c>
       <c r="H3" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="I3" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="J3" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>446.51</v>
+        <v>446.48</v>
       </c>
       <c r="N3" t="n">
-        <v>420.95</v>
+        <v>420.94</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -773,58 +777,58 @@
         <v>479</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.51</v>
+        <v>2.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>49100</v>
+        <v>48900</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7100</v>
+        <v>6900</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.9</v>
+        <v>16.43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9432.T</t>
+          <t>6976.T</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NTT</t>
+          <t>太陽誘電</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>158</v>
+        <v>10000</v>
       </c>
       <c r="E4" t="n">
-        <v>173.3</v>
+        <v>11135</v>
       </c>
       <c r="F4" t="n">
-        <v>46.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.78</v>
+        <v>16.22</v>
       </c>
       <c r="H4" t="n">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="I4" t="n">
-        <v>1.55</v>
+        <v>354.95</v>
       </c>
       <c r="J4" t="n">
-        <v>2.13</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -833,18 +837,18 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>158.85</v>
+        <v>11589.09</v>
       </c>
       <c r="N4" t="n">
-        <v>153.25</v>
+        <v>8337.969999999999</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>🟢 強い上昇</t>
+          <t>🟡 反発中</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -866,6 +870,119 @@
         </is>
       </c>
       <c r="T4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・25日線から大きく上に乖離しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>RSIやや過熱、上昇加速、+1σ、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>10955</v>
+      </c>
+      <c r="X4" t="n">
+        <v>180</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>11135</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1135</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>11.35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>158</v>
+      </c>
+      <c r="E5" t="n">
+        <v>172.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>158.84</v>
+      </c>
+      <c r="N5" t="n">
+        <v>153.25</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>75</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -876,145 +993,32 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>25日線上、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>172.1</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>17330</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>15800</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1530</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9.68</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>10850</v>
-      </c>
-      <c r="F5" t="n">
-        <v>67</v>
-      </c>
-      <c r="G5" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="I5" t="n">
-        <v>332.22</v>
-      </c>
-      <c r="J5" t="n">
-        <v>71.05</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>11585.29</v>
-      </c>
-      <c r="N5" t="n">
-        <v>8336.540000000001</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>75</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・25日線から大きく上に乖離しています。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>RSIやや過熱、上昇加速、+1σ、MACD買い、反発局面</t>
+          <t>25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>10955</v>
+        <v>172.1</v>
       </c>
       <c r="X5" t="n">
-        <v>-105</v>
+        <v>0.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.96</v>
+        <v>0.46</v>
       </c>
       <c r="Z5" t="n">
-        <v>10850</v>
+        <v>17290</v>
       </c>
       <c r="AA5" t="n">
-        <v>10000</v>
+        <v>15800</v>
       </c>
       <c r="AB5" t="n">
-        <v>850</v>
+        <v>1490</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.5</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="6">
@@ -1035,22 +1039,22 @@
         <v>2853.77</v>
       </c>
       <c r="E6" t="n">
-        <v>2912</v>
+        <v>2910.5</v>
       </c>
       <c r="F6" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.31</v>
+        <v>-1.36</v>
       </c>
       <c r="H6" t="n">
-        <v>0.44</v>
+        <v>0.85</v>
       </c>
       <c r="I6" t="n">
-        <v>-21.58</v>
+        <v>-21.7</v>
       </c>
       <c r="J6" t="n">
-        <v>-18.98</v>
+        <v>-19</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1063,70 +1067,70 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2911.91</v>
+        <v>2911.89</v>
       </c>
       <c r="N6" t="n">
-        <v>3107.06</v>
+        <v>3107.05</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>🟢 上昇</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🔴 売り注意</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟢 上昇
+・🔴 下降
 ・MACDは売りシグナルです。
 ・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、上昇トレンド</t>
+          <t>押し目、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>2902</v>
       </c>
       <c r="X6" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>37856</v>
+        <v>37836</v>
       </c>
       <c r="AA6" t="n">
         <v>37099</v>
       </c>
       <c r="AB6" t="n">
-        <v>757</v>
+        <v>738</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="7">
@@ -1147,22 +1151,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>8113</v>
+        <v>8146</v>
       </c>
       <c r="F7" t="n">
-        <v>49.6</v>
+        <v>50.6</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.08</v>
+        <v>-0.7</v>
       </c>
       <c r="H7" t="n">
-        <v>0.97</v>
+        <v>1.47</v>
       </c>
       <c r="I7" t="n">
-        <v>-132.55</v>
+        <v>-129.92</v>
       </c>
       <c r="J7" t="n">
-        <v>-118.07</v>
+        <v>-117.54</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1175,10 +1179,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7869.71</v>
+        <v>7870.15</v>
       </c>
       <c r="N7" t="n">
-        <v>8414.389999999999</v>
+        <v>8414.549999999999</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1187,20 +1191,20 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1217,29 +1221,29 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、上昇トレンド</t>
+          <t>RSI適正、押し目、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>7851</v>
       </c>
       <c r="X7" t="n">
-        <v>262</v>
+        <v>295</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.34</v>
+        <v>3.76</v>
       </c>
       <c r="Z7" t="n">
-        <v>8113</v>
+        <v>8146</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="8">
@@ -1260,22 +1264,22 @@
         <v>4795</v>
       </c>
       <c r="E8" t="n">
-        <v>4582</v>
+        <v>4596</v>
       </c>
       <c r="F8" t="n">
-        <v>30.5</v>
+        <v>31.3</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.62</v>
+        <v>-4.34</v>
       </c>
       <c r="H8" t="n">
-        <v>0.55</v>
+        <v>1.03</v>
       </c>
       <c r="I8" t="n">
-        <v>-43.66</v>
+        <v>-42.54</v>
       </c>
       <c r="J8" t="n">
-        <v>-16.29</v>
+        <v>-16.06</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1288,10 +1292,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4667.02</v>
+        <v>4667.21</v>
       </c>
       <c r="N8" t="n">
-        <v>4686.72</v>
+        <v>4686.79</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1336,22 +1340,22 @@
         <v>4590</v>
       </c>
       <c r="X8" t="n">
-        <v>-8</v>
+        <v>6</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.17</v>
+        <v>0.13</v>
       </c>
       <c r="Z8" t="n">
-        <v>22910</v>
+        <v>22980</v>
       </c>
       <c r="AA8" t="n">
         <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1065</v>
+        <v>-995</v>
       </c>
       <c r="AC8" t="n">
-        <v>-4.44</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="9">
@@ -1372,22 +1376,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>17220</v>
+        <v>17505</v>
       </c>
       <c r="F9" t="n">
-        <v>52.2</v>
+        <v>54.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.05</v>
+        <v>-3.54</v>
       </c>
       <c r="H9" t="n">
-        <v>0.57</v>
+        <v>0.97</v>
       </c>
       <c r="I9" t="n">
-        <v>5.62</v>
+        <v>28.35</v>
       </c>
       <c r="J9" t="n">
-        <v>54.72</v>
+        <v>59.27</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1396,14 +1400,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>20140.98</v>
+        <v>20144.78</v>
       </c>
       <c r="N9" t="n">
-        <v>14319.29</v>
+        <v>14320.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1416,7 +1420,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1434,7 +1438,7 @@
 ・🟡 反発中
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
@@ -1442,29 +1446,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、-1σ、MACD売り、反発局面</t>
+          <t>RSI適正、押し目、MACD売り、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>17900</v>
       </c>
       <c r="X9" t="n">
-        <v>-680</v>
+        <v>-395</v>
       </c>
       <c r="Y9" t="n">
-        <v>-3.8</v>
+        <v>-2.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>17220</v>
+        <v>17505</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-38290</v>
+        <v>-38005</v>
       </c>
       <c r="AC9" t="n">
-        <v>-68.98</v>
+        <v>-68.47</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1489,22 +1489,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>42.77</v>
+        <v>41.86</v>
       </c>
       <c r="F10" t="n">
-        <v>63.4</v>
+        <v>52.6</v>
       </c>
       <c r="G10" t="n">
-        <v>5.28</v>
+        <v>2.64</v>
       </c>
       <c r="H10" t="n">
-        <v>1.11</v>
+        <v>0.87</v>
       </c>
       <c r="I10" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="J10" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>34.5</v>
+        <v>34.63</v>
       </c>
       <c r="N10" t="n">
-        <v>32.26</v>
+        <v>32.32</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1549,7 +1549,8 @@
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは買いシグナルです。
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -1558,29 +1559,29 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>44.94</v>
+        <v>42.77</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.17</v>
+        <v>-0.91</v>
       </c>
       <c r="Y10" t="n">
-        <v>-4.83</v>
+        <v>-2.13</v>
       </c>
       <c r="Z10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6070</v>
+        <v>-6071</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.3</v>
+        <v>-99.31999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1489,22 +1489,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>41.86</v>
+        <v>39.98</v>
       </c>
       <c r="F10" t="n">
-        <v>52.6</v>
+        <v>44.4</v>
       </c>
       <c r="G10" t="n">
-        <v>2.64</v>
+        <v>-2.01</v>
       </c>
       <c r="H10" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="I10" t="n">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="J10" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>34.63</v>
+        <v>34.74</v>
       </c>
       <c r="N10" t="n">
-        <v>32.32</v>
+        <v>32.37</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1529,20 +1529,20 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1550,7 +1550,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -1559,29 +1558,29 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>42.77</v>
+        <v>41.86</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.91</v>
+        <v>-1.88</v>
       </c>
       <c r="Y10" t="n">
-        <v>-2.13</v>
+        <v>-4.49</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6071</v>
+        <v>-6073</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.31999999999999</v>
+        <v>-99.34999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>4125</v>
+        <v>4030</v>
       </c>
       <c r="F2" t="n">
-        <v>84.7</v>
+        <v>75.8</v>
       </c>
       <c r="G2" t="n">
-        <v>18.72</v>
+        <v>15.28</v>
       </c>
       <c r="H2" t="n">
-        <v>1.48</v>
+        <v>0.5</v>
       </c>
       <c r="I2" t="n">
-        <v>137.29</v>
+        <v>156.54</v>
       </c>
       <c r="J2" t="n">
-        <v>66.08</v>
+        <v>84.17</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3225.19</v>
+        <v>3244.84</v>
       </c>
       <c r="N2" t="n">
-        <v>2769.72</v>
+        <v>2775.9</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -649,36 +649,32 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>RSI過熱、上昇加速、+2σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3890</v>
+        <v>4125</v>
       </c>
       <c r="X2" t="n">
-        <v>235</v>
+        <v>-95</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.04</v>
+        <v>-2.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>16500</v>
+        <v>16120</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>5700</v>
+        <v>5320</v>
       </c>
       <c r="AC2" t="n">
-        <v>52.78</v>
+        <v>49.26</v>
       </c>
     </row>
     <row r="3">
@@ -699,26 +695,26 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="F3" t="n">
-        <v>57.8</v>
+        <v>52.7</v>
       </c>
       <c r="G3" t="n">
-        <v>3.72</v>
+        <v>4.38</v>
       </c>
       <c r="H3" t="n">
-        <v>1.44</v>
+        <v>0.68</v>
       </c>
       <c r="I3" t="n">
-        <v>3.58</v>
+        <v>4.79</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>446.48</v>
+        <v>448.05</v>
       </c>
       <c r="N3" t="n">
-        <v>420.94</v>
+        <v>421.63</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -756,192 +752,191 @@
         </is>
       </c>
       <c r="T3" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>489</v>
+      </c>
+      <c r="X3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>49300</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>7300</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>17.38</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>173.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>159.26</v>
+      </c>
+      <c r="N4" t="n">
+        <v>153.36</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>90</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、ゴールデンクロス、+1σ、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>479</v>
-      </c>
-      <c r="X3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>48900</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>42000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>6900</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>16.43</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>11135</v>
-      </c>
-      <c r="F4" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="G4" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I4" t="n">
-        <v>354.95</v>
-      </c>
-      <c r="J4" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>11589.09</v>
-      </c>
-      <c r="N4" t="n">
-        <v>8337.969999999999</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>75</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・25日線から大きく上に乖離しています。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSIやや過熱、上昇加速、+1σ、MACD買い、反発局面</t>
+          <t>25日線上、ゴールデンクロス、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>10955</v>
+        <v>172.9</v>
       </c>
       <c r="X4" t="n">
-        <v>180</v>
+        <v>0.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.64</v>
+        <v>0.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>11135</v>
+        <v>17320</v>
       </c>
       <c r="AA4" t="n">
-        <v>10000</v>
+        <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1135</v>
+        <v>1520</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.35</v>
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9432.T</t>
+          <t>7203.T</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT</t>
+          <t>トヨタ自動車</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>158</v>
+        <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>172.9</v>
+        <v>2968</v>
       </c>
       <c r="F5" t="n">
-        <v>45.5</v>
+        <v>48.2</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="H5" t="n">
-        <v>0.95</v>
+        <v>0.64</v>
       </c>
       <c r="I5" t="n">
-        <v>1.52</v>
+        <v>-16.05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.12</v>
+        <v>-18.41</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -954,14 +949,14 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>158.84</v>
+        <v>2915.52</v>
       </c>
       <c r="N5" t="n">
-        <v>153.25</v>
+        <v>3106.1</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>🟢 強い上昇</t>
+          <t>🟢 上昇</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -970,280 +965,283 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>25日線上、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>172.1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>17290</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>15800</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1490</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>9.43</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>トヨタ自動車</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>13</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2853.77</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2910.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-1.36</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-21.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-19</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>2911.89</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3107.05</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>🔴 売り注意</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>10</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、下降トレンド</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>2902</v>
-      </c>
-      <c r="X6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>37836</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>738</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.99</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8146</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-129.92</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-117.54</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>7870.15</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8414.549999999999</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>75</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
-・MACDは売りシグナルです。
+・MACDは買いシグナルです。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>25日線上、MACD買い、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>2910.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>38584</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>37099</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1485</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8125</v>
+      </c>
+      <c r="F6" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-108.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-115.79</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>7885.15</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8397.65</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>75</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは買いシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>押し目、MACD買い、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>8146</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-21</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8125</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>132</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10115</v>
+      </c>
+      <c r="F7" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I7" t="n">
+        <v>309.79</v>
+      </c>
+      <c r="J7" t="n">
+        <v>122.44</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>11491.11</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8370.639999999999</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>95</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、上昇トレンド</t>
+          <t>RSI適正、25日線上、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>7851</v>
+        <v>11135</v>
       </c>
       <c r="X7" t="n">
-        <v>295</v>
+        <v>-1020</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.76</v>
+        <v>-9.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>8146</v>
+        <v>10115</v>
       </c>
       <c r="AA7" t="n">
-        <v>7993</v>
+        <v>10000</v>
       </c>
       <c r="AB7" t="n">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="8">
@@ -1264,22 +1262,22 @@
         <v>4795</v>
       </c>
       <c r="E8" t="n">
-        <v>4596</v>
+        <v>4633</v>
       </c>
       <c r="F8" t="n">
-        <v>31.3</v>
+        <v>31.6</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.34</v>
+        <v>-3.44</v>
       </c>
       <c r="H8" t="n">
-        <v>1.03</v>
+        <v>0.49</v>
       </c>
       <c r="I8" t="n">
-        <v>-42.54</v>
+        <v>-44.79</v>
       </c>
       <c r="J8" t="n">
-        <v>-16.06</v>
+        <v>-21.81</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1292,10 +1290,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4667.21</v>
+        <v>4668.32</v>
       </c>
       <c r="N8" t="n">
-        <v>4686.79</v>
+        <v>4691.56</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1337,25 +1335,25 @@
         </is>
       </c>
       <c r="W8" t="n">
-        <v>4590</v>
+        <v>4596</v>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.13</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>22980</v>
+        <v>23165</v>
       </c>
       <c r="AA8" t="n">
         <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-995</v>
+        <v>-810</v>
       </c>
       <c r="AC8" t="n">
-        <v>-4.15</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="9">
@@ -1376,38 +1374,38 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>17505</v>
+        <v>15330</v>
       </c>
       <c r="F9" t="n">
-        <v>54.5</v>
+        <v>42.2</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.54</v>
+        <v>-15.21</v>
       </c>
       <c r="H9" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="I9" t="n">
-        <v>28.35</v>
+        <v>-200.7</v>
       </c>
       <c r="J9" t="n">
-        <v>59.27</v>
+        <v>7.27</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-2S</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>20144.78</v>
+        <v>19866.07</v>
       </c>
       <c r="N9" t="n">
-        <v>14320.72</v>
+        <v>14380.88</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1416,20 +1414,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🔴 売り注意</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1437,38 +1435,43 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・25日線から大きく下に乖離しています。
+・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、反発局面</t>
+          <t>25日線大幅割れ、デッドクロス、-2σ、MACD売り、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>17900</v>
+        <v>17505</v>
       </c>
       <c r="X9" t="n">
-        <v>-395</v>
+        <v>-2175</v>
       </c>
       <c r="Y9" t="n">
-        <v>-2.21</v>
+        <v>-12.43</v>
       </c>
       <c r="Z9" t="n">
-        <v>17505</v>
+        <v>15330</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-38005</v>
+        <v>-40180</v>
       </c>
       <c r="AC9" t="n">
-        <v>-68.47</v>
+        <v>-72.38</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>4030</v>
+        <v>3905</v>
       </c>
       <c r="F2" t="n">
-        <v>75.8</v>
+        <v>68.3</v>
       </c>
       <c r="G2" t="n">
-        <v>15.28</v>
+        <v>11.87</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="I2" t="n">
-        <v>156.54</v>
+        <v>146.57</v>
       </c>
       <c r="J2" t="n">
-        <v>84.17</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -605,14 +605,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+2S</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3244.84</v>
+        <v>3243.17</v>
       </c>
       <c r="N2" t="n">
-        <v>2775.9</v>
+        <v>2775.27</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,20 +621,20 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -642,39 +642,42 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・買われ過ぎ水準です。
 ・25日線から大きく上に乖離しています。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>RSI過熱、上昇加速、+2σ、MACD買い、長期上昇</t>
+          <t>RSIやや過熱、上昇加速、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
         <v>4125</v>
       </c>
       <c r="X2" t="n">
-        <v>-95</v>
+        <v>-220</v>
       </c>
       <c r="Y2" t="n">
-        <v>-2.3</v>
+        <v>-5.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>16120</v>
+        <v>15620</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>5320</v>
+        <v>4820</v>
       </c>
       <c r="AC2" t="n">
-        <v>49.26</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="3">
@@ -695,22 +698,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F3" t="n">
-        <v>52.7</v>
+        <v>55.1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.38</v>
+        <v>5.19</v>
       </c>
       <c r="H3" t="n">
-        <v>0.68</v>
+        <v>1.02</v>
       </c>
       <c r="I3" t="n">
-        <v>4.79</v>
+        <v>5.11</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>448.05</v>
+        <v>448.1</v>
       </c>
       <c r="N3" t="n">
-        <v>421.63</v>
+        <v>421.65</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -772,22 +775,22 @@
         <v>489</v>
       </c>
       <c r="X3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.82</v>
+        <v>1.64</v>
       </c>
       <c r="Z3" t="n">
-        <v>49300</v>
+        <v>49700</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7300</v>
+        <v>7700</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.38</v>
+        <v>18.33</v>
       </c>
     </row>
     <row r="4">
@@ -808,22 +811,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>173.2</v>
+        <v>173.3</v>
       </c>
       <c r="F4" t="n">
-        <v>35.2</v>
+        <v>35.7</v>
       </c>
       <c r="G4" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="H4" t="n">
-        <v>0.75</v>
+        <v>1.34</v>
       </c>
       <c r="I4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -885,58 +888,58 @@
         <v>172.9</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>17320</v>
+        <v>17330</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1520</v>
+        <v>1530</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.619999999999999</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7203.T</t>
+          <t>6976.T</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>トヨタ自動車</t>
+          <t>太陽誘電</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2853.77</v>
+        <v>10000</v>
       </c>
       <c r="E5" t="n">
-        <v>2968</v>
+        <v>10590</v>
       </c>
       <c r="F5" t="n">
-        <v>48.2</v>
+        <v>67.2</v>
       </c>
       <c r="G5" t="n">
-        <v>0.74</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-16.05</v>
+        <v>347.68</v>
       </c>
       <c r="J5" t="n">
-        <v>-18.41</v>
+        <v>130.02</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -945,18 +948,18 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2915.52</v>
+        <v>11497.45</v>
       </c>
       <c r="N5" t="n">
-        <v>3106.1</v>
+        <v>8373.02</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>🟢 上昇</t>
+          <t>🟡 反発中</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -978,6 +981,118 @@
         </is>
       </c>
       <c r="T5" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>RSIやや過熱、25日線上、+1σ、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>11135</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-545</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-4.89</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>10590</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>590</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>トヨタ自動車</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2853.77</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2984</v>
+      </c>
+      <c r="F6" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-14.77</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-18.16</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>2915.73</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3106.18</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>100</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -988,109 +1103,109 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>25日線上、MACD買い、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、MACD買い、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
         <v>2910.5</v>
       </c>
-      <c r="X5" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>38584</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="X6" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>38792</v>
+      </c>
+      <c r="AA6" t="n">
         <v>37099</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1485</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4</v>
+      <c r="AB6" t="n">
+        <v>1693</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.56</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>7974.T</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>任天堂</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>7993</v>
       </c>
-      <c r="E6" t="n">
-        <v>8125</v>
-      </c>
-      <c r="F6" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-108.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-115.79</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="E7" t="n">
+        <v>8172</v>
+      </c>
+      <c r="F7" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-105.05</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-115.04</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>7885.15</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8397.65</v>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="M7" t="n">
+        <v>7885.77</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8397.889999999999</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>🟢 上昇</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>🟡 買い</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q7" t="n">
         <v>75</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -1100,148 +1215,32 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
         <is>
           <t>押し目、MACD買い、上昇トレンド</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="W7" t="n">
         <v>8146</v>
       </c>
-      <c r="X6" t="n">
-        <v>-21</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>8125</v>
-      </c>
-      <c r="AA6" t="n">
+      <c r="X7" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>8172</v>
+      </c>
+      <c r="AA7" t="n">
         <v>7993</v>
       </c>
-      <c r="AB6" t="n">
-        <v>132</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E7" t="n">
-        <v>10115</v>
-      </c>
-      <c r="F7" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I7" t="n">
-        <v>309.79</v>
-      </c>
-      <c r="J7" t="n">
-        <v>122.44</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>11491.11</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8370.639999999999</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>🟢 強い買い</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>95</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
-        <v>11135</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1020</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-9.16</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>10115</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>10000</v>
-      </c>
       <c r="AB7" t="n">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.15</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="8">
@@ -1262,22 +1261,22 @@
         <v>4795</v>
       </c>
       <c r="E8" t="n">
-        <v>4633</v>
+        <v>4700</v>
       </c>
       <c r="F8" t="n">
-        <v>31.6</v>
+        <v>37.1</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.44</v>
+        <v>-2.1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.49</v>
+        <v>1.07</v>
       </c>
       <c r="I8" t="n">
-        <v>-44.79</v>
+        <v>-39.45</v>
       </c>
       <c r="J8" t="n">
-        <v>-21.81</v>
+        <v>-20.74</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1286,74 +1285,74 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4668.32</v>
+        <v>4669.21</v>
       </c>
       <c r="N8" t="n">
-        <v>4691.56</v>
+        <v>4691.89</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>🔴 下降</t>
+          <t>🟢 上昇</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🔴 売り注意</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🔴 下降
+・🟢 上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、下降トレンド</t>
+          <t>押し目、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>4596</v>
       </c>
       <c r="X8" t="n">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>23165</v>
+        <v>23500</v>
       </c>
       <c r="AA8" t="n">
         <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-810</v>
+        <v>-475</v>
       </c>
       <c r="AC8" t="n">
-        <v>-3.38</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="9">
@@ -1374,22 +1373,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>15330</v>
+        <v>15180</v>
       </c>
       <c r="F9" t="n">
-        <v>42.2</v>
+        <v>41.4</v>
       </c>
       <c r="G9" t="n">
-        <v>-15.21</v>
+        <v>-16.02</v>
       </c>
       <c r="H9" t="n">
-        <v>0.98</v>
+        <v>1.53</v>
       </c>
       <c r="I9" t="n">
-        <v>-200.7</v>
+        <v>-212.67</v>
       </c>
       <c r="J9" t="n">
-        <v>7.27</v>
+        <v>4.88</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1402,10 +1401,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>19866.07</v>
+        <v>19864.07</v>
       </c>
       <c r="N9" t="n">
-        <v>14380.88</v>
+        <v>14380.13</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1418,11 +1417,11 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1437,6 +1436,7 @@
 ・MACDは売りシグナルです。
 ・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・25日線から大きく下に乖離しています。
+・出来高が増加しています。
 ・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
@@ -1449,29 +1449,29 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25日線大幅割れ、デッドクロス、-2σ、MACD売り、反発局面</t>
+          <t>25日線大幅割れ、出来高微増、デッドクロス、-2σ、MACD売り、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>17505</v>
       </c>
       <c r="X9" t="n">
-        <v>-2175</v>
+        <v>-2325</v>
       </c>
       <c r="Y9" t="n">
-        <v>-12.43</v>
+        <v>-13.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>15330</v>
+        <v>15180</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-40180</v>
+        <v>-40330</v>
       </c>
       <c r="AC9" t="n">
-        <v>-72.38</v>
+        <v>-72.65000000000001</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1492,22 +1492,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>39.98</v>
+        <v>39.07</v>
       </c>
       <c r="F10" t="n">
-        <v>44.4</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.01</v>
+        <v>-4.13</v>
       </c>
       <c r="H10" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="I10" t="n">
-        <v>1.25</v>
+        <v>0.93</v>
       </c>
       <c r="J10" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>34.74</v>
+        <v>34.85</v>
       </c>
       <c r="N10" t="n">
-        <v>32.37</v>
+        <v>32.41</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1565,25 +1565,25 @@
         </is>
       </c>
       <c r="W10" t="n">
-        <v>41.86</v>
+        <v>39.98</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.88</v>
+        <v>-0.91</v>
       </c>
       <c r="Y10" t="n">
-        <v>-4.49</v>
+        <v>-2.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6073</v>
+        <v>-6074</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.34999999999999</v>
+        <v>-99.36</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3905</v>
+        <v>3915</v>
       </c>
       <c r="F2" t="n">
-        <v>68.3</v>
+        <v>74.7</v>
       </c>
       <c r="G2" t="n">
-        <v>11.87</v>
+        <v>11.56</v>
       </c>
       <c r="H2" t="n">
-        <v>0.92</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>146.57</v>
+        <v>152.97</v>
       </c>
       <c r="J2" t="n">
-        <v>82.18000000000001</v>
+        <v>96.34</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3243.17</v>
+        <v>3261.71</v>
       </c>
       <c r="N2" t="n">
-        <v>2775.27</v>
+        <v>2779.07</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -642,42 +642,39 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
+・買われ過ぎ水準です。
 ・25日線から大きく上に乖離しています。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>RSIやや過熱、上昇加速、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>4125</v>
+        <v>3905</v>
       </c>
       <c r="X2" t="n">
-        <v>-220</v>
+        <v>10</v>
       </c>
       <c r="Y2" t="n">
-        <v>-5.33</v>
+        <v>0.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>15620</v>
+        <v>15660</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4820</v>
+        <v>4860</v>
       </c>
       <c r="AC2" t="n">
-        <v>44.63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -698,22 +695,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F3" t="n">
-        <v>55.1</v>
+        <v>53.2</v>
       </c>
       <c r="G3" t="n">
-        <v>5.19</v>
+        <v>4.65</v>
       </c>
       <c r="H3" t="n">
-        <v>1.02</v>
+        <v>0.55</v>
       </c>
       <c r="I3" t="n">
-        <v>5.11</v>
+        <v>6.17</v>
       </c>
       <c r="J3" t="n">
-        <v>4.06</v>
+        <v>4.48</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>448.1</v>
+        <v>449.83</v>
       </c>
       <c r="N3" t="n">
-        <v>421.65</v>
+        <v>422.32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -772,250 +769,255 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.64</v>
+        <v>-0.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>49700</v>
+        <v>49600</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7700</v>
+        <v>7600</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.33</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11410</v>
+      </c>
+      <c r="F4" t="n">
+        <v>70</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I4" t="n">
+        <v>403.44</v>
+      </c>
+      <c r="J4" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>11424.96</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8412.75</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>75</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・買われ過ぎ水準です。
+・25日線から大きく上に乖離しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>RSIやや過熱、上昇加速、+1σ、MACD買い、反発局面</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>10590</v>
+      </c>
+      <c r="X4" t="n">
+        <v>820</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>11410</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1410</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>9432.T</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>NTT</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C5" t="n">
         <v>100</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>158</v>
       </c>
-      <c r="E4" t="n">
-        <v>173.3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="E5" t="n">
+        <v>172.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>159.26</v>
-      </c>
-      <c r="N4" t="n">
-        <v>153.36</v>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="M5" t="n">
+        <v>159.67</v>
+      </c>
+      <c r="N5" t="n">
+        <v>153.47</v>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>🟢 強い上昇</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>🟢 強い買い</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>90</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>75</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>25日線上、ゴールデンクロス、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>172.9</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>17330</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>15800</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1530</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9.68</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>6976.T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>太陽誘電</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>10590</v>
-      </c>
-      <c r="F5" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>347.68</v>
-      </c>
-      <c r="J5" t="n">
-        <v>130.02</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>11497.45</v>
-      </c>
-      <c r="N5" t="n">
-        <v>8373.02</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>85</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD買い、反発局面</t>
+          <t>25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>11135</v>
+        <v>173.3</v>
       </c>
       <c r="X5" t="n">
-        <v>-545</v>
+        <v>-1.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>-4.89</v>
+        <v>-0.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>10590</v>
+        <v>17220</v>
       </c>
       <c r="AA5" t="n">
-        <v>10000</v>
+        <v>15800</v>
       </c>
       <c r="AB5" t="n">
-        <v>590</v>
+        <v>1420</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.9</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="6">
@@ -1036,22 +1038,22 @@
         <v>2853.77</v>
       </c>
       <c r="E6" t="n">
-        <v>2984</v>
+        <v>2995</v>
       </c>
       <c r="F6" t="n">
-        <v>50.1</v>
+        <v>52.3</v>
       </c>
       <c r="G6" t="n">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="H6" t="n">
-        <v>1.19</v>
+        <v>0.37</v>
       </c>
       <c r="I6" t="n">
-        <v>-14.77</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-18.16</v>
+        <v>-16.19</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1060,14 +1062,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2915.73</v>
+        <v>2920.19</v>
       </c>
       <c r="N6" t="n">
-        <v>3106.18</v>
+        <v>3104.92</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1093,6 +1095,119 @@
         </is>
       </c>
       <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、+1σ、MACD買い、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>2984</v>
+      </c>
+      <c r="X6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>38935</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>37099</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1836</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8268</v>
+      </c>
+      <c r="F7" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-76.70999999999999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-107.38</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>7903.79</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8382.860000000001</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>85</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -1103,144 +1218,32 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、MACD買い、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>2910.5</v>
-      </c>
-      <c r="X6" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>38792</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1693</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.56</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8172</v>
-      </c>
-      <c r="F7" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-105.05</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-115.04</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>7885.77</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8397.889999999999</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>75</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、MACD買い、上昇トレンド</t>
+          <t>25日線上、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>8146</v>
+        <v>8172</v>
       </c>
       <c r="X7" t="n">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.32</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>8172</v>
+        <v>8268</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.24</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="8">
@@ -1261,22 +1264,22 @@
         <v>4795</v>
       </c>
       <c r="E8" t="n">
-        <v>4700</v>
+        <v>4705</v>
       </c>
       <c r="F8" t="n">
-        <v>37.1</v>
+        <v>38.9</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1</v>
+        <v>-1.76</v>
       </c>
       <c r="H8" t="n">
-        <v>1.07</v>
+        <v>0.32</v>
       </c>
       <c r="I8" t="n">
-        <v>-39.45</v>
+        <v>-36.18</v>
       </c>
       <c r="J8" t="n">
-        <v>-20.74</v>
+        <v>-23.83</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1289,10 +1292,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4669.21</v>
+        <v>4671.52</v>
       </c>
       <c r="N8" t="n">
-        <v>4691.89</v>
+        <v>4696.94</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1334,25 +1337,25 @@
         </is>
       </c>
       <c r="W8" t="n">
-        <v>4596</v>
+        <v>4700</v>
       </c>
       <c r="X8" t="n">
-        <v>104</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.26</v>
+        <v>0.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>23500</v>
+        <v>23525</v>
       </c>
       <c r="AA8" t="n">
         <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-475</v>
+        <v>-450</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.98</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="9">
@@ -1373,26 +1376,26 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>15180</v>
+        <v>14910</v>
       </c>
       <c r="F9" t="n">
-        <v>41.4</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>-16.02</v>
+        <v>-17.08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.53</v>
+        <v>0.71</v>
       </c>
       <c r="I9" t="n">
-        <v>-212.67</v>
+        <v>-420.62</v>
       </c>
       <c r="J9" t="n">
-        <v>4.88</v>
+        <v>-80.22</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1401,10 +1404,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>19864.07</v>
+        <v>19652.69</v>
       </c>
       <c r="N9" t="n">
-        <v>14380.13</v>
+        <v>14439.35</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1413,20 +1416,20 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🔴 売り注意</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1434,44 +1437,39 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
+・売られ過ぎ水準です。
 ・25日線から大きく下に乖離しています。
-・出来高が増加しています。
 ・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25日線大幅割れ、出来高微増、デッドクロス、-2σ、MACD売り、反発局面</t>
+          <t>RSI売られすぎ、25日線大幅割れ、-2σ、MACD売り、反発局面</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>17505</v>
+        <v>15180</v>
       </c>
       <c r="X9" t="n">
-        <v>-2325</v>
+        <v>-270</v>
       </c>
       <c r="Y9" t="n">
-        <v>-13.28</v>
+        <v>-1.78</v>
       </c>
       <c r="Z9" t="n">
-        <v>15180</v>
+        <v>14910</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-40330</v>
+        <v>-40600</v>
       </c>
       <c r="AC9" t="n">
-        <v>-72.65000000000001</v>
+        <v>-73.14</v>
       </c>
     </row>
     <row r="10">
@@ -1501,7 +1499,7 @@
         <v>-4.13</v>
       </c>
       <c r="H10" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="n">
         <v>0.93</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3915</v>
+        <v>3925</v>
       </c>
       <c r="F2" t="n">
-        <v>74.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>11.56</v>
+        <v>11.83</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="I2" t="n">
-        <v>152.97</v>
+        <v>153.76</v>
       </c>
       <c r="J2" t="n">
-        <v>96.34</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3261.71</v>
+        <v>3261.84</v>
       </c>
       <c r="N2" t="n">
-        <v>2779.07</v>
+        <v>2779.12</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -659,22 +659,22 @@
         <v>3905</v>
       </c>
       <c r="X2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.26</v>
+        <v>0.51</v>
       </c>
       <c r="Z2" t="n">
-        <v>15660</v>
+        <v>15700</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4860</v>
+        <v>4900</v>
       </c>
       <c r="AC2" t="n">
-        <v>45</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="3">
@@ -695,22 +695,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="F3" t="n">
-        <v>53.2</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>4.65</v>
+        <v>3.64</v>
       </c>
       <c r="H3" t="n">
-        <v>0.55</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>6.17</v>
+        <v>5.77</v>
       </c>
       <c r="J3" t="n">
-        <v>4.48</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>449.83</v>
+        <v>449.76</v>
       </c>
       <c r="N3" t="n">
-        <v>422.32</v>
+        <v>422.29</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -772,22 +772,22 @@
         <v>497</v>
       </c>
       <c r="X3" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.2</v>
+        <v>-1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>49600</v>
+        <v>49100</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7600</v>
+        <v>7100</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.1</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="4">
@@ -808,22 +808,22 @@
         <v>10000</v>
       </c>
       <c r="E4" t="n">
-        <v>11410</v>
+        <v>10970</v>
       </c>
       <c r="F4" t="n">
-        <v>70</v>
+        <v>67.2</v>
       </c>
       <c r="G4" t="n">
-        <v>16.96</v>
+        <v>12.65</v>
       </c>
       <c r="H4" t="n">
-        <v>0.57</v>
+        <v>0.93</v>
       </c>
       <c r="I4" t="n">
-        <v>403.44</v>
+        <v>368.34</v>
       </c>
       <c r="J4" t="n">
-        <v>184.7</v>
+        <v>177.68</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>11424.96</v>
+        <v>11419.1</v>
       </c>
       <c r="N4" t="n">
-        <v>8412.75</v>
+        <v>8410.549999999999</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -869,18 +869,13 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
-・買われ過ぎ水準です。
 ・25日線から大きく上に乖離しています。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>RSIやや過熱、上昇加速、+1σ、MACD買い、反発局面</t>
@@ -890,22 +885,22 @@
         <v>10590</v>
       </c>
       <c r="X4" t="n">
-        <v>820</v>
+        <v>380</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.74</v>
+        <v>3.59</v>
       </c>
       <c r="Z4" t="n">
-        <v>11410</v>
+        <v>10970</v>
       </c>
       <c r="AA4" t="n">
         <v>10000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1410</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.1</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -926,22 +921,22 @@
         <v>158</v>
       </c>
       <c r="E5" t="n">
-        <v>172.2</v>
+        <v>172.5</v>
       </c>
       <c r="F5" t="n">
-        <v>40.3</v>
+        <v>41.3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="H5" t="n">
-        <v>0.48</v>
+        <v>0.98</v>
       </c>
       <c r="I5" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="J5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1002,22 +997,22 @@
         <v>173.3</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.63</v>
+        <v>-0.46</v>
       </c>
       <c r="Z5" t="n">
-        <v>17220</v>
+        <v>17250</v>
       </c>
       <c r="AA5" t="n">
         <v>15800</v>
       </c>
       <c r="AB5" t="n">
-        <v>1420</v>
+        <v>1450</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.99</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="6">
@@ -1038,22 +1033,22 @@
         <v>2853.77</v>
       </c>
       <c r="E6" t="n">
-        <v>2995</v>
+        <v>3011</v>
       </c>
       <c r="F6" t="n">
-        <v>52.3</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="H6" t="n">
-        <v>0.37</v>
+        <v>0.91</v>
       </c>
       <c r="I6" t="n">
-        <v>-8.300000000000001</v>
+        <v>-7.02</v>
       </c>
       <c r="J6" t="n">
-        <v>-16.19</v>
+        <v>-15.93</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2920.19</v>
+        <v>2920.41</v>
       </c>
       <c r="N6" t="n">
-        <v>3104.92</v>
+        <v>3105</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1115,22 +1110,22 @@
         <v>2984</v>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.37</v>
+        <v>0.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>38935</v>
+        <v>39143</v>
       </c>
       <c r="AA6" t="n">
         <v>37099</v>
       </c>
       <c r="AB6" t="n">
-        <v>1836</v>
+        <v>2044</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.95</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="7">
@@ -1151,22 +1146,22 @@
         <v>7993</v>
       </c>
       <c r="E7" t="n">
-        <v>8268</v>
+        <v>8278</v>
       </c>
       <c r="F7" t="n">
-        <v>47.3</v>
+        <v>47.7</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="H7" t="n">
-        <v>0.44</v>
+        <v>0.85</v>
       </c>
       <c r="I7" t="n">
-        <v>-76.70999999999999</v>
+        <v>-75.91</v>
       </c>
       <c r="J7" t="n">
-        <v>-107.38</v>
+        <v>-107.22</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1179,10 +1174,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7903.79</v>
+        <v>7903.92</v>
       </c>
       <c r="N7" t="n">
-        <v>8382.860000000001</v>
+        <v>8382.91</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1228,22 +1223,22 @@
         <v>8172</v>
       </c>
       <c r="X7" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>8268</v>
+        <v>8278</v>
       </c>
       <c r="AA7" t="n">
         <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.44</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="8">
@@ -1264,22 +1259,22 @@
         <v>4795</v>
       </c>
       <c r="E8" t="n">
-        <v>4705</v>
+        <v>4763</v>
       </c>
       <c r="F8" t="n">
-        <v>38.9</v>
+        <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.76</v>
+        <v>-0.59</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32</v>
+        <v>0.99</v>
       </c>
       <c r="I8" t="n">
-        <v>-36.18</v>
+        <v>-31.55</v>
       </c>
       <c r="J8" t="n">
-        <v>-23.83</v>
+        <v>-22.9</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1292,10 +1287,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4671.52</v>
+        <v>4672.29</v>
       </c>
       <c r="N8" t="n">
-        <v>4696.94</v>
+        <v>4697.23</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1340,22 +1335,22 @@
         <v>4700</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.11</v>
+        <v>1.34</v>
       </c>
       <c r="Z8" t="n">
-        <v>23525</v>
+        <v>23815</v>
       </c>
       <c r="AA8" t="n">
         <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-450</v>
+        <v>-160</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.88</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="9">
@@ -1376,22 +1371,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>14910</v>
+        <v>14690</v>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>26.2</v>
       </c>
       <c r="G9" t="n">
-        <v>-17.08</v>
+        <v>-18.27</v>
       </c>
       <c r="H9" t="n">
-        <v>0.71</v>
+        <v>1.18</v>
       </c>
       <c r="I9" t="n">
-        <v>-420.62</v>
+        <v>-438.17</v>
       </c>
       <c r="J9" t="n">
-        <v>-80.22</v>
+        <v>-83.73</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1404,10 +1399,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>19652.69</v>
+        <v>19649.76</v>
       </c>
       <c r="N9" t="n">
-        <v>14439.35</v>
+        <v>14438.25</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1454,22 +1449,22 @@
         <v>15180</v>
       </c>
       <c r="X9" t="n">
-        <v>-270</v>
+        <v>-490</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.78</v>
+        <v>-3.23</v>
       </c>
       <c r="Z9" t="n">
-        <v>14910</v>
+        <v>14690</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-40600</v>
+        <v>-40820</v>
       </c>
       <c r="AC9" t="n">
-        <v>-73.14</v>
+        <v>-73.54000000000001</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1485,38 +1485,38 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>39.07</v>
+        <v>35.78</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>34.1</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.13</v>
+        <v>-11.93</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8</v>
+        <v>1.08</v>
       </c>
       <c r="I10" t="n">
-        <v>0.93</v>
+        <v>0.4</v>
       </c>
       <c r="J10" t="n">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>34.85</v>
+        <v>34.95</v>
       </c>
       <c r="N10" t="n">
-        <v>32.41</v>
+        <v>32.43</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1525,20 +1525,20 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟠 利益確定検討</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1546,37 +1546,43 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・25日線から大きく下に乖離しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>25日線大幅割れ、デッドクロス、-1σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>39.98</v>
+        <v>39.07</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.91</v>
+        <v>-3.29</v>
       </c>
       <c r="Y10" t="n">
-        <v>-2.28</v>
+        <v>-8.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6074</v>
+        <v>-6077</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.36</v>
+        <v>-99.41</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3925</v>
+        <v>3875</v>
       </c>
       <c r="F2" t="n">
-        <v>74.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>11.83</v>
+        <v>9.99</v>
       </c>
       <c r="H2" t="n">
-        <v>0.76</v>
+        <v>0.25</v>
       </c>
       <c r="I2" t="n">
-        <v>153.76</v>
+        <v>153.66</v>
       </c>
       <c r="J2" t="n">
-        <v>96.48999999999999</v>
+        <v>107.93</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3261.84</v>
+        <v>3278.52</v>
       </c>
       <c r="N2" t="n">
-        <v>2779.12</v>
+        <v>2783.16</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -643,7 +643,6 @@
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
 ・買われ過ぎ水準です。
-・25日線から大きく上に乖離しています。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -652,29 +651,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>RSIやや過熱、上昇加速、+1σ、MACD買い、長期上昇</t>
+          <t>RSIやや過熱、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3905</v>
+        <v>3925</v>
       </c>
       <c r="X2" t="n">
-        <v>20</v>
+        <v>-50</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.51</v>
+        <v>-1.27</v>
       </c>
       <c r="Z2" t="n">
-        <v>15700</v>
+        <v>15500</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4900</v>
+        <v>4700</v>
       </c>
       <c r="AC2" t="n">
-        <v>45.37</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="3">
@@ -695,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>54.2</v>
       </c>
       <c r="G3" t="n">
-        <v>3.64</v>
+        <v>4.4</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="I3" t="n">
-        <v>5.77</v>
+        <v>6.54</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.83</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>449.76</v>
+        <v>451.37</v>
       </c>
       <c r="N3" t="n">
-        <v>422.29</v>
+        <v>422.99</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -769,61 +768,61 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="X3" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Z3" t="n">
-        <v>49100</v>
+        <v>49500</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7100</v>
+        <v>7500</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.9</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6976.T</t>
+          <t>9432.T</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>太陽誘電</t>
+          <t>NTT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>10000</v>
+        <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>10970</v>
+        <v>173.3</v>
       </c>
       <c r="F4" t="n">
-        <v>67.2</v>
+        <v>55.4</v>
       </c>
       <c r="G4" t="n">
-        <v>12.65</v>
+        <v>0.65</v>
       </c>
       <c r="H4" t="n">
-        <v>0.93</v>
+        <v>0.45</v>
       </c>
       <c r="I4" t="n">
-        <v>368.34</v>
+        <v>1.46</v>
       </c>
       <c r="J4" t="n">
-        <v>177.68</v>
+        <v>1.81</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -832,239 +831,240 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>11419.1</v>
+        <v>160.08</v>
       </c>
       <c r="N4" t="n">
-        <v>8410.549999999999</v>
+        <v>153.59</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>🟡 反発中</t>
+          <t>🟢 強い上昇</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟡 反発中
-・MACDは買いシグナルです。
-・25日線から大きく上に乖離しています。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSIやや過熱、上昇加速、+1σ、MACD買い、反発局面</t>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>10590</v>
+        <v>172.5</v>
       </c>
       <c r="X4" t="n">
-        <v>380</v>
+        <v>0.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.59</v>
+        <v>0.46</v>
       </c>
       <c r="Z4" t="n">
-        <v>10970</v>
+        <v>17330</v>
       </c>
       <c r="AA4" t="n">
-        <v>10000</v>
+        <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>1530</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9432.T</t>
+          <t>7203.T</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT</t>
+          <t>トヨタ自動車</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2853.77</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3015</v>
+      </c>
+      <c r="F5" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-12.85</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>2925.39</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3103.95</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
         <v>100</v>
       </c>
-      <c r="D5" t="n">
-        <v>158</v>
-      </c>
-      <c r="E5" t="n">
-        <v>172.5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>159.67</v>
-      </c>
-      <c r="N5" t="n">
-        <v>153.47</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>75</v>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
+・🟢 上昇
+・MACDは買いシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>25日線上、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、ゴールデンクロス、+1σ、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>173.3</v>
+        <v>3011</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.46</v>
+        <v>0.13</v>
       </c>
       <c r="Z5" t="n">
-        <v>17250</v>
+        <v>39195</v>
       </c>
       <c r="AA5" t="n">
-        <v>15800</v>
+        <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>1450</v>
+        <v>2096</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.18</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7203.T</t>
+          <t>7974.T</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>トヨタ自動車</t>
+          <t>任天堂</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2853.77</v>
+        <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>3011</v>
+        <v>8305</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>54.6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="H6" t="n">
-        <v>0.91</v>
+        <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-7.02</v>
+        <v>-50.06</v>
       </c>
       <c r="J6" t="n">
-        <v>-15.93</v>
+        <v>-95.79000000000001</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2920.41</v>
+        <v>7923.21</v>
       </c>
       <c r="N6" t="n">
-        <v>3105</v>
+        <v>8368.77</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1094,151 +1094,155 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、+1σ、MACD買い、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>2984</v>
-      </c>
-      <c r="X6" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>39143</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2044</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.51</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8278</v>
-      </c>
-      <c r="F7" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-75.91</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-107.22</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>7903.92</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8382.91</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>85</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは買いシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、ゴールデンクロス、MACD買い、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>8278</v>
+      </c>
+      <c r="X6" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8305</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>312</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10105</v>
+      </c>
+      <c r="F7" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>311.32</v>
+      </c>
+      <c r="J7" t="n">
+        <v>204.41</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>11329.28</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8444.34</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>95</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは買いシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>25日線上、MACD買い、上昇トレンド</t>
+          <t>RSI適正、25日線上、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>8172</v>
+        <v>10970</v>
       </c>
       <c r="X7" t="n">
-        <v>106</v>
+        <v>-865</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>-7.89</v>
       </c>
       <c r="Z7" t="n">
-        <v>8278</v>
+        <v>10105</v>
       </c>
       <c r="AA7" t="n">
-        <v>7993</v>
+        <v>10000</v>
       </c>
       <c r="AB7" t="n">
-        <v>285</v>
+        <v>105</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.57</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="8">
@@ -1259,22 +1263,22 @@
         <v>4795</v>
       </c>
       <c r="E8" t="n">
-        <v>4763</v>
+        <v>4641</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>43.6</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.59</v>
+        <v>-2.98</v>
       </c>
       <c r="H8" t="n">
-        <v>0.99</v>
+        <v>0.44</v>
       </c>
       <c r="I8" t="n">
-        <v>-31.55</v>
+        <v>-34.74</v>
       </c>
       <c r="J8" t="n">
-        <v>-22.9</v>
+        <v>-25.27</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1283,74 +1287,74 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4672.29</v>
+        <v>4674.55</v>
       </c>
       <c r="N8" t="n">
-        <v>4697.23</v>
+        <v>4702.75</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>🟢 上昇</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🔴 売り注意</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟢 上昇
+・🔴 下降
 ・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、上昇トレンド</t>
+          <t>押し目、-1σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>4700</v>
+        <v>4763</v>
       </c>
       <c r="X8" t="n">
-        <v>63</v>
+        <v>-122</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.34</v>
+        <v>-2.56</v>
       </c>
       <c r="Z8" t="n">
-        <v>23815</v>
+        <v>23205</v>
       </c>
       <c r="AA8" t="n">
         <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-160</v>
+        <v>-770</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.67</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="9">
@@ -1371,22 +1375,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>14690</v>
+        <v>13040</v>
       </c>
       <c r="F9" t="n">
-        <v>26.2</v>
+        <v>21.3</v>
       </c>
       <c r="G9" t="n">
-        <v>-18.27</v>
+        <v>-26.61</v>
       </c>
       <c r="H9" t="n">
-        <v>1.18</v>
+        <v>0.87</v>
       </c>
       <c r="I9" t="n">
-        <v>-438.17</v>
+        <v>-741.47</v>
       </c>
       <c r="J9" t="n">
-        <v>-83.73</v>
+        <v>-215.28</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1399,72 +1403,76 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>19649.76</v>
+        <v>19412.51</v>
       </c>
       <c r="N9" t="n">
-        <v>14438.25</v>
+        <v>14488.97</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>🟡 反発中</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🔴 売り注意</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟡 反発中
+・🔴 下降
 ・MACDは売りシグナルです。
 ・売られ過ぎ水準です。
 ・25日線から大きく下に乖離しています。
 ・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr"/>
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>RSI売られすぎ、25日線大幅割れ、-2σ、MACD売り、反発局面</t>
+          <t>RSI売られすぎ、25日線大幅割れ、-2σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>15180</v>
+        <v>14690</v>
       </c>
       <c r="X9" t="n">
-        <v>-490</v>
+        <v>-1650</v>
       </c>
       <c r="Y9" t="n">
-        <v>-3.23</v>
+        <v>-11.23</v>
       </c>
       <c r="Z9" t="n">
-        <v>14690</v>
+        <v>13040</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-40820</v>
+        <v>-42470</v>
       </c>
       <c r="AC9" t="n">
-        <v>-73.54000000000001</v>
+        <v>-76.51000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1494,7 +1502,7 @@
         <v>-11.93</v>
       </c>
       <c r="H10" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I10" t="n">
         <v>0.4</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3875</v>
+        <v>3845</v>
       </c>
       <c r="F2" t="n">
-        <v>72.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="G2" t="n">
-        <v>9.99</v>
+        <v>9.17</v>
       </c>
       <c r="H2" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I2" t="n">
-        <v>153.66</v>
+        <v>151.27</v>
       </c>
       <c r="J2" t="n">
-        <v>107.93</v>
+        <v>107.45</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3278.52</v>
+        <v>3278.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2783.16</v>
+        <v>2783.01</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -658,22 +658,22 @@
         <v>3925</v>
       </c>
       <c r="X2" t="n">
-        <v>-50</v>
+        <v>-80</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.27</v>
+        <v>-2.04</v>
       </c>
       <c r="Z2" t="n">
-        <v>15500</v>
+        <v>15380</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4700</v>
+        <v>4580</v>
       </c>
       <c r="AC2" t="n">
-        <v>43.52</v>
+        <v>42.41</v>
       </c>
     </row>
     <row r="3">
@@ -703,7 +703,7 @@
         <v>4.4</v>
       </c>
       <c r="H3" t="n">
-        <v>0.38</v>
+        <v>0.76</v>
       </c>
       <c r="I3" t="n">
         <v>6.54</v>
@@ -816,7 +816,7 @@
         <v>0.65</v>
       </c>
       <c r="H4" t="n">
-        <v>0.45</v>
+        <v>1.02</v>
       </c>
       <c r="I4" t="n">
         <v>1.46</v>
@@ -920,22 +920,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3015</v>
+        <v>3029</v>
       </c>
       <c r="F5" t="n">
-        <v>61.7</v>
+        <v>63</v>
       </c>
       <c r="G5" t="n">
-        <v>2.41</v>
+        <v>2.87</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6</v>
+        <v>1.39</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>-12.85</v>
+        <v>-12.63</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2925.39</v>
+        <v>2925.58</v>
       </c>
       <c r="N5" t="n">
-        <v>3103.95</v>
+        <v>3104.02</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -997,22 +997,22 @@
         <v>3011</v>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.13</v>
+        <v>0.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>39195</v>
+        <v>39377</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2096</v>
+        <v>2278</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.65</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="6">
@@ -1033,22 +1033,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8305</v>
+        <v>8228</v>
       </c>
       <c r="F6" t="n">
-        <v>54.6</v>
+        <v>51.3</v>
       </c>
       <c r="G6" t="n">
-        <v>2.12</v>
+        <v>1.21</v>
       </c>
       <c r="H6" t="n">
-        <v>0.66</v>
+        <v>1.26</v>
       </c>
       <c r="I6" t="n">
-        <v>-50.06</v>
+        <v>-56.2</v>
       </c>
       <c r="J6" t="n">
-        <v>-95.79000000000001</v>
+        <v>-97.01000000000001</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7923.21</v>
+        <v>7922.19</v>
       </c>
       <c r="N6" t="n">
-        <v>8368.77</v>
+        <v>8368.389999999999</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1111,22 +1111,22 @@
         <v>8278</v>
       </c>
       <c r="X6" t="n">
-        <v>27</v>
+        <v>-50</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.33</v>
+        <v>-0.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>8305</v>
+        <v>8228</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>312</v>
+        <v>235</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.9</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="7">
@@ -1147,22 +1147,22 @@
         <v>10000</v>
       </c>
       <c r="E7" t="n">
-        <v>10105</v>
+        <v>9864</v>
       </c>
       <c r="F7" t="n">
-        <v>61.7</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
-        <v>3.46</v>
+        <v>1.09</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="I7" t="n">
-        <v>311.32</v>
+        <v>292.1</v>
       </c>
       <c r="J7" t="n">
-        <v>204.41</v>
+        <v>200.56</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>11329.28</v>
+        <v>11326.07</v>
       </c>
       <c r="N7" t="n">
-        <v>8444.34</v>
+        <v>8443.139999999999</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1208,6 +1208,7 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは買いシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
@@ -1227,22 +1228,22 @@
         <v>10970</v>
       </c>
       <c r="X7" t="n">
-        <v>-865</v>
+        <v>-1106</v>
       </c>
       <c r="Y7" t="n">
-        <v>-7.89</v>
+        <v>-10.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>10105</v>
+        <v>9864</v>
       </c>
       <c r="AA7" t="n">
         <v>10000</v>
       </c>
       <c r="AB7" t="n">
-        <v>105</v>
+        <v>-136</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.05</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="8">
@@ -1263,22 +1264,22 @@
         <v>4795</v>
       </c>
       <c r="E8" t="n">
-        <v>4641</v>
+        <v>4674</v>
       </c>
       <c r="F8" t="n">
-        <v>43.6</v>
+        <v>45.4</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.98</v>
+        <v>-2.32</v>
       </c>
       <c r="H8" t="n">
-        <v>0.44</v>
+        <v>1.17</v>
       </c>
       <c r="I8" t="n">
-        <v>-34.74</v>
+        <v>-32.11</v>
       </c>
       <c r="J8" t="n">
-        <v>-25.27</v>
+        <v>-24.74</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1287,14 +1288,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4674.55</v>
+        <v>4674.99</v>
       </c>
       <c r="N8" t="n">
-        <v>4702.75</v>
+        <v>4702.91</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1307,7 +1308,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1324,7 +1325,8 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは売りシグナルです。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
@@ -1332,29 +1334,29 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、-1σ、MACD売り、下降トレンド</t>
+          <t>押し目、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>4763</v>
       </c>
       <c r="X8" t="n">
-        <v>-122</v>
+        <v>-89</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.56</v>
+        <v>-1.87</v>
       </c>
       <c r="Z8" t="n">
-        <v>23205</v>
+        <v>23370</v>
       </c>
       <c r="AA8" t="n">
         <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-770</v>
+        <v>-605</v>
       </c>
       <c r="AC8" t="n">
-        <v>-3.21</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="9">
@@ -1375,22 +1377,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>13040</v>
+        <v>12880</v>
       </c>
       <c r="F9" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n">
-        <v>-26.61</v>
+        <v>-27.49</v>
       </c>
       <c r="H9" t="n">
-        <v>0.87</v>
+        <v>1.45</v>
       </c>
       <c r="I9" t="n">
-        <v>-741.47</v>
+        <v>-754.24</v>
       </c>
       <c r="J9" t="n">
-        <v>-215.28</v>
+        <v>-217.83</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1403,10 +1405,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>19412.51</v>
+        <v>19410.38</v>
       </c>
       <c r="N9" t="n">
-        <v>14488.97</v>
+        <v>14488.17</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1457,22 +1459,22 @@
         <v>14690</v>
       </c>
       <c r="X9" t="n">
-        <v>-1650</v>
+        <v>-1810</v>
       </c>
       <c r="Y9" t="n">
-        <v>-11.23</v>
+        <v>-12.32</v>
       </c>
       <c r="Z9" t="n">
-        <v>13040</v>
+        <v>12880</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-42470</v>
+        <v>-42630</v>
       </c>
       <c r="AC9" t="n">
-        <v>-76.51000000000001</v>
+        <v>-76.8</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1495,38 +1495,38 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>35.78</v>
+        <v>35.09</v>
       </c>
       <c r="F10" t="n">
-        <v>34.1</v>
+        <v>26</v>
       </c>
       <c r="G10" t="n">
-        <v>-11.93</v>
+        <v>-13.43</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>1.24</v>
+        <v>0.98</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>-2S</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>34.95</v>
+        <v>35.03</v>
       </c>
       <c r="N10" t="n">
-        <v>32.43</v>
+        <v>32.46</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1535,20 +1535,20 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>🟠 利益確定検討</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1556,43 +1556,39 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
+・売られ過ぎ水準です。
 ・25日線から大きく下に乖離しています。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>25日線大幅割れ、デッドクロス、-1σ、MACD売り、長期上昇</t>
+          <t>RSI売られすぎ、25日線大幅割れ、-2σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>39.07</v>
+        <v>35.78</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.29</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>-8.42</v>
+        <v>-1.93</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6077</v>
+        <v>-6078</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.41</v>
+        <v>-99.43000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3845</v>
+        <v>4065</v>
       </c>
       <c r="F2" t="n">
-        <v>70.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>9.17</v>
+        <v>14.66</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="I2" t="n">
-        <v>151.27</v>
+        <v>165.14</v>
       </c>
       <c r="J2" t="n">
-        <v>107.45</v>
+        <v>118.99</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3278.12</v>
+        <v>3294.91</v>
       </c>
       <c r="N2" t="n">
-        <v>2783.01</v>
+        <v>2788.05</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,20 +621,20 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -643,37 +643,42 @@
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
 ・買われ過ぎ水準です。
+・25日線から大きく上に乖離しています。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSI過熱、上昇加速、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3925</v>
+        <v>3845</v>
       </c>
       <c r="X2" t="n">
-        <v>-80</v>
+        <v>220</v>
       </c>
       <c r="Y2" t="n">
-        <v>-2.04</v>
+        <v>5.72</v>
       </c>
       <c r="Z2" t="n">
-        <v>15380</v>
+        <v>16260</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4580</v>
+        <v>5460</v>
       </c>
       <c r="AC2" t="n">
-        <v>42.41</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="3">
@@ -694,22 +699,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="F3" t="n">
-        <v>54.2</v>
+        <v>73.3</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4</v>
+        <v>9.94</v>
       </c>
       <c r="H3" t="n">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>6.54</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>4.83</v>
+        <v>5.74</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -718,14 +723,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>+2S</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>451.37</v>
+        <v>453.48</v>
       </c>
       <c r="N3" t="n">
-        <v>422.99</v>
+        <v>423.86</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -738,7 +743,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -755,38 +760,42 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・買われ過ぎ水準です。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSIやや過熱、25日線上、+2σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="X3" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.8100000000000001</v>
+        <v>5.86</v>
       </c>
       <c r="Z3" t="n">
-        <v>49500</v>
+        <v>52400</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7500</v>
+        <v>10400</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.86</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="4">
@@ -807,22 +816,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>173.3</v>
+        <v>174.2</v>
       </c>
       <c r="F4" t="n">
-        <v>55.4</v>
+        <v>54.1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.65</v>
+        <v>0.98</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02</v>
+        <v>0.43</v>
       </c>
       <c r="I4" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="J4" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -835,10 +844,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>160.08</v>
+        <v>160.51</v>
       </c>
       <c r="N4" t="n">
-        <v>153.59</v>
+        <v>153.71</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -881,25 +890,25 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>172.5</v>
+        <v>173.3</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="Z4" t="n">
-        <v>17330</v>
+        <v>17420</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1530</v>
+        <v>1620</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.68</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="5">
@@ -920,38 +929,38 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3029</v>
+        <v>3079</v>
       </c>
       <c r="F5" t="n">
-        <v>63</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>2.87</v>
+        <v>4.51</v>
       </c>
       <c r="H5" t="n">
-        <v>1.39</v>
+        <v>0.48</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5600000000000001</v>
+        <v>10.49</v>
       </c>
       <c r="J5" t="n">
-        <v>-12.63</v>
+        <v>-8.01</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>+2S</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2925.58</v>
+        <v>2931.23</v>
       </c>
       <c r="N5" t="n">
-        <v>3104.02</v>
+        <v>3103.19</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -960,20 +969,20 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -981,152 +990,149 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>RSIやや過熱、25日線上、+2σ、MACD買い、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>3029</v>
+      </c>
+      <c r="X5" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>40027</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>37099</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2928</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.89</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8535</v>
+      </c>
+      <c r="F6" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-15.63</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-80.73999999999999</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>7944.53</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8356.24</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>95</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは買いシグナルです。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、ゴールデンクロス、+1σ、MACD買い、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>3011</v>
-      </c>
-      <c r="X5" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>39377</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2278</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>6.14</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E6" t="n">
-        <v>8228</v>
-      </c>
-      <c r="F6" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-56.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-97.01000000000001</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>7922.19</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8368.389999999999</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>🟢 強い買い</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>100</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、ゴールデンクロス、MACD買い、上昇トレンド</t>
+          <t>RSIやや過熱、25日線上、+1σ、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>8278</v>
+        <v>8228</v>
       </c>
       <c r="X6" t="n">
-        <v>-50</v>
+        <v>307</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.6</v>
+        <v>3.73</v>
       </c>
       <c r="Z6" t="n">
-        <v>8228</v>
+        <v>8535</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>235</v>
+        <v>542</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.94</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="7">
@@ -1147,22 +1153,22 @@
         <v>10000</v>
       </c>
       <c r="E7" t="n">
-        <v>9864</v>
+        <v>9962</v>
       </c>
       <c r="F7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>1.09</v>
+        <v>2.02</v>
       </c>
       <c r="H7" t="n">
-        <v>1.09</v>
+        <v>0.74</v>
       </c>
       <c r="I7" t="n">
-        <v>292.1</v>
+        <v>236.85</v>
       </c>
       <c r="J7" t="n">
-        <v>200.56</v>
+        <v>207.82</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1175,10 +1181,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>11326.07</v>
+        <v>11209.2</v>
       </c>
       <c r="N7" t="n">
-        <v>8443.139999999999</v>
+        <v>8476.139999999999</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1214,36 +1220,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>RSI適正、25日線上、MACD買い、反発局面</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>10970</v>
+        <v>9864</v>
       </c>
       <c r="X7" t="n">
-        <v>-1106</v>
+        <v>98</v>
       </c>
       <c r="Y7" t="n">
-        <v>-10.08</v>
+        <v>0.99</v>
       </c>
       <c r="Z7" t="n">
-        <v>9864</v>
+        <v>9962</v>
       </c>
       <c r="AA7" t="n">
         <v>10000</v>
       </c>
       <c r="AB7" t="n">
-        <v>-136</v>
+        <v>-38</v>
       </c>
       <c r="AC7" t="n">
-        <v>-1.36</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="8">
@@ -1264,22 +1266,22 @@
         <v>4795</v>
       </c>
       <c r="E8" t="n">
-        <v>4674</v>
+        <v>4737</v>
       </c>
       <c r="F8" t="n">
-        <v>45.4</v>
+        <v>46.4</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.32</v>
+        <v>-0.84</v>
       </c>
       <c r="H8" t="n">
-        <v>1.17</v>
+        <v>0.4</v>
       </c>
       <c r="I8" t="n">
-        <v>-32.11</v>
+        <v>-27.15</v>
       </c>
       <c r="J8" t="n">
-        <v>-24.74</v>
+        <v>-25.23</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1292,71 +1294,71 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4674.99</v>
+        <v>4680.24</v>
       </c>
       <c r="N8" t="n">
-        <v>4702.91</v>
+        <v>4709</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>🔴 下降</t>
+          <t>🟢 上昇</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🔴 売り注意</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🔴 下降
+・🟢 上昇
 ・MACDは売りシグナルです。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、下降トレンド</t>
+          <t>押し目、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>4763</v>
+        <v>4674</v>
       </c>
       <c r="X8" t="n">
-        <v>-89</v>
+        <v>63</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.87</v>
+        <v>1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>23370</v>
+        <v>23685</v>
       </c>
       <c r="AA8" t="n">
         <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-605</v>
+        <v>-290</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.52</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="9">
@@ -1377,22 +1379,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>12880</v>
+        <v>13310</v>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="G9" t="n">
-        <v>-27.49</v>
+        <v>-23.95</v>
       </c>
       <c r="H9" t="n">
-        <v>1.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-754.24</v>
+        <v>-958.97</v>
       </c>
       <c r="J9" t="n">
-        <v>-217.83</v>
+        <v>-366.06</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1405,10 +1407,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>19410.38</v>
+        <v>19126.29</v>
       </c>
       <c r="N9" t="n">
-        <v>14488.17</v>
+        <v>14539.22</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1445,36 +1447,32 @@
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>RSI売られすぎ、25日線大幅割れ、-2σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>14690</v>
+        <v>12880</v>
       </c>
       <c r="X9" t="n">
-        <v>-1810</v>
+        <v>430</v>
       </c>
       <c r="Y9" t="n">
-        <v>-12.32</v>
+        <v>3.34</v>
       </c>
       <c r="Z9" t="n">
-        <v>12880</v>
+        <v>13310</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-42630</v>
+        <v>-42200</v>
       </c>
       <c r="AC9" t="n">
-        <v>-76.8</v>
+        <v>-76.02</v>
       </c>
     </row>
     <row r="10">
@@ -1504,7 +1502,7 @@
         <v>-13.43</v>
       </c>
       <c r="H10" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="I10" t="n">
         <v>-0.07000000000000001</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>4065</v>
+        <v>4070</v>
       </c>
       <c r="F2" t="n">
-        <v>75.09999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="G2" t="n">
-        <v>14.66</v>
+        <v>14.8</v>
       </c>
       <c r="H2" t="n">
-        <v>0.29</v>
+        <v>0.59</v>
       </c>
       <c r="I2" t="n">
-        <v>165.14</v>
+        <v>165.53</v>
       </c>
       <c r="J2" t="n">
-        <v>118.99</v>
+        <v>119.07</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3294.91</v>
+        <v>3294.97</v>
       </c>
       <c r="N2" t="n">
-        <v>2788.05</v>
+        <v>2788.08</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -663,22 +663,22 @@
         <v>3845</v>
       </c>
       <c r="X2" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.72</v>
+        <v>5.85</v>
       </c>
       <c r="Z2" t="n">
-        <v>16260</v>
+        <v>16280</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>5460</v>
+        <v>5480</v>
       </c>
       <c r="AC2" t="n">
-        <v>50.56</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="3">
@@ -699,22 +699,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="F3" t="n">
-        <v>73.3</v>
+        <v>71</v>
       </c>
       <c r="G3" t="n">
-        <v>9.94</v>
+        <v>8.33</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.47</v>
       </c>
       <c r="I3" t="n">
-        <v>9.380000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="J3" t="n">
-        <v>5.74</v>
+        <v>5.61</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>453.48</v>
+        <v>453.37</v>
       </c>
       <c r="N3" t="n">
-        <v>423.86</v>
+        <v>423.82</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -766,11 +766,7 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>RSIやや過熱、25日線上、+2σ、MACD買い、長期上昇</t>
@@ -780,22 +776,22 @@
         <v>495</v>
       </c>
       <c r="X3" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.86</v>
+        <v>4.24</v>
       </c>
       <c r="Z3" t="n">
-        <v>52400</v>
+        <v>51600</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>10400</v>
+        <v>9600</v>
       </c>
       <c r="AC3" t="n">
-        <v>24.76</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="4">
@@ -816,19 +812,19 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>174.2</v>
+        <v>174.5</v>
       </c>
       <c r="F4" t="n">
-        <v>54.1</v>
+        <v>55.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.98</v>
+        <v>1.15</v>
       </c>
       <c r="H4" t="n">
-        <v>0.43</v>
+        <v>0.84</v>
       </c>
       <c r="I4" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="J4" t="n">
         <v>1.75</v>
@@ -893,22 +889,22 @@
         <v>173.3</v>
       </c>
       <c r="X4" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.52</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>17420</v>
+        <v>17450</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1620</v>
+        <v>1650</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.25</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="5">
@@ -929,22 +925,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3079</v>
+        <v>3094</v>
       </c>
       <c r="F5" t="n">
-        <v>65.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.51</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.48</v>
+        <v>1.05</v>
       </c>
       <c r="I5" t="n">
-        <v>10.49</v>
+        <v>11.69</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.01</v>
+        <v>-7.77</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -957,10 +953,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2931.23</v>
+        <v>2931.43</v>
       </c>
       <c r="N5" t="n">
-        <v>3103.19</v>
+        <v>3103.27</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1005,22 +1001,22 @@
         <v>3029</v>
       </c>
       <c r="X5" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>40027</v>
+        <v>40222</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2928</v>
+        <v>3123</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.89</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="6">
@@ -1041,22 +1037,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8535</v>
+        <v>8479</v>
       </c>
       <c r="F6" t="n">
-        <v>65.2</v>
+        <v>63.8</v>
       </c>
       <c r="G6" t="n">
-        <v>5.1</v>
+        <v>4.44</v>
       </c>
       <c r="H6" t="n">
-        <v>0.68</v>
+        <v>1.1</v>
       </c>
       <c r="I6" t="n">
-        <v>-15.63</v>
+        <v>-20.1</v>
       </c>
       <c r="J6" t="n">
-        <v>-80.73999999999999</v>
+        <v>-81.63</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1069,10 +1065,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7944.53</v>
+        <v>7943.79</v>
       </c>
       <c r="N6" t="n">
-        <v>8356.24</v>
+        <v>8355.959999999999</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1085,7 +1081,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1110,29 +1106,29 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD買い、上昇トレンド</t>
+          <t>RSI適正、25日線上、+1σ、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>8228</v>
       </c>
       <c r="X6" t="n">
-        <v>307</v>
+        <v>251</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.73</v>
+        <v>3.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>8535</v>
+        <v>8479</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>542</v>
+        <v>486</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.78</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="7">
@@ -1153,22 +1149,22 @@
         <v>10000</v>
       </c>
       <c r="E7" t="n">
-        <v>9962</v>
+        <v>10070</v>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>58.8</v>
       </c>
       <c r="G7" t="n">
-        <v>2.02</v>
+        <v>3.08</v>
       </c>
       <c r="H7" t="n">
-        <v>0.74</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
-        <v>236.85</v>
+        <v>245.47</v>
       </c>
       <c r="J7" t="n">
-        <v>207.82</v>
+        <v>209.55</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1181,10 +1177,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>11209.2</v>
+        <v>11210.64</v>
       </c>
       <c r="N7" t="n">
-        <v>8476.139999999999</v>
+        <v>8476.68</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1230,22 +1226,22 @@
         <v>9864</v>
       </c>
       <c r="X7" t="n">
-        <v>98</v>
+        <v>206</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.99</v>
+        <v>2.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>9962</v>
+        <v>10070</v>
       </c>
       <c r="AA7" t="n">
         <v>10000</v>
       </c>
       <c r="AB7" t="n">
-        <v>-38</v>
+        <v>70</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.38</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="8">
@@ -1266,22 +1262,22 @@
         <v>4795</v>
       </c>
       <c r="E8" t="n">
-        <v>4737</v>
+        <v>4726</v>
       </c>
       <c r="F8" t="n">
-        <v>46.4</v>
+        <v>45.7</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.84</v>
+        <v>-1.07</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4</v>
+        <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>-27.15</v>
+        <v>-28.03</v>
       </c>
       <c r="J8" t="n">
-        <v>-25.23</v>
+        <v>-25.4</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1294,10 +1290,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4680.24</v>
+        <v>4680.09</v>
       </c>
       <c r="N8" t="n">
-        <v>4709</v>
+        <v>4708.95</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1343,22 +1339,22 @@
         <v>4674</v>
       </c>
       <c r="X8" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>23685</v>
+        <v>23630</v>
       </c>
       <c r="AA8" t="n">
         <v>23975</v>
       </c>
       <c r="AB8" t="n">
-        <v>-290</v>
+        <v>-345</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.21</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="9">
@@ -1379,22 +1375,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>13310</v>
+        <v>13375</v>
       </c>
       <c r="F9" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="G9" t="n">
-        <v>-23.95</v>
+        <v>-23.59</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>-958.97</v>
+        <v>-953.79</v>
       </c>
       <c r="J9" t="n">
-        <v>-366.06</v>
+        <v>-365.02</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1407,10 +1403,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>19126.29</v>
+        <v>19127.16</v>
       </c>
       <c r="N9" t="n">
-        <v>14539.22</v>
+        <v>14539.55</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1457,22 +1453,22 @@
         <v>12880</v>
       </c>
       <c r="X9" t="n">
-        <v>430</v>
+        <v>495</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.34</v>
+        <v>3.84</v>
       </c>
       <c r="Z9" t="n">
-        <v>13310</v>
+        <v>13375</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-42200</v>
+        <v>-42135</v>
       </c>
       <c r="AC9" t="n">
-        <v>-76.02</v>
+        <v>-75.91</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1489,22 +1489,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>35.09</v>
+        <v>31.63</v>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>23.3</v>
       </c>
       <c r="G10" t="n">
-        <v>-13.43</v>
+        <v>-21.31</v>
       </c>
       <c r="H10" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.71</v>
       </c>
       <c r="J10" t="n">
-        <v>0.98</v>
+        <v>0.64</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1517,72 +1517,76 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>35.03</v>
+        <v>35.08</v>
       </c>
       <c r="N10" t="n">
-        <v>32.46</v>
+        <v>32.47</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>🟢 強い上昇</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🔴 売り注意</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟢 強い上昇
+・🔴 下降
 ・MACDは売りシグナルです。
 ・売られ過ぎ水準です。
 ・25日線から大きく下に乖離しています。
 ・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr"/>
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI売られすぎ、25日線大幅割れ、-2σ、MACD売り、長期上昇</t>
+          <t>RSI売られすぎ、25日線大幅割れ、-2σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>35.78</v>
+        <v>35.09</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-3.46</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.93</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6078</v>
+        <v>-6081</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.43000000000001</v>
+        <v>-99.48</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>4070</v>
+        <v>3960</v>
       </c>
       <c r="F2" t="n">
-        <v>75.2</v>
+        <v>69.7</v>
       </c>
       <c r="G2" t="n">
-        <v>14.8</v>
+        <v>11.02</v>
       </c>
       <c r="H2" t="n">
-        <v>0.59</v>
+        <v>0.31</v>
       </c>
       <c r="I2" t="n">
-        <v>165.53</v>
+        <v>166.05</v>
       </c>
       <c r="J2" t="n">
-        <v>119.07</v>
+        <v>128.46</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3294.97</v>
+        <v>3312.56</v>
       </c>
       <c r="N2" t="n">
-        <v>2788.08</v>
+        <v>2792.89</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,20 +621,20 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -642,43 +642,38 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・買われ過ぎ水準です。
 ・25日線から大きく上に乖離しています。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>RSI過熱、上昇加速、+1σ、MACD買い、長期上昇</t>
+          <t>RSIやや過熱、上昇加速、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3845</v>
+        <v>4070</v>
       </c>
       <c r="X2" t="n">
-        <v>225</v>
+        <v>-110</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.85</v>
+        <v>-2.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>16280</v>
+        <v>15840</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>5480</v>
+        <v>5040</v>
       </c>
       <c r="AC2" t="n">
-        <v>50.74</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="3">
@@ -699,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="F3" t="n">
-        <v>71</v>
+        <v>59.8</v>
       </c>
       <c r="G3" t="n">
-        <v>8.33</v>
+        <v>4.64</v>
       </c>
       <c r="H3" t="n">
-        <v>1.47</v>
+        <v>0.39</v>
       </c>
       <c r="I3" t="n">
-        <v>8.75</v>
+        <v>9.1</v>
       </c>
       <c r="J3" t="n">
-        <v>5.61</v>
+        <v>6.31</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -723,14 +718,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+2S</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>453.37</v>
+        <v>455.11</v>
       </c>
       <c r="N3" t="n">
-        <v>423.82</v>
+        <v>424.52</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -743,7 +738,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -760,8 +755,8 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・買われ過ぎ水準です。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+・RSIは良好な水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -769,29 +764,29 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、+2σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>-16</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.24</v>
+        <v>-3.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>51600</v>
+        <v>50000</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>9600</v>
+        <v>8000</v>
       </c>
       <c r="AC3" t="n">
-        <v>22.86</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="4">
@@ -812,19 +807,19 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>174.5</v>
+        <v>176.4</v>
       </c>
       <c r="F4" t="n">
-        <v>55.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>1.15</v>
+        <v>2.09</v>
       </c>
       <c r="H4" t="n">
-        <v>0.84</v>
+        <v>0.45</v>
       </c>
       <c r="I4" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="J4" t="n">
         <v>1.75</v>
@@ -836,14 +831,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>160.51</v>
+        <v>160.97</v>
       </c>
       <c r="N4" t="n">
-        <v>153.71</v>
+        <v>153.84</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -852,20 +847,20 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -873,8 +868,8 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・買われ過ぎ水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -882,29 +877,29 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>RSIやや過熱、25日線上、+1σ、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>173.3</v>
+        <v>174.5</v>
       </c>
       <c r="X4" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="Z4" t="n">
-        <v>17450</v>
+        <v>17640</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1650</v>
+        <v>1840</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.44</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="5">
@@ -925,22 +920,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3094</v>
+        <v>3089</v>
       </c>
       <c r="F5" t="n">
-        <v>66.5</v>
+        <v>66.2</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>4.59</v>
       </c>
       <c r="H5" t="n">
-        <v>1.05</v>
+        <v>0.36</v>
       </c>
       <c r="I5" t="n">
-        <v>11.69</v>
+        <v>19.87</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.77</v>
+        <v>-2.24</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -953,10 +948,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2931.43</v>
+        <v>2936.33</v>
       </c>
       <c r="N5" t="n">
-        <v>3103.27</v>
+        <v>3102.42</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>3029</v>
+        <v>3094</v>
       </c>
       <c r="X5" t="n">
-        <v>65</v>
+        <v>-5</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.15</v>
+        <v>-0.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>40222</v>
+        <v>40157</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>3123</v>
+        <v>3058</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.42</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="6">
@@ -1037,22 +1032,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8479</v>
+        <v>8555</v>
       </c>
       <c r="F6" t="n">
-        <v>63.8</v>
+        <v>70.7</v>
       </c>
       <c r="G6" t="n">
-        <v>4.44</v>
+        <v>5.47</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-20.1</v>
+        <v>14.48</v>
       </c>
       <c r="J6" t="n">
-        <v>-81.63</v>
+        <v>-62.41</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1065,10 +1060,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7943.79</v>
+        <v>7970</v>
       </c>
       <c r="N6" t="n">
-        <v>8355.959999999999</v>
+        <v>8344.860000000001</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1081,7 +1076,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1098,6 +1093,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
+・買われ過ぎ水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -1106,65 +1102,65 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+1σ、MACD買い、上昇トレンド</t>
+          <t>RSIやや過熱、25日線上、+1σ、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>8228</v>
+        <v>8479</v>
       </c>
       <c r="X6" t="n">
-        <v>251</v>
+        <v>76</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.05</v>
+        <v>0.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>8479</v>
+        <v>8555</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>486</v>
+        <v>562</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.08</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6976.T</t>
+          <t>8058.T</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>太陽誘電</t>
+          <t>三菱商事</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>10000</v>
+        <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>10070</v>
+        <v>4770</v>
       </c>
       <c r="F7" t="n">
-        <v>58.8</v>
+        <v>50.8</v>
       </c>
       <c r="G7" t="n">
-        <v>3.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>0.31</v>
       </c>
       <c r="I7" t="n">
-        <v>245.47</v>
+        <v>-21</v>
       </c>
       <c r="J7" t="n">
-        <v>209.55</v>
+        <v>-24.52</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1177,14 +1173,14 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>11210.64</v>
+        <v>4685.74</v>
       </c>
       <c r="N7" t="n">
-        <v>8476.68</v>
+        <v>4715.06</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>🟡 反発中</t>
+          <t>🟢 上昇</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1208,153 +1204,157 @@
       <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
+・🟢 上昇
+・MACDは買いシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>RSI適正、押し目、MACD買い、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>4726</v>
+      </c>
+      <c r="X7" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>23850</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>23975</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-125</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6976.T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>太陽誘電</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9384</v>
+      </c>
+      <c r="F8" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-4.09</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I8" t="n">
+        <v>151.41</v>
+      </c>
+      <c r="J8" t="n">
+        <v>197.92</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>11113.14</v>
+      </c>
+      <c r="N8" t="n">
+        <v>8507.049999999999</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>65</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
 ・🟡 反発中
-・MACDは買いシグナルです。
+・MACDは売りシグナルです。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、MACD買い、反発局面</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
-        <v>9864</v>
-      </c>
-      <c r="X7" t="n">
-        <v>206</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Z7" t="n">
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>RSI適正、押し目、MACD売り、反発局面</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
         <v>10070</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="X8" t="n">
+        <v>-686</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-6.81</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9384</v>
+      </c>
+      <c r="AA8" t="n">
         <v>10000</v>
       </c>
-      <c r="AB7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>8058.T</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>三菱商事</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4795</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4726</v>
-      </c>
-      <c r="F8" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-28.03</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-25.4</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>4680.09</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4708.95</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>55</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>4674</v>
-      </c>
-      <c r="X8" t="n">
-        <v>52</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>23630</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>23975</v>
-      </c>
       <c r="AB8" t="n">
-        <v>-345</v>
+        <v>-616</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.44</v>
+        <v>-6.16</v>
       </c>
     </row>
     <row r="9">
@@ -1375,22 +1375,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>13375</v>
+        <v>13450</v>
       </c>
       <c r="F9" t="n">
-        <v>21.8</v>
+        <v>24.6</v>
       </c>
       <c r="G9" t="n">
-        <v>-23.59</v>
+        <v>-22.15</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I9" t="n">
-        <v>-953.79</v>
+        <v>-1093.28</v>
       </c>
       <c r="J9" t="n">
-        <v>-365.02</v>
+        <v>-510.67</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>19127.16</v>
+        <v>18896.8</v>
       </c>
       <c r="N9" t="n">
-        <v>14539.55</v>
+        <v>14590.95</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1450,25 +1450,25 @@
         </is>
       </c>
       <c r="W9" t="n">
-        <v>12880</v>
+        <v>13375</v>
       </c>
       <c r="X9" t="n">
-        <v>495</v>
+        <v>75</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>13375</v>
+        <v>13450</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-42135</v>
+        <v>-42060</v>
       </c>
       <c r="AC9" t="n">
-        <v>-75.91</v>
+        <v>-75.77</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3960</v>
+        <v>3990</v>
       </c>
       <c r="F2" t="n">
-        <v>69.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>11.02</v>
+        <v>11.82</v>
       </c>
       <c r="H2" t="n">
-        <v>0.31</v>
+        <v>0.64</v>
       </c>
       <c r="I2" t="n">
-        <v>166.05</v>
+        <v>168.44</v>
       </c>
       <c r="J2" t="n">
-        <v>128.46</v>
+        <v>128.94</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3312.56</v>
+        <v>3312.96</v>
       </c>
       <c r="N2" t="n">
-        <v>2792.89</v>
+        <v>2793.04</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -642,6 +642,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
+・買われ過ぎ水準です。
 ・25日線から大きく上に乖離しています。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
@@ -658,22 +659,22 @@
         <v>4070</v>
       </c>
       <c r="X2" t="n">
-        <v>-110</v>
+        <v>-80</v>
       </c>
       <c r="Y2" t="n">
-        <v>-2.7</v>
+        <v>-1.97</v>
       </c>
       <c r="Z2" t="n">
-        <v>15840</v>
+        <v>15960</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>5040</v>
+        <v>5160</v>
       </c>
       <c r="AC2" t="n">
-        <v>46.67</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="3">
@@ -694,22 +695,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F3" t="n">
-        <v>59.8</v>
+        <v>58.2</v>
       </c>
       <c r="G3" t="n">
-        <v>4.64</v>
+        <v>4.04</v>
       </c>
       <c r="H3" t="n">
-        <v>0.39</v>
+        <v>0.85</v>
       </c>
       <c r="I3" t="n">
-        <v>9.1</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>6.31</v>
+        <v>6.26</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>455.11</v>
+        <v>455.07</v>
       </c>
       <c r="N3" t="n">
-        <v>424.52</v>
+        <v>424.5</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -771,22 +772,22 @@
         <v>516</v>
       </c>
       <c r="X3" t="n">
-        <v>-16</v>
+        <v>-19</v>
       </c>
       <c r="Y3" t="n">
-        <v>-3.1</v>
+        <v>-3.68</v>
       </c>
       <c r="Z3" t="n">
-        <v>50000</v>
+        <v>49700</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>8000</v>
+        <v>7700</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.05</v>
+        <v>18.33</v>
       </c>
     </row>
     <row r="4">
@@ -807,22 +808,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>176.4</v>
+        <v>175.1</v>
       </c>
       <c r="F4" t="n">
-        <v>70.40000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="G4" t="n">
-        <v>2.09</v>
+        <v>1.36</v>
       </c>
       <c r="H4" t="n">
-        <v>0.45</v>
+        <v>0.86</v>
       </c>
       <c r="I4" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="J4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -835,10 +836,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>160.97</v>
+        <v>160.95</v>
       </c>
       <c r="N4" t="n">
-        <v>153.84</v>
+        <v>153.83</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -868,7 +869,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
-・買われ過ぎ水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -884,22 +884,22 @@
         <v>174.5</v>
       </c>
       <c r="X4" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.09</v>
+        <v>0.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>17640</v>
+        <v>17510</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1840</v>
+        <v>1710</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.65</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="5">
@@ -920,22 +920,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3089</v>
+        <v>3102</v>
       </c>
       <c r="F5" t="n">
-        <v>66.2</v>
+        <v>67.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.59</v>
+        <v>5.01</v>
       </c>
       <c r="H5" t="n">
-        <v>0.36</v>
+        <v>0.79</v>
       </c>
       <c r="I5" t="n">
-        <v>19.87</v>
+        <v>20.91</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.24</v>
+        <v>-2.03</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2936.33</v>
+        <v>2936.5</v>
       </c>
       <c r="N5" t="n">
-        <v>3102.42</v>
+        <v>3102.48</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -996,22 +996,22 @@
         <v>3094</v>
       </c>
       <c r="X5" t="n">
-        <v>-5</v>
+        <v>8</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.16</v>
+        <v>0.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>40157</v>
+        <v>40326</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>3058</v>
+        <v>3227</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.24</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1032,22 +1032,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8555</v>
+        <v>8541</v>
       </c>
       <c r="F6" t="n">
-        <v>70.7</v>
+        <v>70.3</v>
       </c>
       <c r="G6" t="n">
-        <v>5.47</v>
+        <v>5.31</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>14.48</v>
+        <v>13.36</v>
       </c>
       <c r="J6" t="n">
-        <v>-62.41</v>
+        <v>-62.63</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7970</v>
+        <v>7969.81</v>
       </c>
       <c r="N6" t="n">
-        <v>8344.860000000001</v>
+        <v>8344.790000000001</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1109,22 +1109,22 @@
         <v>8479</v>
       </c>
       <c r="X6" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
       <c r="Z6" t="n">
-        <v>8555</v>
+        <v>8541</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.03</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="7">
@@ -1145,22 +1145,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4770</v>
+        <v>4761</v>
       </c>
       <c r="F7" t="n">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.25</v>
       </c>
       <c r="H7" t="n">
-        <v>0.31</v>
+        <v>0.77</v>
       </c>
       <c r="I7" t="n">
-        <v>-21</v>
+        <v>-21.72</v>
       </c>
       <c r="J7" t="n">
-        <v>-24.52</v>
+        <v>-24.67</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4685.74</v>
+        <v>4685.62</v>
       </c>
       <c r="N7" t="n">
-        <v>4715.06</v>
+        <v>4715.02</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1222,22 +1222,22 @@
         <v>4726</v>
       </c>
       <c r="X7" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.93</v>
+        <v>0.74</v>
       </c>
       <c r="Z7" t="n">
-        <v>23850</v>
+        <v>23805</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>-125</v>
+        <v>-170</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.52</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="8">
@@ -1258,22 +1258,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>9384</v>
+        <v>9582</v>
       </c>
       <c r="F8" t="n">
-        <v>52.8</v>
+        <v>54.6</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.09</v>
+        <v>-2.15</v>
       </c>
       <c r="H8" t="n">
-        <v>0.74</v>
+        <v>1.2</v>
       </c>
       <c r="I8" t="n">
-        <v>151.41</v>
+        <v>167.21</v>
       </c>
       <c r="J8" t="n">
-        <v>197.92</v>
+        <v>201.08</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>11113.14</v>
+        <v>11115.78</v>
       </c>
       <c r="N8" t="n">
-        <v>8507.049999999999</v>
+        <v>8508.040000000001</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1325,11 +1325,7 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>RSI適正、押し目、MACD売り、反発局面</t>
@@ -1339,22 +1335,22 @@
         <v>10070</v>
       </c>
       <c r="X8" t="n">
-        <v>-686</v>
+        <v>-488</v>
       </c>
       <c r="Y8" t="n">
-        <v>-6.81</v>
+        <v>-4.85</v>
       </c>
       <c r="Z8" t="n">
-        <v>9384</v>
+        <v>9582</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-616</v>
+        <v>-418</v>
       </c>
       <c r="AC8" t="n">
-        <v>-6.16</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="9">
@@ -1375,22 +1371,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>13450</v>
+        <v>13600</v>
       </c>
       <c r="F9" t="n">
-        <v>24.6</v>
+        <v>25.9</v>
       </c>
       <c r="G9" t="n">
-        <v>-22.15</v>
+        <v>-21.31</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I9" t="n">
-        <v>-1093.28</v>
+        <v>-1081.31</v>
       </c>
       <c r="J9" t="n">
-        <v>-510.67</v>
+        <v>-508.28</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1399,39 +1395,153 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>18898.8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>14591.7</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>🔴 売り注意</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>15</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・25日線から大きく下に乖離しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>RSI売られすぎ、25日線大幅割れ、-1σ、MACD売り、下降トレンド</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>13375</v>
+      </c>
+      <c r="X9" t="n">
+        <v>225</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>13600</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>55510</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-41910</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-75.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SUPER MICRO COMP</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6113</v>
+      </c>
+      <c r="E10" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="F10" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-21.31</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>-2S</t>
         </is>
       </c>
-      <c r="M9" t="n">
-        <v>18896.8</v>
-      </c>
-      <c r="N9" t="n">
-        <v>14590.95</v>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="M10" t="n">
+        <v>35.08</v>
+      </c>
+      <c r="N10" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>🔴 下降</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>🔴 売り注意</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q10" t="n">
         <v>20</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🔴 下降
@@ -1443,120 +1553,6 @@
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>RSI売られすぎ、25日線大幅割れ、-2σ、MACD売り、下降トレンド</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>13375</v>
-      </c>
-      <c r="X9" t="n">
-        <v>75</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>13450</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>55510</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-42060</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-75.77</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SMCI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SUPER MICRO COMP</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6113</v>
-      </c>
-      <c r="E10" t="n">
-        <v>31.63</v>
-      </c>
-      <c r="F10" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-21.31</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-2S</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>35.08</v>
-      </c>
-      <c r="N10" t="n">
-        <v>32.47</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>🔴 売り注意</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>20</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・25日線から大きく下に乖離しています。
-・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>⚠️ 急落</t>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1485,22 +1485,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>31.63</v>
+        <v>32.1</v>
       </c>
       <c r="F10" t="n">
-        <v>23.3</v>
+        <v>26.1</v>
       </c>
       <c r="G10" t="n">
-        <v>-21.31</v>
+        <v>-19.77</v>
       </c>
       <c r="H10" t="n">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.71</v>
+        <v>-1.17</v>
       </c>
       <c r="J10" t="n">
-        <v>0.64</v>
+        <v>0.28</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>35.08</v>
+        <v>35.15</v>
       </c>
       <c r="N10" t="n">
-        <v>32.47</v>
+        <v>32.48</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1553,24 +1553,20 @@
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>RSI売られすぎ、25日線大幅割れ、-2σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>35.09</v>
+        <v>31.63</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.46</v>
+        <v>0.47</v>
       </c>
       <c r="Y10" t="n">
-        <v>-9.859999999999999</v>
+        <v>1.49</v>
       </c>
       <c r="Z10" t="n">
         <v>32</v>
@@ -1582,7 +1578,7 @@
         <v>-6081</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.48</v>
+        <v>-99.47</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3990</v>
+        <v>3860</v>
       </c>
       <c r="F2" t="n">
-        <v>71.09999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="G2" t="n">
-        <v>11.82</v>
+        <v>7.53</v>
       </c>
       <c r="H2" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="I2" t="n">
-        <v>168.44</v>
+        <v>158.43</v>
       </c>
       <c r="J2" t="n">
-        <v>128.94</v>
+        <v>134.84</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -605,14 +605,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3312.96</v>
+        <v>3327.63</v>
       </c>
       <c r="N2" t="n">
-        <v>2793.04</v>
+        <v>2797.73</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -642,9 +642,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・買われ過ぎ水準です。
-・25日線から大きく上に乖離しています。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -652,29 +650,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>RSIやや過熱、上昇加速、+1σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>4070</v>
+        <v>3990</v>
       </c>
       <c r="X2" t="n">
-        <v>-80</v>
+        <v>-130</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.97</v>
+        <v>-3.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>15960</v>
+        <v>15440</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>5160</v>
+        <v>4640</v>
       </c>
       <c r="AC2" t="n">
-        <v>47.78</v>
+        <v>42.96</v>
       </c>
     </row>
     <row r="3">
@@ -695,22 +693,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="F3" t="n">
-        <v>58.2</v>
+        <v>54.2</v>
       </c>
       <c r="G3" t="n">
-        <v>4.04</v>
+        <v>1.59</v>
       </c>
       <c r="H3" t="n">
-        <v>0.85</v>
+        <v>0.53</v>
       </c>
       <c r="I3" t="n">
-        <v>8.859999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>6.26</v>
+        <v>6.62</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -719,14 +717,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>455.07</v>
+        <v>456.36</v>
       </c>
       <c r="N3" t="n">
-        <v>424.5</v>
+        <v>425.12</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -757,123 +755,124 @@
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
 ・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>497</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>48700</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>6700</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>15.95</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>175.7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>161.38</v>
+      </c>
+      <c r="N4" t="n">
+        <v>153.95</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>85</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★★★☆</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・買われ過ぎ水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、+1σ、MACD買い、長期上昇</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>516</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-19</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-3.68</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>49700</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>42000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>7700</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>18.33</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>9432.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NTT</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>158</v>
-      </c>
-      <c r="E4" t="n">
-        <v>175.1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>160.95</v>
-      </c>
-      <c r="N4" t="n">
-        <v>153.83</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>85</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
@@ -881,7 +880,7 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>174.5</v>
+        <v>175.1</v>
       </c>
       <c r="X4" t="n">
         <v>0.6</v>
@@ -890,16 +889,16 @@
         <v>0.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>17510</v>
+        <v>17570</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1710</v>
+        <v>1770</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.82</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="5">
@@ -920,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3102</v>
+        <v>3094</v>
       </c>
       <c r="F5" t="n">
-        <v>67.5</v>
+        <v>75</v>
       </c>
       <c r="G5" t="n">
-        <v>5.01</v>
+        <v>4.5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.79</v>
+        <v>0.32</v>
       </c>
       <c r="I5" t="n">
-        <v>20.91</v>
+        <v>27.26</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.03</v>
+        <v>3.83</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -948,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2936.5</v>
+        <v>2941.41</v>
       </c>
       <c r="N5" t="n">
-        <v>3102.48</v>
+        <v>3101.37</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -977,154 +976,155 @@
         </is>
       </c>
       <c r="T5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは買いシグナルです。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>RSIやや過熱、25日線上、+2σ、MACD買い、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>3094</v>
-      </c>
-      <c r="X5" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>40326</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>37099</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>3227</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E6" t="n">
-        <v>8541</v>
-      </c>
-      <c r="F6" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="I6" t="n">
-        <v>13.36</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-62.63</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>7969.81</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8344.790000000001</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>🟢 強い買い</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>95</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
 ・買われ過ぎ水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>RSIやや過熱、25日線上、+2σ、MACD買い、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>3102</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-8</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>40222</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>37099</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3123</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.42</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8630</v>
+      </c>
+      <c r="F6" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-40.8</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>+2S</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>7992.41</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8335.709999999999</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>70</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは買いシグナルです。
+・買われ過ぎ水準です。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD買い、上昇トレンド</t>
+          <t>RSI過熱、25日線上、+2σ、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>8479</v>
+        <v>8541</v>
       </c>
       <c r="X6" t="n">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.73</v>
+        <v>1.04</v>
       </c>
       <c r="Z6" t="n">
-        <v>8541</v>
+        <v>8630</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>548</v>
+        <v>637</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.86</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="7">
@@ -1145,22 +1145,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4761</v>
+        <v>4736</v>
       </c>
       <c r="F7" t="n">
-        <v>50.3</v>
+        <v>56.8</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.25</v>
+        <v>-0.57</v>
       </c>
       <c r="H7" t="n">
-        <v>0.77</v>
+        <v>0.34</v>
       </c>
       <c r="I7" t="n">
-        <v>-21.72</v>
+        <v>-18.53</v>
       </c>
       <c r="J7" t="n">
-        <v>-24.67</v>
+        <v>-23.44</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4685.62</v>
+        <v>4690.67</v>
       </c>
       <c r="N7" t="n">
-        <v>4715.02</v>
+        <v>4721.01</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1219,25 +1219,25 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4726</v>
+        <v>4761</v>
       </c>
       <c r="X7" t="n">
-        <v>35</v>
+        <v>-25</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.74</v>
+        <v>-0.53</v>
       </c>
       <c r="Z7" t="n">
-        <v>23805</v>
+        <v>23680</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>-170</v>
+        <v>-295</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.71</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="8">
@@ -1258,22 +1258,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>9582</v>
+        <v>9434</v>
       </c>
       <c r="F8" t="n">
-        <v>54.6</v>
+        <v>52.7</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.15</v>
+        <v>-3.86</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2</v>
+        <v>0.67</v>
       </c>
       <c r="I8" t="n">
-        <v>167.21</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>201.08</v>
+        <v>179.3</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>11115.78</v>
+        <v>10994.66</v>
       </c>
       <c r="N8" t="n">
-        <v>8508.040000000001</v>
+        <v>8538.629999999999</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1332,25 +1332,25 @@
         </is>
       </c>
       <c r="W8" t="n">
-        <v>10070</v>
+        <v>9582</v>
       </c>
       <c r="X8" t="n">
-        <v>-488</v>
+        <v>-148</v>
       </c>
       <c r="Y8" t="n">
-        <v>-4.85</v>
+        <v>-1.54</v>
       </c>
       <c r="Z8" t="n">
-        <v>9582</v>
+        <v>9434</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-418</v>
+        <v>-566</v>
       </c>
       <c r="AC8" t="n">
-        <v>-4.18</v>
+        <v>-5.66</v>
       </c>
     </row>
     <row r="9">
@@ -1371,22 +1371,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>13600</v>
+        <v>13385</v>
       </c>
       <c r="F9" t="n">
-        <v>25.9</v>
+        <v>24.4</v>
       </c>
       <c r="G9" t="n">
-        <v>-21.31</v>
+        <v>-21.53</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>0.55</v>
       </c>
       <c r="I9" t="n">
-        <v>-1081.31</v>
+        <v>-1186.05</v>
       </c>
       <c r="J9" t="n">
-        <v>-508.28</v>
+        <v>-643.83</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>18898.8</v>
+        <v>18684.16</v>
       </c>
       <c r="N9" t="n">
-        <v>14591.7</v>
+        <v>14643.05</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1446,25 +1446,25 @@
         </is>
       </c>
       <c r="W9" t="n">
-        <v>13375</v>
+        <v>13600</v>
       </c>
       <c r="X9" t="n">
-        <v>225</v>
+        <v>-215</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.68</v>
+        <v>-1.58</v>
       </c>
       <c r="Z9" t="n">
-        <v>13600</v>
+        <v>13385</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-41910</v>
+        <v>-42125</v>
       </c>
       <c r="AC9" t="n">
-        <v>-75.5</v>
+        <v>-75.89</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3860</v>
+        <v>3835</v>
       </c>
       <c r="F2" t="n">
-        <v>64.8</v>
+        <v>63.9</v>
       </c>
       <c r="G2" t="n">
-        <v>7.53</v>
+        <v>6.87</v>
       </c>
       <c r="H2" t="n">
-        <v>0.84</v>
+        <v>1.34</v>
       </c>
       <c r="I2" t="n">
-        <v>158.43</v>
+        <v>156.44</v>
       </c>
       <c r="J2" t="n">
-        <v>134.84</v>
+        <v>134.44</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3327.63</v>
+        <v>3327.29</v>
       </c>
       <c r="N2" t="n">
-        <v>2797.73</v>
+        <v>2797.61</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -657,22 +657,22 @@
         <v>3990</v>
       </c>
       <c r="X2" t="n">
-        <v>-130</v>
+        <v>-155</v>
       </c>
       <c r="Y2" t="n">
-        <v>-3.26</v>
+        <v>-3.88</v>
       </c>
       <c r="Z2" t="n">
-        <v>15440</v>
+        <v>15340</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4640</v>
+        <v>4540</v>
       </c>
       <c r="AC2" t="n">
-        <v>42.96</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="3">
@@ -693,22 +693,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F3" t="n">
-        <v>54.2</v>
+        <v>53.8</v>
       </c>
       <c r="G3" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="H3" t="n">
-        <v>0.53</v>
+        <v>0.95</v>
       </c>
       <c r="I3" t="n">
-        <v>8.050000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="J3" t="n">
-        <v>6.62</v>
+        <v>6.6</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>456.36</v>
+        <v>456.35</v>
       </c>
       <c r="N3" t="n">
-        <v>425.12</v>
+        <v>425.11</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -770,22 +770,22 @@
         <v>497</v>
       </c>
       <c r="X3" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2.01</v>
+        <v>-2.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>48700</v>
+        <v>48600</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6700</v>
+        <v>6600</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.95</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="4">
@@ -806,22 +806,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>175.7</v>
+        <v>177.1</v>
       </c>
       <c r="F4" t="n">
-        <v>73.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>1.57</v>
+        <v>2.34</v>
       </c>
       <c r="H4" t="n">
-        <v>0.48</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="J4" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>161.38</v>
+        <v>161.4</v>
       </c>
       <c r="N4" t="n">
         <v>153.95</v>
@@ -846,27 +846,27 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは売りシグナルです。
+・MACDは買いシグナルです。
 ・買われ過ぎ水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
@@ -876,29 +876,29 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD売り、長期上昇</t>
+          <t>RSI過熱、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>175.1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.34</v>
+        <v>1.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>17570</v>
+        <v>17710</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1770</v>
+        <v>1910</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.2</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3094</v>
+        <v>3102</v>
       </c>
       <c r="F5" t="n">
-        <v>75</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>4.5</v>
+        <v>4.76</v>
       </c>
       <c r="H5" t="n">
-        <v>0.32</v>
+        <v>0.71</v>
       </c>
       <c r="I5" t="n">
-        <v>27.26</v>
+        <v>27.89</v>
       </c>
       <c r="J5" t="n">
-        <v>3.83</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2941.41</v>
+        <v>2941.52</v>
       </c>
       <c r="N5" t="n">
-        <v>3101.37</v>
+        <v>3101.41</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -959,20 +959,20 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -989,29 +989,29 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、+2σ、MACD買い、上昇トレンド</t>
+          <t>RSI過熱、25日線上、+2σ、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>3102</v>
       </c>
       <c r="X5" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.26</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>40222</v>
+        <v>40326</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>3123</v>
+        <v>3227</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.42</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1032,22 +1032,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8630</v>
+        <v>8680</v>
       </c>
       <c r="F6" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="G6" t="n">
-        <v>6.29</v>
+        <v>6.88</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>46.53</v>
+        <v>50.51</v>
       </c>
       <c r="J6" t="n">
-        <v>-40.8</v>
+        <v>-40</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7992.41</v>
+        <v>7993.08</v>
       </c>
       <c r="N6" t="n">
-        <v>8335.709999999999</v>
+        <v>8335.959999999999</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1109,22 +1109,22 @@
         <v>8541</v>
       </c>
       <c r="X6" t="n">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="Z6" t="n">
-        <v>8630</v>
+        <v>8680</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>637</v>
+        <v>687</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.97</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="7">
@@ -1145,22 +1145,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4736</v>
+        <v>4712</v>
       </c>
       <c r="F7" t="n">
-        <v>56.8</v>
+        <v>55</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.57</v>
+        <v>-1.06</v>
       </c>
       <c r="H7" t="n">
-        <v>0.34</v>
+        <v>0.8</v>
       </c>
       <c r="I7" t="n">
-        <v>-18.53</v>
+        <v>-20.44</v>
       </c>
       <c r="J7" t="n">
-        <v>-23.44</v>
+        <v>-23.82</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4690.67</v>
+        <v>4690.35</v>
       </c>
       <c r="N7" t="n">
-        <v>4721.01</v>
+        <v>4720.89</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1222,22 +1222,22 @@
         <v>4761</v>
       </c>
       <c r="X7" t="n">
-        <v>-25</v>
+        <v>-49</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.53</v>
+        <v>-1.03</v>
       </c>
       <c r="Z7" t="n">
-        <v>23680</v>
+        <v>23560</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>-295</v>
+        <v>-415</v>
       </c>
       <c r="AC7" t="n">
-        <v>-1.23</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="8">
@@ -1258,22 +1258,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>9434</v>
+        <v>9095</v>
       </c>
       <c r="F8" t="n">
-        <v>52.7</v>
+        <v>49.8</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.86</v>
+        <v>-7.19</v>
       </c>
       <c r="H8" t="n">
-        <v>0.67</v>
+        <v>1.13</v>
       </c>
       <c r="I8" t="n">
-        <v>92.18000000000001</v>
+        <v>65.14</v>
       </c>
       <c r="J8" t="n">
-        <v>179.3</v>
+        <v>173.89</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10994.66</v>
+        <v>10990.14</v>
       </c>
       <c r="N8" t="n">
-        <v>8538.629999999999</v>
+        <v>8536.93</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1298,20 +1298,20 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟠 利益確定検討</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1325,32 +1325,36 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、反発局面</t>
+          <t>押し目、MACD売り、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>9582</v>
       </c>
       <c r="X8" t="n">
-        <v>-148</v>
+        <v>-487</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.54</v>
+        <v>-5.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>9434</v>
+        <v>9095</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-566</v>
+        <v>-905</v>
       </c>
       <c r="AC8" t="n">
-        <v>-5.66</v>
+        <v>-9.050000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1371,22 +1375,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>13385</v>
+        <v>13140</v>
       </c>
       <c r="F9" t="n">
-        <v>24.4</v>
+        <v>23.7</v>
       </c>
       <c r="G9" t="n">
-        <v>-21.53</v>
+        <v>-22.92</v>
       </c>
       <c r="H9" t="n">
-        <v>0.55</v>
+        <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-1186.05</v>
+        <v>-1205.59</v>
       </c>
       <c r="J9" t="n">
-        <v>-643.83</v>
+        <v>-647.74</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1399,10 +1403,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>18684.16</v>
+        <v>18680.89</v>
       </c>
       <c r="N9" t="n">
-        <v>14643.05</v>
+        <v>14641.83</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1449,22 +1453,22 @@
         <v>13600</v>
       </c>
       <c r="X9" t="n">
-        <v>-215</v>
+        <v>-460</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.58</v>
+        <v>-3.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>13385</v>
+        <v>13140</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-42125</v>
+        <v>-42370</v>
       </c>
       <c r="AC9" t="n">
-        <v>-75.89</v>
+        <v>-76.33</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1489,22 +1489,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>32.1</v>
+        <v>32.47</v>
       </c>
       <c r="F10" t="n">
-        <v>26.1</v>
+        <v>27.4</v>
       </c>
       <c r="G10" t="n">
-        <v>-19.77</v>
+        <v>-18.59</v>
       </c>
       <c r="H10" t="n">
-        <v>0.89</v>
+        <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.17</v>
+        <v>-1.49</v>
       </c>
       <c r="J10" t="n">
-        <v>0.28</v>
+        <v>-0.08</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1513,14 +1513,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-2S</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>35.15</v>
+        <v>35.22</v>
       </c>
       <c r="N10" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
 ・MACDは売りシグナルです。
 ・売られ過ぎ水準です。
 ・25日線から大きく下に乖離しています。
-・ボリンジャーバンド-2σ付近です。売られすぎから反発する可能性があります。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
@@ -1560,17 +1560,17 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI売られすぎ、25日線大幅割れ、-2σ、MACD売り、下降トレンド</t>
+          <t>RSI売られすぎ、25日線大幅割れ、-1σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>31.63</v>
+        <v>32.1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.47</v>
+        <v>0.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.49</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
         <v>32</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3835</v>
+        <v>3890</v>
       </c>
       <c r="F2" t="n">
-        <v>63.9</v>
+        <v>65</v>
       </c>
       <c r="G2" t="n">
-        <v>6.87</v>
+        <v>7.76</v>
       </c>
       <c r="H2" t="n">
-        <v>1.34</v>
+        <v>0.37</v>
       </c>
       <c r="I2" t="n">
-        <v>156.44</v>
+        <v>149.64</v>
       </c>
       <c r="J2" t="n">
-        <v>134.44</v>
+        <v>137.48</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3327.29</v>
+        <v>3343.15</v>
       </c>
       <c r="N2" t="n">
-        <v>2797.61</v>
+        <v>2802.39</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -654,25 +654,25 @@
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3990</v>
+        <v>3835</v>
       </c>
       <c r="X2" t="n">
-        <v>-155</v>
+        <v>55</v>
       </c>
       <c r="Y2" t="n">
-        <v>-3.88</v>
+        <v>1.43</v>
       </c>
       <c r="Z2" t="n">
-        <v>15340</v>
+        <v>15560</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4540</v>
+        <v>4760</v>
       </c>
       <c r="AC2" t="n">
-        <v>42.04</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="3">
@@ -693,22 +693,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F3" t="n">
-        <v>53.8</v>
+        <v>59.7</v>
       </c>
       <c r="G3" t="n">
-        <v>1.39</v>
+        <v>2.43</v>
       </c>
       <c r="H3" t="n">
-        <v>0.95</v>
+        <v>0.37</v>
       </c>
       <c r="I3" t="n">
-        <v>7.97</v>
+        <v>7.74</v>
       </c>
       <c r="J3" t="n">
-        <v>6.6</v>
+        <v>6.83</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>456.35</v>
+        <v>457.69</v>
       </c>
       <c r="N3" t="n">
-        <v>425.11</v>
+        <v>425.8</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -767,25 +767,25 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="X3" t="n">
-        <v>-11</v>
+        <v>7</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2.21</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>48600</v>
+        <v>49300</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6600</v>
+        <v>7300</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.71</v>
+        <v>17.38</v>
       </c>
     </row>
     <row r="4">
@@ -806,22 +806,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>177.1</v>
+        <v>175.6</v>
       </c>
       <c r="F4" t="n">
-        <v>76.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="G4" t="n">
-        <v>2.34</v>
+        <v>1.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>0.6</v>
       </c>
       <c r="I4" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="J4" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>161.4</v>
+        <v>161.84</v>
       </c>
       <c r="N4" t="n">
-        <v>153.95</v>
+        <v>154.08</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -867,7 +867,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・買われ過ぎ水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -876,65 +875,65 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSI過熱、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSIやや過熱、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>175.1</v>
+        <v>177.1</v>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>-1.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.14</v>
+        <v>-0.85</v>
       </c>
       <c r="Z4" t="n">
-        <v>17710</v>
+        <v>17560</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1910</v>
+        <v>1760</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.09</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7203.T</t>
+          <t>7974.T</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>トヨタ自動車</t>
+          <t>任天堂</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2853.77</v>
+        <v>7993</v>
       </c>
       <c r="E5" t="n">
-        <v>3102</v>
+        <v>8714</v>
       </c>
       <c r="F5" t="n">
-        <v>76.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>4.76</v>
+        <v>6.91</v>
       </c>
       <c r="H5" t="n">
-        <v>0.71</v>
+        <v>0.44</v>
       </c>
       <c r="I5" t="n">
-        <v>27.89</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>3.95</v>
+        <v>-15.65</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,10 +946,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2941.52</v>
+        <v>8018.4</v>
       </c>
       <c r="N5" t="n">
-        <v>3101.41</v>
+        <v>8329.290000000001</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -993,61 +992,61 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>3102</v>
+        <v>8680</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>40326</v>
+        <v>8714</v>
       </c>
       <c r="AA5" t="n">
-        <v>37099</v>
+        <v>7993</v>
       </c>
       <c r="AB5" t="n">
-        <v>3227</v>
+        <v>721</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.699999999999999</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7974.T</t>
+          <t>7203.T</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>任天堂</t>
+          <t>トヨタ自動車</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>7993</v>
+        <v>2853.77</v>
       </c>
       <c r="E6" t="n">
-        <v>8680</v>
+        <v>3093</v>
       </c>
       <c r="F6" t="n">
-        <v>78.7</v>
+        <v>72.3</v>
       </c>
       <c r="G6" t="n">
-        <v>6.88</v>
+        <v>4.24</v>
       </c>
       <c r="H6" t="n">
-        <v>0.88</v>
+        <v>0.45</v>
       </c>
       <c r="I6" t="n">
-        <v>50.51</v>
+        <v>32.33</v>
       </c>
       <c r="J6" t="n">
-        <v>-40</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1056,14 +1055,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+2S</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>7993.08</v>
+        <v>2947.03</v>
       </c>
       <c r="N6" t="n">
-        <v>8335.959999999999</v>
+        <v>3100.14</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1072,20 +1071,20 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1094,7 +1093,7 @@
 ・🟢 上昇
 ・MACDは買いシグナルです。
 ・買われ過ぎ水準です。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -1102,29 +1101,29 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSI過熱、25日線上、+2σ、MACD買い、上昇トレンド</t>
+          <t>RSIやや過熱、25日線上、+1σ、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>8541</v>
+        <v>3102</v>
       </c>
       <c r="X6" t="n">
-        <v>139</v>
+        <v>-9</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.63</v>
+        <v>-0.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>8680</v>
+        <v>40209</v>
       </c>
       <c r="AA6" t="n">
-        <v>7993</v>
+        <v>37099</v>
       </c>
       <c r="AB6" t="n">
-        <v>687</v>
+        <v>3110</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1145,22 +1144,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4712</v>
+        <v>4750</v>
       </c>
       <c r="F7" t="n">
-        <v>55</v>
+        <v>48.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.06</v>
+        <v>-0.11</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8</v>
+        <v>0.42</v>
       </c>
       <c r="I7" t="n">
-        <v>-20.44</v>
+        <v>-16.17</v>
       </c>
       <c r="J7" t="n">
-        <v>-23.82</v>
+        <v>-22.29</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1173,10 +1172,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4690.35</v>
+        <v>4696.47</v>
       </c>
       <c r="N7" t="n">
-        <v>4720.89</v>
+        <v>4727.02</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1185,20 +1184,20 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1215,29 +1214,29 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD買い、上昇トレンド</t>
+          <t>押し目、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4761</v>
+        <v>4712</v>
       </c>
       <c r="X7" t="n">
-        <v>-49</v>
+        <v>38</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.03</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>23560</v>
+        <v>23750</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>-415</v>
+        <v>-225</v>
       </c>
       <c r="AC7" t="n">
-        <v>-1.73</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1258,26 +1257,26 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>9095</v>
+        <v>9468</v>
       </c>
       <c r="F8" t="n">
-        <v>49.8</v>
+        <v>51.1</v>
       </c>
       <c r="G8" t="n">
-        <v>-7.19</v>
+        <v>-3.42</v>
       </c>
       <c r="H8" t="n">
-        <v>1.13</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>65.14</v>
+        <v>14.19</v>
       </c>
       <c r="J8" t="n">
-        <v>173.89</v>
+        <v>141.95</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1286,10 +1285,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10990.14</v>
+        <v>10849.04</v>
       </c>
       <c r="N8" t="n">
-        <v>8536.93</v>
+        <v>8567.1</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1302,16 +1301,16 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1319,42 +1318,39 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは売りシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、反発局面</t>
+          <t>RSI適正、押し目、デッドクロス、MACD売り、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>9582</v>
+        <v>9095</v>
       </c>
       <c r="X8" t="n">
-        <v>-487</v>
+        <v>373</v>
       </c>
       <c r="Y8" t="n">
-        <v>-5.08</v>
+        <v>4.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>9095</v>
+        <v>9468</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-905</v>
+        <v>-532</v>
       </c>
       <c r="AC8" t="n">
-        <v>-9.050000000000001</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="9">
@@ -1375,22 +1371,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>13140</v>
+        <v>13560</v>
       </c>
       <c r="F9" t="n">
-        <v>23.7</v>
+        <v>25.4</v>
       </c>
       <c r="G9" t="n">
-        <v>-22.92</v>
+        <v>-19.36</v>
       </c>
       <c r="H9" t="n">
-        <v>0.88</v>
+        <v>0.58</v>
       </c>
       <c r="I9" t="n">
-        <v>-1205.59</v>
+        <v>-1255.72</v>
       </c>
       <c r="J9" t="n">
-        <v>-647.74</v>
+        <v>-769.34</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1403,10 +1399,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>18680.89</v>
+        <v>18463.11</v>
       </c>
       <c r="N9" t="n">
-        <v>14641.83</v>
+        <v>14692.75</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1450,25 +1446,25 @@
         </is>
       </c>
       <c r="W9" t="n">
-        <v>13600</v>
+        <v>13140</v>
       </c>
       <c r="X9" t="n">
-        <v>-460</v>
+        <v>420</v>
       </c>
       <c r="Y9" t="n">
-        <v>-3.38</v>
+        <v>3.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>13140</v>
+        <v>13560</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-42370</v>
+        <v>-41950</v>
       </c>
       <c r="AC9" t="n">
-        <v>-76.33</v>
+        <v>-75.56999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1498,7 +1494,7 @@
         <v>-18.59</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="I10" t="n">
         <v>-1.49</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3890</v>
+        <v>3800</v>
       </c>
       <c r="F2" t="n">
-        <v>65</v>
+        <v>62.5</v>
       </c>
       <c r="G2" t="n">
-        <v>7.76</v>
+        <v>5.37</v>
       </c>
       <c r="H2" t="n">
-        <v>0.37</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="n">
-        <v>149.64</v>
+        <v>142.46</v>
       </c>
       <c r="J2" t="n">
-        <v>137.48</v>
+        <v>136.05</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3343.15</v>
+        <v>3341.95</v>
       </c>
       <c r="N2" t="n">
-        <v>2802.39</v>
+        <v>2801.94</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -657,22 +657,22 @@
         <v>3835</v>
       </c>
       <c r="X2" t="n">
-        <v>55</v>
+        <v>-35</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.43</v>
+        <v>-0.91</v>
       </c>
       <c r="Z2" t="n">
-        <v>15560</v>
+        <v>15200</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4760</v>
+        <v>4400</v>
       </c>
       <c r="AC2" t="n">
-        <v>44.07</v>
+        <v>40.74</v>
       </c>
     </row>
     <row r="3">
@@ -693,22 +693,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="F3" t="n">
-        <v>59.7</v>
+        <v>57.9</v>
       </c>
       <c r="G3" t="n">
-        <v>2.43</v>
+        <v>1.43</v>
       </c>
       <c r="H3" t="n">
-        <v>0.37</v>
+        <v>0.66</v>
       </c>
       <c r="I3" t="n">
-        <v>7.74</v>
+        <v>7.34</v>
       </c>
       <c r="J3" t="n">
-        <v>6.83</v>
+        <v>6.75</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>457.69</v>
+        <v>457.63</v>
       </c>
       <c r="N3" t="n">
-        <v>425.8</v>
+        <v>425.78</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -770,22 +770,22 @@
         <v>486</v>
       </c>
       <c r="X3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.44</v>
+        <v>0.41</v>
       </c>
       <c r="Z3" t="n">
-        <v>49300</v>
+        <v>48800</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7300</v>
+        <v>6800</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.38</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="4">
@@ -806,22 +806,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>175.6</v>
+        <v>176.2</v>
       </c>
       <c r="F4" t="n">
-        <v>66.7</v>
+        <v>70.2</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6</v>
+        <v>1.07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="J4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>161.84</v>
+        <v>161.85</v>
       </c>
       <c r="N4" t="n">
-        <v>154.08</v>
+        <v>154.09</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -867,6 +867,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
+・買われ過ぎ水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -882,22 +883,22 @@
         <v>177.1</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5</v>
+        <v>-0.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.85</v>
+        <v>-0.51</v>
       </c>
       <c r="Z4" t="n">
-        <v>17560</v>
+        <v>17620</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1760</v>
+        <v>1820</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.14</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="5">
@@ -918,22 +919,22 @@
         <v>7993</v>
       </c>
       <c r="E5" t="n">
-        <v>8714</v>
+        <v>8715</v>
       </c>
       <c r="F5" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="G5" t="n">
-        <v>6.91</v>
+        <v>6.92</v>
       </c>
       <c r="H5" t="n">
-        <v>0.44</v>
+        <v>0.74</v>
       </c>
       <c r="I5" t="n">
-        <v>81.76000000000001</v>
+        <v>81.84</v>
       </c>
       <c r="J5" t="n">
-        <v>-15.65</v>
+        <v>-15.64</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -946,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>8018.4</v>
+        <v>8018.41</v>
       </c>
       <c r="N5" t="n">
-        <v>8329.290000000001</v>
+        <v>8329.299999999999</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -995,22 +996,22 @@
         <v>8680</v>
       </c>
       <c r="X5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>8714</v>
+        <v>8715</v>
       </c>
       <c r="AA5" t="n">
         <v>7993</v>
       </c>
       <c r="AB5" t="n">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.02</v>
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1031,22 +1032,22 @@
         <v>2853.77</v>
       </c>
       <c r="E6" t="n">
-        <v>3093</v>
+        <v>3094</v>
       </c>
       <c r="F6" t="n">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
       <c r="G6" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
       <c r="H6" t="n">
-        <v>0.45</v>
+        <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>32.33</v>
+        <v>32.41</v>
       </c>
       <c r="J6" t="n">
-        <v>9.630000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1059,7 +1060,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2947.03</v>
+        <v>2947.05</v>
       </c>
       <c r="N6" t="n">
         <v>3100.14</v>
@@ -1108,22 +1109,22 @@
         <v>3102</v>
       </c>
       <c r="X6" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.29</v>
+        <v>-0.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>40209</v>
+        <v>40222</v>
       </c>
       <c r="AA6" t="n">
         <v>37099</v>
       </c>
       <c r="AB6" t="n">
-        <v>3110</v>
+        <v>3123</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.380000000000001</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="7">
@@ -1144,22 +1145,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4750</v>
+        <v>4746</v>
       </c>
       <c r="F7" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.11</v>
+        <v>-0.2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.42</v>
+        <v>0.99</v>
       </c>
       <c r="I7" t="n">
-        <v>-16.17</v>
+        <v>-16.49</v>
       </c>
       <c r="J7" t="n">
-        <v>-22.29</v>
+        <v>-22.35</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1172,10 +1173,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4696.47</v>
+        <v>4696.42</v>
       </c>
       <c r="N7" t="n">
-        <v>4727.02</v>
+        <v>4727</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1221,22 +1222,22 @@
         <v>4712</v>
       </c>
       <c r="X7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="Z7" t="n">
-        <v>23750</v>
+        <v>23730</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>-225</v>
+        <v>-245</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="8">
@@ -1257,22 +1258,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>9468</v>
+        <v>9253</v>
       </c>
       <c r="F8" t="n">
-        <v>51.1</v>
+        <v>49.4</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.42</v>
+        <v>-5.53</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="I8" t="n">
-        <v>14.19</v>
+        <v>-2.97</v>
       </c>
       <c r="J8" t="n">
-        <v>141.95</v>
+        <v>138.52</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1285,10 +1286,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10849.04</v>
+        <v>10846.17</v>
       </c>
       <c r="N8" t="n">
-        <v>8567.1</v>
+        <v>8566.030000000001</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1297,20 +1298,20 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟠 利益確定検討</t>
+          <t>🔴 売り注意</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★★☆☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1328,29 +1329,29 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、デッドクロス、MACD売り、反発局面</t>
+          <t>押し目、デッドクロス、MACD売り、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>9095</v>
       </c>
       <c r="X8" t="n">
-        <v>373</v>
+        <v>158</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.1</v>
+        <v>1.74</v>
       </c>
       <c r="Z8" t="n">
-        <v>9468</v>
+        <v>9253</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-532</v>
+        <v>-747</v>
       </c>
       <c r="AC8" t="n">
-        <v>-5.32</v>
+        <v>-7.47</v>
       </c>
     </row>
     <row r="9">
@@ -1371,22 +1372,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>13560</v>
+        <v>13510</v>
       </c>
       <c r="F9" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>-19.36</v>
+        <v>-19.65</v>
       </c>
       <c r="H9" t="n">
-        <v>0.58</v>
+        <v>0.9</v>
       </c>
       <c r="I9" t="n">
-        <v>-1255.72</v>
+        <v>-1259.71</v>
       </c>
       <c r="J9" t="n">
-        <v>-769.34</v>
+        <v>-770.14</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1399,10 +1400,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>18463.11</v>
+        <v>18462.44</v>
       </c>
       <c r="N9" t="n">
-        <v>14692.75</v>
+        <v>14692.5</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1449,22 +1450,22 @@
         <v>13140</v>
       </c>
       <c r="X9" t="n">
-        <v>420</v>
+        <v>370</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="Z9" t="n">
-        <v>13560</v>
+        <v>13510</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-41950</v>
+        <v>-42000</v>
       </c>
       <c r="AC9" t="n">
-        <v>-75.56999999999999</v>
+        <v>-75.66</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1486,100 +1486,104 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="F10" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>35.34</v>
+      </c>
+      <c r="N10" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>60</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・25日線から大きく下に乖離しています。
+・出来高が増加しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>25日線大幅割れ、出来高微増、-1σ、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
         <v>32.47</v>
       </c>
-      <c r="F10" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-18.59</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>35.22</v>
-      </c>
-      <c r="N10" t="n">
-        <v>32.49</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>🔴 売り注意</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>15</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・25日線から大きく下に乖離しています。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>RSI売られすぎ、25日線大幅割れ、-1σ、MACD売り、下降トレンド</t>
-        </is>
-      </c>
-      <c r="W10" t="n">
-        <v>32.1</v>
-      </c>
       <c r="X10" t="n">
-        <v>0.37</v>
+        <v>3.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6081</v>
+        <v>-6077</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.47</v>
+        <v>-99.42</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3800</v>
+        <v>3755</v>
       </c>
       <c r="F2" t="n">
-        <v>62.5</v>
+        <v>59.5</v>
       </c>
       <c r="G2" t="n">
-        <v>5.37</v>
+        <v>3.56</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="I2" t="n">
-        <v>142.46</v>
+        <v>126.29</v>
       </c>
       <c r="J2" t="n">
-        <v>136.05</v>
+        <v>134.09</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3341.95</v>
+        <v>3355.24</v>
       </c>
       <c r="N2" t="n">
-        <v>2801.94</v>
+        <v>2805.7</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -641,7 +641,8 @@
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは買いシグナルです。
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -650,29 +651,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3835</v>
+        <v>3800</v>
       </c>
       <c r="X2" t="n">
-        <v>-35</v>
+        <v>-45</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.91</v>
+        <v>-1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>15200</v>
+        <v>15020</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4400</v>
+        <v>4220</v>
       </c>
       <c r="AC2" t="n">
-        <v>40.74</v>
+        <v>39.07</v>
       </c>
     </row>
     <row r="3">
@@ -693,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F3" t="n">
-        <v>57.9</v>
+        <v>58.3</v>
       </c>
       <c r="G3" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="H3" t="n">
-        <v>0.66</v>
+        <v>0.3</v>
       </c>
       <c r="I3" t="n">
-        <v>7.34</v>
+        <v>6.92</v>
       </c>
       <c r="J3" t="n">
-        <v>6.75</v>
+        <v>6.78</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -721,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>457.63</v>
+        <v>458.97</v>
       </c>
       <c r="N3" t="n">
-        <v>425.78</v>
+        <v>426.43</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -767,7 +768,7 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="X3" t="n">
         <v>2</v>
@@ -776,16 +777,16 @@
         <v>0.41</v>
       </c>
       <c r="Z3" t="n">
-        <v>48800</v>
+        <v>49000</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6800</v>
+        <v>7000</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.19</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="4">
@@ -806,22 +807,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>176.2</v>
+        <v>178</v>
       </c>
       <c r="F4" t="n">
-        <v>70.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>1.73</v>
+        <v>2.66</v>
       </c>
       <c r="H4" t="n">
-        <v>1.07</v>
+        <v>0.53</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -834,10 +835,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>161.85</v>
+        <v>162.34</v>
       </c>
       <c r="N4" t="n">
-        <v>154.09</v>
+        <v>154.22</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -850,7 +851,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -876,29 +877,29 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSI過熱、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>177.1</v>
+        <v>176.2</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.9</v>
+        <v>1.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.51</v>
+        <v>1.02</v>
       </c>
       <c r="Z4" t="n">
-        <v>17620</v>
+        <v>17800</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1820</v>
+        <v>2000</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.52</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +920,22 @@
         <v>7993</v>
       </c>
       <c r="E5" t="n">
-        <v>8715</v>
+        <v>8776</v>
       </c>
       <c r="F5" t="n">
-        <v>78.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>6.92</v>
+        <v>7.31</v>
       </c>
       <c r="H5" t="n">
-        <v>0.74</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>81.84</v>
+        <v>110.31</v>
       </c>
       <c r="J5" t="n">
-        <v>-15.64</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -943,14 +944,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+2S</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>8018.41</v>
+        <v>8042.36</v>
       </c>
       <c r="N5" t="n">
-        <v>8329.299999999999</v>
+        <v>8321.610000000001</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -959,136 +960,23 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは買いシグナルです。
-・買われ過ぎ水準です。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>RSI過熱、25日線上、+2σ、MACD買い、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>8680</v>
-      </c>
-      <c r="X5" t="n">
-        <v>35</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>8715</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>7993</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>722</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>9.029999999999999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>トヨタ自動車</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>13</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2853.77</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3094</v>
-      </c>
-      <c r="F6" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I6" t="n">
-        <v>32.41</v>
-      </c>
-      <c r="J6" t="n">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>2947.05</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3100.14</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>🟢 強い買い</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>95</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -1099,6 +987,119 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>RSI過熱、25日線上、+1σ、MACD買い、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>8715</v>
+      </c>
+      <c r="X5" t="n">
+        <v>61</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>8776</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>7993</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>783</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>トヨタ自動車</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2853.77</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3089</v>
+      </c>
+      <c r="F6" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I6" t="n">
+        <v>35.18</v>
+      </c>
+      <c r="J6" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>2952.51</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3099.04</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>95</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは買いシグナルです。
+・買われ過ぎ水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
@@ -1106,25 +1107,25 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>3102</v>
+        <v>3094</v>
       </c>
       <c r="X6" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.26</v>
+        <v>-0.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>40222</v>
+        <v>40157</v>
       </c>
       <c r="AA6" t="n">
         <v>37099</v>
       </c>
       <c r="AB6" t="n">
-        <v>3123</v>
+        <v>3058</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.42</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="7">
@@ -1145,26 +1146,26 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4746</v>
+        <v>4823</v>
       </c>
       <c r="F7" t="n">
-        <v>48.2</v>
+        <v>57.4</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2</v>
+        <v>1.52</v>
       </c>
       <c r="H7" t="n">
-        <v>0.99</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-16.49</v>
+        <v>-7.07</v>
       </c>
       <c r="J7" t="n">
-        <v>-22.35</v>
+        <v>-19.3</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1173,10 +1174,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4696.42</v>
+        <v>4703.55</v>
       </c>
       <c r="N7" t="n">
-        <v>4727</v>
+        <v>4733.67</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1185,20 +1186,20 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1206,6 +1207,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
@@ -1215,29 +1217,29 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>押し目、MACD買い、上昇トレンド</t>
+          <t>RSI適正、25日線上、ゴールデンクロス、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4712</v>
+        <v>4746</v>
       </c>
       <c r="X7" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.72</v>
+        <v>1.62</v>
       </c>
       <c r="Z7" t="n">
-        <v>23730</v>
+        <v>24115</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>-245</v>
+        <v>140</v>
       </c>
       <c r="AC7" t="n">
-        <v>-1.02</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="8">
@@ -1258,26 +1260,26 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>9253</v>
+        <v>8955</v>
       </c>
       <c r="F8" t="n">
-        <v>49.4</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.53</v>
+        <v>-8.5</v>
       </c>
       <c r="H8" t="n">
-        <v>1.07</v>
+        <v>0.78</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.97</v>
+        <v>-80.06</v>
       </c>
       <c r="J8" t="n">
-        <v>138.52</v>
+        <v>94.8</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1286,10 +1288,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10846.17</v>
+        <v>10665</v>
       </c>
       <c r="N8" t="n">
-        <v>8566.030000000001</v>
+        <v>8593.57</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1298,11 +1300,11 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🔴 売り注意</t>
+          <t>🟠 利益確定検討</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1319,8 +1321,6 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは売りシグナルです。
-・デッドクロスが発生し、短期的な下落に注意が必要です。
-・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
@@ -1329,29 +1329,29 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、デッドクロス、MACD売り、反発局面</t>
+          <t>押し目、MACD売り、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>9095</v>
+        <v>9253</v>
       </c>
       <c r="X8" t="n">
-        <v>158</v>
+        <v>-298</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.74</v>
+        <v>-3.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>9253</v>
+        <v>8955</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-747</v>
+        <v>-1045</v>
       </c>
       <c r="AC8" t="n">
-        <v>-7.47</v>
+        <v>-10.45</v>
       </c>
     </row>
     <row r="9">
@@ -1372,22 +1372,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>13510</v>
+        <v>13060</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>-19.65</v>
+        <v>-21.4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>0.58</v>
       </c>
       <c r="I9" t="n">
-        <v>-1259.71</v>
+        <v>-1323.66</v>
       </c>
       <c r="J9" t="n">
-        <v>-770.14</v>
+        <v>-880.84</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>18462.44</v>
+        <v>18244.89</v>
       </c>
       <c r="N9" t="n">
-        <v>14692.5</v>
+        <v>14741.22</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1447,25 +1447,25 @@
         </is>
       </c>
       <c r="W9" t="n">
-        <v>13140</v>
+        <v>13510</v>
       </c>
       <c r="X9" t="n">
-        <v>370</v>
+        <v>-450</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.82</v>
+        <v>-3.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>13510</v>
+        <v>13060</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-42000</v>
+        <v>-42450</v>
       </c>
       <c r="AC9" t="n">
-        <v>-75.66</v>
+        <v>-76.47</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3755</v>
+        <v>3765</v>
       </c>
       <c r="F2" t="n">
-        <v>59.5</v>
+        <v>59.9</v>
       </c>
       <c r="G2" t="n">
-        <v>3.56</v>
+        <v>3.82</v>
       </c>
       <c r="H2" t="n">
-        <v>0.74</v>
+        <v>1.18</v>
       </c>
       <c r="I2" t="n">
-        <v>126.29</v>
+        <v>127.09</v>
       </c>
       <c r="J2" t="n">
-        <v>134.09</v>
+        <v>134.25</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3355.24</v>
+        <v>3355.37</v>
       </c>
       <c r="N2" t="n">
-        <v>2805.7</v>
+        <v>2805.75</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -658,22 +658,22 @@
         <v>3800</v>
       </c>
       <c r="X2" t="n">
-        <v>-45</v>
+        <v>-35</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.18</v>
+        <v>-0.92</v>
       </c>
       <c r="Z2" t="n">
-        <v>15020</v>
+        <v>15060</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4220</v>
+        <v>4260</v>
       </c>
       <c r="AC2" t="n">
-        <v>39.07</v>
+        <v>39.44</v>
       </c>
     </row>
     <row r="3">
@@ -694,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F3" t="n">
-        <v>58.3</v>
+        <v>57.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1.58</v>
+        <v>1.18</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3</v>
+        <v>0.59</v>
       </c>
       <c r="I3" t="n">
-        <v>6.92</v>
+        <v>6.76</v>
       </c>
       <c r="J3" t="n">
-        <v>6.78</v>
+        <v>6.75</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>458.97</v>
+        <v>458.95</v>
       </c>
       <c r="N3" t="n">
-        <v>426.43</v>
+        <v>426.42</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -771,22 +771,22 @@
         <v>488</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>49000</v>
+        <v>48800</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7000</v>
+        <v>6800</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.67</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="4">
@@ -807,19 +807,19 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>178</v>
+        <v>178.1</v>
       </c>
       <c r="F4" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="H4" t="n">
-        <v>0.53</v>
+        <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="J4" t="n">
         <v>1.84</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>162.34</v>
+        <v>162.35</v>
       </c>
       <c r="N4" t="n">
         <v>154.22</v>
@@ -884,22 +884,22 @@
         <v>176.2</v>
       </c>
       <c r="X4" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>17800</v>
+        <v>17810</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.66</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="5">
@@ -920,22 +920,22 @@
         <v>7993</v>
       </c>
       <c r="E5" t="n">
-        <v>8776</v>
+        <v>8699</v>
       </c>
       <c r="F5" t="n">
-        <v>79.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="G5" t="n">
-        <v>7.31</v>
+        <v>6.41</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="I5" t="n">
-        <v>110.31</v>
+        <v>104.17</v>
       </c>
       <c r="J5" t="n">
-        <v>9.550000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>8042.36</v>
+        <v>8041.33</v>
       </c>
       <c r="N5" t="n">
-        <v>8321.610000000001</v>
+        <v>8321.23</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -997,22 +997,22 @@
         <v>8715</v>
       </c>
       <c r="X5" t="n">
-        <v>61</v>
+        <v>-16</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.7</v>
+        <v>-0.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>8776</v>
+        <v>8699</v>
       </c>
       <c r="AA5" t="n">
         <v>7993</v>
       </c>
       <c r="AB5" t="n">
-        <v>783</v>
+        <v>706</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.800000000000001</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="6">
@@ -1033,22 +1033,22 @@
         <v>2853.77</v>
       </c>
       <c r="E6" t="n">
-        <v>3089</v>
+        <v>3084</v>
       </c>
       <c r="F6" t="n">
-        <v>71.2</v>
+        <v>70.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.95</v>
+        <v>3.79</v>
       </c>
       <c r="H6" t="n">
-        <v>0.38</v>
+        <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>35.18</v>
+        <v>34.78</v>
       </c>
       <c r="J6" t="n">
-        <v>14.75</v>
+        <v>14.67</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2952.51</v>
+        <v>2952.45</v>
       </c>
       <c r="N6" t="n">
-        <v>3099.04</v>
+        <v>3099.02</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1110,22 +1110,22 @@
         <v>3094</v>
       </c>
       <c r="X6" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.16</v>
+        <v>-0.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>40157</v>
+        <v>40092</v>
       </c>
       <c r="AA6" t="n">
         <v>37099</v>
       </c>
       <c r="AB6" t="n">
-        <v>3058</v>
+        <v>2993</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.24</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="7">
@@ -1146,26 +1146,26 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4823</v>
+        <v>4795</v>
       </c>
       <c r="F7" t="n">
-        <v>57.4</v>
+        <v>55.6</v>
       </c>
       <c r="G7" t="n">
-        <v>1.52</v>
+        <v>0.96</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="I7" t="n">
-        <v>-7.07</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-19.3</v>
+        <v>-19.74</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4703.55</v>
+        <v>4703.18</v>
       </c>
       <c r="N7" t="n">
-        <v>4733.67</v>
+        <v>4733.53</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1207,7 +1207,6 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
@@ -1217,29 +1216,29 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、ゴールデンクロス、MACD買い、上昇トレンド</t>
+          <t>RSI適正、25日線上、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>4746</v>
       </c>
       <c r="X7" t="n">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.62</v>
+        <v>1.03</v>
       </c>
       <c r="Z7" t="n">
-        <v>24115</v>
+        <v>23975</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1260,22 +1259,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>8955</v>
+        <v>8700</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>38.3</v>
       </c>
       <c r="G8" t="n">
-        <v>-8.5</v>
+        <v>-11.01</v>
       </c>
       <c r="H8" t="n">
-        <v>0.78</v>
+        <v>1.16</v>
       </c>
       <c r="I8" t="n">
-        <v>-80.06</v>
+        <v>-100.41</v>
       </c>
       <c r="J8" t="n">
-        <v>94.8</v>
+        <v>90.73</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1284,14 +1283,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>-1S</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10665</v>
+        <v>10661.6</v>
       </c>
       <c r="N8" t="n">
-        <v>8593.57</v>
+        <v>8592.290000000001</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1300,11 +1299,11 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟠 利益確定検討</t>
+          <t>🔴 売り注意</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1321,37 +1320,42 @@
           <t>【AI分析レポート】
 ・🟡 反発中
 ・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
+・25日線から大きく下に乖離しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、反発局面</t>
+          <t>25日線大幅割れ、-1σ、MACD売り、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
         <v>9253</v>
       </c>
       <c r="X8" t="n">
-        <v>-298</v>
+        <v>-553</v>
       </c>
       <c r="Y8" t="n">
-        <v>-3.22</v>
+        <v>-5.98</v>
       </c>
       <c r="Z8" t="n">
-        <v>8955</v>
+        <v>8700</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1045</v>
+        <v>-1300</v>
       </c>
       <c r="AC8" t="n">
-        <v>-10.45</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="9">
@@ -1372,22 +1376,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>13060</v>
+        <v>12595</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="G9" t="n">
-        <v>-21.4</v>
+        <v>-24.11</v>
       </c>
       <c r="H9" t="n">
-        <v>0.58</v>
+        <v>1.05</v>
       </c>
       <c r="I9" t="n">
-        <v>-1323.66</v>
+        <v>-1360.75</v>
       </c>
       <c r="J9" t="n">
-        <v>-880.84</v>
+        <v>-888.26</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1400,10 +1404,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>18244.89</v>
+        <v>18238.69</v>
       </c>
       <c r="N9" t="n">
-        <v>14741.22</v>
+        <v>14738.89</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1440,7 +1444,11 @@
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>RSI売られすぎ、25日線大幅割れ、-1σ、MACD売り、下降トレンド</t>
@@ -1450,22 +1458,22 @@
         <v>13510</v>
       </c>
       <c r="X9" t="n">
-        <v>-450</v>
+        <v>-915</v>
       </c>
       <c r="Y9" t="n">
-        <v>-3.33</v>
+        <v>-6.77</v>
       </c>
       <c r="Z9" t="n">
-        <v>13060</v>
+        <v>12595</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-42450</v>
+        <v>-42915</v>
       </c>
       <c r="AC9" t="n">
-        <v>-76.47</v>
+        <v>-77.31</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1494,104 +1494,104 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
+        <v>33.72</v>
+      </c>
+      <c r="F10" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-14.78</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="N10" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>🟠 利益確定検討</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>50</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・25日線から大きく下に乖離しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>RSI売られすぎ、25日線大幅割れ、-1σ、MACD売り、反発局面</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
         <v>35.57</v>
       </c>
-      <c r="F10" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>35.34</v>
-      </c>
-      <c r="N10" t="n">
-        <v>32.52</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>60</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・25日線から大きく下に乖離しています。
-・出来高が増加しています。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>25日線大幅割れ、出来高微増、-1σ、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W10" t="n">
-        <v>32.47</v>
-      </c>
       <c r="X10" t="n">
-        <v>3.1</v>
+        <v>-1.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.550000000000001</v>
+        <v>-5.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6077</v>
+        <v>-6079</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.42</v>
+        <v>-99.45</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3765</v>
+        <v>3650</v>
       </c>
       <c r="F2" t="n">
-        <v>59.9</v>
+        <v>58.1</v>
       </c>
       <c r="G2" t="n">
-        <v>3.82</v>
+        <v>0.31</v>
       </c>
       <c r="H2" t="n">
-        <v>1.18</v>
+        <v>0.6</v>
       </c>
       <c r="I2" t="n">
-        <v>127.09</v>
+        <v>104.43</v>
       </c>
       <c r="J2" t="n">
-        <v>134.25</v>
+        <v>128.29</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3355.37</v>
+        <v>3365.29</v>
       </c>
       <c r="N2" t="n">
-        <v>2805.75</v>
+        <v>2808.89</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -655,25 +655,25 @@
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3800</v>
+        <v>3765</v>
       </c>
       <c r="X2" t="n">
-        <v>-35</v>
+        <v>-115</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.92</v>
+        <v>-3.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>15060</v>
+        <v>14600</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4260</v>
+        <v>3800</v>
       </c>
       <c r="AC2" t="n">
-        <v>39.44</v>
+        <v>35.19</v>
       </c>
     </row>
     <row r="3">
@@ -694,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F3" t="n">
-        <v>57.5</v>
+        <v>60.2</v>
       </c>
       <c r="G3" t="n">
-        <v>1.18</v>
+        <v>0.67</v>
       </c>
       <c r="H3" t="n">
-        <v>0.59</v>
+        <v>0.9</v>
       </c>
       <c r="I3" t="n">
-        <v>6.76</v>
+        <v>6.07</v>
       </c>
       <c r="J3" t="n">
-        <v>6.75</v>
+        <v>6.62</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>458.95</v>
+        <v>459.91</v>
       </c>
       <c r="N3" t="n">
-        <v>426.42</v>
+        <v>427.06</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -754,8 +754,7 @@
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
-・MACDは買いシグナルです。
-・RSIは良好な水準です。
+・MACDは売りシグナルです。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -764,29 +763,29 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>488</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0.41</v>
       </c>
       <c r="Z3" t="n">
-        <v>48800</v>
+        <v>48600</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6800</v>
+        <v>6600</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.19</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="4">
@@ -807,22 +806,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>178.1</v>
+        <v>178.3</v>
       </c>
       <c r="F4" t="n">
-        <v>82.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="H4" t="n">
-        <v>1.02</v>
+        <v>0.76</v>
       </c>
       <c r="I4" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="J4" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -835,10 +834,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>162.35</v>
+        <v>162.81</v>
       </c>
       <c r="N4" t="n">
-        <v>154.22</v>
+        <v>154.36</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -881,61 +880,61 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>176.2</v>
+        <v>178.1</v>
       </c>
       <c r="X4" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.08</v>
+        <v>0.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>17810</v>
+        <v>17830</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>2010</v>
+        <v>2030</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.72</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7974.T</t>
+          <t>7203.T</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>任天堂</t>
+          <t>トヨタ自動車</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>7993</v>
+        <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>8699</v>
+        <v>3095</v>
       </c>
       <c r="F5" t="n">
-        <v>77.8</v>
+        <v>85.7</v>
       </c>
       <c r="G5" t="n">
-        <v>6.41</v>
+        <v>3.99</v>
       </c>
       <c r="H5" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="I5" t="n">
-        <v>104.17</v>
+        <v>37.12</v>
       </c>
       <c r="J5" t="n">
-        <v>8.33</v>
+        <v>19.16</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -948,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>8041.33</v>
+        <v>2957.1</v>
       </c>
       <c r="N5" t="n">
-        <v>8321.23</v>
+        <v>3098.25</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -994,61 +993,61 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>8715</v>
+        <v>3084</v>
       </c>
       <c r="X5" t="n">
-        <v>-16</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.18</v>
+        <v>0.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>8699</v>
+        <v>40235</v>
       </c>
       <c r="AA5" t="n">
-        <v>7993</v>
+        <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>706</v>
+        <v>3136</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.83</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7203.T</t>
+          <t>7974.T</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>トヨタ自動車</t>
+          <t>任天堂</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2853.77</v>
+        <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>3084</v>
+        <v>8615</v>
       </c>
       <c r="F6" t="n">
-        <v>70.3</v>
+        <v>78.2</v>
       </c>
       <c r="G6" t="n">
-        <v>3.79</v>
+        <v>5.21</v>
       </c>
       <c r="H6" t="n">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>34.78</v>
+        <v>113.78</v>
       </c>
       <c r="J6" t="n">
-        <v>14.67</v>
+        <v>29.42</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1061,10 +1060,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2952.45</v>
+        <v>8061.04</v>
       </c>
       <c r="N6" t="n">
-        <v>3099.02</v>
+        <v>8313.129999999999</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1073,20 +1072,20 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1103,29 +1102,29 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD買い、上昇トレンド</t>
+          <t>RSI過熱、25日線上、+1σ、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>3094</v>
+        <v>8699</v>
       </c>
       <c r="X6" t="n">
-        <v>-10</v>
+        <v>-84</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.32</v>
+        <v>-0.97</v>
       </c>
       <c r="Z6" t="n">
-        <v>40092</v>
+        <v>8615</v>
       </c>
       <c r="AA6" t="n">
-        <v>37099</v>
+        <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>2993</v>
+        <v>622</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.07</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="7">
@@ -1146,26 +1145,26 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4795</v>
+        <v>4734</v>
       </c>
       <c r="F7" t="n">
-        <v>55.6</v>
+        <v>52.9</v>
       </c>
       <c r="G7" t="n">
-        <v>0.96</v>
+        <v>-0.16</v>
       </c>
       <c r="H7" t="n">
-        <v>1.13</v>
+        <v>0.63</v>
       </c>
       <c r="I7" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.43</v>
       </c>
       <c r="J7" t="n">
-        <v>-19.74</v>
+        <v>-17.48</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1174,10 +1173,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4703.18</v>
+        <v>4708.58</v>
       </c>
       <c r="N7" t="n">
-        <v>4733.53</v>
+        <v>4740.03</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1207,6 +1206,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
+・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
 ・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
@@ -1216,29 +1216,29 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD買い、上昇トレンド</t>
+          <t>RSI適正、押し目、ゴールデンクロス、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4746</v>
+        <v>4795</v>
       </c>
       <c r="X7" t="n">
-        <v>49</v>
+        <v>-61</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.03</v>
+        <v>-1.27</v>
       </c>
       <c r="Z7" t="n">
-        <v>23975</v>
+        <v>23670</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>-305</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="8">
@@ -1259,22 +1259,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>8700</v>
+        <v>8039</v>
       </c>
       <c r="F8" t="n">
-        <v>38.3</v>
+        <v>34.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-11.01</v>
+        <v>-17.56</v>
       </c>
       <c r="H8" t="n">
-        <v>1.16</v>
+        <v>0.59</v>
       </c>
       <c r="I8" t="n">
-        <v>-100.41</v>
+        <v>-228.33</v>
       </c>
       <c r="J8" t="n">
-        <v>90.73</v>
+        <v>26.92</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1287,14 +1287,14 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10661.6</v>
+        <v>10498.14</v>
       </c>
       <c r="N8" t="n">
-        <v>8592.290000000001</v>
+        <v>8614.99</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>🟡 反発中</t>
+          <t>🔴 下降</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1318,12 +1318,12 @@
       <c r="T8" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟡 反発中
+・🔴 下降
 ・MACDは売りシグナルです。
 ・25日線から大きく下に乖離しています。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1333,29 +1333,29 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>25日線大幅割れ、-1σ、MACD売り、反発局面</t>
+          <t>25日線大幅割れ、-1σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>9253</v>
+        <v>8700</v>
       </c>
       <c r="X8" t="n">
-        <v>-553</v>
+        <v>-661</v>
       </c>
       <c r="Y8" t="n">
-        <v>-5.98</v>
+        <v>-7.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>8700</v>
+        <v>8039</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1300</v>
+        <v>-1961</v>
       </c>
       <c r="AC8" t="n">
-        <v>-13</v>
+        <v>-19.61</v>
       </c>
     </row>
     <row r="9">
@@ -1376,22 +1376,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>12595</v>
+        <v>12100</v>
       </c>
       <c r="F9" t="n">
-        <v>14.2</v>
+        <v>11.6</v>
       </c>
       <c r="G9" t="n">
-        <v>-24.11</v>
+        <v>-26.25</v>
       </c>
       <c r="H9" t="n">
-        <v>1.05</v>
+        <v>0.93</v>
       </c>
       <c r="I9" t="n">
-        <v>-1360.75</v>
+        <v>-1463.89</v>
       </c>
       <c r="J9" t="n">
-        <v>-888.26</v>
+        <v>-1003.39</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>18238.69</v>
+        <v>18061.09</v>
       </c>
       <c r="N9" t="n">
-        <v>14738.89</v>
+        <v>14781.72</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1444,36 +1444,32 @@
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>RSI売られすぎ、25日線大幅割れ、-1σ、MACD売り、下降トレンド</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>13510</v>
+        <v>12595</v>
       </c>
       <c r="X9" t="n">
-        <v>-915</v>
+        <v>-495</v>
       </c>
       <c r="Y9" t="n">
-        <v>-6.77</v>
+        <v>-3.93</v>
       </c>
       <c r="Z9" t="n">
-        <v>12595</v>
+        <v>12100</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-42915</v>
+        <v>-43410</v>
       </c>
       <c r="AC9" t="n">
-        <v>-77.31</v>
+        <v>-78.2</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3650</v>
+        <v>3665</v>
       </c>
       <c r="F2" t="n">
-        <v>58.1</v>
+        <v>58.7</v>
       </c>
       <c r="G2" t="n">
-        <v>0.31</v>
+        <v>0.71</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6</v>
+        <v>1.12</v>
       </c>
       <c r="I2" t="n">
-        <v>104.43</v>
+        <v>105.63</v>
       </c>
       <c r="J2" t="n">
-        <v>128.29</v>
+        <v>128.53</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3365.29</v>
+        <v>3365.49</v>
       </c>
       <c r="N2" t="n">
-        <v>2808.89</v>
+        <v>2808.97</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -658,22 +658,22 @@
         <v>3765</v>
       </c>
       <c r="X2" t="n">
-        <v>-115</v>
+        <v>-100</v>
       </c>
       <c r="Y2" t="n">
-        <v>-3.05</v>
+        <v>-2.66</v>
       </c>
       <c r="Z2" t="n">
-        <v>14600</v>
+        <v>14660</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>3800</v>
+        <v>3860</v>
       </c>
       <c r="AC2" t="n">
-        <v>35.19</v>
+        <v>35.74</v>
       </c>
     </row>
     <row r="3">
@@ -694,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F3" t="n">
-        <v>60.2</v>
+        <v>60.7</v>
       </c>
       <c r="G3" t="n">
-        <v>0.67</v>
+        <v>0.87</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9</v>
+        <v>1.35</v>
       </c>
       <c r="I3" t="n">
-        <v>6.07</v>
+        <v>6.15</v>
       </c>
       <c r="J3" t="n">
-        <v>6.62</v>
+        <v>6.63</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>459.91</v>
+        <v>459.92</v>
       </c>
       <c r="N3" t="n">
         <v>427.06</v>
@@ -770,22 +770,22 @@
         <v>488</v>
       </c>
       <c r="X3" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.41</v>
+        <v>-0.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>48600</v>
+        <v>48700</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6600</v>
+        <v>6700</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.71</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="4">
@@ -806,22 +806,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>178.3</v>
+        <v>174.8</v>
       </c>
       <c r="F4" t="n">
-        <v>85.59999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>2.76</v>
+        <v>0.82</v>
       </c>
       <c r="H4" t="n">
-        <v>0.76</v>
+        <v>1.32</v>
       </c>
       <c r="I4" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="J4" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -830,14 +830,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>162.81</v>
+        <v>162.76</v>
       </c>
       <c r="N4" t="n">
-        <v>154.36</v>
+        <v>154.34</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -867,8 +867,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・買われ過ぎ水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -876,29 +875,29 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSI過熱、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSIやや過熱、25日線上、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>178.1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2</v>
+        <v>-3.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.11</v>
+        <v>-1.85</v>
       </c>
       <c r="Z4" t="n">
-        <v>17830</v>
+        <v>17480</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>2030</v>
+        <v>1680</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.85</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +918,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3095</v>
+        <v>3105</v>
       </c>
       <c r="F5" t="n">
-        <v>85.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>3.99</v>
+        <v>4.32</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6</v>
+        <v>1.25</v>
       </c>
       <c r="I5" t="n">
-        <v>37.12</v>
+        <v>37.92</v>
       </c>
       <c r="J5" t="n">
-        <v>19.16</v>
+        <v>19.32</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,10 +946,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2957.1</v>
+        <v>2957.23</v>
       </c>
       <c r="N5" t="n">
-        <v>3098.25</v>
+        <v>3098.3</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -996,22 +995,22 @@
         <v>3084</v>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="Z5" t="n">
-        <v>40235</v>
+        <v>40365</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>3136</v>
+        <v>3266</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.449999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1032,22 +1031,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8615</v>
+        <v>8539</v>
       </c>
       <c r="F6" t="n">
-        <v>78.2</v>
+        <v>74</v>
       </c>
       <c r="G6" t="n">
-        <v>5.21</v>
+        <v>4.32</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.36</v>
       </c>
       <c r="I6" t="n">
-        <v>113.78</v>
+        <v>107.72</v>
       </c>
       <c r="J6" t="n">
-        <v>29.42</v>
+        <v>28.2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1060,10 +1059,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>8061.04</v>
+        <v>8060.03</v>
       </c>
       <c r="N6" t="n">
-        <v>8313.129999999999</v>
+        <v>8312.75</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1072,20 +1071,20 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1102,29 +1101,29 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSI過熱、25日線上、+1σ、MACD買い、上昇トレンド</t>
+          <t>RSIやや過熱、25日線上、+1σ、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>8699</v>
       </c>
       <c r="X6" t="n">
-        <v>-84</v>
+        <v>-160</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.97</v>
+        <v>-1.84</v>
       </c>
       <c r="Z6" t="n">
-        <v>8615</v>
+        <v>8539</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>622</v>
+        <v>546</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.78</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="7">
@@ -1145,22 +1144,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4734</v>
+        <v>4715</v>
       </c>
       <c r="F7" t="n">
-        <v>52.9</v>
+        <v>51.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.16</v>
+        <v>-0.55</v>
       </c>
       <c r="H7" t="n">
-        <v>0.63</v>
+        <v>1.23</v>
       </c>
       <c r="I7" t="n">
-        <v>-8.43</v>
+        <v>-9.94</v>
       </c>
       <c r="J7" t="n">
-        <v>-17.48</v>
+        <v>-17.78</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1173,10 +1172,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4708.58</v>
+        <v>4708.33</v>
       </c>
       <c r="N7" t="n">
-        <v>4740.03</v>
+        <v>4739.94</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1223,22 +1222,22 @@
         <v>4795</v>
       </c>
       <c r="X7" t="n">
-        <v>-61</v>
+        <v>-80</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.27</v>
+        <v>-1.67</v>
       </c>
       <c r="Z7" t="n">
-        <v>23670</v>
+        <v>23575</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>-305</v>
+        <v>-400</v>
       </c>
       <c r="AC7" t="n">
-        <v>-1.27</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="8">
@@ -1259,22 +1258,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>8039</v>
+        <v>8364</v>
       </c>
       <c r="F8" t="n">
-        <v>34.5</v>
+        <v>36.3</v>
       </c>
       <c r="G8" t="n">
-        <v>-17.56</v>
+        <v>-14.34</v>
       </c>
       <c r="H8" t="n">
-        <v>0.59</v>
+        <v>0.97</v>
       </c>
       <c r="I8" t="n">
-        <v>-228.33</v>
+        <v>-202.41</v>
       </c>
       <c r="J8" t="n">
-        <v>26.92</v>
+        <v>32.11</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1287,10 +1286,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10498.14</v>
+        <v>10502.47</v>
       </c>
       <c r="N8" t="n">
-        <v>8614.99</v>
+        <v>8616.620000000001</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1326,11 +1325,7 @@
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>25日線大幅割れ、-1σ、MACD売り、下降トレンド</t>
@@ -1340,22 +1335,22 @@
         <v>8700</v>
       </c>
       <c r="X8" t="n">
-        <v>-661</v>
+        <v>-336</v>
       </c>
       <c r="Y8" t="n">
-        <v>-7.6</v>
+        <v>-3.86</v>
       </c>
       <c r="Z8" t="n">
-        <v>8039</v>
+        <v>8364</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1961</v>
+        <v>-1636</v>
       </c>
       <c r="AC8" t="n">
-        <v>-19.61</v>
+        <v>-16.36</v>
       </c>
     </row>
     <row r="9">
@@ -1376,22 +1371,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>12100</v>
+        <v>12755</v>
       </c>
       <c r="F9" t="n">
-        <v>11.6</v>
+        <v>13.8</v>
       </c>
       <c r="G9" t="n">
-        <v>-26.25</v>
+        <v>-22.38</v>
       </c>
       <c r="H9" t="n">
-        <v>0.93</v>
+        <v>1.4</v>
       </c>
       <c r="I9" t="n">
-        <v>-1463.89</v>
+        <v>-1411.64</v>
       </c>
       <c r="J9" t="n">
-        <v>-1003.39</v>
+        <v>-992.9400000000001</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1404,10 +1399,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>18061.09</v>
+        <v>18069.82</v>
       </c>
       <c r="N9" t="n">
-        <v>14781.72</v>
+        <v>14784.99</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1454,22 +1449,22 @@
         <v>12595</v>
       </c>
       <c r="X9" t="n">
-        <v>-495</v>
+        <v>160</v>
       </c>
       <c r="Y9" t="n">
-        <v>-3.93</v>
+        <v>1.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>12100</v>
+        <v>12755</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-43410</v>
+        <v>-42755</v>
       </c>
       <c r="AC9" t="n">
-        <v>-78.2</v>
+        <v>-77.02</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1485,22 +1485,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>33.72</v>
+        <v>32.94</v>
       </c>
       <c r="F10" t="n">
-        <v>26.7</v>
+        <v>26.3</v>
       </c>
       <c r="G10" t="n">
-        <v>-14.78</v>
+        <v>-16.23</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9</v>
+        <v>0.65</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.59</v>
+        <v>-1.73</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6</v>
+        <v>-0.83</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>35.42</v>
+        <v>35.48</v>
       </c>
       <c r="N10" t="n">
-        <v>32.53</v>
+        <v>32.55</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1553,36 +1553,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>⚠️ 急落</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>RSI売られすぎ、25日線大幅割れ、-1σ、MACD売り、反発局面</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>35.57</v>
+        <v>33.72</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.85</v>
+        <v>-0.78</v>
       </c>
       <c r="Y10" t="n">
-        <v>-5.2</v>
+        <v>-2.31</v>
       </c>
       <c r="Z10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6079</v>
+        <v>-6080</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.45</v>
+        <v>-99.45999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3665</v>
+        <v>3660</v>
       </c>
       <c r="F2" t="n">
-        <v>58.7</v>
+        <v>53.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.71</v>
+        <v>0.22</v>
       </c>
       <c r="H2" t="n">
-        <v>1.12</v>
+        <v>0.44</v>
       </c>
       <c r="I2" t="n">
-        <v>105.63</v>
+        <v>87.2</v>
       </c>
       <c r="J2" t="n">
-        <v>128.53</v>
+        <v>120.26</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3365.49</v>
+        <v>3375.16</v>
       </c>
       <c r="N2" t="n">
-        <v>2808.97</v>
+        <v>2811.66</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -655,25 +655,25 @@
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3765</v>
+        <v>3665</v>
       </c>
       <c r="X2" t="n">
-        <v>-100</v>
+        <v>-5</v>
       </c>
       <c r="Y2" t="n">
-        <v>-2.66</v>
+        <v>-0.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>14660</v>
+        <v>14640</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>3860</v>
+        <v>3840</v>
       </c>
       <c r="AC2" t="n">
-        <v>35.74</v>
+        <v>35.56</v>
       </c>
     </row>
     <row r="3">
@@ -694,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="F3" t="n">
-        <v>60.7</v>
+        <v>61.8</v>
       </c>
       <c r="G3" t="n">
-        <v>0.87</v>
+        <v>1.56</v>
       </c>
       <c r="H3" t="n">
-        <v>1.35</v>
+        <v>0.52</v>
       </c>
       <c r="I3" t="n">
-        <v>6.15</v>
+        <v>5.93</v>
       </c>
       <c r="J3" t="n">
-        <v>6.63</v>
+        <v>6.49</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>459.92</v>
+        <v>460.75</v>
       </c>
       <c r="N3" t="n">
-        <v>427.06</v>
+        <v>427.69</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -767,25 +767,25 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="X3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.2</v>
+        <v>0.82</v>
       </c>
       <c r="Z3" t="n">
-        <v>48700</v>
+        <v>49100</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6700</v>
+        <v>7100</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.95</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="4">
@@ -806,22 +806,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>174.8</v>
+        <v>177.5</v>
       </c>
       <c r="F4" t="n">
-        <v>66.40000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.82</v>
+        <v>2.33</v>
       </c>
       <c r="H4" t="n">
-        <v>1.32</v>
+        <v>0.42</v>
       </c>
       <c r="I4" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="J4" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -830,14 +830,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>162.76</v>
+        <v>163.21</v>
       </c>
       <c r="N4" t="n">
-        <v>154.34</v>
+        <v>154.47</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -867,7 +867,8 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
+・買われ過ぎ水準です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
         </is>
@@ -875,29 +876,29 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、MACD買い、長期上昇</t>
+          <t>RSIやや過熱、25日線上、+1σ、MACD買い、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>178.1</v>
+        <v>174.8</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.3</v>
+        <v>2.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.85</v>
+        <v>1.54</v>
       </c>
       <c r="Z4" t="n">
-        <v>17480</v>
+        <v>17750</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1680</v>
+        <v>1950</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.63</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="5">
@@ -918,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3105</v>
+        <v>3131</v>
       </c>
       <c r="F5" t="n">
-        <v>86.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>4.32</v>
+        <v>4.96</v>
       </c>
       <c r="H5" t="n">
-        <v>1.25</v>
+        <v>0.45</v>
       </c>
       <c r="I5" t="n">
-        <v>37.92</v>
+        <v>42.02</v>
       </c>
       <c r="J5" t="n">
-        <v>19.32</v>
+        <v>23.86</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -946,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2957.23</v>
+        <v>2961.9</v>
       </c>
       <c r="N5" t="n">
-        <v>3098.3</v>
+        <v>3097.61</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -992,25 +993,25 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>3084</v>
+        <v>3105</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.68</v>
+        <v>0.84</v>
       </c>
       <c r="Z5" t="n">
-        <v>40365</v>
+        <v>40703</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>3266</v>
+        <v>3604</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1031,22 +1032,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8539</v>
+        <v>8584</v>
       </c>
       <c r="F6" t="n">
-        <v>74</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>4.32</v>
+        <v>4.63</v>
       </c>
       <c r="H6" t="n">
-        <v>1.36</v>
+        <v>0.42</v>
       </c>
       <c r="I6" t="n">
-        <v>107.72</v>
+        <v>112.86</v>
       </c>
       <c r="J6" t="n">
-        <v>28.2</v>
+        <v>45.13</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1059,10 +1060,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>8060.03</v>
+        <v>8079.39</v>
       </c>
       <c r="N6" t="n">
-        <v>8312.75</v>
+        <v>8303.93</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1071,20 +1072,20 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1101,29 +1102,29 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD買い、上昇トレンド</t>
+          <t>RSI過熱、25日線上、+1σ、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>8699</v>
+        <v>8539</v>
       </c>
       <c r="X6" t="n">
-        <v>-160</v>
+        <v>45</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.84</v>
+        <v>0.53</v>
       </c>
       <c r="Z6" t="n">
-        <v>8539</v>
+        <v>8584</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>546</v>
+        <v>591</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.83</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="7">
@@ -1144,38 +1145,38 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4715</v>
+        <v>4935</v>
       </c>
       <c r="F7" t="n">
-        <v>51.5</v>
+        <v>62.4</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.55</v>
+        <v>4.01</v>
       </c>
       <c r="H7" t="n">
-        <v>1.23</v>
+        <v>0.74</v>
       </c>
       <c r="I7" t="n">
-        <v>-9.94</v>
+        <v>7.22</v>
       </c>
       <c r="J7" t="n">
-        <v>-17.78</v>
+        <v>-12.78</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+2S</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4708.33</v>
+        <v>4715.47</v>
       </c>
       <c r="N7" t="n">
-        <v>4739.94</v>
+        <v>4747.39</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1188,7 +1189,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1205,9 +1206,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
-・ゴールデンクロスが発生し、上昇トレンド入りの可能性があります。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -1215,29 +1214,29 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、ゴールデンクロス、MACD買い、上昇トレンド</t>
+          <t>RSI適正、25日線上、+2σ、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4795</v>
+        <v>4715</v>
       </c>
       <c r="X7" t="n">
-        <v>-80</v>
+        <v>220</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.67</v>
+        <v>4.67</v>
       </c>
       <c r="Z7" t="n">
-        <v>23575</v>
+        <v>24675</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>-400</v>
+        <v>700</v>
       </c>
       <c r="AC7" t="n">
-        <v>-1.67</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="8">
@@ -1258,22 +1257,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>8364</v>
+        <v>8478</v>
       </c>
       <c r="F8" t="n">
-        <v>36.3</v>
+        <v>33.3</v>
       </c>
       <c r="G8" t="n">
-        <v>-14.34</v>
+        <v>-12.93</v>
       </c>
       <c r="H8" t="n">
-        <v>0.97</v>
+        <v>0.67</v>
       </c>
       <c r="I8" t="n">
-        <v>-202.41</v>
+        <v>-270.92</v>
       </c>
       <c r="J8" t="n">
-        <v>32.11</v>
+        <v>-28.5</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1286,10 +1285,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10502.47</v>
+        <v>10342.73</v>
       </c>
       <c r="N8" t="n">
-        <v>8616.620000000001</v>
+        <v>8641.4</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1332,25 +1331,25 @@
         </is>
       </c>
       <c r="W8" t="n">
-        <v>8700</v>
+        <v>8364</v>
       </c>
       <c r="X8" t="n">
-        <v>-336</v>
+        <v>114</v>
       </c>
       <c r="Y8" t="n">
-        <v>-3.86</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>8364</v>
+        <v>8478</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1636</v>
+        <v>-1522</v>
       </c>
       <c r="AC8" t="n">
-        <v>-16.36</v>
+        <v>-15.22</v>
       </c>
     </row>
     <row r="9">
@@ -1371,22 +1370,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>12755</v>
+        <v>12380</v>
       </c>
       <c r="F9" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-22.38</v>
+        <v>-23.76</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4</v>
+        <v>0.64</v>
       </c>
       <c r="I9" t="n">
-        <v>-1411.64</v>
+        <v>-1465.34</v>
       </c>
       <c r="J9" t="n">
-        <v>-992.9400000000001</v>
+        <v>-1087.42</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1399,10 +1398,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>18069.82</v>
+        <v>17864.67</v>
       </c>
       <c r="N9" t="n">
-        <v>14784.99</v>
+        <v>14828.9</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1446,25 +1445,25 @@
         </is>
       </c>
       <c r="W9" t="n">
-        <v>12595</v>
+        <v>12755</v>
       </c>
       <c r="X9" t="n">
-        <v>160</v>
+        <v>-375</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.27</v>
+        <v>-2.94</v>
       </c>
       <c r="Z9" t="n">
-        <v>12755</v>
+        <v>12380</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-42755</v>
+        <v>-43130</v>
       </c>
       <c r="AC9" t="n">
-        <v>-77.02</v>
+        <v>-77.7</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3660</v>
+        <v>3715</v>
       </c>
       <c r="F2" t="n">
-        <v>53.3</v>
+        <v>55</v>
       </c>
       <c r="G2" t="n">
-        <v>0.22</v>
+        <v>1.66</v>
       </c>
       <c r="H2" t="n">
-        <v>0.44</v>
+        <v>0.97</v>
       </c>
       <c r="I2" t="n">
-        <v>87.2</v>
+        <v>91.59</v>
       </c>
       <c r="J2" t="n">
-        <v>120.26</v>
+        <v>121.14</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3375.16</v>
+        <v>3375.89</v>
       </c>
       <c r="N2" t="n">
-        <v>2811.66</v>
+        <v>2811.94</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -658,22 +658,22 @@
         <v>3665</v>
       </c>
       <c r="X2" t="n">
-        <v>-5</v>
+        <v>50</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.14</v>
+        <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>14640</v>
+        <v>14860</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>3840</v>
+        <v>4060</v>
       </c>
       <c r="AC2" t="n">
-        <v>35.56</v>
+        <v>37.59</v>
       </c>
     </row>
     <row r="3">
@@ -694,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F3" t="n">
-        <v>61.8</v>
+        <v>61.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="H3" t="n">
-        <v>0.52</v>
+        <v>1.15</v>
       </c>
       <c r="I3" t="n">
-        <v>5.93</v>
+        <v>5.85</v>
       </c>
       <c r="J3" t="n">
-        <v>6.49</v>
+        <v>6.48</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>460.75</v>
+        <v>460.73</v>
       </c>
       <c r="N3" t="n">
         <v>427.69</v>
@@ -770,22 +770,22 @@
         <v>487</v>
       </c>
       <c r="X3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.82</v>
+        <v>0.62</v>
       </c>
       <c r="Z3" t="n">
-        <v>49100</v>
+        <v>49000</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7100</v>
+        <v>7000</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.9</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="4">
@@ -806,22 +806,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>177.5</v>
+        <v>176.4</v>
       </c>
       <c r="F4" t="n">
-        <v>71.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33</v>
+        <v>1.72</v>
       </c>
       <c r="H4" t="n">
-        <v>0.42</v>
+        <v>0.84</v>
       </c>
       <c r="I4" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>163.21</v>
+        <v>163.19</v>
       </c>
       <c r="N4" t="n">
-        <v>154.47</v>
+        <v>154.46</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -867,7 +867,6 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは買いシグナルです。
-・買われ過ぎ水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -883,22 +882,22 @@
         <v>174.8</v>
       </c>
       <c r="X4" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.54</v>
+        <v>0.92</v>
       </c>
       <c r="Z4" t="n">
-        <v>17750</v>
+        <v>17640</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1950</v>
+        <v>1840</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.34</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +918,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3131</v>
+        <v>3117</v>
       </c>
       <c r="F5" t="n">
-        <v>85.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="G5" t="n">
-        <v>4.96</v>
+        <v>4.51</v>
       </c>
       <c r="H5" t="n">
-        <v>0.45</v>
+        <v>0.92</v>
       </c>
       <c r="I5" t="n">
-        <v>42.02</v>
+        <v>40.9</v>
       </c>
       <c r="J5" t="n">
-        <v>23.86</v>
+        <v>23.64</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,10 +946,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2961.9</v>
+        <v>2961.72</v>
       </c>
       <c r="N5" t="n">
-        <v>3097.61</v>
+        <v>3097.54</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -996,22 +995,22 @@
         <v>3105</v>
       </c>
       <c r="X5" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.84</v>
+        <v>0.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>40703</v>
+        <v>40521</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>3604</v>
+        <v>3422</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.710000000000001</v>
+        <v>9.220000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1032,22 +1031,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8584</v>
+        <v>8576</v>
       </c>
       <c r="F6" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="G6" t="n">
-        <v>4.63</v>
+        <v>4.53</v>
       </c>
       <c r="H6" t="n">
-        <v>0.42</v>
+        <v>0.73</v>
       </c>
       <c r="I6" t="n">
-        <v>112.86</v>
+        <v>112.22</v>
       </c>
       <c r="J6" t="n">
-        <v>45.13</v>
+        <v>45.01</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1060,10 +1059,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>8079.39</v>
+        <v>8079.28</v>
       </c>
       <c r="N6" t="n">
-        <v>8303.93</v>
+        <v>8303.889999999999</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1109,22 +1108,22 @@
         <v>8539</v>
       </c>
       <c r="X6" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.53</v>
+        <v>0.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>8584</v>
+        <v>8576</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.39</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="7">
@@ -1145,22 +1144,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4935</v>
+        <v>4910</v>
       </c>
       <c r="F7" t="n">
-        <v>62.4</v>
+        <v>61.4</v>
       </c>
       <c r="G7" t="n">
-        <v>4.01</v>
+        <v>3.51</v>
       </c>
       <c r="H7" t="n">
-        <v>0.74</v>
+        <v>1.25</v>
       </c>
       <c r="I7" t="n">
-        <v>7.22</v>
+        <v>5.22</v>
       </c>
       <c r="J7" t="n">
-        <v>-12.78</v>
+        <v>-13.18</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1169,14 +1168,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+2S</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4715.47</v>
+        <v>4715.13</v>
       </c>
       <c r="N7" t="n">
-        <v>4747.39</v>
+        <v>4747.27</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1189,7 +1188,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1206,7 +1205,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -1214,29 +1213,29 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+2σ、MACD買い、上昇トレンド</t>
+          <t>RSI適正、25日線上、+1σ、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>4715</v>
       </c>
       <c r="X7" t="n">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.67</v>
+        <v>4.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>24675</v>
+        <v>24550</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>700</v>
+        <v>575</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.92</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="8">
@@ -1257,22 +1256,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>8478</v>
+        <v>8572</v>
       </c>
       <c r="F8" t="n">
-        <v>33.3</v>
+        <v>34.3</v>
       </c>
       <c r="G8" t="n">
-        <v>-12.93</v>
+        <v>-12</v>
       </c>
       <c r="H8" t="n">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="I8" t="n">
-        <v>-270.92</v>
+        <v>-263.42</v>
       </c>
       <c r="J8" t="n">
-        <v>-28.5</v>
+        <v>-27</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1285,10 +1284,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10342.73</v>
+        <v>10343.99</v>
       </c>
       <c r="N8" t="n">
-        <v>8641.4</v>
+        <v>8641.870000000001</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1334,22 +1333,22 @@
         <v>8364</v>
       </c>
       <c r="X8" t="n">
-        <v>114</v>
+        <v>208</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>2.49</v>
       </c>
       <c r="Z8" t="n">
-        <v>8478</v>
+        <v>8572</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1522</v>
+        <v>-1428</v>
       </c>
       <c r="AC8" t="n">
-        <v>-15.22</v>
+        <v>-14.28</v>
       </c>
     </row>
     <row r="9">
@@ -1370,22 +1369,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>12380</v>
+        <v>12550</v>
       </c>
       <c r="F9" t="n">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
       <c r="G9" t="n">
-        <v>-23.76</v>
+        <v>-22.74</v>
       </c>
       <c r="H9" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="I9" t="n">
-        <v>-1465.34</v>
+        <v>-1451.78</v>
       </c>
       <c r="J9" t="n">
-        <v>-1087.42</v>
+        <v>-1084.7</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1398,10 +1397,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>17864.67</v>
+        <v>17866.93</v>
       </c>
       <c r="N9" t="n">
-        <v>14828.9</v>
+        <v>14829.75</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1448,22 +1447,22 @@
         <v>12755</v>
       </c>
       <c r="X9" t="n">
-        <v>-375</v>
+        <v>-205</v>
       </c>
       <c r="Y9" t="n">
-        <v>-2.94</v>
+        <v>-1.61</v>
       </c>
       <c r="Z9" t="n">
-        <v>12380</v>
+        <v>12550</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-43130</v>
+        <v>-42960</v>
       </c>
       <c r="AC9" t="n">
-        <v>-77.7</v>
+        <v>-77.39</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1483,22 +1483,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>32.94</v>
+        <v>32.69</v>
       </c>
       <c r="F10" t="n">
-        <v>26.3</v>
+        <v>25.1</v>
       </c>
       <c r="G10" t="n">
-        <v>-16.23</v>
+        <v>-16.14</v>
       </c>
       <c r="H10" t="n">
-        <v>0.65</v>
+        <v>0.52</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.73</v>
+        <v>-1.84</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.83</v>
+        <v>-1.03</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>35.48</v>
+        <v>35.54</v>
       </c>
       <c r="N10" t="n">
-        <v>32.55</v>
+        <v>32.56</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1558,13 +1558,13 @@
         </is>
       </c>
       <c r="W10" t="n">
-        <v>33.72</v>
+        <v>32.94</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.78</v>
+        <v>-0.25</v>
       </c>
       <c r="Y10" t="n">
-        <v>-2.31</v>
+        <v>-0.76</v>
       </c>
       <c r="Z10" t="n">
         <v>33</v>
@@ -1576,7 +1576,7 @@
         <v>-6080</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.45999999999999</v>
+        <v>-99.47</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -584,19 +584,19 @@
         <v>3715</v>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>47.6</v>
       </c>
       <c r="G2" t="n">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="H2" t="n">
-        <v>0.97</v>
+        <v>0.37</v>
       </c>
       <c r="I2" t="n">
-        <v>91.59</v>
+        <v>79.55</v>
       </c>
       <c r="J2" t="n">
-        <v>121.14</v>
+        <v>112.82</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3375.89</v>
+        <v>3384.96</v>
       </c>
       <c r="N2" t="n">
-        <v>2811.94</v>
+        <v>2815.4</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,20 +621,20 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -651,17 +651,17 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3665</v>
+        <v>3715</v>
       </c>
       <c r="X2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>14860</v>
@@ -694,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F3" t="n">
-        <v>61.5</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="H3" t="n">
-        <v>1.15</v>
+        <v>0.34</v>
       </c>
       <c r="I3" t="n">
-        <v>5.85</v>
+        <v>5.62</v>
       </c>
       <c r="J3" t="n">
-        <v>6.48</v>
+        <v>6.3</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>460.73</v>
+        <v>461.52</v>
       </c>
       <c r="N3" t="n">
-        <v>427.69</v>
+        <v>428.33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -751,6 +751,119 @@
         </is>
       </c>
       <c r="T3" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>490</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>49100</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>7100</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>175.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>163.6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>154.57</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>95</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -760,144 +873,32 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>487</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>49000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>42000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>7000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>16.67</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>9432.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NTT</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>158</v>
-      </c>
-      <c r="E4" t="n">
-        <v>176.4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>163.19</v>
-      </c>
-      <c r="N4" t="n">
-        <v>154.46</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>🟢 強い買い</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>100</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは買いシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD買い、長期上昇</t>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>174.8</v>
+        <v>176.4</v>
       </c>
       <c r="X4" t="n">
-        <v>1.6</v>
+        <v>-1.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.92</v>
+        <v>-0.74</v>
       </c>
       <c r="Z4" t="n">
-        <v>17640</v>
+        <v>17510</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1840</v>
+        <v>1710</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.65</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="5">
@@ -918,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3117</v>
+        <v>3107</v>
       </c>
       <c r="F5" t="n">
-        <v>85</v>
+        <v>80.2</v>
       </c>
       <c r="G5" t="n">
-        <v>4.51</v>
+        <v>3.98</v>
       </c>
       <c r="H5" t="n">
-        <v>0.92</v>
+        <v>0.46</v>
       </c>
       <c r="I5" t="n">
-        <v>40.9</v>
+        <v>41.98</v>
       </c>
       <c r="J5" t="n">
-        <v>23.64</v>
+        <v>27.31</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -946,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2961.72</v>
+        <v>2964.82</v>
       </c>
       <c r="N5" t="n">
-        <v>3097.54</v>
+        <v>3096.7</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -992,25 +993,25 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>3105</v>
+        <v>3117</v>
       </c>
       <c r="X5" t="n">
-        <v>12</v>
+        <v>-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.39</v>
+        <v>-0.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>40521</v>
+        <v>40391</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>3422</v>
+        <v>3292</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.220000000000001</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1031,22 +1032,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8576</v>
+        <v>8501</v>
       </c>
       <c r="F6" t="n">
-        <v>80.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>4.53</v>
+        <v>3.43</v>
       </c>
       <c r="H6" t="n">
-        <v>0.73</v>
+        <v>0.52</v>
       </c>
       <c r="I6" t="n">
-        <v>112.22</v>
+        <v>108.48</v>
       </c>
       <c r="J6" t="n">
-        <v>45.01</v>
+        <v>57.7</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1055,14 +1056,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>8079.28</v>
+        <v>8098.85</v>
       </c>
       <c r="N6" t="n">
-        <v>8303.889999999999</v>
+        <v>8293.459999999999</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1093,7 +1094,7 @@
 ・🟢 上昇
 ・MACDは買いシグナルです。
 ・買われ過ぎ水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -1101,29 +1102,29 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSI過熱、25日線上、+1σ、MACD買い、上昇トレンド</t>
+          <t>RSI過熱、25日線上、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>8539</v>
+        <v>8576</v>
       </c>
       <c r="X6" t="n">
-        <v>37</v>
+        <v>-75</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.43</v>
+        <v>-0.87</v>
       </c>
       <c r="Z6" t="n">
-        <v>8576</v>
+        <v>8501</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>583</v>
+        <v>508</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.29</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="7">
@@ -1144,22 +1145,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4910</v>
+        <v>4905</v>
       </c>
       <c r="F7" t="n">
-        <v>61.4</v>
+        <v>60.9</v>
       </c>
       <c r="G7" t="n">
-        <v>3.51</v>
+        <v>3.38</v>
       </c>
       <c r="H7" t="n">
-        <v>1.25</v>
+        <v>0.37</v>
       </c>
       <c r="I7" t="n">
-        <v>5.22</v>
+        <v>16.65</v>
       </c>
       <c r="J7" t="n">
-        <v>-13.18</v>
+        <v>-7.22</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1172,10 +1173,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4715.13</v>
+        <v>4721.21</v>
       </c>
       <c r="N7" t="n">
-        <v>4747.27</v>
+        <v>4754.54</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1217,25 +1218,25 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4715</v>
+        <v>4910</v>
       </c>
       <c r="X7" t="n">
-        <v>195</v>
+        <v>-5</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.14</v>
+        <v>-0.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>24550</v>
+        <v>24525</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>575</v>
+        <v>550</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="8">
@@ -1256,22 +1257,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>8572</v>
+        <v>8736</v>
       </c>
       <c r="F8" t="n">
-        <v>34.3</v>
+        <v>28.7</v>
       </c>
       <c r="G8" t="n">
-        <v>-12</v>
+        <v>-10.1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.98</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-263.42</v>
+        <v>-295.14</v>
       </c>
       <c r="J8" t="n">
-        <v>-27</v>
+        <v>-80.63</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1284,71 +1285,72 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10343.99</v>
+        <v>10216.55</v>
       </c>
       <c r="N8" t="n">
-        <v>8641.870000000001</v>
+        <v>8668.15</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>🔴 下降</t>
+          <t>🟡 反発中</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🔴 売り注意</t>
+          <t>🟠 利益確定検討</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>★☆☆☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🔴 下降
+・🟡 反発中
 ・MACDは売りシグナルです。
+・売られ過ぎ水準です。
 ・25日線から大きく下に乖離しています。
 ・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>25日線大幅割れ、-1σ、MACD売り、下降トレンド</t>
+          <t>RSI売られすぎ、25日線大幅割れ、-1σ、MACD売り、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>8364</v>
+        <v>8572</v>
       </c>
       <c r="X8" t="n">
-        <v>208</v>
+        <v>164</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.49</v>
+        <v>1.91</v>
       </c>
       <c r="Z8" t="n">
-        <v>8572</v>
+        <v>8736</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1428</v>
+        <v>-1264</v>
       </c>
       <c r="AC8" t="n">
-        <v>-14.28</v>
+        <v>-12.64</v>
       </c>
     </row>
     <row r="9">
@@ -1369,22 +1371,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>12550</v>
+        <v>12570</v>
       </c>
       <c r="F9" t="n">
-        <v>13.8</v>
+        <v>14.6</v>
       </c>
       <c r="G9" t="n">
-        <v>-22.74</v>
+        <v>-21.78</v>
       </c>
       <c r="H9" t="n">
-        <v>0.95</v>
+        <v>0.78</v>
       </c>
       <c r="I9" t="n">
-        <v>-1451.78</v>
+        <v>-1465.08</v>
       </c>
       <c r="J9" t="n">
-        <v>-1084.7</v>
+        <v>-1160.78</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1397,10 +1399,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>17866.93</v>
+        <v>17671.91</v>
       </c>
       <c r="N9" t="n">
-        <v>14829.75</v>
+        <v>14873.58</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1444,25 +1446,25 @@
         </is>
       </c>
       <c r="W9" t="n">
-        <v>12755</v>
+        <v>12550</v>
       </c>
       <c r="X9" t="n">
-        <v>-205</v>
+        <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.61</v>
+        <v>0.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>12550</v>
+        <v>12570</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-42960</v>
+        <v>-42940</v>
       </c>
       <c r="AC9" t="n">
-        <v>-77.39</v>
+        <v>-77.36</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3715</v>
+        <v>3760</v>
       </c>
       <c r="F2" t="n">
-        <v>47.6</v>
+        <v>49.3</v>
       </c>
       <c r="G2" t="n">
-        <v>1.22</v>
+        <v>2.39</v>
       </c>
       <c r="H2" t="n">
-        <v>0.37</v>
+        <v>0.9</v>
       </c>
       <c r="I2" t="n">
-        <v>79.55</v>
+        <v>83.14</v>
       </c>
       <c r="J2" t="n">
-        <v>112.82</v>
+        <v>113.54</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3384.96</v>
+        <v>3385.56</v>
       </c>
       <c r="N2" t="n">
-        <v>2815.4</v>
+        <v>2815.62</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -658,22 +658,22 @@
         <v>3715</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>14860</v>
+        <v>15040</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4060</v>
+        <v>4240</v>
       </c>
       <c r="AC2" t="n">
-        <v>37.59</v>
+        <v>39.26</v>
       </c>
     </row>
     <row r="3">
@@ -694,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>56.9</v>
       </c>
       <c r="G3" t="n">
-        <v>1.45</v>
+        <v>0.26</v>
       </c>
       <c r="H3" t="n">
-        <v>0.34</v>
+        <v>0.93</v>
       </c>
       <c r="I3" t="n">
-        <v>5.62</v>
+        <v>5.14</v>
       </c>
       <c r="J3" t="n">
-        <v>6.3</v>
+        <v>6.21</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>461.52</v>
+        <v>461.44</v>
       </c>
       <c r="N3" t="n">
-        <v>428.33</v>
+        <v>428.3</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -771,22 +771,22 @@
         <v>490</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2</v>
+        <v>-1.02</v>
       </c>
       <c r="Z3" t="n">
-        <v>49100</v>
+        <v>48500</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7100</v>
+        <v>6500</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.9</v>
+        <v>15.48</v>
       </c>
     </row>
     <row r="4">
@@ -807,22 +807,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>175.1</v>
+        <v>174</v>
       </c>
       <c r="F4" t="n">
-        <v>64.2</v>
+        <v>60.4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.96</v>
+        <v>0.35</v>
       </c>
       <c r="H4" t="n">
-        <v>0.49</v>
+        <v>1.13</v>
       </c>
       <c r="I4" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="J4" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>163.6</v>
+        <v>163.58</v>
       </c>
       <c r="N4" t="n">
-        <v>154.57</v>
+        <v>154.56</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -883,22 +883,22 @@
         <v>176.4</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3</v>
+        <v>-2.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.74</v>
+        <v>-1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>17510</v>
+        <v>17400</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1710</v>
+        <v>1600</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.82</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3107</v>
+        <v>3102</v>
       </c>
       <c r="F5" t="n">
-        <v>80.2</v>
+        <v>78.8</v>
       </c>
       <c r="G5" t="n">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="H5" t="n">
-        <v>0.46</v>
+        <v>1.03</v>
       </c>
       <c r="I5" t="n">
-        <v>41.98</v>
+        <v>41.58</v>
       </c>
       <c r="J5" t="n">
-        <v>27.31</v>
+        <v>27.23</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2964.82</v>
+        <v>2964.75</v>
       </c>
       <c r="N5" t="n">
-        <v>3096.7</v>
+        <v>3096.68</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -996,22 +996,22 @@
         <v>3117</v>
       </c>
       <c r="X5" t="n">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.32</v>
+        <v>-0.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>40391</v>
+        <v>40326</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>3292</v>
+        <v>3227</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.869999999999999</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1032,22 +1032,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8501</v>
+        <v>8453</v>
       </c>
       <c r="F6" t="n">
-        <v>75.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="G6" t="n">
-        <v>3.43</v>
+        <v>2.87</v>
       </c>
       <c r="H6" t="n">
-        <v>0.52</v>
+        <v>0.92</v>
       </c>
       <c r="I6" t="n">
-        <v>108.48</v>
+        <v>104.66</v>
       </c>
       <c r="J6" t="n">
-        <v>57.7</v>
+        <v>56.94</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>8098.85</v>
+        <v>8098.21</v>
       </c>
       <c r="N6" t="n">
-        <v>8293.459999999999</v>
+        <v>8293.219999999999</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1072,20 +1072,20 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1102,29 +1102,29 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSI過熱、25日線上、MACD買い、上昇トレンド</t>
+          <t>RSIやや過熱、25日線上、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>8576</v>
       </c>
       <c r="X6" t="n">
-        <v>-75</v>
+        <v>-123</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.87</v>
+        <v>-1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>8501</v>
+        <v>8453</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>508</v>
+        <v>460</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.36</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="7">
@@ -1145,22 +1145,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4905</v>
+        <v>4936</v>
       </c>
       <c r="F7" t="n">
-        <v>60.9</v>
+        <v>62.3</v>
       </c>
       <c r="G7" t="n">
-        <v>3.38</v>
+        <v>4.01</v>
       </c>
       <c r="H7" t="n">
-        <v>0.37</v>
+        <v>0.86</v>
       </c>
       <c r="I7" t="n">
-        <v>16.65</v>
+        <v>19.12</v>
       </c>
       <c r="J7" t="n">
-        <v>-7.22</v>
+        <v>-6.72</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1169,14 +1169,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>+2S</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4721.21</v>
+        <v>4721.63</v>
       </c>
       <c r="N7" t="n">
-        <v>4754.54</v>
+        <v>4754.7</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -1214,29 +1214,29 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+1σ、MACD買い、上昇トレンド</t>
+          <t>RSI適正、25日線上、+2σ、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>4910</v>
       </c>
       <c r="X7" t="n">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.1</v>
+        <v>0.53</v>
       </c>
       <c r="Z7" t="n">
-        <v>24525</v>
+        <v>24680</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>550</v>
+        <v>705</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.29</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="8">
@@ -1257,22 +1257,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>8736</v>
+        <v>8587</v>
       </c>
       <c r="F8" t="n">
-        <v>28.7</v>
+        <v>26.8</v>
       </c>
       <c r="G8" t="n">
-        <v>-10.1</v>
+        <v>-11.58</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="I8" t="n">
-        <v>-295.14</v>
+        <v>-307.03</v>
       </c>
       <c r="J8" t="n">
-        <v>-80.63</v>
+        <v>-83.01000000000001</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1285,35 +1285,263 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10216.55</v>
+        <v>10214.56</v>
       </c>
       <c r="N8" t="n">
-        <v>8668.15</v>
+        <v>8667.4</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>🔴 売り注意</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>15</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・25日線から大きく下に乖離しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>RSI売られすぎ、25日線大幅割れ、-1σ、MACD売り、下降トレンド</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>8572</v>
+      </c>
+      <c r="X8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>8587</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-1413</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-14.13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>55510</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12605</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-21.57</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-1462.29</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1160.22</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>17672.38</v>
+      </c>
+      <c r="N9" t="n">
+        <v>14873.75</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>🔴 売り注意</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>15</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・25日線から大きく下に乖離しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>RSI売られすぎ、25日線大幅割れ、-1σ、MACD売り、下降トレンド</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>12550</v>
+      </c>
+      <c r="X9" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>12605</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>55510</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-42905</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-77.29000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SUPER MICRO COMP</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6113</v>
+      </c>
+      <c r="E10" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="F10" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-16.14</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="N10" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>🟠 利益確定検討</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q10" t="n">
         <v>50</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -1325,234 +1553,6 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>RSI売られすぎ、25日線大幅割れ、-1σ、MACD売り、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>8572</v>
-      </c>
-      <c r="X8" t="n">
-        <v>164</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>8736</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-1264</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-12.64</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>55510</v>
-      </c>
-      <c r="E9" t="n">
-        <v>12570</v>
-      </c>
-      <c r="F9" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-21.78</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-1465.08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-1160.78</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>17671.91</v>
-      </c>
-      <c r="N9" t="n">
-        <v>14873.58</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>🔴 売り注意</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>15</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・25日線から大きく下に乖離しています。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>RSI売られすぎ、25日線大幅割れ、-1σ、MACD売り、下降トレンド</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>12550</v>
-      </c>
-      <c r="X9" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>12570</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>55510</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-42940</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-77.36</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SMCI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SUPER MICRO COMP</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6113</v>
-      </c>
-      <c r="E10" t="n">
-        <v>32.69</v>
-      </c>
-      <c r="F10" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-16.14</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-1.84</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>35.54</v>
-      </c>
-      <c r="N10" t="n">
-        <v>32.56</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>🟠 利益確定検討</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>50</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・25日線から大きく下に乖離しています。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1485,22 +1485,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>32.69</v>
+        <v>35.09</v>
       </c>
       <c r="F10" t="n">
-        <v>25.1</v>
+        <v>28.1</v>
       </c>
       <c r="G10" t="n">
-        <v>-16.14</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.52</v>
+        <v>0.74</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.84</v>
+        <v>-1.71</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.03</v>
+        <v>-1.17</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1509,14 +1509,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>35.54</v>
+        <v>35.64</v>
       </c>
       <c r="N10" t="n">
-        <v>32.56</v>
+        <v>32.59</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1525,11 +1525,11 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>🟠 利益確定検討</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1547,38 +1547,41 @@
 ・🟡 反発中
 ・MACDは売りシグナルです。
 ・売られ過ぎ水準です。
-・25日線から大きく下に乖離しています。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 🟡 下落からの反発局面です。
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>RSI売られすぎ、25日線大幅割れ、-1σ、MACD売り、反発局面</t>
+          <t>RSI売られすぎ、押し目、MACD売り、反発局面</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>32.94</v>
+        <v>32.69</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.25</v>
+        <v>2.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.76</v>
+        <v>7.34</v>
       </c>
       <c r="Z10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6080</v>
+        <v>-6078</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.47</v>
+        <v>-99.43000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3760</v>
+        <v>3835</v>
       </c>
       <c r="F2" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>2.39</v>
+        <v>3.99</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9</v>
+        <v>0.64</v>
       </c>
       <c r="I2" t="n">
-        <v>83.14</v>
+        <v>81.56</v>
       </c>
       <c r="J2" t="n">
-        <v>113.54</v>
+        <v>107.15</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3385.56</v>
+        <v>3396.43</v>
       </c>
       <c r="N2" t="n">
-        <v>2815.62</v>
+        <v>2819.69</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,20 +621,20 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -651,29 +651,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>25日線上、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3715</v>
+        <v>3760</v>
       </c>
       <c r="X2" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.21</v>
+        <v>1.99</v>
       </c>
       <c r="Z2" t="n">
-        <v>15040</v>
+        <v>15340</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4240</v>
+        <v>4540</v>
       </c>
       <c r="AC2" t="n">
-        <v>39.26</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="3">
@@ -694,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="F3" t="n">
         <v>56.9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.26</v>
+        <v>-0.7</v>
       </c>
       <c r="H3" t="n">
-        <v>0.93</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>5.14</v>
+        <v>4.13</v>
       </c>
       <c r="J3" t="n">
-        <v>6.21</v>
+        <v>5.79</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>461.44</v>
+        <v>462.05</v>
       </c>
       <c r="N3" t="n">
-        <v>428.3</v>
+        <v>428.87</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -734,20 +734,20 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -764,29 +764,29 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>RSI適正、押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="X3" t="n">
         <v>-5</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.02</v>
+        <v>-1.03</v>
       </c>
       <c r="Z3" t="n">
-        <v>48500</v>
+        <v>48000</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6500</v>
+        <v>6000</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.48</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="4">
@@ -807,22 +807,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>174</v>
+        <v>172.1</v>
       </c>
       <c r="F4" t="n">
-        <v>60.4</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>0.35</v>
+        <v>-0.63</v>
       </c>
       <c r="H4" t="n">
-        <v>1.13</v>
+        <v>0.37</v>
       </c>
       <c r="I4" t="n">
-        <v>1.73</v>
+        <v>1.38</v>
       </c>
       <c r="J4" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>163.58</v>
+        <v>163.93</v>
       </c>
       <c r="N4" t="n">
-        <v>154.56</v>
+        <v>154.66</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -847,20 +847,20 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -868,6 +868,7 @@
           <t>【AI分析レポート】
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -876,29 +877,29 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>RSI適正、押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>176.4</v>
+        <v>174</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.4</v>
+        <v>-1.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.36</v>
+        <v>-1.09</v>
       </c>
       <c r="Z4" t="n">
-        <v>17400</v>
+        <v>17210</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1600</v>
+        <v>1410</v>
       </c>
       <c r="AC4" t="n">
-        <v>10.13</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="5">
@@ -919,22 +920,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3102</v>
+        <v>3086</v>
       </c>
       <c r="F5" t="n">
-        <v>78.8</v>
+        <v>82.7</v>
       </c>
       <c r="G5" t="n">
-        <v>3.82</v>
+        <v>3.14</v>
       </c>
       <c r="H5" t="n">
-        <v>1.03</v>
+        <v>0.37</v>
       </c>
       <c r="I5" t="n">
-        <v>41.58</v>
+        <v>40.36</v>
       </c>
       <c r="J5" t="n">
-        <v>27.23</v>
+        <v>29.85</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,10 +948,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2964.75</v>
+        <v>2967.28</v>
       </c>
       <c r="N5" t="n">
-        <v>3096.68</v>
+        <v>3095.81</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -993,25 +994,25 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>3117</v>
+        <v>3102</v>
       </c>
       <c r="X5" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.48</v>
+        <v>-0.52</v>
       </c>
       <c r="Z5" t="n">
-        <v>40326</v>
+        <v>40118</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>3227</v>
+        <v>3019</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1032,22 +1033,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8453</v>
+        <v>8263</v>
       </c>
       <c r="F6" t="n">
-        <v>72.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>2.87</v>
+        <v>0.66</v>
       </c>
       <c r="H6" t="n">
-        <v>0.92</v>
+        <v>0.59</v>
       </c>
       <c r="I6" t="n">
-        <v>104.66</v>
+        <v>82.38</v>
       </c>
       <c r="J6" t="n">
-        <v>56.94</v>
+        <v>62.03</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1060,10 +1061,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>8098.21</v>
+        <v>8113.08</v>
       </c>
       <c r="N6" t="n">
-        <v>8293.219999999999</v>
+        <v>8281.870000000001</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1093,7 +1094,6 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
-・買われ過ぎ水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -1106,25 +1106,25 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>8576</v>
+        <v>8453</v>
       </c>
       <c r="X6" t="n">
-        <v>-123</v>
+        <v>-190</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.43</v>
+        <v>-2.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>8453</v>
+        <v>8263</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>460</v>
+        <v>270</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.76</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="7">
@@ -1145,22 +1145,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4936</v>
+        <v>4879</v>
       </c>
       <c r="F7" t="n">
-        <v>62.3</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
-        <v>4.01</v>
+        <v>2.84</v>
       </c>
       <c r="H7" t="n">
-        <v>0.86</v>
+        <v>0.38</v>
       </c>
       <c r="I7" t="n">
-        <v>19.12</v>
+        <v>25.24</v>
       </c>
       <c r="J7" t="n">
-        <v>-6.72</v>
+        <v>-0.33</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1169,14 +1169,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+2S</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4721.63</v>
+        <v>4727.45</v>
       </c>
       <c r="N7" t="n">
-        <v>4754.7</v>
+        <v>4761.64</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
-・ボリンジャーバンド+2σ付近です。買われすぎの可能性があり、利益確定売りに注意です。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -1214,29 +1214,29 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+2σ、MACD買い、上昇トレンド</t>
+          <t>RSI適正、25日線上、+1σ、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4910</v>
+        <v>4936</v>
       </c>
       <c r="X7" t="n">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.53</v>
+        <v>-1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>24680</v>
+        <v>24395</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>705</v>
+        <v>420</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.94</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="8">
@@ -1257,214 +1257,219 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
+        <v>9309</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-280.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-122.42</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>10121.69</v>
+      </c>
+      <c r="N8" t="n">
+        <v>8696.559999999999</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>🟡 反発中</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>🟠 利益確定検討</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>45</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟡 反発中
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>押し目、MACD売り、反発局面</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
         <v>8587</v>
       </c>
-      <c r="F8" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-11.58</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-307.03</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-83.01000000000001</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="X8" t="n">
+        <v>722</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9309</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-691</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-6.91</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>55510</v>
+      </c>
+      <c r="E9" t="n">
+        <v>14240</v>
+      </c>
+      <c r="F9" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-10.87</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-1323.44</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1192.86</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>10214.56</v>
-      </c>
-      <c r="N8" t="n">
-        <v>8667.4</v>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>17540.47</v>
+      </c>
+      <c r="N9" t="n">
+        <v>14927.16</v>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>🔴 下降</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>🔴 売り注意</t>
         </is>
       </c>
-      <c r="Q8" t="n">
-        <v>15</v>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは売りシグナルです。
-・売られ過ぎ水準です。
 ・25日線から大きく下に乖離しています。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+・ボリンジャーバンド中心付近で推移しています。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>RSI売られすぎ、25日線大幅割れ、-1σ、MACD売り、下降トレンド</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>8572</v>
-      </c>
-      <c r="X8" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>8587</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-1413</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-14.13</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>55510</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>🚀 急騰</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>25日線大幅割れ、MACD売り、下降トレンド</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
         <v>12605</v>
       </c>
-      <c r="F9" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-21.57</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-1462.29</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-1160.22</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-1S</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>17672.38</v>
-      </c>
-      <c r="N9" t="n">
-        <v>14873.75</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>🔴 売り注意</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>15</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・25日線から大きく下に乖離しています。
-・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>RSI売られすぎ、25日線大幅割れ、-1σ、MACD売り、下降トレンド</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>12550</v>
-      </c>
       <c r="X9" t="n">
-        <v>55</v>
+        <v>1635</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.44</v>
+        <v>12.97</v>
       </c>
       <c r="Z9" t="n">
-        <v>12605</v>
+        <v>14240</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-42905</v>
+        <v>-41270</v>
       </c>
       <c r="AC9" t="n">
-        <v>-77.29000000000001</v>
+        <v>-74.34999999999999</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3835</v>
+        <v>3870</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>51.2</v>
       </c>
       <c r="G2" t="n">
-        <v>3.99</v>
+        <v>4.9</v>
       </c>
       <c r="H2" t="n">
-        <v>0.64</v>
+        <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>81.56</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>107.15</v>
+        <v>107.7</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3396.43</v>
+        <v>3396.89</v>
       </c>
       <c r="N2" t="n">
-        <v>2819.69</v>
+        <v>2819.86</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -658,22 +658,22 @@
         <v>3760</v>
       </c>
       <c r="X2" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.99</v>
+        <v>2.93</v>
       </c>
       <c r="Z2" t="n">
-        <v>15340</v>
+        <v>15480</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4540</v>
+        <v>4680</v>
       </c>
       <c r="AC2" t="n">
-        <v>42.04</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="3">
@@ -694,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F3" t="n">
-        <v>56.9</v>
+        <v>57.9</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7</v>
+        <v>-0.31</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.45</v>
       </c>
       <c r="I3" t="n">
-        <v>4.13</v>
+        <v>4.29</v>
       </c>
       <c r="J3" t="n">
-        <v>5.79</v>
+        <v>5.82</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>462.05</v>
+        <v>462.08</v>
       </c>
       <c r="N3" t="n">
-        <v>428.87</v>
+        <v>428.88</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -771,22 +771,22 @@
         <v>485</v>
       </c>
       <c r="X3" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.03</v>
+        <v>-0.62</v>
       </c>
       <c r="Z3" t="n">
-        <v>48000</v>
+        <v>48200</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.29</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="4">
@@ -807,22 +807,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>172.1</v>
+        <v>171.9</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>49.5</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.63</v>
+        <v>-0.74</v>
       </c>
       <c r="H4" t="n">
-        <v>0.37</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="J4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>163.93</v>
       </c>
       <c r="N4" t="n">
-        <v>154.66</v>
+        <v>154.65</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -847,20 +847,20 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -877,29 +877,29 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>174</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.9</v>
+        <v>-2.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.09</v>
+        <v>-1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>17210</v>
+        <v>17190</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1410</v>
+        <v>1390</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.92</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -920,22 +920,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3086</v>
+        <v>3051</v>
       </c>
       <c r="F5" t="n">
-        <v>82.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>3.14</v>
+        <v>2.02</v>
       </c>
       <c r="H5" t="n">
-        <v>0.37</v>
+        <v>0.93</v>
       </c>
       <c r="I5" t="n">
-        <v>40.36</v>
+        <v>37.56</v>
       </c>
       <c r="J5" t="n">
-        <v>29.85</v>
+        <v>29.29</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -944,14 +944,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2967.28</v>
+        <v>2966.81</v>
       </c>
       <c r="N5" t="n">
-        <v>3095.81</v>
+        <v>3095.64</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -960,20 +960,20 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -982,7 +982,7 @@
 ・🟢 上昇
 ・MACDは買いシグナルです。
 ・買われ過ぎ水準です。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -990,29 +990,29 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>RSI過熱、25日線上、+1σ、MACD買い、上昇トレンド</t>
+          <t>RSIやや過熱、25日線上、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>3102</v>
       </c>
       <c r="X5" t="n">
-        <v>-16</v>
+        <v>-51</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.52</v>
+        <v>-1.64</v>
       </c>
       <c r="Z5" t="n">
-        <v>40118</v>
+        <v>39663</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>3019</v>
+        <v>2564</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.140000000000001</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="6">
@@ -1033,22 +1033,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8263</v>
+        <v>8311</v>
       </c>
       <c r="F6" t="n">
-        <v>65.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.66</v>
+        <v>1.22</v>
       </c>
       <c r="H6" t="n">
-        <v>0.59</v>
+        <v>0.96</v>
       </c>
       <c r="I6" t="n">
-        <v>82.38</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>62.03</v>
+        <v>62.79</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>8113.08</v>
+        <v>8113.72</v>
       </c>
       <c r="N6" t="n">
-        <v>8281.870000000001</v>
+        <v>8282.110000000001</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1109,22 +1109,22 @@
         <v>8453</v>
       </c>
       <c r="X6" t="n">
-        <v>-190</v>
+        <v>-142</v>
       </c>
       <c r="Y6" t="n">
-        <v>-2.25</v>
+        <v>-1.68</v>
       </c>
       <c r="Z6" t="n">
-        <v>8263</v>
+        <v>8311</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>270</v>
+        <v>318</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.38</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="7">
@@ -1145,22 +1145,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4879</v>
+        <v>4847</v>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>58.9</v>
       </c>
       <c r="G7" t="n">
-        <v>2.84</v>
+        <v>2.19</v>
       </c>
       <c r="H7" t="n">
-        <v>0.38</v>
+        <v>0.92</v>
       </c>
       <c r="I7" t="n">
-        <v>25.24</v>
+        <v>22.69</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.33</v>
+        <v>-0.84</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4727.45</v>
+        <v>4727.03</v>
       </c>
       <c r="N7" t="n">
-        <v>4761.64</v>
+        <v>4761.48</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1206,6 +1206,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -1221,22 +1222,22 @@
         <v>4936</v>
       </c>
       <c r="X7" t="n">
-        <v>-57</v>
+        <v>-89</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.15</v>
+        <v>-1.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>24395</v>
+        <v>24235</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>420</v>
+        <v>260</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.75</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="8">
@@ -1257,22 +1258,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>9309</v>
+        <v>9200</v>
       </c>
       <c r="F8" t="n">
-        <v>31.7</v>
+        <v>30.4</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.29</v>
+        <v>-5.37</v>
       </c>
       <c r="H8" t="n">
-        <v>0.52</v>
+        <v>0.77</v>
       </c>
       <c r="I8" t="n">
-        <v>-280.1</v>
+        <v>-288.79</v>
       </c>
       <c r="J8" t="n">
-        <v>-122.42</v>
+        <v>-124.16</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1285,10 +1286,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10121.69</v>
+        <v>10120.24</v>
       </c>
       <c r="N8" t="n">
-        <v>8696.559999999999</v>
+        <v>8696.02</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1337,22 +1338,22 @@
         <v>8587</v>
       </c>
       <c r="X8" t="n">
-        <v>722</v>
+        <v>613</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.41</v>
+        <v>7.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>9309</v>
+        <v>9200</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-691</v>
+        <v>-800</v>
       </c>
       <c r="AC8" t="n">
-        <v>-6.91</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="9">
@@ -1373,22 +1374,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>14240</v>
+        <v>14340</v>
       </c>
       <c r="F9" t="n">
-        <v>30.8</v>
+        <v>31.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-10.87</v>
+        <v>-10.27</v>
       </c>
       <c r="H9" t="n">
-        <v>0.85</v>
+        <v>1.4</v>
       </c>
       <c r="I9" t="n">
-        <v>-1323.44</v>
+        <v>-1315.46</v>
       </c>
       <c r="J9" t="n">
-        <v>-1192.86</v>
+        <v>-1191.27</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1401,10 +1402,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>17540.47</v>
+        <v>17541.8</v>
       </c>
       <c r="N9" t="n">
-        <v>14927.16</v>
+        <v>14927.66</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1454,22 +1455,22 @@
         <v>12605</v>
       </c>
       <c r="X9" t="n">
-        <v>1635</v>
+        <v>1735</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.97</v>
+        <v>13.76</v>
       </c>
       <c r="Z9" t="n">
-        <v>14240</v>
+        <v>14340</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-41270</v>
+        <v>-41170</v>
       </c>
       <c r="AC9" t="n">
-        <v>-74.34999999999999</v>
+        <v>-74.17</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1491,103 +1491,98 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
+        <v>35.81</v>
+      </c>
+      <c r="F10" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-6.98</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="N10" t="n">
+        <v>32.62</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>⚪ 様子見</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>65</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>押し目、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
         <v>35.09</v>
       </c>
-      <c r="F10" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-9.380000000000001</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-1.17</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>35.64</v>
-      </c>
-      <c r="N10" t="n">
-        <v>32.59</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>60</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・売られ過ぎ水準です。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>RSI売られすぎ、押し目、MACD売り、反発局面</t>
-        </is>
-      </c>
-      <c r="W10" t="n">
-        <v>32.69</v>
-      </c>
       <c r="X10" t="n">
-        <v>2.4</v>
+        <v>0.72</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.34</v>
+        <v>2.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6078</v>
+        <v>-6077</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.43000000000001</v>
+        <v>-99.41</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3870</v>
+        <v>3750</v>
       </c>
       <c r="F2" t="n">
-        <v>51.2</v>
+        <v>45.4</v>
       </c>
       <c r="G2" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1</v>
+        <v>0.67</v>
       </c>
       <c r="I2" t="n">
-        <v>84.34999999999999</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>107.7</v>
+        <v>101.12</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3396.89</v>
+        <v>3407.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2819.86</v>
+        <v>2823.5</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -621,20 +621,20 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -651,29 +651,29 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
+          <t>25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3760</v>
+        <v>3870</v>
       </c>
       <c r="X2" t="n">
-        <v>110</v>
+        <v>-120</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.93</v>
+        <v>-3.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>15480</v>
+        <v>15000</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4680</v>
+        <v>4200</v>
       </c>
       <c r="AC2" t="n">
-        <v>43.33</v>
+        <v>38.89</v>
       </c>
     </row>
     <row r="3">
@@ -694,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F3" t="n">
-        <v>57.9</v>
+        <v>49.5</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.31</v>
+        <v>-1.03</v>
       </c>
       <c r="H3" t="n">
-        <v>1.45</v>
+        <v>0.59</v>
       </c>
       <c r="I3" t="n">
-        <v>4.29</v>
+        <v>3.25</v>
       </c>
       <c r="J3" t="n">
-        <v>5.82</v>
+        <v>5.31</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>462.08</v>
+        <v>462.8</v>
       </c>
       <c r="N3" t="n">
-        <v>428.88</v>
+        <v>429.44</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -734,20 +734,20 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>⚪ 様子見</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -764,29 +764,29 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="X3" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.62</v>
+        <v>-0.83</v>
       </c>
       <c r="Z3" t="n">
-        <v>48200</v>
+        <v>47800</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.76</v>
+        <v>13.81</v>
       </c>
     </row>
     <row r="4">
@@ -807,22 +807,22 @@
         <v>158</v>
       </c>
       <c r="E4" t="n">
-        <v>171.9</v>
+        <v>172.3</v>
       </c>
       <c r="F4" t="n">
-        <v>49.5</v>
+        <v>50.5</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.74</v>
+        <v>-0.46</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="I4" t="n">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>163.93</v>
+        <v>164.27</v>
       </c>
       <c r="N4" t="n">
-        <v>154.65</v>
+        <v>154.75</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -847,20 +847,20 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -877,29 +877,29 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>RSI適正、押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>174</v>
+        <v>171.9</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.1</v>
+        <v>0.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.21</v>
+        <v>0.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>17190</v>
+        <v>17230</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1390</v>
+        <v>1430</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -920,22 +920,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3051</v>
+        <v>3081</v>
       </c>
       <c r="F5" t="n">
-        <v>73.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="G5" t="n">
-        <v>2.02</v>
+        <v>2.88</v>
       </c>
       <c r="H5" t="n">
-        <v>0.93</v>
+        <v>0.45</v>
       </c>
       <c r="I5" t="n">
-        <v>37.56</v>
+        <v>36.38</v>
       </c>
       <c r="J5" t="n">
-        <v>29.29</v>
+        <v>30.71</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2966.81</v>
+        <v>2970.02</v>
       </c>
       <c r="N5" t="n">
-        <v>3095.64</v>
+        <v>3094.79</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -960,20 +960,20 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -990,29 +990,29 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、MACD買い、上昇トレンド</t>
+          <t>RSI過熱、25日線上、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>3102</v>
+        <v>3051</v>
       </c>
       <c r="X5" t="n">
-        <v>-51</v>
+        <v>30</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.64</v>
+        <v>0.98</v>
       </c>
       <c r="Z5" t="n">
-        <v>39663</v>
+        <v>40053</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2564</v>
+        <v>2954</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.91</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="6">
@@ -1033,22 +1033,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8311</v>
+        <v>8259</v>
       </c>
       <c r="F6" t="n">
-        <v>67.7</v>
+        <v>63.7</v>
       </c>
       <c r="G6" t="n">
-        <v>1.22</v>
+        <v>0.63</v>
       </c>
       <c r="H6" t="n">
-        <v>0.96</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>86.20999999999999</v>
+        <v>66.63</v>
       </c>
       <c r="J6" t="n">
-        <v>62.79</v>
+        <v>63.56</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>8113.72</v>
+        <v>8129.37</v>
       </c>
       <c r="N6" t="n">
-        <v>8282.110000000001</v>
+        <v>8271.440000000001</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1102,29 +1102,29 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、MACD買い、上昇トレンド</t>
+          <t>RSI適正、25日線上、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>8453</v>
+        <v>8311</v>
       </c>
       <c r="X6" t="n">
-        <v>-142</v>
+        <v>-52</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.68</v>
+        <v>-0.63</v>
       </c>
       <c r="Z6" t="n">
-        <v>8311</v>
+        <v>8259</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>318</v>
+        <v>266</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.98</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="7">
@@ -1145,22 +1145,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4847</v>
+        <v>4867</v>
       </c>
       <c r="F7" t="n">
-        <v>58.9</v>
+        <v>65.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.19</v>
+        <v>2.63</v>
       </c>
       <c r="H7" t="n">
-        <v>0.92</v>
+        <v>0.34</v>
       </c>
       <c r="I7" t="n">
-        <v>22.69</v>
+        <v>26.82</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.84</v>
+        <v>4.69</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4727.03</v>
+        <v>4733.17</v>
       </c>
       <c r="N7" t="n">
-        <v>4761.48</v>
+        <v>4768.29</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1206,7 +1206,6 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
-・RSIは良好な水準です。
 ・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -1215,29 +1214,29 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+1σ、MACD買い、上昇トレンド</t>
+          <t>RSIやや過熱、25日線上、+1σ、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4936</v>
+        <v>4847</v>
       </c>
       <c r="X7" t="n">
-        <v>-89</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.8</v>
+        <v>0.41</v>
       </c>
       <c r="Z7" t="n">
-        <v>24235</v>
+        <v>24335</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>260</v>
+        <v>360</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8">
@@ -1258,22 +1257,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>9200</v>
+        <v>8914</v>
       </c>
       <c r="F8" t="n">
-        <v>30.4</v>
+        <v>31.6</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.37</v>
+        <v>-8.15</v>
       </c>
       <c r="H8" t="n">
-        <v>0.77</v>
+        <v>0.61</v>
       </c>
       <c r="I8" t="n">
-        <v>-288.79</v>
+        <v>-294.03</v>
       </c>
       <c r="J8" t="n">
-        <v>-124.16</v>
+        <v>-158.14</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1286,10 +1285,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10120.24</v>
+        <v>10040.55</v>
       </c>
       <c r="N8" t="n">
-        <v>8696.02</v>
+        <v>8723.17</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1324,36 +1323,32 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>押し目、MACD売り、反発局面</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>8587</v>
+        <v>9200</v>
       </c>
       <c r="X8" t="n">
-        <v>613</v>
+        <v>-286</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.14</v>
+        <v>-3.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>9200</v>
+        <v>8914</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-800</v>
+        <v>-1086</v>
       </c>
       <c r="AC8" t="n">
-        <v>-8</v>
+        <v>-10.86</v>
       </c>
     </row>
     <row r="9">
@@ -1374,22 +1369,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>14340</v>
+        <v>14850</v>
       </c>
       <c r="F9" t="n">
-        <v>31.5</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>-10.27</v>
+        <v>-6.29</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4</v>
+        <v>0.88</v>
       </c>
       <c r="I9" t="n">
-        <v>-1315.46</v>
+        <v>-1144.75</v>
       </c>
       <c r="J9" t="n">
-        <v>-1191.27</v>
+        <v>-1181.96</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1402,10 +1397,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>17541.8</v>
+        <v>17420.38</v>
       </c>
       <c r="N9" t="n">
-        <v>14927.66</v>
+        <v>14984.52</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1418,11 +1413,11 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1434,43 +1429,38 @@
         <is>
           <t>【AI分析レポート】
 ・🔴 下降
-・MACDは売りシグナルです。
-・25日線から大きく下に乖離しています。
+・MACDは買いシグナルです。
 ・ボリンジャーバンド中心付近で推移しています。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>🚀 急騰</t>
-        </is>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>25日線大幅割れ、MACD売り、下降トレンド</t>
+          <t>押し目、MACD買い、下降トレンド</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>12605</v>
+        <v>14340</v>
       </c>
       <c r="X9" t="n">
-        <v>1735</v>
+        <v>510</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.76</v>
+        <v>3.56</v>
       </c>
       <c r="Z9" t="n">
-        <v>14340</v>
+        <v>14850</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-41170</v>
+        <v>-40660</v>
       </c>
       <c r="AC9" t="n">
-        <v>-74.17</v>
+        <v>-73.25</v>
       </c>
     </row>
     <row r="10">
@@ -1500,7 +1490,7 @@
         <v>-6.98</v>
       </c>
       <c r="H10" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>-1.53</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3750</v>
+        <v>3770</v>
       </c>
       <c r="F2" t="n">
-        <v>45.4</v>
+        <v>46</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2</v>
+        <v>1.72</v>
       </c>
       <c r="H2" t="n">
-        <v>0.67</v>
+        <v>1.12</v>
       </c>
       <c r="I2" t="n">
-        <v>74.76000000000001</v>
+        <v>76.36</v>
       </c>
       <c r="J2" t="n">
-        <v>101.12</v>
+        <v>101.43</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3407.45</v>
+        <v>3407.72</v>
       </c>
       <c r="N2" t="n">
-        <v>2823.5</v>
+        <v>2823.6</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -658,22 +658,22 @@
         <v>3870</v>
       </c>
       <c r="X2" t="n">
-        <v>-120</v>
+        <v>-100</v>
       </c>
       <c r="Y2" t="n">
-        <v>-3.1</v>
+        <v>-2.58</v>
       </c>
       <c r="Z2" t="n">
-        <v>15000</v>
+        <v>15080</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4200</v>
+        <v>4280</v>
       </c>
       <c r="AC2" t="n">
-        <v>38.89</v>
+        <v>39.63</v>
       </c>
     </row>
     <row r="3">
@@ -694,22 +694,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="F3" t="n">
-        <v>49.5</v>
+        <v>46.6</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.03</v>
+        <v>-2.22</v>
       </c>
       <c r="H3" t="n">
-        <v>0.59</v>
+        <v>2.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="J3" t="n">
-        <v>5.31</v>
+        <v>5.21</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>462.8</v>
+        <v>462.72</v>
       </c>
       <c r="N3" t="n">
-        <v>429.44</v>
+        <v>429.41</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -734,23 +734,137 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>75</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
+・出来高が急増しています。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>押し目、出来高増加、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>482</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>47200</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5200</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>12.38</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>171.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>164.26</v>
+      </c>
+      <c r="N4" t="n">
+        <v>154.75</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>⚪ 様子見</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q4" t="n">
         <v>65</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>★★★☆☆</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -761,145 +875,32 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>482</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>47800</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>42000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5800</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>13.81</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>9432.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NTT</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>158</v>
-      </c>
-      <c r="E4" t="n">
-        <v>172.3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>164.27</v>
-      </c>
-      <c r="N4" t="n">
-        <v>154.75</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>85</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>171.9</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4</v>
+        <v>-0.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.23</v>
+        <v>-0.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>17230</v>
+        <v>17150</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1430</v>
+        <v>1350</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.050000000000001</v>
+        <v>8.539999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -920,22 +921,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3081</v>
+        <v>3077</v>
       </c>
       <c r="F5" t="n">
-        <v>75.8</v>
+        <v>75.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="H5" t="n">
-        <v>0.45</v>
+        <v>1.7</v>
       </c>
       <c r="I5" t="n">
-        <v>36.38</v>
+        <v>36.07</v>
       </c>
       <c r="J5" t="n">
-        <v>30.71</v>
+        <v>30.65</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -948,10 +949,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2970.02</v>
+        <v>2969.96</v>
       </c>
       <c r="N5" t="n">
-        <v>3094.79</v>
+        <v>3094.77</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -964,7 +965,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -982,6 +983,7 @@
 ・🟢 上昇
 ・MACDは買いシグナルです。
 ・買われ過ぎ水準です。
+・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -990,65 +992,65 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>RSI過熱、25日線上、MACD買い、上昇トレンド</t>
+          <t>RSI過熱、25日線上、出来高微増、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>3051</v>
       </c>
       <c r="X5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="Z5" t="n">
-        <v>40053</v>
+        <v>40001</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2954</v>
+        <v>2902</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.96</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7974.T</t>
+          <t>8058.T</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>任天堂</t>
+          <t>三菱商事</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>7993</v>
+        <v>4795</v>
       </c>
       <c r="E6" t="n">
-        <v>8259</v>
+        <v>4908</v>
       </c>
       <c r="F6" t="n">
-        <v>63.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.63</v>
+        <v>3.46</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.59</v>
       </c>
       <c r="I6" t="n">
-        <v>66.63</v>
+        <v>30.09</v>
       </c>
       <c r="J6" t="n">
-        <v>63.56</v>
+        <v>5.35</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1057,14 +1059,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>+1S</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>8129.37</v>
+        <v>4733.71</v>
       </c>
       <c r="N6" t="n">
-        <v>8271.440000000001</v>
+        <v>4768.49</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1094,149 +1096,151 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
+・出来高が急増しています。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>RSIやや過熱、25日線上、出来高増加、+1σ、MACD買い、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>4847</v>
+      </c>
+      <c r="X6" t="n">
+        <v>61</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>24540</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>23975</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>565</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7974.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>任天堂</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7993</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8158</v>
+      </c>
+      <c r="F7" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>58.57</v>
+      </c>
+      <c r="J7" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>8128.03</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8270.940000000001</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>🟡 買い</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは売りシグナルです。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>RSI適正、25日線上、MACD買い、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>8311</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-52</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>8259</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>7993</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>266</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>8058.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>三菱商事</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4795</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4867</v>
-      </c>
-      <c r="F7" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I7" t="n">
-        <v>26.82</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>+1S</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>4733.17</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4768.29</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>🟢 強い買い</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>95</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは買いシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSIやや過熱、25日線上、+1σ、MACD買い、上昇トレンド</t>
+          <t>RSI適正、押し目、MACD売り、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>4847</v>
+        <v>8311</v>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>-153</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.41</v>
+        <v>-1.84</v>
       </c>
       <c r="Z7" t="n">
-        <v>24335</v>
+        <v>8158</v>
       </c>
       <c r="AA7" t="n">
-        <v>23975</v>
+        <v>7993</v>
       </c>
       <c r="AB7" t="n">
-        <v>360</v>
+        <v>165</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.5</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="8">
@@ -1257,22 +1261,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>8914</v>
+        <v>9231</v>
       </c>
       <c r="F8" t="n">
-        <v>31.6</v>
+        <v>33.8</v>
       </c>
       <c r="G8" t="n">
-        <v>-8.15</v>
+        <v>-5.01</v>
       </c>
       <c r="H8" t="n">
-        <v>0.61</v>
+        <v>0.98</v>
       </c>
       <c r="I8" t="n">
-        <v>-294.03</v>
+        <v>-268.74</v>
       </c>
       <c r="J8" t="n">
-        <v>-158.14</v>
+        <v>-153.08</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1285,10 +1289,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>10040.55</v>
+        <v>10044.77</v>
       </c>
       <c r="N8" t="n">
-        <v>8723.17</v>
+        <v>8724.75</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1333,22 +1337,22 @@
         <v>9200</v>
       </c>
       <c r="X8" t="n">
-        <v>-286</v>
+        <v>31</v>
       </c>
       <c r="Y8" t="n">
-        <v>-3.11</v>
+        <v>0.34</v>
       </c>
       <c r="Z8" t="n">
-        <v>8914</v>
+        <v>9231</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1086</v>
+        <v>-769</v>
       </c>
       <c r="AC8" t="n">
-        <v>-10.86</v>
+        <v>-7.69</v>
       </c>
     </row>
     <row r="9">
@@ -1369,51 +1373,51 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>14850</v>
+        <v>14505</v>
       </c>
       <c r="F9" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-1172.27</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1187.47</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>17415.78</v>
+      </c>
+      <c r="N9" t="n">
+        <v>14982.79</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>🔴 売り注意</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
         <v>35</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-6.29</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-1144.75</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-1181.96</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>17420.38</v>
-      </c>
-      <c r="N9" t="n">
-        <v>14984.52</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>🔴 売り注意</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>30</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1430,6 +1434,7 @@
           <t>【AI分析レポート】
 ・🔴 下降
 ・MACDは買いシグナルです。
+・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 ⚠️ 下落トレンドです。
 無理な買いは避け、反転サインを待ちましょう。</t>
@@ -1438,29 +1443,29 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>押し目、MACD買い、下降トレンド</t>
+          <t>押し目、出来高微増、MACD買い、下降トレンド</t>
         </is>
       </c>
       <c r="W9" t="n">
         <v>14340</v>
       </c>
       <c r="X9" t="n">
-        <v>510</v>
+        <v>165</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.56</v>
+        <v>1.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>14850</v>
+        <v>14505</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-40660</v>
+        <v>-41005</v>
       </c>
       <c r="AC9" t="n">
-        <v>-73.25</v>
+        <v>-73.87</v>
       </c>
     </row>
     <row r="10">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1486,22 +1486,22 @@
         <v>6113</v>
       </c>
       <c r="E10" t="n">
-        <v>35.81</v>
+        <v>34.43</v>
       </c>
       <c r="F10" t="n">
-        <v>33.5</v>
+        <v>32.8</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.98</v>
+        <v>-9.9</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.53</v>
+        <v>-1.49</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.24</v>
+        <v>-1.29</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1514,70 +1514,70 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>35.74</v>
+        <v>35.84</v>
       </c>
       <c r="N10" t="n">
-        <v>32.62</v>
+        <v>32.64</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>🟢 強い上昇</t>
+          <t>🟡 反発中</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>⚪ 様子見</t>
+          <t>🟠 利益確定検討</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★☆☆☆☆</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>【AI分析レポート】
-・🟢 強い上昇
+・🟡 反発中
 ・MACDは売りシグナルです。
 ・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
+🟡 下落からの反発局面です。
+今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>押し目、MACD売り、反発局面</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>35.09</v>
+        <v>35.81</v>
       </c>
       <c r="X10" t="n">
-        <v>0.72</v>
+        <v>-1.38</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.05</v>
+        <v>-3.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA10" t="n">
         <v>6113</v>
       </c>
       <c r="AB10" t="n">
-        <v>-6077</v>
+        <v>-6079</v>
       </c>
       <c r="AC10" t="n">
-        <v>-99.41</v>
+        <v>-99.44</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3770</v>
+        <v>3750</v>
       </c>
       <c r="F2" t="n">
-        <v>46</v>
+        <v>35.3</v>
       </c>
       <c r="G2" t="n">
-        <v>1.72</v>
+        <v>0.72</v>
       </c>
       <c r="H2" t="n">
-        <v>1.12</v>
+        <v>0.28</v>
       </c>
       <c r="I2" t="n">
-        <v>76.36</v>
+        <v>67.63</v>
       </c>
       <c r="J2" t="n">
-        <v>101.43</v>
+        <v>94.67</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3407.72</v>
+        <v>3419.33</v>
       </c>
       <c r="N2" t="n">
-        <v>2823.6</v>
+        <v>2827.59</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -638,6 +638,231 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>25日線上、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>3770</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>10800</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>4200</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>38.89</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3673.T</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ブロードリーフ</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>420</v>
+      </c>
+      <c r="E3" t="n">
+        <v>478</v>
+      </c>
+      <c r="F3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>463.45</v>
+      </c>
+      <c r="N3" t="n">
+        <v>429.99</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>🟠 利益確定検討</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>50</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 強い上昇
+・MACDは売りシグナルです。
+・デッドクロスが発生し、短期的な下落に注意が必要です。
+・ボリンジャーバンド中心付近で推移しています。
+📈 中長期的にも強い上昇トレンドが継続しています。
+押し目買い候補として注目です。</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>押し目、デッドクロス、MACD売り、長期上昇</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>472</v>
+      </c>
+      <c r="X3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>47800</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>42000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5800</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13.81</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9432.T</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NTT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>173.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>51</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>164.61</v>
+      </c>
+      <c r="N4" t="n">
+        <v>154.84</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>🟢 強い上昇</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>95</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 強い上昇
@@ -648,259 +873,32 @@
 押し目買い候補として注目です。</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>25日線上、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>3870</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-100</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-2.58</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>15080</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>10800</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>4280</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>39.63</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>3673.T</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ブロードリーフ</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>100</v>
-      </c>
-      <c r="D3" t="n">
-        <v>420</v>
-      </c>
-      <c r="E3" t="n">
-        <v>472</v>
-      </c>
-      <c r="F3" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-2.22</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>462.72</v>
-      </c>
-      <c r="N3" t="n">
-        <v>429.41</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>75</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・出来高が急増しています。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>押し目、出来高増加、MACD売り、長期上昇</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>482</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-10</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-2.07</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>47200</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>42000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5200</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>12.38</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>9432.T</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NTT</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D4" t="n">
-        <v>158</v>
-      </c>
-      <c r="E4" t="n">
-        <v>171.5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>164.26</v>
-      </c>
-      <c r="N4" t="n">
-        <v>154.75</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>🟢 強い上昇</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>⚪ 様子見</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>65</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 強い上昇
-・MACDは売りシグナルです。
-・RSIは良好な水準です。
-・ボリンジャーバンド中心付近で推移しています。
-📈 中長期的にも強い上昇トレンドが継続しています。
-押し目買い候補として注目です。</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>押し目、MACD売り、長期上昇</t>
+          <t>RSI適正、25日線上、MACD売り、長期上昇</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>171.9</v>
+        <v>171.5</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4</v>
+        <v>1.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.23</v>
+        <v>1.05</v>
       </c>
       <c r="Z4" t="n">
-        <v>17150</v>
+        <v>17330</v>
       </c>
       <c r="AA4" t="n">
         <v>15800</v>
       </c>
       <c r="AB4" t="n">
-        <v>1350</v>
+        <v>1530</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.539999999999999</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="5">
@@ -921,22 +919,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3077</v>
+        <v>3053</v>
       </c>
       <c r="F5" t="n">
-        <v>75.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7</v>
+        <v>0.37</v>
       </c>
       <c r="I5" t="n">
-        <v>36.07</v>
+        <v>32.57</v>
       </c>
       <c r="J5" t="n">
-        <v>30.65</v>
+        <v>31.03</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -949,10 +947,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2969.96</v>
+        <v>2973.65</v>
       </c>
       <c r="N5" t="n">
-        <v>3094.77</v>
+        <v>3093.57</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -961,20 +959,20 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟡 買い</t>
+          <t>🟢 強い買い</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -982,8 +980,6 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
-・買われ過ぎ水準です。
-・出来高が増加しています。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -992,65 +988,65 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>RSI過熱、25日線上、出来高微増、MACD買い、上昇トレンド</t>
+          <t>RSIやや過熱、25日線上、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>3051</v>
+        <v>3077</v>
       </c>
       <c r="X5" t="n">
-        <v>26</v>
+        <v>-24</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.85</v>
+        <v>-0.78</v>
       </c>
       <c r="Z5" t="n">
-        <v>40001</v>
+        <v>39689</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2902</v>
+        <v>2590</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.82</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8058.T</t>
+          <t>7974.T</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>三菱商事</t>
+          <t>任天堂</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4795</v>
+        <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>4908</v>
+        <v>8262</v>
       </c>
       <c r="F6" t="n">
-        <v>67.09999999999999</v>
+        <v>54.1</v>
       </c>
       <c r="G6" t="n">
-        <v>3.46</v>
+        <v>0.68</v>
       </c>
       <c r="H6" t="n">
-        <v>2.59</v>
+        <v>0.51</v>
       </c>
       <c r="I6" t="n">
-        <v>30.09</v>
+        <v>44.54</v>
       </c>
       <c r="J6" t="n">
-        <v>5.35</v>
+        <v>58.47</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1059,14 +1055,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4733.71</v>
+        <v>8143.25</v>
       </c>
       <c r="N6" t="n">
-        <v>4768.49</v>
+        <v>8260.02</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1075,136 +1071,23 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟢 強い買い</t>
+          <t>🟡 買い</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★☆</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟢 上昇
-・MACDは買いシグナルです。
-・出来高が急増しています。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
-👍 上昇トレンドを維持しています。
-順張りが有利な局面です。</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>RSIやや過熱、25日線上、出来高増加、+1σ、MACD買い、上昇トレンド</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>4847</v>
-      </c>
-      <c r="X6" t="n">
-        <v>61</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>24540</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>23975</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>565</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.36</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7974.T</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>任天堂</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7993</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8158</v>
-      </c>
-      <c r="F7" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I7" t="n">
-        <v>58.57</v>
-      </c>
-      <c r="J7" t="n">
-        <v>61.95</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>8128.03</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8270.940000000001</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🟢 上昇</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>🟡 買い</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>75</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟢 上昇
@@ -1215,32 +1098,144 @@
 順張りが有利な局面です。</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>RSI適正、25日線上、MACD売り、上昇トレンド</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>8158</v>
+      </c>
+      <c r="X6" t="n">
+        <v>104</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8262</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7993</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>269</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>8058.T</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>三菱商事</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4795</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4841</v>
+      </c>
+      <c r="F7" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I7" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>+1S</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>4740.2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4774.84</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>🟢 上昇</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>🟢 強い買い</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>100</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🟢 上昇
+・MACDは買いシグナルです。
+・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+👍 上昇トレンドを維持しています。
+順張りが有利な局面です。</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSI適正、押し目、MACD売り、上昇トレンド</t>
+          <t>RSI適正、25日線上、+1σ、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>8311</v>
+        <v>4908</v>
       </c>
       <c r="X7" t="n">
-        <v>-153</v>
+        <v>-67</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.84</v>
+        <v>-1.37</v>
       </c>
       <c r="Z7" t="n">
-        <v>8158</v>
+        <v>24205</v>
       </c>
       <c r="AA7" t="n">
-        <v>7993</v>
+        <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>165</v>
+        <v>230</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.06</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="8">
@@ -1261,63 +1256,298 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
+        <v>8442</v>
+      </c>
+      <c r="F8" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-12.97</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-312.91</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-185.05</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-1S</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>9962.57</v>
+      </c>
+      <c r="N8" t="n">
+        <v>8748.889999999999</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>🔴 売り注意</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>15</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは売りシグナルです。
+・売られ過ぎ水準です。
+・25日線から大きく下に乖離しています。
+・ボリンジャーバンド-1σ付近です。やや弱含みですが、反発に注目です。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>RSI売られすぎ、25日線大幅割れ、-1σ、MACD売り、下降トレンド</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
         <v>9231</v>
       </c>
-      <c r="F8" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-5.01</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-268.74</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-153.08</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="X8" t="n">
+        <v>-789</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>8442</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-1558</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-15.58</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>285A.T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>キオクシアホールディングス</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>55510</v>
+      </c>
+      <c r="E9" t="n">
+        <v>13300</v>
+      </c>
+      <c r="F9" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-14.95</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-1142.85</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1178.54</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>10044.77</v>
-      </c>
-      <c r="N8" t="n">
-        <v>8724.75</v>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="M9" t="n">
+        <v>17247.07</v>
+      </c>
+      <c r="N9" t="n">
+        <v>15030.38</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🔴 下降</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>🔴 売り注意</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>15</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>【AI分析レポート】
+・🔴 下降
+・MACDは買いシグナルです。
+・25日線から大きく下に乖離しています。
+・ボリンジャーバンド中心付近で推移しています。
+⚠️ 下落トレンドです。
+無理な買いは避け、反転サインを待ちましょう。</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>⚠️ 急落</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>25日線大幅割れ、MACD買い、下降トレンド</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>14505</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-1205</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-8.31</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>13300</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>55510</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-42210</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-76.04000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SUPER MICRO COMP</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6113</v>
+      </c>
+      <c r="E10" t="n">
+        <v>34.43</v>
+      </c>
+      <c r="F10" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>中心</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="N10" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>🟡 反発中</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>🟠 利益確定検討</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q10" t="n">
         <v>45</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>★☆☆☆☆</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>【AI分析レポート】
 ・🟡 反発中
@@ -1327,231 +1557,6 @@
 今後のトレンド転換に注目しましょう。</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>押し目、MACD売り、反発局面</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>9200</v>
-      </c>
-      <c r="X8" t="n">
-        <v>31</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9231</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-769</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-7.69</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>285A.T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>キオクシアホールディングス</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>55510</v>
-      </c>
-      <c r="E9" t="n">
-        <v>14505</v>
-      </c>
-      <c r="F9" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-8.390000000000001</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-1172.27</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-1187.47</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>17415.78</v>
-      </c>
-      <c r="N9" t="n">
-        <v>14982.79</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🔴 下降</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>🔴 売り注意</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>35</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🔴 下降
-・MACDは買いシグナルです。
-・出来高が増加しています。
-・ボリンジャーバンド中心付近で推移しています。
-⚠️ 下落トレンドです。
-無理な買いは避け、反転サインを待ちましょう。</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>押し目、出来高微増、MACD買い、下降トレンド</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>14340</v>
-      </c>
-      <c r="X9" t="n">
-        <v>165</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>14505</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>55510</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-41005</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-73.87</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SMCI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SUPER MICRO COMP</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6113</v>
-      </c>
-      <c r="E10" t="n">
-        <v>34.43</v>
-      </c>
-      <c r="F10" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>中心</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>35.84</v>
-      </c>
-      <c r="N10" t="n">
-        <v>32.64</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>🟡 反発中</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>🟠 利益確定検討</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>45</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>★☆☆☆☆</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>【AI分析レポート】
-・🟡 反発中
-・MACDは売りシグナルです。
-・ボリンジャーバンド中心付近で推移しています。
-🟡 下落からの反発局面です。
-今後のトレンド転換に注目しましょう。</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -581,22 +581,22 @@
         <v>2700</v>
       </c>
       <c r="E2" t="n">
-        <v>3750</v>
+        <v>3790</v>
       </c>
       <c r="F2" t="n">
-        <v>35.3</v>
+        <v>36.9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.72</v>
+        <v>1.75</v>
       </c>
       <c r="H2" t="n">
-        <v>0.28</v>
+        <v>0.84</v>
       </c>
       <c r="I2" t="n">
-        <v>67.63</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>94.67</v>
+        <v>95.31</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3419.33</v>
+        <v>3419.87</v>
       </c>
       <c r="N2" t="n">
-        <v>2827.59</v>
+        <v>2827.79</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -657,22 +657,22 @@
         <v>3770</v>
       </c>
       <c r="X2" t="n">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.53</v>
+        <v>0.53</v>
       </c>
       <c r="Z2" t="n">
-        <v>15000</v>
+        <v>15160</v>
       </c>
       <c r="AA2" t="n">
         <v>10800</v>
       </c>
       <c r="AB2" t="n">
-        <v>4200</v>
+        <v>4360</v>
       </c>
       <c r="AC2" t="n">
-        <v>38.89</v>
+        <v>40.37</v>
       </c>
     </row>
     <row r="3">
@@ -693,22 +693,22 @@
         <v>420</v>
       </c>
       <c r="E3" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F3" t="n">
-        <v>44.4</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9</v>
+        <v>-0.7</v>
       </c>
       <c r="H3" t="n">
-        <v>0.21</v>
+        <v>0.49</v>
       </c>
       <c r="I3" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="J3" t="n">
-        <v>4.58</v>
+        <v>4.59</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>463.45</v>
+        <v>463.47</v>
       </c>
       <c r="N3" t="n">
         <v>429.99</v>
@@ -755,6 +755,7 @@
 ・🟢 強い上昇
 ・MACDは売りシグナルです。
 ・デッドクロスが発生し、短期的な下落に注意が必要です。
+・RSIは良好な水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 📈 中長期的にも強い上昇トレンドが継続しています。
 押し目買い候補として注目です。</t>
@@ -770,22 +771,22 @@
         <v>472</v>
       </c>
       <c r="X3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="Z3" t="n">
-        <v>47800</v>
+        <v>47900</v>
       </c>
       <c r="AA3" t="n">
         <v>42000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5800</v>
+        <v>5900</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.81</v>
+        <v>14.05</v>
       </c>
     </row>
     <row r="4">
@@ -815,7 +816,7 @@
         <v>0.11</v>
       </c>
       <c r="H4" t="n">
-        <v>0.37</v>
+        <v>0.82</v>
       </c>
       <c r="I4" t="n">
         <v>0.92</v>
@@ -919,22 +920,22 @@
         <v>2853.77</v>
       </c>
       <c r="E5" t="n">
-        <v>3053</v>
+        <v>3070</v>
       </c>
       <c r="F5" t="n">
-        <v>69.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="H5" t="n">
-        <v>0.37</v>
+        <v>0.82</v>
       </c>
       <c r="I5" t="n">
-        <v>32.57</v>
+        <v>33.92</v>
       </c>
       <c r="J5" t="n">
-        <v>31.03</v>
+        <v>31.3</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -947,10 +948,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2973.65</v>
+        <v>2973.87</v>
       </c>
       <c r="N5" t="n">
-        <v>3093.57</v>
+        <v>3093.65</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -980,6 +981,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
+・買われ過ぎ水準です。
 ・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
@@ -995,22 +997,22 @@
         <v>3077</v>
       </c>
       <c r="X5" t="n">
-        <v>-24</v>
+        <v>-7</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.78</v>
+        <v>-0.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>39689</v>
+        <v>39910</v>
       </c>
       <c r="AA5" t="n">
         <v>37099</v>
       </c>
       <c r="AB5" t="n">
-        <v>2590</v>
+        <v>2811</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.98</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="6">
@@ -1031,22 +1033,22 @@
         <v>7993</v>
       </c>
       <c r="E6" t="n">
-        <v>8262</v>
+        <v>8289</v>
       </c>
       <c r="F6" t="n">
-        <v>54.1</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.51</v>
+        <v>0.78</v>
       </c>
       <c r="I6" t="n">
-        <v>44.54</v>
+        <v>46.7</v>
       </c>
       <c r="J6" t="n">
-        <v>58.47</v>
+        <v>58.9</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1059,10 +1061,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>8143.25</v>
+        <v>8143.61</v>
       </c>
       <c r="N6" t="n">
-        <v>8260.02</v>
+        <v>8260.16</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1108,22 +1110,22 @@
         <v>8158</v>
       </c>
       <c r="X6" t="n">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.27</v>
+        <v>1.61</v>
       </c>
       <c r="Z6" t="n">
-        <v>8262</v>
+        <v>8289</v>
       </c>
       <c r="AA6" t="n">
         <v>7993</v>
       </c>
       <c r="AB6" t="n">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.37</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="7">
@@ -1144,22 +1146,22 @@
         <v>4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4841</v>
+        <v>4805</v>
       </c>
       <c r="F7" t="n">
-        <v>62.3</v>
+        <v>60.2</v>
       </c>
       <c r="G7" t="n">
-        <v>1.97</v>
+        <v>1.24</v>
       </c>
       <c r="H7" t="n">
-        <v>0.19</v>
+        <v>0.53</v>
       </c>
       <c r="I7" t="n">
-        <v>30.21</v>
+        <v>27.34</v>
       </c>
       <c r="J7" t="n">
-        <v>10.32</v>
+        <v>9.74</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1168,14 +1170,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+1S</t>
+          <t>中心</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4740.2</v>
+        <v>4739.72</v>
       </c>
       <c r="N7" t="n">
-        <v>4774.84</v>
+        <v>4774.66</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1205,7 +1207,7 @@
           <t>【AI分析レポート】
 ・🟢 上昇
 ・MACDは買いシグナルです。
-・ボリンジャーバンド+1σ付近です。上昇基調ですが、過熱感に注意しましょう。
+・ボリンジャーバンド中心付近で推移しています。
 👍 上昇トレンドを維持しています。
 順張りが有利な局面です。</t>
         </is>
@@ -1213,29 +1215,29 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>RSI適正、25日線上、+1σ、MACD買い、上昇トレンド</t>
+          <t>RSI適正、25日線上、MACD買い、上昇トレンド</t>
         </is>
       </c>
       <c r="W7" t="n">
         <v>4908</v>
       </c>
       <c r="X7" t="n">
-        <v>-67</v>
+        <v>-103</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.37</v>
+        <v>-2.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>24205</v>
+        <v>24025</v>
       </c>
       <c r="AA7" t="n">
         <v>23975</v>
       </c>
       <c r="AB7" t="n">
-        <v>230</v>
+        <v>50</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.96</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="8">
@@ -1256,22 +1258,22 @@
         <v>10000</v>
       </c>
       <c r="E8" t="n">
-        <v>8442</v>
+        <v>8553</v>
       </c>
       <c r="F8" t="n">
-        <v>27.2</v>
+        <v>27.8</v>
       </c>
       <c r="G8" t="n">
-        <v>-12.97</v>
+        <v>-11.86</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>-312.91</v>
+        <v>-304.06</v>
       </c>
       <c r="J8" t="n">
-        <v>-185.05</v>
+        <v>-183.27</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1284,10 +1286,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>9962.57</v>
+        <v>9964.049999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>8748.889999999999</v>
+        <v>8749.440000000001</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1338,22 +1340,22 @@
         <v>9231</v>
       </c>
       <c r="X8" t="n">
-        <v>-789</v>
+        <v>-678</v>
       </c>
       <c r="Y8" t="n">
-        <v>-8.550000000000001</v>
+        <v>-7.34</v>
       </c>
       <c r="Z8" t="n">
-        <v>8442</v>
+        <v>8553</v>
       </c>
       <c r="AA8" t="n">
         <v>10000</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1558</v>
+        <v>-1447</v>
       </c>
       <c r="AC8" t="n">
-        <v>-15.58</v>
+        <v>-14.47</v>
       </c>
     </row>
     <row r="9">
@@ -1374,22 +1376,22 @@
         <v>55510</v>
       </c>
       <c r="E9" t="n">
-        <v>13300</v>
+        <v>13470</v>
       </c>
       <c r="F9" t="n">
-        <v>30.2</v>
+        <v>30.7</v>
       </c>
       <c r="G9" t="n">
-        <v>-14.95</v>
+        <v>-13.9</v>
       </c>
       <c r="H9" t="n">
-        <v>0.45</v>
+        <v>0.78</v>
       </c>
       <c r="I9" t="n">
-        <v>-1142.85</v>
+        <v>-1129.28</v>
       </c>
       <c r="J9" t="n">
-        <v>-1178.54</v>
+        <v>-1175.83</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1402,10 +1404,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>17247.07</v>
+        <v>17249.33</v>
       </c>
       <c r="N9" t="n">
-        <v>15030.38</v>
+        <v>15031.23</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1455,22 +1457,22 @@
         <v>14505</v>
       </c>
       <c r="X9" t="n">
-        <v>-1205</v>
+        <v>-1035</v>
       </c>
       <c r="Y9" t="n">
-        <v>-8.31</v>
+        <v>-7.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>13300</v>
+        <v>13470</v>
       </c>
       <c r="AA9" t="n">
         <v>55510</v>
       </c>
       <c r="AB9" t="n">
-        <v>-42210</v>
+        <v>-42040</v>
       </c>
       <c r="AC9" t="n">
-        <v>-76.04000000000001</v>
+        <v>-75.73</v>
       </c>
     </row>
     <row r="10">
